--- a/backend/public/BOSCH_STOCK1.xlsx
+++ b/backend/public/BOSCH_STOCK1.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abc\Desktop\bk eng stock\updateStock\Update-Stock\backend\public\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A584694-3E3E-41C7-B574-736F127BD8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730"/>
   </bookViews>
   <sheets>
     <sheet name="ELEMENT" sheetId="1" r:id="rId1"/>
@@ -48,7 +42,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'DIESEL FILTER&amp;OIL FILTER'!$A$3:$N$634</definedName>
     <definedName name="Z_8145F22A_AD74_4799_898B_BCECC4FA34F9_.wvu.PrintArea" localSheetId="5" hidden="1">'DIESEL FILTER&amp;OIL FILTER'!$A$3:$N$634</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
   <customWorkbookViews>
     <customWorkbookView name="pcs - Personal View" guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" mergeInterval="0" personalView="1" maximized="1" xWindow="1" yWindow="1" windowWidth="800" windowHeight="379" tabRatio="628" activeSheetId="5"/>
   </customWorkbookViews>
@@ -10940,10 +10934,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_ &quot;Rs.&quot;\ * #,##0.00_ ;_ &quot;Rs.&quot;\ * \-#,##0.00_ ;_ &quot;Rs.&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ &quot;Rs.&quot;\ * #,##0.00_ ;_ &quot;Rs.&quot;\ * \-#,##0.00_ ;_ &quot;Rs.&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -11253,7 +11247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
@@ -11464,7 +11458,7 @@
     <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11507,10 +11501,10 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="4" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2" xfId="5"/>
     <cellStyle name="Currency" xfId="3" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 3" xfId="2"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="32">
@@ -11912,9 +11906,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -11952,7 +11946,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -11986,7 +11980,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -12021,10 +12014,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -12197,7 +12189,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J440"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -13593,7 +13585,7 @@
       </c>
       <c r="D66" s="17"/>
       <c r="E66" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F66" s="17"/>
       <c r="G66" s="17"/>
@@ -13909,7 +13901,7 @@
       </c>
       <c r="D82" s="17"/>
       <c r="E82" s="19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" s="17"/>
       <c r="G82" s="17"/>
@@ -13928,7 +13920,7 @@
       </c>
       <c r="D83" s="17"/>
       <c r="E83" s="19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
@@ -15047,7 +15039,7 @@
       </c>
       <c r="D136" s="17"/>
       <c r="E136" s="19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F136" s="17"/>
       <c r="G136" s="17"/>
@@ -15672,7 +15664,7 @@
         <v>2168</v>
       </c>
       <c r="E167" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F167" s="17" t="s">
         <v>2167</v>
@@ -16085,7 +16077,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F172" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
+  <autoFilter ref="A1:F172"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="110" topLeftCell="A104">
       <selection activeCell="G107" sqref="G107"/>
@@ -16099,7 +16092,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:H293"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16170,7 +16163,7 @@
         <v>1826</v>
       </c>
       <c r="E3" s="75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="74">
         <v>1974</v>
@@ -17506,7 +17499,7 @@
         <v>387</v>
       </c>
       <c r="E72" s="75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F72" s="74">
         <v>2206</v>
@@ -18762,7 +18755,7 @@
         <v>2076</v>
       </c>
       <c r="E137" s="75">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F137" s="74" t="s">
         <v>2793</v>
@@ -18862,7 +18855,7 @@
         <v>822</v>
       </c>
       <c r="E142" s="75">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="F142" s="74">
         <v>746</v>
@@ -19532,7 +19525,7 @@
         <v>2704</v>
       </c>
       <c r="E175" s="75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F175" s="74">
         <v>1947</v>
@@ -20114,7 +20107,7 @@
       </c>
       <c r="D204" s="74"/>
       <c r="E204" s="75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F204" s="74">
         <v>2434</v>
@@ -20534,7 +20527,7 @@
         <v>1859</v>
       </c>
       <c r="E225" s="75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F225" s="74">
         <v>9251</v>
@@ -20622,7 +20615,7 @@
         <v>2443</v>
       </c>
       <c r="E229" s="75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F229" s="74">
         <v>12762</v>
@@ -21872,7 +21865,7 @@
       </c>
       <c r="D287" s="74"/>
       <c r="E287" s="75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F287" s="74">
         <v>10302</v>
@@ -21998,7 +21991,7 @@
     </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:I293" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
+  <autoFilter ref="A1:I293"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="110" topLeftCell="A1208">
       <selection activeCell="D1139" sqref="D1139"/>
@@ -22043,7 +22036,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:H1391"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22133,7 +22126,7 @@
         <v>3508</v>
       </c>
       <c r="E4" s="71">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="F4" s="70">
         <v>287</v>
@@ -22155,7 +22148,7 @@
         <v>3509</v>
       </c>
       <c r="E5" s="71">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="F5" s="70">
         <v>167</v>
@@ -22177,7 +22170,7 @@
         <v>3510</v>
       </c>
       <c r="E6" s="71">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="F6" s="70">
         <v>182</v>
@@ -31175,7 +31168,7 @@
     </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:H54" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
+  <autoFilter ref="A1:H54"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="120" topLeftCell="A52">
       <selection activeCell="D57" sqref="D57"/>
@@ -31196,7 +31189,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:H311"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12"/>
@@ -31286,7 +31279,7 @@
         <v>1295</v>
       </c>
       <c r="E4" s="19">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F4" s="17">
         <v>1772</v>
@@ -31870,7 +31863,7 @@
         <v>2374</v>
       </c>
       <c r="E32" s="19">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F32" s="17">
         <v>2740</v>
@@ -32120,7 +32113,7 @@
         <v>1331</v>
       </c>
       <c r="E44" s="19">
-        <v>449</v>
+        <v>389</v>
       </c>
       <c r="F44" s="17">
         <v>247</v>
@@ -32141,7 +32134,7 @@
         <v>1331</v>
       </c>
       <c r="E45" s="19">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F45" s="17">
         <v>676</v>
@@ -32505,7 +32498,7 @@
       </c>
       <c r="D63" s="32"/>
       <c r="E63" s="84">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="F63" s="32">
         <v>115</v>
@@ -33092,7 +33085,7 @@
     </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:H92" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
+  <autoFilter ref="A1:H92"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="115" topLeftCell="A35">
       <selection activeCell="D44" sqref="D44"/>
@@ -33109,7 +33102,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:F99"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -33935,7 +33928,7 @@
         <v>2506</v>
       </c>
       <c r="E41">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F41">
         <v>561</v>
@@ -35026,7 +35019,7 @@
     </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:F98" xr:uid="{00000000-0009-0000-0000-00000C000000}"/>
+  <autoFilter ref="A1:F98"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}">
       <selection activeCell="A2" sqref="A2"/>
@@ -35042,7 +35035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A2:C18"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -35123,7 +35116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -35714,7 +35707,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A3:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -35887,7 +35880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -36578,7 +36571,7 @@
       </c>
       <c r="D38" s="26"/>
       <c r="E38" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F38" s="9"/>
     </row>
@@ -41303,7 +41296,7 @@
     </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:G275" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:G275"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" topLeftCell="A335">
       <selection activeCell="C348" sqref="C348"/>
@@ -41317,7 +41310,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:H772"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -44970,7 +44963,7 @@
     </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:H129" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:H129"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="110" topLeftCell="A239">
       <selection activeCell="D241" sqref="D241"/>
@@ -44984,7 +44977,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:H478"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -45118,7 +45111,7 @@
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7" s="33">
         <v>502</v>
@@ -46365,7 +46358,7 @@
       </c>
       <c r="D84" s="33"/>
       <c r="E84" s="35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F84" s="33"/>
     </row>
@@ -47146,7 +47139,7 @@
       </c>
       <c r="D132" s="33"/>
       <c r="E132" s="35">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F132" s="33">
         <v>247</v>
@@ -49225,7 +49218,7 @@
       </c>
       <c r="D257" s="33"/>
       <c r="E257" s="35">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F257" s="33">
         <v>137</v>
@@ -49261,7 +49254,7 @@
         <v>2724</v>
       </c>
       <c r="E259" s="35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F259" s="33">
         <v>327</v>
@@ -49739,7 +49732,7 @@
       </c>
       <c r="D288" s="33"/>
       <c r="E288" s="35">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="F288" s="33"/>
     </row>
@@ -49863,7 +49856,7 @@
       </c>
       <c r="D295" s="33"/>
       <c r="E295" s="35">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F295" s="33">
         <v>696</v>
@@ -50226,7 +50219,7 @@
       </c>
       <c r="D316" s="33"/>
       <c r="E316" s="35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F316" s="33">
         <v>865</v>
@@ -50334,7 +50327,7 @@
         <v>3591</v>
       </c>
       <c r="E322" s="35">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F322" s="33" t="s">
         <v>2935</v>
@@ -50632,7 +50625,7 @@
         <v>3327</v>
       </c>
       <c r="E338" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F338" s="33">
         <v>9850</v>
@@ -50738,7 +50731,7 @@
         <v>3330</v>
       </c>
       <c r="E344" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F344" s="33">
         <v>6480</v>
@@ -51432,7 +51425,7 @@
     </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:H376" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:H376"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="110" topLeftCell="A2437">
       <selection activeCell="D2444" sqref="D2444"/>
@@ -51446,7 +51439,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:G571"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -51761,7 +51754,7 @@
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="56">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" s="35">
         <v>2025</v>
@@ -51860,7 +51853,7 @@
         <v>2698</v>
       </c>
       <c r="E24" s="56">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F24" s="35" t="s">
         <v>2820</v>
@@ -53019,7 +53012,7 @@
         <v>2708</v>
       </c>
       <c r="E91" s="56">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F91" s="35">
         <v>855</v>
@@ -53145,7 +53138,7 @@
         <v>2704</v>
       </c>
       <c r="E98" s="56">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="F98" s="56">
         <v>1320</v>
@@ -53763,7 +53756,7 @@
         <v>2707</v>
       </c>
       <c r="E133" s="56">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F133" s="35" t="s">
         <v>3585</v>
@@ -53826,7 +53819,7 @@
         <v>518894</v>
       </c>
       <c r="E136" s="56">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F136" s="35" t="s">
         <v>3583</v>
@@ -54025,7 +54018,7 @@
         <v>2700</v>
       </c>
       <c r="E147" s="56">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F147" s="35">
         <v>554</v>
@@ -54085,7 +54078,7 @@
         <v>2703</v>
       </c>
       <c r="E150" s="56">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F150" s="35">
         <v>893</v>
@@ -54552,7 +54545,7 @@
         <v>2704</v>
       </c>
       <c r="E175" s="56">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F175" s="56">
         <v>2310</v>
@@ -54630,7 +54623,7 @@
         <v>2704</v>
       </c>
       <c r="E179" s="56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F179" s="35">
         <v>681</v>
@@ -54939,7 +54932,7 @@
         <v>2704</v>
       </c>
       <c r="E195" s="56">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F195" s="35">
         <v>4839</v>
@@ -55035,7 +55028,7 @@
         <v>2698</v>
       </c>
       <c r="E200" s="56">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F200" s="35">
         <v>1399</v>
@@ -55123,7 +55116,7 @@
         <v>2704</v>
       </c>
       <c r="E205" s="56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F205" s="35">
         <v>1199</v>
@@ -55518,7 +55511,7 @@
       </c>
       <c r="D227" s="33"/>
       <c r="E227" s="56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F227" s="35">
         <v>2749</v>
@@ -57098,7 +57091,7 @@
     </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:G231" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:G231"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="110" topLeftCell="A1207">
       <selection activeCell="F1213" sqref="F1213"/>
@@ -57124,7 +57117,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:J293"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -57184,7 +57177,7 @@
       </c>
       <c r="D3" s="33"/>
       <c r="E3" s="33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3" s="35">
         <v>161</v>
@@ -57202,7 +57195,7 @@
       </c>
       <c r="D4" s="33"/>
       <c r="E4" s="33">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F4" s="35">
         <v>146</v>
@@ -57309,7 +57302,7 @@
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33">
-        <v>643</v>
+        <v>863</v>
       </c>
       <c r="F10" s="35">
         <v>193</v>
@@ -57327,7 +57320,7 @@
       </c>
       <c r="D11" s="33"/>
       <c r="E11" s="33">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="F11" s="35">
         <v>184</v>
@@ -57345,7 +57338,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="F12" s="35">
         <v>184</v>
@@ -57422,7 +57415,7 @@
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F16" s="35">
         <v>400</v>
@@ -57440,7 +57433,7 @@
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F17" s="35">
         <v>396</v>
@@ -57476,7 +57469,7 @@
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="33">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F19" s="35" t="s">
         <v>2789</v>
@@ -57532,7 +57525,7 @@
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="33">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F22" s="35">
         <v>363</v>
@@ -57676,7 +57669,7 @@
         <v>3357</v>
       </c>
       <c r="E30" s="60">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F30" s="33">
         <v>586</v>
@@ -57754,7 +57747,7 @@
       </c>
       <c r="D34" s="33"/>
       <c r="E34" s="53">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="F34" s="35">
         <v>392</v>
@@ -57852,10 +57845,10 @@
       </c>
       <c r="D39" s="33"/>
       <c r="E39" s="33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="35">
-        <v>2208</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -57980,7 +57973,7 @@
         <v>3368</v>
       </c>
       <c r="E46" s="60">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F46" s="35">
         <v>208</v>
@@ -58114,7 +58107,7 @@
         <v>3372</v>
       </c>
       <c r="E54" s="42">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F54" s="35">
         <v>211</v>
@@ -58150,7 +58143,7 @@
       </c>
       <c r="D56" s="33"/>
       <c r="E56" s="33">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="F56" s="35">
         <v>120</v>
@@ -58168,7 +58161,7 @@
       </c>
       <c r="D57" s="33"/>
       <c r="E57" s="33">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="F57" s="35">
         <v>260</v>
@@ -58256,7 +58249,7 @@
       </c>
       <c r="D62" s="33"/>
       <c r="E62" s="33">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F62" s="35">
         <v>298</v>
@@ -58440,7 +58433,7 @@
       </c>
       <c r="D73" s="33"/>
       <c r="E73" s="42">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F73" s="35">
         <v>295</v>
@@ -58498,7 +58491,7 @@
       </c>
       <c r="D76" s="33"/>
       <c r="E76" s="33">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="F76" s="35">
         <v>239</v>
@@ -58516,7 +58509,7 @@
       </c>
       <c r="D77" s="33"/>
       <c r="E77" s="42">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="F77" s="35">
         <v>124</v>
@@ -58534,7 +58527,7 @@
       </c>
       <c r="D78" s="33"/>
       <c r="E78" s="33">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="F78" s="35">
         <v>253</v>
@@ -58677,7 +58670,9 @@
       <c r="D86" s="33" t="s">
         <v>3380</v>
       </c>
-      <c r="E86" s="33"/>
+      <c r="E86" s="33">
+        <v>5</v>
+      </c>
       <c r="F86" s="35">
         <v>410</v>
       </c>
@@ -58696,7 +58691,7 @@
         <v>3382</v>
       </c>
       <c r="E87" s="33">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F87" s="33">
         <v>330</v>
@@ -58802,7 +58797,7 @@
       </c>
       <c r="D93" s="33"/>
       <c r="E93" s="33">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F93" s="35">
         <v>1656</v>
@@ -58859,7 +58854,7 @@
       </c>
       <c r="D96" s="33"/>
       <c r="E96" s="33">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F96" s="35">
         <v>288</v>
@@ -59049,7 +59044,7 @@
         <v>3387</v>
       </c>
       <c r="E106" s="60">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F106" s="35">
         <v>396</v>
@@ -59127,7 +59122,7 @@
         <v>1573</v>
       </c>
       <c r="E110" s="33">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F110" s="35">
         <v>494</v>
@@ -59177,7 +59172,7 @@
       </c>
       <c r="D113" s="33"/>
       <c r="E113" s="33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F113" s="35">
         <v>746</v>
@@ -59738,7 +59733,7 @@
         <v>1859</v>
       </c>
       <c r="E143" s="35">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F143" s="33">
         <v>371</v>
@@ -60029,7 +60024,7 @@
         <v>1859</v>
       </c>
       <c r="E160" s="33">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F160" s="35">
         <v>234</v>
@@ -60049,7 +60044,7 @@
         <v>2423</v>
       </c>
       <c r="E161" s="33">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F161" s="35">
         <v>300</v>
@@ -60089,7 +60084,7 @@
         <v>3409</v>
       </c>
       <c r="E163" s="33">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="F163" s="35">
         <v>686</v>
@@ -60169,7 +60164,7 @@
         <v>2553</v>
       </c>
       <c r="E167" s="33">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F167" s="35" t="s">
         <v>2936</v>
@@ -60269,7 +60264,7 @@
         <v>3421</v>
       </c>
       <c r="E172" s="33">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F172" s="35">
         <v>649</v>
@@ -60289,7 +60284,7 @@
         <v>3422</v>
       </c>
       <c r="E173" s="33">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F173" s="35">
         <v>759</v>
@@ -60389,7 +60384,7 @@
         <v>3428</v>
       </c>
       <c r="E178" s="33">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F178" s="35">
         <v>288</v>
@@ -60479,7 +60474,7 @@
         <v>290</v>
       </c>
       <c r="E183" s="33">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F183" s="35">
         <v>170</v>
@@ -60499,7 +60494,7 @@
         <v>318</v>
       </c>
       <c r="E184" s="33">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F184" s="35">
         <v>186</v>
@@ -60579,7 +60574,7 @@
         <v>2247</v>
       </c>
       <c r="E188" s="33">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F188" s="35">
         <v>229</v>
@@ -60599,7 +60594,7 @@
         <v>3433</v>
       </c>
       <c r="E189" s="33">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F189" s="35" t="s">
         <v>2788</v>
@@ -60619,7 +60614,7 @@
         <v>3434</v>
       </c>
       <c r="E190" s="33">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="F190" s="33" t="s">
         <v>3023</v>
@@ -60815,7 +60810,7 @@
         <v>3440</v>
       </c>
       <c r="E200" s="33">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="F200" s="35">
         <v>155</v>
@@ -61013,7 +61008,7 @@
         <v>3447</v>
       </c>
       <c r="E210" s="33">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F210" s="35">
         <v>345</v>
@@ -61063,7 +61058,7 @@
         <v>836</v>
       </c>
       <c r="E213" s="33">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F213" s="35">
         <v>592</v>
@@ -61163,7 +61158,7 @@
         <v>3453</v>
       </c>
       <c r="E218" s="33">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F218" s="33" t="s">
         <v>2941</v>
@@ -61183,7 +61178,7 @@
         <v>2393</v>
       </c>
       <c r="E219" s="33">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F219" s="33">
         <v>244</v>
@@ -61323,7 +61318,7 @@
         <v>3459</v>
       </c>
       <c r="E226" s="33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F226" s="33">
         <v>440</v>
@@ -61463,7 +61458,7 @@
         <v>3466</v>
       </c>
       <c r="E233" s="33">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F233" s="35">
         <v>353</v>
@@ -61941,7 +61936,7 @@
         <v>3067</v>
       </c>
       <c r="E257" s="33">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F257" s="35">
         <v>546</v>
@@ -62019,7 +62014,7 @@
         <v>3066</v>
       </c>
       <c r="E261" s="33">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F261" s="35">
         <v>550</v>
@@ -62640,7 +62635,7 @@
     </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:J293" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:J293"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="110" topLeftCell="A1045">
       <selection activeCell="D1055" sqref="D1055"/>
@@ -62664,7 +62659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -63787,7 +63782,7 @@
         <v>344</v>
       </c>
       <c r="E61" s="62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" s="4">
         <v>2214</v>
@@ -64185,7 +64180,7 @@
     </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:F80" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A1:F80"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="110" topLeftCell="A503">
       <selection activeCell="E514" sqref="E514"/>
@@ -64198,7 +64193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -64264,7 +64259,7 @@
         <v>290</v>
       </c>
       <c r="E3" s="35">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F3" s="33">
         <v>1465</v>
@@ -64993,8 +64988,8 @@
       <c r="F43" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:F43" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <sheetProtection password="CFE1" sheet="1" objects="1" scenarios="1"/>
+  <autoFilter ref="A1:F43"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="120" topLeftCell="A217">
       <selection activeCell="C224" sqref="C224"/>
@@ -65007,7 +65002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:G119"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -65174,7 +65169,7 @@
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="35">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F9" s="33" t="s">
         <v>2815</v>
@@ -65474,7 +65469,7 @@
       </c>
       <c r="D26" s="33"/>
       <c r="E26" s="35">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F26" s="33">
         <v>18</v>
@@ -65524,7 +65519,7 @@
       </c>
       <c r="D29" s="33"/>
       <c r="E29" s="35">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="F29" s="33">
         <v>21</v>
@@ -65953,7 +65948,7 @@
         <v>2290</v>
       </c>
       <c r="E53" s="35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F53" s="33">
         <v>5355</v>
@@ -65973,7 +65968,7 @@
         <v>2295</v>
       </c>
       <c r="E54" s="35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F54" s="33">
         <v>5355</v>
@@ -66015,7 +66010,7 @@
         <v>2670</v>
       </c>
       <c r="E57" s="35">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F57" s="33">
         <v>750</v>
@@ -67013,7 +67008,7 @@
     </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:G119" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <autoFilter ref="A1:G119"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="116" topLeftCell="A1179">
       <selection activeCell="F1188" sqref="F1188"/>

--- a/backend/public/BOSCH_STOCK1.xlsx
+++ b/backend/public/BOSCH_STOCK1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="ELEMENT" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,6 @@
   <customWorkbookViews>
     <customWorkbookView name="pcs - Personal View" guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" mergeInterval="0" personalView="1" maximized="1" xWindow="1" yWindow="1" windowWidth="800" windowHeight="379" tabRatio="628" activeSheetId="5"/>
   </customWorkbookViews>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -14277,7 +14276,7 @@
       </c>
       <c r="D100" s="17"/>
       <c r="E100" s="19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F100" s="17" t="s">
         <v>2650</v>
@@ -16161,7 +16160,7 @@
         <v>1825</v>
       </c>
       <c r="E3" s="75">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F3" s="74">
         <v>1974</v>
@@ -16415,7 +16414,7 @@
         <v>2703</v>
       </c>
       <c r="E15" s="75">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F15" s="74">
         <v>179</v>
@@ -17497,7 +17496,7 @@
         <v>387</v>
       </c>
       <c r="E72" s="75">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F72" s="74">
         <v>2206</v>
@@ -19817,7 +19816,7 @@
       </c>
       <c r="D189" s="74"/>
       <c r="E189" s="75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F189" s="74" t="s">
         <v>3580</v>
@@ -22043,7 +22042,7 @@
     <col min="2" max="2" width="37.85546875" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" customWidth="1"/>
     <col min="4" max="4" width="22.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="7" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="7" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" style="21" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="6"/>
     <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -22168,7 +22167,7 @@
         <v>3509</v>
       </c>
       <c r="E6" s="71">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="F6" s="70">
         <v>182</v>
@@ -22260,7 +22259,7 @@
         <v>3513</v>
       </c>
       <c r="E10" s="71">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="F10" s="70">
         <v>225</v>
@@ -31945,7 +31944,7 @@
         <v>2306</v>
       </c>
       <c r="E36" s="19">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F36" s="17">
         <v>418</v>
@@ -32111,7 +32110,7 @@
         <v>1331</v>
       </c>
       <c r="E44" s="19">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="F44" s="17">
         <v>247</v>
@@ -32132,7 +32131,7 @@
         <v>1331</v>
       </c>
       <c r="E45" s="19">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F45" s="17">
         <v>676</v>
@@ -32172,7 +32171,7 @@
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="17"/>
       <c r="G47" s="32"/>
@@ -32522,7 +32521,7 @@
         <v>2865</v>
       </c>
       <c r="E64" s="84">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="F64" s="32">
         <v>251</v>
@@ -33387,7 +33386,7 @@
         <v>2450</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F15">
         <v>935</v>
@@ -35991,7 +35990,7 @@
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F7" s="9"/>
     </row>
@@ -36009,7 +36008,7 @@
         <v>2378</v>
       </c>
       <c r="E8" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F8" s="9"/>
     </row>
@@ -43096,7 +43095,7 @@
       <c r="C100" s="33"/>
       <c r="D100" s="38"/>
       <c r="E100" s="35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F100" s="33" t="s">
         <v>2650</v>
@@ -47950,7 +47949,7 @@
       </c>
       <c r="D183" s="33"/>
       <c r="E183" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F183" s="33"/>
     </row>
@@ -48236,7 +48235,7 @@
       </c>
       <c r="D200" s="33"/>
       <c r="E200" s="35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F200" s="33"/>
     </row>
@@ -49309,7 +49308,7 @@
         <v>399</v>
       </c>
       <c r="E263" s="35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F263" s="33">
         <v>645</v>
@@ -49711,7 +49710,7 @@
       </c>
       <c r="D288" s="33"/>
       <c r="E288" s="35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F288" s="33"/>
     </row>
@@ -49835,7 +49834,7 @@
       </c>
       <c r="D295" s="33"/>
       <c r="E295" s="35">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F295" s="33">
         <v>696</v>
@@ -50198,7 +50197,7 @@
       </c>
       <c r="D316" s="33"/>
       <c r="E316" s="35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F316" s="33">
         <v>865</v>
@@ -50378,7 +50377,7 @@
         <v>3323</v>
       </c>
       <c r="E326" s="35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F326" s="33" t="s">
         <v>2820</v>
@@ -53624,7 +53623,7 @@
         <v>2703</v>
       </c>
       <c r="E127" s="56">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F127" s="35">
         <v>772</v>
@@ -54524,7 +54523,7 @@
         <v>2703</v>
       </c>
       <c r="E175" s="56">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F175" s="56">
         <v>2310</v>
@@ -57174,7 +57173,7 @@
       </c>
       <c r="D4" s="33"/>
       <c r="E4" s="33">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F4" s="35">
         <v>146</v>
@@ -57281,7 +57280,7 @@
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33">
-        <v>829</v>
+        <v>798</v>
       </c>
       <c r="F10" s="35">
         <v>193</v>
@@ -57448,7 +57447,7 @@
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="33">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="F19" s="35" t="s">
         <v>2788</v>
@@ -57688,7 +57687,7 @@
         <v>3358</v>
       </c>
       <c r="E32" s="60">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F32" s="33">
         <v>424</v>
@@ -58160,7 +58159,7 @@
         <v>3397</v>
       </c>
       <c r="E58" s="42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" s="35">
         <v>408</v>
@@ -58328,7 +58327,7 @@
       </c>
       <c r="D68" s="33"/>
       <c r="E68" s="33">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F68" s="35">
         <v>208</v>
@@ -58506,7 +58505,7 @@
       </c>
       <c r="D78" s="33"/>
       <c r="E78" s="33">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F78" s="35">
         <v>253</v>
@@ -58758,7 +58757,7 @@
       </c>
       <c r="D92" s="33"/>
       <c r="E92" s="33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" s="35">
         <v>1325</v>
@@ -58963,7 +58962,7 @@
       </c>
       <c r="D103" s="33"/>
       <c r="E103" s="33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F103" s="35">
         <v>335</v>
@@ -59151,7 +59150,7 @@
       </c>
       <c r="D113" s="33"/>
       <c r="E113" s="33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F113" s="35">
         <v>746</v>
@@ -59573,7 +59572,7 @@
       </c>
       <c r="D136" s="33"/>
       <c r="E136" s="33">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F136" s="33">
         <v>1045</v>
@@ -60003,7 +60002,7 @@
         <v>1858</v>
       </c>
       <c r="E160" s="33">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F160" s="35">
         <v>234</v>
@@ -60043,7 +60042,7 @@
         <v>3406</v>
       </c>
       <c r="E162" s="33">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F162" s="35">
         <v>638</v>
@@ -60063,7 +60062,7 @@
         <v>3408</v>
       </c>
       <c r="E163" s="33">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F163" s="35">
         <v>686</v>
@@ -60083,7 +60082,7 @@
         <v>3409</v>
       </c>
       <c r="E164" s="60">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F164" s="33">
         <v>868</v>
@@ -60123,7 +60122,7 @@
         <v>3411</v>
       </c>
       <c r="E166" s="33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F166" s="35" t="s">
         <v>2848</v>
@@ -60183,7 +60182,7 @@
         <v>3415</v>
       </c>
       <c r="E169" s="33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F169" s="35">
         <v>1454</v>
@@ -60453,7 +60452,7 @@
         <v>290</v>
       </c>
       <c r="E183" s="33">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="F183" s="35">
         <v>170</v>
@@ -60671,7 +60670,7 @@
         <v>2799</v>
       </c>
       <c r="E194" s="42">
-        <v>22</v>
+        <v>247</v>
       </c>
       <c r="F194" s="35">
         <v>170</v>
@@ -60691,7 +60690,7 @@
         <v>3436</v>
       </c>
       <c r="E195" s="42">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F195" s="35" t="s">
         <v>3005</v>
@@ -61117,7 +61116,7 @@
         <v>3451</v>
       </c>
       <c r="E217" s="33">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F217" s="33">
         <v>330</v>
@@ -61137,7 +61136,7 @@
         <v>3452</v>
       </c>
       <c r="E218" s="33">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F218" s="33" t="s">
         <v>2940</v>
@@ -61417,7 +61416,7 @@
         <v>3464</v>
       </c>
       <c r="E232" s="33">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F232" s="35">
         <v>1026</v>
@@ -61557,7 +61556,7 @@
         <v>3471</v>
       </c>
       <c r="E239" s="33">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F239" s="35">
         <v>494</v>
@@ -61617,7 +61616,7 @@
         <v>3474</v>
       </c>
       <c r="E242" s="33">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F242" s="35">
         <v>258</v>
@@ -61775,7 +61774,7 @@
       </c>
       <c r="D250" s="33"/>
       <c r="E250" s="33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F250" s="35" t="s">
         <v>2943</v>
@@ -61815,7 +61814,7 @@
         <v>2884</v>
       </c>
       <c r="E252" s="33">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F252" s="35">
         <v>567</v>
@@ -61953,7 +61952,7 @@
         <v>2988</v>
       </c>
       <c r="E259" s="33">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F259" s="35">
         <v>505</v>
@@ -62111,7 +62110,7 @@
         <v>3575</v>
       </c>
       <c r="E267" s="33">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F267" s="35">
         <v>536</v>
@@ -63839,7 +63838,7 @@
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" s="4">
         <v>4394</v>
@@ -65148,7 +65147,7 @@
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="35">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F9" s="33" t="s">
         <v>2814</v>
@@ -65947,7 +65946,7 @@
         <v>2294</v>
       </c>
       <c r="E54" s="35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" s="33">
         <v>5355</v>

--- a/backend/public/BOSCH_STOCK1.xlsx
+++ b/backend/public/BOSCH_STOCK1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730" firstSheet="3" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ELEMENT" sheetId="1" r:id="rId1"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="D100" s="17"/>
       <c r="E100" s="19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F100" s="17" t="s">
         <v>2650</v>
@@ -14891,7 +14891,7 @@
       </c>
       <c r="D129" s="17"/>
       <c r="E129" s="19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F129" s="17"/>
       <c r="G129" s="17"/>
@@ -15181,7 +15181,7 @@
       </c>
       <c r="D143" s="17"/>
       <c r="E143" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F143" s="17"/>
       <c r="G143" s="17"/>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="D158" s="17"/>
       <c r="E158" s="19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F158" s="17"/>
       <c r="G158" s="17"/>
@@ -16230,7 +16230,7 @@
         <v>2703</v>
       </c>
       <c r="E6" s="75">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="74">
         <v>2322</v>
@@ -18852,7 +18852,7 @@
         <v>822</v>
       </c>
       <c r="E142" s="75">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F142" s="74">
         <v>746</v>
@@ -19058,7 +19058,7 @@
         <v>1396</v>
       </c>
       <c r="E152" s="75">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F152" s="74">
         <v>969</v>
@@ -19892,7 +19892,7 @@
       <c r="C193" s="74"/>
       <c r="D193" s="74"/>
       <c r="E193" s="75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F193" s="74">
         <v>2405</v>
@@ -20590,7 +20590,7 @@
         <v>2441</v>
       </c>
       <c r="E228" s="75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F228" s="74">
         <v>14552</v>
@@ -22167,7 +22167,7 @@
         <v>3509</v>
       </c>
       <c r="E6" s="71">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F6" s="70">
         <v>182</v>
@@ -22331,7 +22331,7 @@
         <v>3516</v>
       </c>
       <c r="E13" s="71">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="F13" s="70">
         <v>288</v>
@@ -31505,7 +31505,7 @@
         <v>1303</v>
       </c>
       <c r="E15" s="19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" s="17">
         <v>6968</v>
@@ -31818,7 +31818,7 @@
         <v>2372</v>
       </c>
       <c r="E30" s="19">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F30" s="17">
         <v>1709</v>
@@ -32110,7 +32110,7 @@
         <v>1331</v>
       </c>
       <c r="E44" s="19">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="F44" s="17">
         <v>247</v>
@@ -33206,7 +33206,7 @@
         <v>2246</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>815</v>
@@ -36008,7 +36008,7 @@
         <v>2378</v>
       </c>
       <c r="E8" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F8" s="9"/>
     </row>
@@ -36966,7 +36966,7 @@
         <v>693</v>
       </c>
       <c r="E61" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61" s="9"/>
     </row>
@@ -37038,7 +37038,7 @@
         <v>769</v>
       </c>
       <c r="E65" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F65" s="9"/>
     </row>
@@ -40138,7 +40138,7 @@
         <v>1542</v>
       </c>
       <c r="E217" s="10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F217" s="9"/>
       <c r="G217" t="s">
@@ -42656,7 +42656,7 @@
       <c r="C74" s="33"/>
       <c r="D74" s="38"/>
       <c r="E74" s="35">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F74" s="33"/>
       <c r="H74" t="s">
@@ -42960,7 +42960,7 @@
       <c r="C92" s="33"/>
       <c r="D92" s="38"/>
       <c r="E92" s="35">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F92" s="33"/>
       <c r="H92" t="s">
@@ -42977,7 +42977,7 @@
       <c r="C93" s="33"/>
       <c r="D93" s="38"/>
       <c r="E93" s="35">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F93" s="33" t="s">
         <v>2596</v>
@@ -43095,7 +43095,7 @@
       <c r="C100" s="33"/>
       <c r="D100" s="38"/>
       <c r="E100" s="35">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F100" s="33" t="s">
         <v>2650</v>
@@ -45683,7 +45683,7 @@
       </c>
       <c r="D43" s="33"/>
       <c r="E43" s="35">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F43" s="33">
         <v>154</v>
@@ -45797,7 +45797,7 @@
       </c>
       <c r="D50" s="33"/>
       <c r="E50" s="35">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F50" s="33"/>
     </row>
@@ -47117,7 +47117,7 @@
       </c>
       <c r="D132" s="33"/>
       <c r="E132" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" s="33">
         <v>247</v>
@@ -49710,7 +49710,7 @@
       </c>
       <c r="D288" s="33"/>
       <c r="E288" s="35">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F288" s="33"/>
     </row>
@@ -49816,7 +49816,7 @@
       </c>
       <c r="D294" s="33"/>
       <c r="E294" s="35">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F294" s="33">
         <v>696</v>
@@ -52384,7 +52384,7 @@
         <v>2697</v>
       </c>
       <c r="E57" s="56">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F57" s="35">
         <v>2075</v>
@@ -52520,7 +52520,7 @@
         <v>2703</v>
       </c>
       <c r="E65" s="56">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F65" s="35" t="s">
         <v>2764</v>
@@ -53696,7 +53696,7 @@
         <v>2698</v>
       </c>
       <c r="E131" s="56">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F131" s="35" t="s">
         <v>3127</v>
@@ -53734,7 +53734,7 @@
         <v>2706</v>
       </c>
       <c r="E133" s="56">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F133" s="35" t="s">
         <v>3584</v>
@@ -53797,7 +53797,7 @@
         <v>518894</v>
       </c>
       <c r="E136" s="56">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F136" s="35" t="s">
         <v>3582</v>
@@ -54699,7 +54699,7 @@
         <v>2709</v>
       </c>
       <c r="E184" s="56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F184" s="35">
         <v>1739</v>
@@ -54832,7 +54832,7 @@
         <v>2703</v>
       </c>
       <c r="E191" s="56">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F191" s="35">
         <v>1106</v>
@@ -57280,7 +57280,7 @@
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33">
-        <v>798</v>
+        <v>768</v>
       </c>
       <c r="F10" s="35">
         <v>193</v>
@@ -57298,7 +57298,7 @@
       </c>
       <c r="D11" s="33"/>
       <c r="E11" s="33">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F11" s="35">
         <v>184</v>
@@ -57316,7 +57316,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33">
-        <v>724</v>
+        <v>709</v>
       </c>
       <c r="F12" s="35">
         <v>184</v>
@@ -57393,7 +57393,7 @@
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F16" s="35">
         <v>400</v>
@@ -57411,7 +57411,7 @@
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F17" s="35">
         <v>396</v>
@@ -57627,7 +57627,7 @@
         <v>3355</v>
       </c>
       <c r="E29" s="60">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F29" s="33">
         <v>379</v>
@@ -57667,7 +57667,7 @@
         <v>3357</v>
       </c>
       <c r="E31" s="60">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F31" s="35">
         <v>268</v>
@@ -57687,7 +57687,7 @@
         <v>3358</v>
       </c>
       <c r="E32" s="60">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F32" s="33">
         <v>424</v>
@@ -58139,7 +58139,7 @@
       </c>
       <c r="D57" s="33"/>
       <c r="E57" s="33">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F57" s="35">
         <v>260</v>
@@ -59328,7 +59328,7 @@
       </c>
       <c r="D123" s="33"/>
       <c r="E123" s="33">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F123" s="35">
         <v>197</v>
@@ -60062,7 +60062,7 @@
         <v>3408</v>
       </c>
       <c r="E163" s="33">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="F163" s="35">
         <v>686</v>
@@ -60162,7 +60162,7 @@
         <v>3413</v>
       </c>
       <c r="E168" s="33">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F168" s="35">
         <v>451</v>
@@ -60322,7 +60322,7 @@
         <v>3425</v>
       </c>
       <c r="E176" s="33">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F176" s="35">
         <v>282</v>
@@ -60472,7 +60472,7 @@
         <v>318</v>
       </c>
       <c r="E184" s="33">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F184" s="35">
         <v>186</v>
@@ -60592,7 +60592,7 @@
         <v>3433</v>
       </c>
       <c r="E190" s="33">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F190" s="33" t="s">
         <v>3022</v>
@@ -60906,7 +60906,7 @@
         <v>3587</v>
       </c>
       <c r="E206" s="33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F206" s="35">
         <v>300</v>
@@ -61116,7 +61116,7 @@
         <v>3451</v>
       </c>
       <c r="E217" s="33">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F217" s="33">
         <v>330</v>
@@ -61156,7 +61156,7 @@
         <v>2392</v>
       </c>
       <c r="E219" s="33">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F219" s="33">
         <v>244</v>
@@ -61436,7 +61436,7 @@
         <v>3465</v>
       </c>
       <c r="E233" s="33">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F233" s="35">
         <v>353</v>
@@ -62273,7 +62273,7 @@
         <v>3484</v>
       </c>
       <c r="E276" s="33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F276" s="33">
         <v>239</v>
@@ -63742,7 +63742,7 @@
         <v>401</v>
       </c>
       <c r="E60" s="62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
@@ -65497,7 +65497,7 @@
       </c>
       <c r="D29" s="33"/>
       <c r="E29" s="35">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="F29" s="33">
         <v>21</v>

--- a/backend/public/BOSCH_STOCK1.xlsx
+++ b/backend/public/BOSCH_STOCK1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730"/>
   </bookViews>
   <sheets>
     <sheet name="ELEMENT" sheetId="1" r:id="rId1"/>
@@ -10118,9 +10118,6 @@
     <t xml:space="preserve">CAMESHAFT </t>
   </si>
   <si>
-    <t xml:space="preserve"> crank senssor </t>
-  </si>
-  <si>
     <t>ley.&amp;mahindra</t>
   </si>
   <si>
@@ -10926,6 +10923,9 @@
   </si>
   <si>
     <t>19 &amp; 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> crank senssor 026121032</t>
   </si>
 </sst>
 </file>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="17"/>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F57" s="17"/>
       <c r="G57" s="17"/>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="D83" s="17"/>
       <c r="E83" s="19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="D120" s="17"/>
       <c r="E120" s="19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F120" s="17"/>
       <c r="G120" s="17"/>
@@ -16160,7 +16160,7 @@
         <v>1825</v>
       </c>
       <c r="E3" s="75">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" s="74">
         <v>1974</v>
@@ -16201,7 +16201,7 @@
         <v>598</v>
       </c>
       <c r="D5" s="74" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="E5" s="75">
         <v>22</v>
@@ -17496,10 +17496,10 @@
         <v>387</v>
       </c>
       <c r="E72" s="75">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F72" s="74">
-        <v>2206</v>
+        <v>2033</v>
       </c>
       <c r="G72" s="74"/>
       <c r="H72" s="74"/>
@@ -17518,7 +17518,7 @@
         <v>412</v>
       </c>
       <c r="E73" s="75">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F73" s="74">
         <v>1530</v>
@@ -18627,7 +18627,7 @@
         <v>625</v>
       </c>
       <c r="D131" s="74" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="E131" s="75">
         <v>2</v>
@@ -18649,7 +18649,7 @@
         <v>625</v>
       </c>
       <c r="D132" s="74" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="E132" s="75">
         <v>0</v>
@@ -18852,7 +18852,7 @@
         <v>822</v>
       </c>
       <c r="E142" s="75">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F142" s="74">
         <v>746</v>
@@ -18973,7 +18973,7 @@
         <v>825</v>
       </c>
       <c r="D148" s="74" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="E148" s="75">
         <v>14</v>
@@ -19013,7 +19013,7 @@
         <v>825</v>
       </c>
       <c r="D150" s="74" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="E150" s="75">
         <v>3</v>
@@ -19097,7 +19097,7 @@
         <v>598</v>
       </c>
       <c r="D154" s="74" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="E154" s="75">
         <v>7</v>
@@ -19819,7 +19819,7 @@
         <v>3</v>
       </c>
       <c r="F189" s="74" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="G189" s="74"/>
       <c r="H189" s="74"/>
@@ -20104,7 +20104,7 @@
       </c>
       <c r="D204" s="74"/>
       <c r="E204" s="75">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F204" s="74">
         <v>2434</v>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="D211" s="74"/>
       <c r="E211" s="75">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F211" s="74">
         <v>2360</v>
@@ -20411,7 +20411,7 @@
     <row r="220" spans="1:8" ht="21">
       <c r="A220" s="74"/>
       <c r="B220" s="74" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="C220" s="74" t="s">
         <v>598</v>
@@ -20524,7 +20524,7 @@
         <v>1858</v>
       </c>
       <c r="E225" s="75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F225" s="74">
         <v>9251</v>
@@ -21001,7 +21001,7 @@
         <v>1</v>
       </c>
       <c r="F247" s="74" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="G247" s="74"/>
       <c r="H247" s="74"/>
@@ -22076,7 +22076,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="92" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="C2" s="92"/>
       <c r="D2" s="92"/>
@@ -22093,10 +22093,10 @@
         <v>1632</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D3" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="E3" s="71">
         <v>247</v>
@@ -22117,10 +22117,10 @@
         <v>1629</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="D4" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="E4" s="71">
         <v>230</v>
@@ -22139,13 +22139,13 @@
         <v>1983</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D5" s="69" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="E5" s="71">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F5" s="70">
         <v>167</v>
@@ -22161,10 +22161,10 @@
         <v>1984</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D6" s="69" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="E6" s="71">
         <v>91</v>
@@ -22185,10 +22185,10 @@
         <v>1985</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D7" s="69" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="E7" s="71">
         <v>220</v>
@@ -22209,10 +22209,10 @@
         <v>1986</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D8" s="69" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="E8" s="71">
         <v>87</v>
@@ -22231,13 +22231,13 @@
         <v>1987</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D9" s="69" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="E9" s="71">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F9" s="70">
         <v>219</v>
@@ -22253,10 +22253,10 @@
         <v>1988</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D10" s="69" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="E10" s="71">
         <v>278</v>
@@ -22277,13 +22277,13 @@
         <v>1989</v>
       </c>
       <c r="C11" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D11" s="69" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="E11" s="71">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F11" s="70">
         <v>242</v>
@@ -22301,10 +22301,10 @@
         <v>1990</v>
       </c>
       <c r="C12" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D12" s="69" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="E12" s="71">
         <v>1066</v>
@@ -22325,10 +22325,10 @@
         <v>1991</v>
       </c>
       <c r="C13" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D13" s="69" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="E13" s="71">
         <v>263</v>
@@ -22349,10 +22349,10 @@
         <v>1992</v>
       </c>
       <c r="C14" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D14" s="69" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="E14" s="71">
         <v>275</v>
@@ -22368,7 +22368,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="93" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="C15" s="93"/>
       <c r="D15" s="93"/>
@@ -22385,7 +22385,7 @@
         <v>690</v>
       </c>
       <c r="C16" s="69" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="D16" s="69" t="s">
         <v>2232</v>
@@ -22407,7 +22407,7 @@
         <v>2067</v>
       </c>
       <c r="C17" s="69" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="D17" s="69" t="s">
         <v>2606</v>
@@ -22429,7 +22429,7 @@
         <v>691</v>
       </c>
       <c r="C18" s="69" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D18" s="69" t="s">
         <v>2607</v>
@@ -22451,7 +22451,7 @@
         <v>692</v>
       </c>
       <c r="C19" s="69" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D19" s="69" t="s">
         <v>2608</v>
@@ -22473,7 +22473,7 @@
         <v>693</v>
       </c>
       <c r="C20" s="69" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="D20" s="69" t="s">
         <v>2231</v>
@@ -22495,7 +22495,7 @@
         <v>694</v>
       </c>
       <c r="C21" s="69" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="D21" s="69" t="s">
         <v>2230</v>
@@ -22514,7 +22514,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="93" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="C22" s="93"/>
       <c r="D22" s="93"/>
@@ -22531,7 +22531,7 @@
         <v>2615</v>
       </c>
       <c r="C23" s="69" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="D23" s="69" t="s">
         <v>2609</v>
@@ -22553,7 +22553,7 @@
         <v>2048</v>
       </c>
       <c r="C24" s="69" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="D24" s="69" t="s">
         <v>2052</v>
@@ -22575,7 +22575,7 @@
         <v>2093</v>
       </c>
       <c r="C25" s="69" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="D25" s="69" t="s">
         <v>2094</v>
@@ -22597,7 +22597,7 @@
         <v>2680</v>
       </c>
       <c r="C26" s="69" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="D26" s="69" t="s">
         <v>1723</v>
@@ -22619,7 +22619,7 @@
         <v>2068</v>
       </c>
       <c r="C27" s="69" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="D27" s="69" t="s">
         <v>2069</v>
@@ -22641,7 +22641,7 @@
         <v>2053</v>
       </c>
       <c r="C28" s="69" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="D28" s="69" t="s">
         <v>2054</v>
@@ -22663,7 +22663,7 @@
         <v>2610</v>
       </c>
       <c r="C29" s="69" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D29" s="69" t="s">
         <v>2611</v>
@@ -31234,7 +31234,7 @@
         <v>1295</v>
       </c>
       <c r="E2" s="84">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="F2" s="32">
         <v>184</v>
@@ -31255,7 +31255,7 @@
         <v>1295</v>
       </c>
       <c r="E3" s="19">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="F3" s="17">
         <v>362</v>
@@ -31297,7 +31297,7 @@
         <v>1295</v>
       </c>
       <c r="E5" s="19">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F5" s="17">
         <v>1098</v>
@@ -31400,7 +31400,7 @@
         <v>1303</v>
       </c>
       <c r="E10" s="19">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F10" s="17">
         <v>1100</v>
@@ -31629,7 +31629,7 @@
         <v>1317</v>
       </c>
       <c r="E21" s="19">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="F21" s="17">
         <v>418</v>
@@ -31692,7 +31692,7 @@
         <v>1314</v>
       </c>
       <c r="E24" s="19">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="F24" s="17">
         <v>446</v>
@@ -31818,7 +31818,7 @@
         <v>2372</v>
       </c>
       <c r="E30" s="19">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="F30" s="17">
         <v>1709</v>
@@ -31923,7 +31923,7 @@
         <v>2306</v>
       </c>
       <c r="E35" s="19">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="F35" s="17">
         <v>216</v>
@@ -32110,7 +32110,7 @@
         <v>1331</v>
       </c>
       <c r="E44" s="19">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="F44" s="17">
         <v>247</v>
@@ -32495,7 +32495,7 @@
       </c>
       <c r="D63" s="32"/>
       <c r="E63" s="84">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F63" s="32">
         <v>115</v>
@@ -33120,7 +33120,7 @@
         <v>417</v>
       </c>
       <c r="C2" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D2" t="s">
         <v>293</v>
@@ -33140,7 +33140,7 @@
         <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D3" t="s">
         <v>2391</v>
@@ -33160,7 +33160,7 @@
         <v>831</v>
       </c>
       <c r="C4" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D4" t="s">
         <v>2392</v>
@@ -33180,7 +33180,7 @@
         <v>2395</v>
       </c>
       <c r="C5" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D5" t="s">
         <v>2393</v>
@@ -33200,7 +33200,7 @@
         <v>2394</v>
       </c>
       <c r="C6" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D6" t="s">
         <v>2246</v>
@@ -33220,7 +33220,7 @@
         <v>402</v>
       </c>
       <c r="C7" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D7" t="s">
         <v>2432</v>
@@ -33240,7 +33240,7 @@
         <v>834</v>
       </c>
       <c r="C8" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D8" t="s">
         <v>3048</v>
@@ -33260,7 +33260,7 @@
         <v>2396</v>
       </c>
       <c r="C9" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D9" t="s">
         <v>2397</v>
@@ -33280,7 +33280,7 @@
         <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D10" t="s">
         <v>2398</v>
@@ -33300,7 +33300,7 @@
         <v>183</v>
       </c>
       <c r="C11" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D11" t="s">
         <v>2399</v>
@@ -33320,7 +33320,7 @@
         <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D12" t="s">
         <v>2400</v>
@@ -33340,7 +33340,7 @@
         <v>186</v>
       </c>
       <c r="C13" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D13" t="s">
         <v>2401</v>
@@ -33360,7 +33360,7 @@
         <v>2402</v>
       </c>
       <c r="C14" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D14" t="s">
         <v>2403</v>
@@ -33380,7 +33380,7 @@
         <v>2404</v>
       </c>
       <c r="C15" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D15" t="s">
         <v>2450</v>
@@ -33400,7 +33400,7 @@
         <v>835</v>
       </c>
       <c r="C16" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D16" t="s">
         <v>2405</v>
@@ -33420,7 +33420,7 @@
         <v>641</v>
       </c>
       <c r="C17" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D17" t="s">
         <v>2406</v>
@@ -33440,7 +33440,7 @@
         <v>410</v>
       </c>
       <c r="C18" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D18" t="s">
         <v>3023</v>
@@ -33460,7 +33460,7 @@
         <v>640</v>
       </c>
       <c r="C19" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D19" t="s">
         <v>2407</v>
@@ -33480,7 +33480,7 @@
         <v>609</v>
       </c>
       <c r="C20" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D20" t="s">
         <v>2408</v>
@@ -33500,7 +33500,7 @@
         <v>525</v>
       </c>
       <c r="C21" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D21" t="s">
         <v>2601</v>
@@ -33520,7 +33520,7 @@
         <v>649</v>
       </c>
       <c r="C22" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D22" t="s">
         <v>2410</v>
@@ -33540,7 +33540,7 @@
         <v>2409</v>
       </c>
       <c r="C23" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D23" t="s">
         <v>2411</v>
@@ -33560,7 +33560,7 @@
         <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D24" t="s">
         <v>2412</v>
@@ -33580,7 +33580,7 @@
         <v>605</v>
       </c>
       <c r="C25" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D25" t="s">
         <v>2413</v>
@@ -33600,7 +33600,7 @@
         <v>403</v>
       </c>
       <c r="C26" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D26" t="s">
         <v>2414</v>
@@ -33620,7 +33620,7 @@
         <v>406</v>
       </c>
       <c r="C27" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D27" t="s">
         <v>318</v>
@@ -33640,7 +33640,7 @@
         <v>401</v>
       </c>
       <c r="C28" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D28" t="s">
         <v>2417</v>
@@ -33660,7 +33660,7 @@
         <v>638</v>
       </c>
       <c r="C29" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D29" t="s">
         <v>2415</v>
@@ -33680,7 +33680,7 @@
         <v>650</v>
       </c>
       <c r="C30" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D30" t="s">
         <v>2416</v>
@@ -33700,7 +33700,7 @@
         <v>832</v>
       </c>
       <c r="C31" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D31" t="s">
         <v>3113</v>
@@ -33720,7 +33720,7 @@
         <v>185</v>
       </c>
       <c r="C32" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D32" t="s">
         <v>2418</v>
@@ -33740,7 +33740,7 @@
         <v>836</v>
       </c>
       <c r="C33" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D33" t="s">
         <v>2419</v>
@@ -33760,7 +33760,7 @@
         <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D34" t="s">
         <v>2420</v>
@@ -33780,7 +33780,7 @@
         <v>2421</v>
       </c>
       <c r="C35" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D35" t="s">
         <v>836</v>
@@ -33800,7 +33800,7 @@
         <v>166</v>
       </c>
       <c r="C36" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D36" t="s">
         <v>2422</v>
@@ -33820,7 +33820,7 @@
         <v>197</v>
       </c>
       <c r="C37" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D37" t="s">
         <v>2423</v>
@@ -33840,7 +33840,7 @@
         <v>198</v>
       </c>
       <c r="C38" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D38" t="s">
         <v>2424</v>
@@ -33860,7 +33860,7 @@
         <v>999</v>
       </c>
       <c r="C39" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D39" t="s">
         <v>2426</v>
@@ -33880,7 +33880,7 @@
         <v>2425</v>
       </c>
       <c r="C40" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D40" t="s">
         <v>2422</v>
@@ -33900,7 +33900,7 @@
         <v>2427</v>
       </c>
       <c r="C41" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D41" t="s">
         <v>2505</v>
@@ -33920,7 +33920,7 @@
         <v>683</v>
       </c>
       <c r="C42" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D42" t="s">
         <v>1750</v>
@@ -33940,7 +33940,7 @@
         <v>983</v>
       </c>
       <c r="C43" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D43" t="s">
         <v>2405</v>
@@ -33960,13 +33960,13 @@
         <v>652</v>
       </c>
       <c r="C44" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D44" t="s">
         <v>2428</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44">
         <v>1028</v>
@@ -33980,7 +33980,7 @@
         <v>828</v>
       </c>
       <c r="C45" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D45" t="s">
         <v>2429</v>
@@ -34000,7 +34000,7 @@
         <v>2430</v>
       </c>
       <c r="C46" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D46" t="s">
         <v>779</v>
@@ -34020,7 +34020,7 @@
         <v>188</v>
       </c>
       <c r="C47" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D47" t="s">
         <v>2438</v>
@@ -34040,7 +34040,7 @@
         <v>187</v>
       </c>
       <c r="C48" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D48" t="s">
         <v>2439</v>
@@ -34060,7 +34060,7 @@
         <v>189</v>
       </c>
       <c r="C49" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D49" t="s">
         <v>3114</v>
@@ -34080,7 +34080,7 @@
         <v>2569</v>
       </c>
       <c r="C50" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D50" t="s">
         <v>2473</v>
@@ -34100,7 +34100,7 @@
         <v>2476</v>
       </c>
       <c r="C51" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D51" t="s">
         <v>2570</v>
@@ -34120,7 +34120,7 @@
         <v>2812</v>
       </c>
       <c r="C52" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D52" t="s">
         <v>2444</v>
@@ -34140,7 +34140,7 @@
         <v>684</v>
       </c>
       <c r="C53" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D53" t="s">
         <v>2571</v>
@@ -34160,7 +34160,7 @@
         <v>103</v>
       </c>
       <c r="C54" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D54" t="s">
         <v>3112</v>
@@ -34180,7 +34180,7 @@
         <v>653</v>
       </c>
       <c r="C55" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D55" t="s">
         <v>2496</v>
@@ -34200,7 +34200,7 @@
         <v>447</v>
       </c>
       <c r="C56" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D56" t="s">
         <v>2497</v>
@@ -34220,7 +34220,7 @@
         <v>2498</v>
       </c>
       <c r="C57" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D57" t="s">
         <v>2499</v>
@@ -34240,7 +34240,7 @@
         <v>2501</v>
       </c>
       <c r="C58" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D58" t="s">
         <v>2500</v>
@@ -34260,7 +34260,7 @@
         <v>438</v>
       </c>
       <c r="C59" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D59" t="s">
         <v>2507</v>
@@ -34280,7 +34280,7 @@
         <v>2506</v>
       </c>
       <c r="C60" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D60" t="s">
         <v>2508</v>
@@ -34300,7 +34300,7 @@
         <v>448</v>
       </c>
       <c r="C61" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D61" t="s">
         <v>2509</v>
@@ -34320,7 +34320,7 @@
         <v>639</v>
       </c>
       <c r="C62" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D62" t="s">
         <v>2528</v>
@@ -34340,7 +34340,7 @@
         <v>607</v>
       </c>
       <c r="C63" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -34354,7 +34354,7 @@
         <v>2936</v>
       </c>
       <c r="C64" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D64" t="s">
         <v>2937</v>
@@ -34374,7 +34374,7 @@
         <v>190</v>
       </c>
       <c r="C65" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D65" t="s">
         <v>3037</v>
@@ -34391,7 +34391,7 @@
         <v>3024</v>
       </c>
       <c r="C66" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D66" t="s">
         <v>3025</v>
@@ -34411,7 +34411,7 @@
         <v>3026</v>
       </c>
       <c r="C67" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D67" t="s">
         <v>3027</v>
@@ -34431,7 +34431,7 @@
         <v>442</v>
       </c>
       <c r="C68" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D68" t="s">
         <v>3123</v>
@@ -34448,7 +34448,7 @@
         <v>3130</v>
       </c>
       <c r="C69" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D69" t="s">
         <v>3131</v>
@@ -34468,7 +34468,7 @@
         <v>430</v>
       </c>
       <c r="C70" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -34485,7 +34485,7 @@
         <v>100</v>
       </c>
       <c r="C71" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D71" t="s">
         <v>3132</v>
@@ -34499,13 +34499,13 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="6" t="s">
+        <v>3567</v>
+      </c>
+      <c r="C72" t="s">
+        <v>3535</v>
+      </c>
+      <c r="D72" t="s">
         <v>3568</v>
-      </c>
-      <c r="C72" t="s">
-        <v>3536</v>
-      </c>
-      <c r="D72" t="s">
-        <v>3569</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -34532,10 +34532,10 @@
         <v>378</v>
       </c>
       <c r="C74" t="s">
+        <v>3536</v>
+      </c>
+      <c r="D74" t="s">
         <v>3537</v>
-      </c>
-      <c r="D74" t="s">
-        <v>3538</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -34552,10 +34552,10 @@
         <v>892</v>
       </c>
       <c r="C75" t="s">
+        <v>3538</v>
+      </c>
+      <c r="D75" t="s">
         <v>3539</v>
-      </c>
-      <c r="D75" t="s">
-        <v>3540</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -34572,10 +34572,10 @@
         <v>202</v>
       </c>
       <c r="C76" t="s">
+        <v>3540</v>
+      </c>
+      <c r="D76" t="s">
         <v>3541</v>
-      </c>
-      <c r="D76" t="s">
-        <v>3542</v>
       </c>
       <c r="E76">
         <v>1</v>
@@ -34592,10 +34592,10 @@
         <v>28</v>
       </c>
       <c r="C77" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D77" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="E77">
         <v>2</v>
@@ -34612,10 +34612,10 @@
         <v>2631</v>
       </c>
       <c r="C78" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D78" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -34629,7 +34629,7 @@
         <v>318026</v>
       </c>
       <c r="C79" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D79" t="s">
         <v>836</v>
@@ -34649,10 +34649,10 @@
         <v>3028</v>
       </c>
       <c r="C80" t="s">
+        <v>3545</v>
+      </c>
+      <c r="D80" t="s">
         <v>3546</v>
-      </c>
-      <c r="D80" t="s">
-        <v>3547</v>
       </c>
       <c r="E80">
         <v>2</v>
@@ -34669,10 +34669,10 @@
         <v>2860</v>
       </c>
       <c r="C81" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="D81" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="E81">
         <v>4</v>
@@ -34689,7 +34689,7 @@
         <v>2925</v>
       </c>
       <c r="C82" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D82" t="s">
         <v>1858</v>
@@ -34709,7 +34709,7 @@
         <v>3031</v>
       </c>
       <c r="C83" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D83" t="s">
         <v>683</v>
@@ -34739,10 +34739,10 @@
         <v>2626</v>
       </c>
       <c r="C85" t="s">
+        <v>3549</v>
+      </c>
+      <c r="D85" t="s">
         <v>3550</v>
-      </c>
-      <c r="D85" t="s">
-        <v>3551</v>
       </c>
       <c r="E85">
         <v>21</v>
@@ -34759,10 +34759,10 @@
         <v>963</v>
       </c>
       <c r="C86" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="D86" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="E86">
         <v>1</v>
@@ -34779,10 +34779,10 @@
         <v>671</v>
       </c>
       <c r="C87" t="s">
+        <v>3552</v>
+      </c>
+      <c r="D87" t="s">
         <v>3553</v>
-      </c>
-      <c r="D87" t="s">
-        <v>3554</v>
       </c>
       <c r="E87">
         <v>10</v>
@@ -34799,7 +34799,7 @@
         <v>2830</v>
       </c>
       <c r="C88" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="D88" t="s">
         <v>2420</v>
@@ -34842,7 +34842,7 @@
         <v>3149</v>
       </c>
       <c r="D90" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="E90">
         <v>3</v>
@@ -34859,10 +34859,10 @@
         <v>3078</v>
       </c>
       <c r="C91" t="s">
+        <v>3555</v>
+      </c>
+      <c r="D91" t="s">
         <v>3556</v>
-      </c>
-      <c r="D91" t="s">
-        <v>3557</v>
       </c>
       <c r="E91">
         <v>1</v>
@@ -34879,10 +34879,10 @@
         <v>8001</v>
       </c>
       <c r="C92" t="s">
+        <v>3557</v>
+      </c>
+      <c r="D92" t="s">
         <v>3558</v>
-      </c>
-      <c r="D92" t="s">
-        <v>3559</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -34896,10 +34896,10 @@
         <v>3142</v>
       </c>
       <c r="C93" t="s">
+        <v>3559</v>
+      </c>
+      <c r="D93" t="s">
         <v>3560</v>
-      </c>
-      <c r="D93" t="s">
-        <v>3561</v>
       </c>
       <c r="E93">
         <v>10</v>
@@ -34916,10 +34916,10 @@
         <v>3145</v>
       </c>
       <c r="C94" t="s">
+        <v>3561</v>
+      </c>
+      <c r="D94" t="s">
         <v>3562</v>
-      </c>
-      <c r="D94" t="s">
-        <v>3563</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -34975,10 +34975,10 @@
         <v>2572</v>
       </c>
       <c r="C98" t="s">
+        <v>3563</v>
+      </c>
+      <c r="D98" t="s">
         <v>3564</v>
-      </c>
-      <c r="D98" t="s">
-        <v>3565</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -34989,10 +34989,10 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="6" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="C99" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
     </row>
   </sheetData>
@@ -36080,7 +36080,7 @@
         <v>1465</v>
       </c>
       <c r="E12" s="10">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>2650</v>
@@ -37020,7 +37020,7 @@
         <v>719</v>
       </c>
       <c r="E64" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F64" s="9"/>
     </row>
@@ -37056,7 +37056,7 @@
         <v>778</v>
       </c>
       <c r="E66" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" s="9"/>
     </row>
@@ -38917,7 +38917,7 @@
         <v>946</v>
       </c>
       <c r="E157" s="10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F157" s="9"/>
       <c r="G157" t="s">
@@ -42597,7 +42597,7 @@
       <c r="C70" s="33"/>
       <c r="D70" s="38"/>
       <c r="E70" s="35">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F70" s="33"/>
     </row>
@@ -42690,7 +42690,7 @@
       <c r="C76" s="33"/>
       <c r="D76" s="38"/>
       <c r="E76" s="35">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F76" s="33"/>
       <c r="H76" t="s">
@@ -45110,7 +45110,7 @@
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="35">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" s="33">
         <v>1670</v>
@@ -45797,7 +45797,7 @@
       </c>
       <c r="D50" s="33"/>
       <c r="E50" s="35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F50" s="33"/>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="D117" s="33"/>
       <c r="E117" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" s="33"/>
     </row>
@@ -49710,7 +49710,7 @@
       </c>
       <c r="D288" s="33"/>
       <c r="E288" s="35">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F288" s="33"/>
     </row>
@@ -50142,7 +50142,7 @@
         <v>1204</v>
       </c>
       <c r="E313" s="35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F313" s="33">
         <v>1411</v>
@@ -50235,7 +50235,7 @@
         <v>1205</v>
       </c>
       <c r="E318" s="35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F318" s="33">
         <v>1029</v>
@@ -50302,7 +50302,7 @@
         <v>1208</v>
       </c>
       <c r="D322" s="33" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="E322" s="35">
         <v>45</v>
@@ -50322,7 +50322,7 @@
         <v>1208</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="E323" s="35">
         <v>38</v>
@@ -50371,10 +50371,10 @@
         <v>3289</v>
       </c>
       <c r="C326" s="33" t="s">
+        <v>3591</v>
+      </c>
+      <c r="D326" s="33" t="s">
         <v>3322</v>
-      </c>
-      <c r="D326" s="33" t="s">
-        <v>3323</v>
       </c>
       <c r="E326" s="35">
         <v>0</v>
@@ -50395,7 +50395,7 @@
       </c>
       <c r="D327" s="33"/>
       <c r="E327" s="35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F327" s="33" t="s">
         <v>2840</v>
@@ -50446,10 +50446,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="33" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="C330" s="33" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="D330" s="33" t="s">
         <v>1750</v>
@@ -50597,13 +50597,13 @@
         <v>3299</v>
       </c>
       <c r="C338" s="33" t="s">
+        <v>3324</v>
+      </c>
+      <c r="D338" s="33" t="s">
         <v>3325</v>
       </c>
-      <c r="D338" s="33" t="s">
-        <v>3326</v>
-      </c>
       <c r="E338" s="35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F338" s="33">
         <v>9850</v>
@@ -50638,7 +50638,7 @@
         <v>2695</v>
       </c>
       <c r="D340" s="33" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="E340" s="35">
         <v>1</v>
@@ -50703,16 +50703,16 @@
         <v>3320</v>
       </c>
       <c r="C344" s="33" t="s">
+        <v>3327</v>
+      </c>
+      <c r="D344" s="33" t="s">
         <v>3328</v>
       </c>
-      <c r="D344" s="33" t="s">
-        <v>3329</v>
-      </c>
       <c r="E344" s="35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F344" s="33">
-        <v>6480</v>
+        <v>5943</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -50997,7 +50997,7 @@
         <v>2961</v>
       </c>
       <c r="C361" s="33" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="D361" s="33" t="s">
         <v>1858</v>
@@ -51231,7 +51231,7 @@
         <v>3101</v>
       </c>
       <c r="C374" s="33" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="D374" s="33" t="s">
         <v>1750</v>
@@ -51728,7 +51728,7 @@
         <v>2719</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="56">
@@ -51793,7 +51793,7 @@
         <v>5</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="G22" t="s">
         <v>2703</v>
@@ -52021,7 +52021,7 @@
       </c>
       <c r="C35" s="33"/>
       <c r="D35" s="33" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="E35" s="56">
         <v>0</v>
@@ -52384,7 +52384,7 @@
         <v>2697</v>
       </c>
       <c r="E57" s="56">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F57" s="35">
         <v>2075</v>
@@ -52407,7 +52407,7 @@
         <v>29</v>
       </c>
       <c r="F58" s="35" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -52964,10 +52964,10 @@
         <v>741</v>
       </c>
       <c r="C90" s="33" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D90" s="33" t="s">
         <v>3334</v>
-      </c>
-      <c r="D90" s="33" t="s">
-        <v>3335</v>
       </c>
       <c r="E90" s="56">
         <v>1</v>
@@ -52990,7 +52990,7 @@
         <v>2707</v>
       </c>
       <c r="E91" s="56">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F91" s="35">
         <v>855</v>
@@ -53004,10 +53004,10 @@
         <v>743</v>
       </c>
       <c r="C92" s="33" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D92" s="33" t="s">
         <v>3336</v>
-      </c>
-      <c r="D92" s="33" t="s">
-        <v>3337</v>
       </c>
       <c r="E92" s="56">
         <v>10</v>
@@ -53116,7 +53116,7 @@
         <v>2703</v>
       </c>
       <c r="E98" s="56">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F98" s="56">
         <v>1320</v>
@@ -53268,7 +53268,7 @@
       </c>
       <c r="C107" s="33"/>
       <c r="D107" s="33" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="E107" s="56">
         <v>7</v>
@@ -53734,10 +53734,10 @@
         <v>2706</v>
       </c>
       <c r="E133" s="56">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F133" s="35" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -53800,7 +53800,7 @@
         <v>72</v>
       </c>
       <c r="F136" s="35" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -53835,10 +53835,10 @@
         <v>1862</v>
       </c>
       <c r="D138" s="33" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="E138" s="56">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F138" s="35">
         <v>1425</v>
@@ -54056,7 +54056,7 @@
         <v>2702</v>
       </c>
       <c r="E150" s="56">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F150" s="35">
         <v>893</v>
@@ -54090,10 +54090,10 @@
         <v>794</v>
       </c>
       <c r="C152" s="33" t="s">
+        <v>3339</v>
+      </c>
+      <c r="D152" s="33" t="s">
         <v>3340</v>
-      </c>
-      <c r="D152" s="33" t="s">
-        <v>3341</v>
       </c>
       <c r="E152" s="56">
         <v>0</v>
@@ -54186,7 +54186,7 @@
         <v>2703</v>
       </c>
       <c r="E157" s="56">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F157" s="35">
         <v>3175</v>
@@ -54266,10 +54266,10 @@
         <v>586</v>
       </c>
       <c r="D161" s="33" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="E161" s="56">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F161" s="35" t="s">
         <v>3128</v>
@@ -54523,7 +54523,7 @@
         <v>2703</v>
       </c>
       <c r="E175" s="56">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F175" s="56">
         <v>2310</v>
@@ -54581,7 +54581,7 @@
         <v>2703</v>
       </c>
       <c r="E178" s="56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F178" s="35">
         <v>1545</v>
@@ -54601,10 +54601,10 @@
         <v>2703</v>
       </c>
       <c r="E179" s="56">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F179" s="35">
-        <v>681</v>
+        <v>627</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -54832,7 +54832,7 @@
         <v>2703</v>
       </c>
       <c r="E191" s="56">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F191" s="35">
         <v>1106</v>
@@ -54980,10 +54980,10 @@
         <v>1716</v>
       </c>
       <c r="C199" s="33" t="s">
+        <v>3342</v>
+      </c>
+      <c r="D199" s="33" t="s">
         <v>3343</v>
-      </c>
-      <c r="D199" s="33" t="s">
-        <v>3344</v>
       </c>
       <c r="E199" s="56">
         <v>13</v>
@@ -55134,7 +55134,7 @@
         <v>2714</v>
       </c>
       <c r="E207" s="56">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F207" s="35" t="s">
         <v>2751</v>
@@ -55348,7 +55348,7 @@
         <v>2730</v>
       </c>
       <c r="E219" s="56">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F219" s="35">
         <v>845</v>
@@ -55560,7 +55560,7 @@
         <v>4</v>
       </c>
       <c r="F231" s="35" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="333" spans="2:5">
@@ -57173,7 +57173,7 @@
       </c>
       <c r="D4" s="33"/>
       <c r="E4" s="33">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F4" s="35">
         <v>146</v>
@@ -57255,7 +57255,7 @@
     <row r="9" spans="1:10">
       <c r="A9" s="33"/>
       <c r="B9" s="33" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1211</v>
@@ -57280,7 +57280,7 @@
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33">
-        <v>768</v>
+        <v>1001</v>
       </c>
       <c r="F10" s="35">
         <v>193</v>
@@ -57312,11 +57312,11 @@
         <v>2225</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33">
-        <v>709</v>
+        <v>682</v>
       </c>
       <c r="F12" s="35">
         <v>184</v>
@@ -57348,10 +57348,10 @@
         <v>1213</v>
       </c>
       <c r="C14" s="33" t="s">
+        <v>3344</v>
+      </c>
+      <c r="D14" s="33" t="s">
         <v>3345</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>3346</v>
       </c>
       <c r="E14" s="42">
         <v>12</v>
@@ -57369,10 +57369,10 @@
         <v>1214</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="E15" s="42">
         <v>7</v>
@@ -57443,7 +57443,7 @@
         <v>1217</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="33">
@@ -57479,10 +57479,10 @@
         <v>2511</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="E21" s="33">
         <v>5</v>
@@ -57499,11 +57499,11 @@
         <v>1453</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="33">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="F22" s="35">
         <v>363</v>
@@ -57601,10 +57601,10 @@
         <v>2681</v>
       </c>
       <c r="C28" s="33" t="s">
+        <v>3352</v>
+      </c>
+      <c r="D28" s="33" t="s">
         <v>3353</v>
-      </c>
-      <c r="D28" s="33" t="s">
-        <v>3354</v>
       </c>
       <c r="E28" s="53">
         <v>12</v>
@@ -57621,10 +57621,10 @@
         <v>2055</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="E29" s="60">
         <v>30</v>
@@ -57641,10 +57641,10 @@
         <v>2106</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="E30" s="60">
         <v>24</v>
@@ -57661,10 +57661,10 @@
         <v>2578</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="E31" s="60">
         <v>8</v>
@@ -57681,10 +57681,10 @@
         <v>2056</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="E32" s="60">
         <v>17</v>
@@ -57701,10 +57701,10 @@
         <v>2687</v>
       </c>
       <c r="C33" s="33" t="s">
+        <v>3358</v>
+      </c>
+      <c r="D33" s="33" t="s">
         <v>3359</v>
-      </c>
-      <c r="D33" s="33" t="s">
-        <v>3360</v>
       </c>
       <c r="E33" s="60">
         <v>4</v>
@@ -57725,7 +57725,7 @@
       </c>
       <c r="D34" s="33"/>
       <c r="E34" s="53">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="F34" s="35">
         <v>392</v>
@@ -57742,10 +57742,10 @@
         <v>2145</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="E35" s="60">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F35" s="35">
         <v>1118</v>
@@ -57759,13 +57759,13 @@
         <v>2445</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="D36" s="33">
         <v>239</v>
       </c>
       <c r="E36" s="60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F36" s="35">
         <v>283</v>
@@ -57779,10 +57779,10 @@
         <v>2664</v>
       </c>
       <c r="C37" s="33" t="s">
+        <v>3362</v>
+      </c>
+      <c r="D37" s="33" t="s">
         <v>3363</v>
-      </c>
-      <c r="D37" s="33" t="s">
-        <v>3364</v>
       </c>
       <c r="E37" s="33">
         <v>3</v>
@@ -57799,13 +57799,13 @@
         <v>2858</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="E38" s="33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F38" s="35">
         <v>1138</v>
@@ -57844,7 +57844,7 @@
         <v>5</v>
       </c>
       <c r="F40" s="35" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -57877,7 +57877,7 @@
       </c>
       <c r="D42" s="33"/>
       <c r="E42" s="60">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F42" s="35">
         <v>1249</v>
@@ -57916,7 +57916,7 @@
         <v>15</v>
       </c>
       <c r="F44" s="35" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -57945,10 +57945,10 @@
         <v>3102</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="E46" s="60">
         <v>104</v>
@@ -58082,10 +58082,10 @@
         <v>1226</v>
       </c>
       <c r="D54" s="33" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="E54" s="42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F54" s="35">
         <v>211</v>
@@ -58121,7 +58121,7 @@
       </c>
       <c r="D56" s="33"/>
       <c r="E56" s="33">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="F56" s="35">
         <v>120</v>
@@ -58139,7 +58139,7 @@
       </c>
       <c r="D57" s="33"/>
       <c r="E57" s="33">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="F57" s="35">
         <v>260</v>
@@ -58156,7 +58156,7 @@
         <v>2381</v>
       </c>
       <c r="D58" s="33" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="E58" s="42">
         <v>1</v>
@@ -58411,7 +58411,7 @@
       </c>
       <c r="D73" s="33"/>
       <c r="E73" s="42">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="F73" s="35">
         <v>295</v>
@@ -58428,7 +58428,7 @@
         <v>2381</v>
       </c>
       <c r="D74" s="33" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="E74" s="42">
         <v>0</v>
@@ -58448,7 +58448,7 @@
         <v>1226</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="E75" s="42">
         <v>5</v>
@@ -58469,7 +58469,7 @@
       </c>
       <c r="D76" s="33"/>
       <c r="E76" s="33">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F76" s="35">
         <v>239</v>
@@ -58505,7 +58505,7 @@
       </c>
       <c r="D78" s="33"/>
       <c r="E78" s="33">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="F78" s="35">
         <v>253</v>
@@ -58551,13 +58551,13 @@
         <v>1258</v>
       </c>
       <c r="C81" s="33" t="s">
+        <v>3373</v>
+      </c>
+      <c r="D81" s="33" t="s">
         <v>3374</v>
       </c>
-      <c r="D81" s="33" t="s">
-        <v>3375</v>
-      </c>
       <c r="E81" s="33">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F81" s="35">
         <v>537</v>
@@ -58606,7 +58606,7 @@
         <v>2381</v>
       </c>
       <c r="D84" s="33" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="E84" s="33">
         <v>10</v>
@@ -58623,10 +58623,10 @@
         <v>1262</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D85" s="33" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="E85" s="33">
         <v>0</v>
@@ -58643,10 +58643,10 @@
         <v>2752</v>
       </c>
       <c r="C86" s="33" t="s">
+        <v>3377</v>
+      </c>
+      <c r="D86" s="33" t="s">
         <v>3378</v>
-      </c>
-      <c r="D86" s="33" t="s">
-        <v>3379</v>
       </c>
       <c r="E86" s="33">
         <v>5</v>
@@ -58663,10 +58663,10 @@
         <v>1263</v>
       </c>
       <c r="C87" s="33" t="s">
+        <v>3379</v>
+      </c>
+      <c r="D87" s="33" t="s">
         <v>3380</v>
-      </c>
-      <c r="D87" s="33" t="s">
-        <v>3381</v>
       </c>
       <c r="E87" s="33">
         <v>70</v>
@@ -58686,7 +58686,7 @@
         <v>2381</v>
       </c>
       <c r="D88" s="33" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="E88" s="33">
         <v>0</v>
@@ -58798,7 +58798,7 @@
         <v>6</v>
       </c>
       <c r="F94" s="61" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -58812,7 +58812,7 @@
         <v>1226</v>
       </c>
       <c r="D95" s="33" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="E95" s="33">
         <v>3</v>
@@ -58832,7 +58832,7 @@
       </c>
       <c r="D96" s="33"/>
       <c r="E96" s="33">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F96" s="35">
         <v>288</v>
@@ -58944,7 +58944,7 @@
         <v>240</v>
       </c>
       <c r="E102" s="33">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F102" s="35">
         <v>407</v>
@@ -58976,10 +58976,10 @@
         <v>2176</v>
       </c>
       <c r="C104" s="33" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="D104" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="E104" s="33">
         <v>10</v>
@@ -58996,10 +58996,10 @@
         <v>2211</v>
       </c>
       <c r="C105" s="33" t="s">
+        <v>3383</v>
+      </c>
+      <c r="D105" s="33" t="s">
         <v>3384</v>
-      </c>
-      <c r="D105" s="33" t="s">
-        <v>3385</v>
       </c>
       <c r="E105" s="60">
         <v>11</v>
@@ -59016,10 +59016,10 @@
         <v>2082</v>
       </c>
       <c r="C106" s="33" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="D106" s="33" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="E106" s="60">
         <v>30</v>
@@ -59036,7 +59036,7 @@
         <v>1972</v>
       </c>
       <c r="C107" s="33" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="D107" s="33" t="s">
         <v>1520</v>
@@ -59077,7 +59077,7 @@
         <v>2480</v>
       </c>
       <c r="D109" s="33" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="E109" s="33">
         <v>7</v>
@@ -59150,7 +59150,7 @@
       </c>
       <c r="D113" s="33"/>
       <c r="E113" s="33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F113" s="35">
         <v>746</v>
@@ -59187,7 +59187,7 @@
         <v>2174</v>
       </c>
       <c r="D115" s="33" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="E115" s="33">
         <v>6</v>
@@ -59274,7 +59274,7 @@
         <v>2947</v>
       </c>
       <c r="C120" s="33" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="D120" s="33" t="s">
         <v>1572</v>
@@ -59328,7 +59328,7 @@
       </c>
       <c r="D123" s="33"/>
       <c r="E123" s="33">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F123" s="35">
         <v>197</v>
@@ -59363,7 +59363,7 @@
         <v>1279</v>
       </c>
       <c r="D125" s="57" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="E125" s="33">
         <v>0</v>
@@ -59403,10 +59403,10 @@
         <v>1283</v>
       </c>
       <c r="C127" s="33" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="D127" s="42" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="E127" s="33">
         <v>0</v>
@@ -59492,10 +59492,10 @@
         <v>2238</v>
       </c>
       <c r="C132" s="33" t="s">
+        <v>3388</v>
+      </c>
+      <c r="D132" s="33" t="s">
         <v>3389</v>
-      </c>
-      <c r="D132" s="33" t="s">
-        <v>3390</v>
       </c>
       <c r="E132" s="33">
         <v>0</v>
@@ -59528,10 +59528,10 @@
         <v>1407</v>
       </c>
       <c r="C134" s="33" t="s">
+        <v>3390</v>
+      </c>
+      <c r="D134" s="33" t="s">
         <v>3391</v>
-      </c>
-      <c r="D134" s="33" t="s">
-        <v>3392</v>
       </c>
       <c r="E134" s="33">
         <v>1</v>
@@ -59551,7 +59551,7 @@
         <v>1279</v>
       </c>
       <c r="D135" s="33" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="E135" s="33">
         <v>7</v>
@@ -59590,7 +59590,7 @@
       </c>
       <c r="D137" s="33"/>
       <c r="E137" s="33">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F137" s="33">
         <v>210</v>
@@ -59604,13 +59604,13 @@
         <v>2869</v>
       </c>
       <c r="C138" s="33" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="D138" s="33" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="E138" s="33">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F138" s="35">
         <v>278</v>
@@ -59687,7 +59687,7 @@
         <v>1279</v>
       </c>
       <c r="D142" s="33" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="E142" s="35">
         <v>8</v>
@@ -59711,7 +59711,7 @@
         <v>1858</v>
       </c>
       <c r="E143" s="35">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F143" s="33">
         <v>371</v>
@@ -59778,7 +59778,7 @@
         <v>1279</v>
       </c>
       <c r="D147" s="33" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="E147" s="33">
         <v>0</v>
@@ -59825,10 +59825,10 @@
         <v>2738</v>
       </c>
       <c r="C150" s="33" t="s">
+        <v>3393</v>
+      </c>
+      <c r="D150" s="33" t="s">
         <v>3394</v>
-      </c>
-      <c r="D150" s="33" t="s">
-        <v>3395</v>
       </c>
       <c r="E150" s="33">
         <v>1</v>
@@ -59845,10 +59845,10 @@
         <v>2739</v>
       </c>
       <c r="C151" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D151" s="33" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="E151" s="33">
         <v>1</v>
@@ -59914,7 +59914,7 @@
       </c>
       <c r="D155" s="33"/>
       <c r="E155" s="35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F155" s="33">
         <v>301</v>
@@ -59961,7 +59961,7 @@
         <v>175</v>
       </c>
       <c r="B158" s="90" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="C158" s="90"/>
       <c r="D158" s="90"/>
@@ -59976,7 +59976,7 @@
         <v>2019</v>
       </c>
       <c r="C159" s="33" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="D159" s="33" t="s">
         <v>836</v>
@@ -59996,13 +59996,13 @@
         <v>1814</v>
       </c>
       <c r="C160" s="33" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="D160" s="33" t="s">
         <v>1858</v>
       </c>
       <c r="E160" s="33">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="F160" s="35">
         <v>234</v>
@@ -60016,7 +60016,7 @@
         <v>2105</v>
       </c>
       <c r="C161" s="33" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="D161" s="33" t="s">
         <v>2422</v>
@@ -60036,10 +60036,10 @@
         <v>2379</v>
       </c>
       <c r="C162" s="57" t="s">
+        <v>3404</v>
+      </c>
+      <c r="D162" s="57" t="s">
         <v>3405</v>
-      </c>
-      <c r="D162" s="57" t="s">
-        <v>3406</v>
       </c>
       <c r="E162" s="33">
         <v>59</v>
@@ -60056,10 +60056,10 @@
         <v>2000</v>
       </c>
       <c r="C163" s="33" t="s">
+        <v>3406</v>
+      </c>
+      <c r="D163" s="33" t="s">
         <v>3407</v>
-      </c>
-      <c r="D163" s="33" t="s">
-        <v>3408</v>
       </c>
       <c r="E163" s="33">
         <v>103</v>
@@ -60076,13 +60076,13 @@
         <v>2261</v>
       </c>
       <c r="C164" s="33" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="D164" s="33" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="E164" s="60">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F164" s="33">
         <v>868</v>
@@ -60096,10 +60096,10 @@
         <v>2366</v>
       </c>
       <c r="C165" s="33" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="D165" s="33" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="E165" s="60">
         <v>4</v>
@@ -60116,10 +60116,10 @@
         <v>1999</v>
       </c>
       <c r="C166" s="33" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="D166" s="33" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="E166" s="33">
         <v>10</v>
@@ -60136,7 +60136,7 @@
         <v>2001</v>
       </c>
       <c r="C167" s="33" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="D167" s="33" t="s">
         <v>2552</v>
@@ -60156,10 +60156,10 @@
         <v>1223</v>
       </c>
       <c r="C168" s="33" t="s">
+        <v>3411</v>
+      </c>
+      <c r="D168" s="33" t="s">
         <v>3412</v>
-      </c>
-      <c r="D168" s="33" t="s">
-        <v>3413</v>
       </c>
       <c r="E168" s="33">
         <v>18</v>
@@ -60176,10 +60176,10 @@
         <v>1941</v>
       </c>
       <c r="C169" s="33" t="s">
+        <v>3413</v>
+      </c>
+      <c r="D169" s="33" t="s">
         <v>3414</v>
-      </c>
-      <c r="D169" s="33" t="s">
-        <v>3415</v>
       </c>
       <c r="E169" s="33">
         <v>25</v>
@@ -60196,10 +60196,10 @@
         <v>2339</v>
       </c>
       <c r="C170" s="33" t="s">
+        <v>3415</v>
+      </c>
+      <c r="D170" s="33" t="s">
         <v>3416</v>
-      </c>
-      <c r="D170" s="33" t="s">
-        <v>3417</v>
       </c>
       <c r="E170" s="33">
         <v>2</v>
@@ -60216,13 +60216,13 @@
         <v>2325</v>
       </c>
       <c r="C171" s="33" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="D171" s="33" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="E171" s="33">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F171" s="35">
         <v>1960</v>
@@ -60236,13 +60236,13 @@
         <v>2483</v>
       </c>
       <c r="C172" s="33" t="s">
+        <v>3418</v>
+      </c>
+      <c r="D172" s="33" t="s">
         <v>3419</v>
       </c>
-      <c r="D172" s="33" t="s">
-        <v>3420</v>
-      </c>
       <c r="E172" s="33">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F172" s="35">
         <v>649</v>
@@ -60256,13 +60256,13 @@
         <v>2487</v>
       </c>
       <c r="C173" s="33" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="D173" s="33" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="E173" s="33">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F173" s="35">
         <v>759</v>
@@ -60276,10 +60276,10 @@
         <v>2486</v>
       </c>
       <c r="C174" s="33" t="s">
+        <v>3421</v>
+      </c>
+      <c r="D174" s="33" t="s">
         <v>3422</v>
-      </c>
-      <c r="D174" s="33" t="s">
-        <v>3423</v>
       </c>
       <c r="E174" s="33">
         <v>29</v>
@@ -60296,7 +60296,7 @@
         <v>2338</v>
       </c>
       <c r="C175" s="33" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="D175" s="33" t="s">
         <v>2528</v>
@@ -60316,10 +60316,10 @@
         <v>2645</v>
       </c>
       <c r="C176" s="33" t="s">
+        <v>3423</v>
+      </c>
+      <c r="D176" s="33" t="s">
         <v>3424</v>
-      </c>
-      <c r="D176" s="33" t="s">
-        <v>3425</v>
       </c>
       <c r="E176" s="33">
         <v>41</v>
@@ -60336,10 +60336,10 @@
         <v>2742</v>
       </c>
       <c r="C177" s="33" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="D177" s="33" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="E177" s="33">
         <v>5</v>
@@ -60356,10 +60356,10 @@
         <v>2647</v>
       </c>
       <c r="C178" s="33" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="D178" s="33" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="E178" s="33">
         <v>76</v>
@@ -60394,10 +60394,10 @@
         <v>2744</v>
       </c>
       <c r="C180" s="33" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="D180" s="33" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="E180" s="33">
         <v>18</v>
@@ -60411,7 +60411,7 @@
         <v>203</v>
       </c>
       <c r="B181" s="90" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="C181" s="90"/>
       <c r="D181" s="90"/>
@@ -60426,10 +60426,10 @@
         <v>1254</v>
       </c>
       <c r="C182" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D182" s="33" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="E182" s="33">
         <v>0</v>
@@ -60446,7 +60446,7 @@
         <v>1255</v>
       </c>
       <c r="C183" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D183" s="33" t="s">
         <v>290</v>
@@ -60466,13 +60466,13 @@
         <v>1264</v>
       </c>
       <c r="C184" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D184" s="33" t="s">
         <v>318</v>
       </c>
       <c r="E184" s="33">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F184" s="35">
         <v>186</v>
@@ -60486,10 +60486,10 @@
         <v>1545</v>
       </c>
       <c r="C185" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D185" s="33" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="E185" s="33">
         <v>18</v>
@@ -60506,10 +60506,10 @@
         <v>1265</v>
       </c>
       <c r="C186" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D186" s="33" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="E186" s="33">
         <v>25</v>
@@ -60526,7 +60526,7 @@
         <v>1266</v>
       </c>
       <c r="C187" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D187" s="33" t="s">
         <v>2422</v>
@@ -60546,7 +60546,7 @@
         <v>1268</v>
       </c>
       <c r="C188" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D188" s="33" t="s">
         <v>2246</v>
@@ -60566,10 +60566,10 @@
         <v>1269</v>
       </c>
       <c r="C189" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D189" s="33" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="E189" s="33">
         <v>48</v>
@@ -60586,13 +60586,13 @@
         <v>1270</v>
       </c>
       <c r="C190" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D190" s="33" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="E190" s="33">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="F190" s="33" t="s">
         <v>3022</v>
@@ -60606,10 +60606,10 @@
         <v>1542</v>
       </c>
       <c r="C191" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D191" s="33" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="E191" s="33">
         <v>32</v>
@@ -60626,10 +60626,10 @@
         <v>1889</v>
       </c>
       <c r="C192" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D192" s="33" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="E192" s="33">
         <v>30</v>
@@ -60646,7 +60646,7 @@
         <v>1273</v>
       </c>
       <c r="C193" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D193" s="33"/>
       <c r="E193" s="33">
@@ -60664,13 +60664,13 @@
         <v>1778</v>
       </c>
       <c r="C194" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D194" s="33" t="s">
         <v>2799</v>
       </c>
       <c r="E194" s="42">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F194" s="35">
         <v>170</v>
@@ -60684,10 +60684,10 @@
         <v>1700</v>
       </c>
       <c r="C195" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D195" s="33" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="E195" s="42">
         <v>30</v>
@@ -60704,7 +60704,7 @@
         <v>1429</v>
       </c>
       <c r="C196" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D196" s="33" t="s">
         <v>1859</v>
@@ -60722,10 +60722,10 @@
         <v>1271</v>
       </c>
       <c r="C197" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D197" s="33" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="E197" s="33">
         <v>13</v>
@@ -60742,10 +60742,10 @@
         <v>1272</v>
       </c>
       <c r="C198" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D198" s="33" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="E198" s="33">
         <v>4</v>
@@ -60762,7 +60762,7 @@
         <v>2790</v>
       </c>
       <c r="C199" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D199" s="33" t="s">
         <v>3143</v>
@@ -60782,10 +60782,10 @@
         <v>2002</v>
       </c>
       <c r="C200" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D200" s="33" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="E200" s="33">
         <v>147</v>
@@ -60802,13 +60802,13 @@
         <v>2357</v>
       </c>
       <c r="C201" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D201" s="33" t="s">
         <v>2438</v>
       </c>
       <c r="E201" s="33">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F201" s="35">
         <v>200</v>
@@ -60822,10 +60822,10 @@
         <v>2340</v>
       </c>
       <c r="C202" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D202" s="33" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="E202" s="33">
         <v>30</v>
@@ -60842,10 +60842,10 @@
         <v>2326</v>
       </c>
       <c r="C203" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D203" s="33" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="E203" s="33">
         <v>12</v>
@@ -60862,10 +60862,10 @@
         <v>2327</v>
       </c>
       <c r="C204" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D204" s="33" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="E204" s="33">
         <v>3</v>
@@ -60882,10 +60882,10 @@
         <v>2329</v>
       </c>
       <c r="C205" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D205" s="33" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="E205" s="33">
         <v>8</v>
@@ -60897,13 +60897,13 @@
     <row r="206" spans="1:6">
       <c r="A206" s="33"/>
       <c r="B206" s="33" t="s">
+        <v>3585</v>
+      </c>
+      <c r="C206" s="33" t="s">
+        <v>3373</v>
+      </c>
+      <c r="D206" s="33" t="s">
         <v>3586</v>
-      </c>
-      <c r="C206" s="33" t="s">
-        <v>3374</v>
-      </c>
-      <c r="D206" s="33" t="s">
-        <v>3587</v>
       </c>
       <c r="E206" s="33">
         <v>1</v>
@@ -60920,10 +60920,10 @@
         <v>2330</v>
       </c>
       <c r="C207" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D207" s="33" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="E207" s="33">
         <v>19</v>
@@ -60940,13 +60940,13 @@
         <v>2558</v>
       </c>
       <c r="C208" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D208" s="33" t="s">
         <v>2408</v>
       </c>
       <c r="E208" s="33">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F208" s="35">
         <v>278</v>
@@ -60960,10 +60960,10 @@
         <v>2478</v>
       </c>
       <c r="C209" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D209" s="33" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="E209" s="33">
         <v>17</v>
@@ -60980,13 +60980,13 @@
         <v>2489</v>
       </c>
       <c r="C210" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D210" s="33" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="E210" s="33">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="F210" s="35">
         <v>345</v>
@@ -61000,7 +61000,7 @@
         <v>2239</v>
       </c>
       <c r="C211" s="33" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="D211" s="33" t="s">
         <v>2839</v>
@@ -61015,7 +61015,7 @@
         <v>237</v>
       </c>
       <c r="B212" s="90" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="C212" s="90"/>
       <c r="D212" s="90"/>
@@ -61030,7 +61030,7 @@
         <v>1970</v>
       </c>
       <c r="C213" s="33" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="D213" s="33" t="s">
         <v>836</v>
@@ -61050,10 +61050,10 @@
         <v>2367</v>
       </c>
       <c r="C214" s="33" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="D214" s="33" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="E214" s="33">
         <v>36</v>
@@ -61070,10 +61070,10 @@
         <v>2311</v>
       </c>
       <c r="C215" s="33" t="s">
+        <v>3447</v>
+      </c>
+      <c r="D215" s="33" t="s">
         <v>3448</v>
-      </c>
-      <c r="D215" s="33" t="s">
-        <v>3449</v>
       </c>
       <c r="E215" s="33">
         <v>18</v>
@@ -61090,13 +61090,13 @@
         <v>2312</v>
       </c>
       <c r="C216" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D216" s="33" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="E216" s="33">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F216" s="33">
         <v>311</v>
@@ -61110,13 +61110,13 @@
         <v>2313</v>
       </c>
       <c r="C217" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D217" s="33" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="E217" s="33">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F217" s="33">
         <v>330</v>
@@ -61130,13 +61130,13 @@
         <v>2314</v>
       </c>
       <c r="C218" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D218" s="33" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="E218" s="33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F218" s="33" t="s">
         <v>2940</v>
@@ -61150,13 +61150,13 @@
         <v>2315</v>
       </c>
       <c r="C219" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D219" s="33" t="s">
         <v>2392</v>
       </c>
       <c r="E219" s="33">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F219" s="33">
         <v>244</v>
@@ -61170,10 +61170,10 @@
         <v>2316</v>
       </c>
       <c r="C220" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D220" s="33" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="E220" s="33">
         <v>9</v>
@@ -61190,10 +61190,10 @@
         <v>2469</v>
       </c>
       <c r="C221" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D221" s="33" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="E221" s="33">
         <v>19</v>
@@ -61210,7 +61210,7 @@
         <v>2317</v>
       </c>
       <c r="C222" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D222" s="33" t="s">
         <v>2405</v>
@@ -61230,10 +61230,10 @@
         <v>2358</v>
       </c>
       <c r="C223" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D223" s="33" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="E223" s="33">
         <v>16</v>
@@ -61250,7 +61250,7 @@
         <v>2318</v>
       </c>
       <c r="C224" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D224" s="33" t="s">
         <v>3023</v>
@@ -61270,10 +61270,10 @@
         <v>2319</v>
       </c>
       <c r="C225" s="33" t="s">
+        <v>3455</v>
+      </c>
+      <c r="D225" s="33" t="s">
         <v>3456</v>
-      </c>
-      <c r="D225" s="33" t="s">
-        <v>3457</v>
       </c>
       <c r="E225" s="33">
         <v>19</v>
@@ -61290,10 +61290,10 @@
         <v>2916</v>
       </c>
       <c r="C226" s="33" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="D226" s="33" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="E226" s="33">
         <v>6</v>
@@ -61310,13 +61310,13 @@
         <v>2320</v>
       </c>
       <c r="C227" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D227" s="33" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="E227" s="33">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F227" s="33" t="s">
         <v>2836</v>
@@ -61330,13 +61330,13 @@
         <v>2321</v>
       </c>
       <c r="C228" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D228" s="33" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="E228" s="33">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F228" s="33">
         <v>315</v>
@@ -61350,10 +61350,10 @@
         <v>2322</v>
       </c>
       <c r="C229" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D229" s="33" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="E229" s="33">
         <v>0</v>
@@ -61370,10 +61370,10 @@
         <v>2323</v>
       </c>
       <c r="C230" s="33" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="D230" s="33" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="E230" s="33">
         <v>18</v>
@@ -61390,13 +61390,13 @@
         <v>2324</v>
       </c>
       <c r="C231" s="33" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="D231" s="33" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="E231" s="33">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F231" s="35" t="s">
         <v>2785</v>
@@ -61410,13 +61410,13 @@
         <v>2333</v>
       </c>
       <c r="C232" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D232" s="33" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="E232" s="33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F232" s="35">
         <v>1026</v>
@@ -61430,10 +61430,10 @@
         <v>1682</v>
       </c>
       <c r="C233" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D233" s="33" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="E233" s="33">
         <v>35</v>
@@ -61450,10 +61450,10 @@
         <v>2345</v>
       </c>
       <c r="C234" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D234" s="33" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="E234" s="33">
         <v>15</v>
@@ -61470,13 +61470,13 @@
         <v>2365</v>
       </c>
       <c r="C235" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D235" s="33" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="E235" s="33">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F235" s="35">
         <v>273</v>
@@ -61490,10 +61490,10 @@
         <v>2346</v>
       </c>
       <c r="C236" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D236" s="33" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="E236" s="33">
         <v>49</v>
@@ -61510,10 +61510,10 @@
         <v>2347</v>
       </c>
       <c r="C237" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D237" s="33" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="E237" s="33">
         <v>38</v>
@@ -61530,10 +61530,10 @@
         <v>2359</v>
       </c>
       <c r="C238" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D238" s="33" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="E238" s="33">
         <v>31</v>
@@ -61553,7 +61553,7 @@
         <v>2983</v>
       </c>
       <c r="D239" s="33" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="E239" s="33">
         <v>28</v>
@@ -61570,10 +61570,10 @@
         <v>2488</v>
       </c>
       <c r="C240" s="33" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="D240" s="33" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="E240" s="33">
         <v>13</v>
@@ -61590,10 +61590,10 @@
         <v>2930</v>
       </c>
       <c r="C241" s="33" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="D241" s="33" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="E241" s="33">
         <v>7</v>
@@ -61610,10 +61610,10 @@
         <v>2534</v>
       </c>
       <c r="C242" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D242" s="33" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="E242" s="33">
         <v>0</v>
@@ -61630,7 +61630,7 @@
         <v>2653</v>
       </c>
       <c r="C243" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D243" s="33" t="s">
         <v>2438</v>
@@ -61650,7 +61650,7 @@
         <v>2735</v>
       </c>
       <c r="C244" s="33" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="D244" s="33" t="s">
         <v>2423</v>
@@ -61670,10 +61670,10 @@
         <v>2736</v>
       </c>
       <c r="C245" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="E245" s="33">
         <v>4</v>
@@ -61690,10 +61690,10 @@
         <v>2737</v>
       </c>
       <c r="C246" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="E246" s="33">
         <v>4</v>
@@ -61710,10 +61710,10 @@
         <v>2740</v>
       </c>
       <c r="C247" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D247" s="33" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="E247" s="33">
         <v>66</v>
@@ -61730,13 +61730,13 @@
         <v>2741</v>
       </c>
       <c r="C248" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D248" s="33" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="E248" s="33">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F248" s="35">
         <v>338</v>
@@ -61750,10 +61750,10 @@
         <v>2743</v>
       </c>
       <c r="C249" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D249" s="33" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="E249" s="33">
         <v>13</v>
@@ -61774,7 +61774,7 @@
       </c>
       <c r="D250" s="33"/>
       <c r="E250" s="33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F250" s="35" t="s">
         <v>2943</v>
@@ -62101,13 +62101,13 @@
     <row r="267" spans="1:7">
       <c r="A267" s="33"/>
       <c r="B267" s="33" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="C267" s="33" t="s">
         <v>2983</v>
       </c>
       <c r="D267" s="33" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="E267" s="33">
         <v>22</v>
@@ -62129,7 +62129,7 @@
         <v>299</v>
       </c>
       <c r="B269" s="90" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="C269" s="90"/>
       <c r="D269" s="90"/>
@@ -62147,7 +62147,7 @@
         <v>2380</v>
       </c>
       <c r="D270" s="33" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="E270" s="33">
         <v>14</v>
@@ -62210,7 +62210,7 @@
         <v>2380</v>
       </c>
       <c r="D273" s="33" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="E273" s="33">
         <v>15</v>
@@ -62230,7 +62230,7 @@
         <v>2380</v>
       </c>
       <c r="D274" s="33" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="E274" s="33">
         <v>15</v>
@@ -62250,7 +62250,7 @@
         <v>2380</v>
       </c>
       <c r="D275" s="33" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="E275" s="33">
         <v>9</v>
@@ -62270,7 +62270,7 @@
         <v>2380</v>
       </c>
       <c r="D276" s="33" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="E276" s="33">
         <v>9</v>
@@ -62290,7 +62290,7 @@
         <v>2380</v>
       </c>
       <c r="D277" s="33" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="E277" s="33">
         <v>12</v>
@@ -62310,7 +62310,7 @@
         <v>2380</v>
       </c>
       <c r="D278" s="33" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="E278" s="33">
         <v>5</v>
@@ -62390,7 +62390,7 @@
         <v>2380</v>
       </c>
       <c r="D282" s="33" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="E282" s="33">
         <v>32</v>
@@ -62553,7 +62553,7 @@
         <v>3071</v>
       </c>
       <c r="E290" s="33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F290" s="35">
         <v>209</v>
@@ -63698,7 +63698,7 @@
         <v>399</v>
       </c>
       <c r="E58" s="62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="4">
         <v>2529</v>
@@ -63899,7 +63899,7 @@
     <row r="69" spans="1:8">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -64626,7 +64626,7 @@
         <v>49</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="C24" s="33" t="s">
         <v>296</v>
@@ -64764,7 +64764,7 @@
         <v>66</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
@@ -65035,10 +65035,10 @@
         <v>410</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="E3" s="35">
         <v>0</v>
@@ -65073,7 +65073,7 @@
         <v>412</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="D5" s="33"/>
       <c r="E5" s="35">
@@ -65147,7 +65147,7 @@
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="35">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="F9" s="33" t="s">
         <v>2814</v>
@@ -65201,7 +65201,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="35">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="F12" s="33">
         <v>155</v>
@@ -65222,7 +65222,7 @@
       </c>
       <c r="D13" s="33"/>
       <c r="E13" s="35">
-        <v>170</v>
+        <v>370</v>
       </c>
       <c r="F13" s="33">
         <v>195</v>
@@ -65370,7 +65370,7 @@
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="35">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="F22" s="33">
         <v>79</v>
@@ -65405,7 +65405,7 @@
         <v>430</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="D24" s="33" t="s">
         <v>3013</v>
@@ -65425,7 +65425,7 @@
         <v>431</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="D25" s="33" t="s">
         <v>432</v>
@@ -65443,7 +65443,7 @@
         <v>433</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="D26" s="33"/>
       <c r="E26" s="35">
@@ -65477,7 +65477,7 @@
         <v>434</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="D28" s="33"/>
       <c r="E28" s="35">
@@ -65493,11 +65493,11 @@
         <v>435</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="D29" s="33"/>
       <c r="E29" s="35">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F29" s="33">
         <v>21</v>
@@ -65511,7 +65511,7 @@
         <v>436</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="D30" s="33"/>
       <c r="E30" s="35">
@@ -65529,7 +65529,7 @@
         <v>1555</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="D31" s="33"/>
       <c r="E31" s="35">
@@ -65579,7 +65579,7 @@
         <v>437</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="D34" s="33"/>
       <c r="E34" s="35">
@@ -65597,7 +65597,7 @@
         <v>438</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="D35" s="33"/>
       <c r="E35" s="35">
@@ -65862,7 +65862,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="91" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="C50" s="91"/>
       <c r="D50" s="91"/>
@@ -65883,7 +65883,7 @@
         <v>2287</v>
       </c>
       <c r="E51" s="35">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F51" s="33">
         <v>6418</v>

--- a/backend/public/BOSCH_STOCK1.xlsx
+++ b/backend/public/BOSCH_STOCK1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730" firstSheet="10" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="ELEMENT" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'BULB,FANBELT,HORN'!$A$1:$G$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">COMPONENTS!$A$1:$H$376</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DELIVERY VALVE&amp;O.H.KIT'!$A$1:$H$129</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DIESEL FILTER&amp;OIL FILTER'!$A$1:$J$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DIESEL FILTER&amp;OIL FILTER'!$A$1:$J$294</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ELEMENT!$A$1:$F$172</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'GLOW PLUG&amp;SPARK PLUG'!$A$1:$F$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">LUBRICANTS!$A$1:$H$91</definedName>
@@ -39,8 +39,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'STARTER PARTS'!$A$1:$G$231</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'WIPER BLADE,PIPE,BRAKEPAD'!$A$1:$H$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'BULB,FANBELT,HORN'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'DIESEL FILTER&amp;OIL FILTER'!$A$3:$N$634</definedName>
-    <definedName name="Z_8145F22A_AD74_4799_898B_BCECC4FA34F9_.wvu.PrintArea" localSheetId="5" hidden="1">'DIESEL FILTER&amp;OIL FILTER'!$A$3:$N$634</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'DIESEL FILTER&amp;OIL FILTER'!$A$3:$N$635</definedName>
+    <definedName name="Z_8145F22A_AD74_4799_898B_BCECC4FA34F9_.wvu.PrintArea" localSheetId="5" hidden="1">'DIESEL FILTER&amp;OIL FILTER'!$A$3:$N$635</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <customWorkbookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5807" uniqueCount="3592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5810" uniqueCount="3594">
   <si>
     <t>0 433 175 443</t>
   </si>
@@ -10926,6 +10926,12 @@
   </si>
   <si>
     <t xml:space="preserve"> crank senssor 026121032</t>
+  </si>
+  <si>
+    <t>1135/1046</t>
+  </si>
+  <si>
+    <t>F 002 H23 561</t>
   </si>
 </sst>
 </file>
@@ -12780,7 +12786,7 @@
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
@@ -14763,7 +14769,7 @@
       </c>
       <c r="D123" s="17"/>
       <c r="E123" s="19">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F123" s="17"/>
       <c r="G123" s="17"/>
@@ -15181,7 +15187,7 @@
       </c>
       <c r="D143" s="17"/>
       <c r="E143" s="19">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F143" s="17"/>
       <c r="G143" s="17"/>
@@ -16160,7 +16166,7 @@
         <v>1825</v>
       </c>
       <c r="E3" s="75">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" s="74">
         <v>1974</v>
@@ -16204,7 +16210,7 @@
         <v>3499</v>
       </c>
       <c r="E5" s="75">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F5" s="74">
         <v>2443</v>
@@ -16414,7 +16420,7 @@
         <v>2703</v>
       </c>
       <c r="E15" s="75">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="F15" s="74">
         <v>179</v>
@@ -17014,7 +17020,7 @@
         <v>2703</v>
       </c>
       <c r="E47" s="75">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F47" s="74">
         <v>1605</v>
@@ -17752,7 +17758,7 @@
         <v>2703</v>
       </c>
       <c r="E85" s="75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F85" s="74">
         <v>2122</v>
@@ -18752,7 +18758,7 @@
         <v>2075</v>
       </c>
       <c r="E137" s="75">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F137" s="74" t="s">
         <v>2792</v>
@@ -18852,7 +18858,7 @@
         <v>822</v>
       </c>
       <c r="E142" s="75">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F142" s="74">
         <v>746</v>
@@ -19058,7 +19064,7 @@
         <v>1396</v>
       </c>
       <c r="E152" s="75">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F152" s="74">
         <v>969</v>
@@ -19206,7 +19212,7 @@
         <v>2703</v>
       </c>
       <c r="E159" s="75">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F159" s="74">
         <v>100</v>
@@ -19544,7 +19550,7 @@
       </c>
       <c r="D176" s="74"/>
       <c r="E176" s="75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F176" s="74">
         <v>1438</v>
@@ -19816,7 +19822,7 @@
       </c>
       <c r="D189" s="74"/>
       <c r="E189" s="75">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F189" s="74" t="s">
         <v>3579</v>
@@ -20084,7 +20090,7 @@
       </c>
       <c r="D203" s="74"/>
       <c r="E203" s="75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F203" s="74">
         <v>2320</v>
@@ -20124,7 +20130,7 @@
       </c>
       <c r="D205" s="74"/>
       <c r="E205" s="75">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F205" s="74">
         <v>2003</v>
@@ -20318,7 +20324,7 @@
       </c>
       <c r="D215" s="74"/>
       <c r="E215" s="75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F215" s="75">
         <v>143</v>
@@ -20612,7 +20618,7 @@
         <v>2442</v>
       </c>
       <c r="E229" s="75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F229" s="74">
         <v>12762</v>
@@ -21152,7 +21158,7 @@
         <v>1858</v>
       </c>
       <c r="E254" s="75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F254" s="74">
         <v>9313</v>
@@ -21330,7 +21336,7 @@
         <v>1354</v>
       </c>
       <c r="E262" s="75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F262" s="74">
         <v>10729</v>
@@ -21440,7 +21446,7 @@
         <v>2905</v>
       </c>
       <c r="E267" s="75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F267" s="74">
         <v>11735</v>
@@ -21484,7 +21490,7 @@
         <v>2904</v>
       </c>
       <c r="E269" s="75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F269" s="74">
         <v>11506</v>
@@ -21696,7 +21702,7 @@
         <v>2903</v>
       </c>
       <c r="E279" s="75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F279" s="74">
         <v>10624</v>
@@ -22099,7 +22105,7 @@
         <v>3505</v>
       </c>
       <c r="E3" s="71">
-        <v>247</v>
+        <v>105</v>
       </c>
       <c r="F3" s="70">
         <v>146</v>
@@ -22167,7 +22173,7 @@
         <v>3508</v>
       </c>
       <c r="E6" s="71">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="F6" s="70">
         <v>182</v>
@@ -22237,7 +22243,7 @@
         <v>3511</v>
       </c>
       <c r="E9" s="71">
-        <v>471</v>
+        <v>371</v>
       </c>
       <c r="F9" s="70">
         <v>219</v>
@@ -22259,7 +22265,7 @@
         <v>3512</v>
       </c>
       <c r="E10" s="71">
-        <v>278</v>
+        <v>178</v>
       </c>
       <c r="F10" s="70">
         <v>225</v>
@@ -22391,7 +22397,7 @@
         <v>2232</v>
       </c>
       <c r="E16" s="71">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F16" s="69">
         <v>334</v>
@@ -22581,7 +22587,7 @@
         <v>2094</v>
       </c>
       <c r="E25" s="71">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F25" s="69">
         <v>444</v>
@@ -22783,7 +22789,7 @@
       </c>
       <c r="D35" s="71"/>
       <c r="E35" s="71">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F35" s="70">
         <v>311</v>
@@ -22843,7 +22849,7 @@
       </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F38" s="70">
         <v>385</v>
@@ -22883,7 +22889,7 @@
       </c>
       <c r="D40" s="71"/>
       <c r="E40" s="71">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F40" s="70">
         <v>428</v>
@@ -31255,7 +31261,7 @@
         <v>1295</v>
       </c>
       <c r="E3" s="19">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="F3" s="17">
         <v>362</v>
@@ -31297,7 +31303,7 @@
         <v>1295</v>
       </c>
       <c r="E5" s="19">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F5" s="17">
         <v>1098</v>
@@ -31339,7 +31345,7 @@
         <v>1295</v>
       </c>
       <c r="E7" s="19">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F7" s="17">
         <v>3385</v>
@@ -31421,7 +31427,7 @@
         <v>1303</v>
       </c>
       <c r="E11" s="19">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F11" s="17">
         <v>1826</v>
@@ -31442,7 +31448,7 @@
         <v>1303</v>
       </c>
       <c r="E12" s="19">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F12" s="17">
         <v>2698</v>
@@ -31650,7 +31656,7 @@
         <v>1317</v>
       </c>
       <c r="E22" s="19">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F22" s="17">
         <v>2056</v>
@@ -31818,7 +31824,7 @@
         <v>2372</v>
       </c>
       <c r="E30" s="19">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F30" s="17">
         <v>1709</v>
@@ -31881,7 +31887,7 @@
         <v>2269</v>
       </c>
       <c r="E33" s="19">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F33" s="17">
         <v>1199</v>
@@ -32007,7 +32013,7 @@
         <v>1321</v>
       </c>
       <c r="E39" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F39" s="17">
         <v>1360</v>
@@ -32047,7 +32053,7 @@
         <v>1321</v>
       </c>
       <c r="E41" s="19">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F41" s="17">
         <v>475</v>
@@ -32110,7 +32116,7 @@
         <v>1331</v>
       </c>
       <c r="E44" s="19">
-        <v>316</v>
+        <v>146</v>
       </c>
       <c r="F44" s="17">
         <v>247</v>
@@ -32131,7 +32137,7 @@
         <v>1331</v>
       </c>
       <c r="E45" s="19">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F45" s="17">
         <v>676</v>
@@ -32171,7 +32177,7 @@
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="17"/>
       <c r="G47" s="32"/>
@@ -32271,7 +32277,7 @@
         <v>2525</v>
       </c>
       <c r="E53" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F53" s="17">
         <v>1804</v>
@@ -32521,7 +32527,7 @@
         <v>2865</v>
       </c>
       <c r="E64" s="84">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="F64" s="32">
         <v>251</v>
@@ -33090,6 +33096,7 @@
     <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75">
@@ -33166,7 +33173,7 @@
         <v>2392</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>1009</v>
@@ -33206,7 +33213,7 @@
         <v>2246</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>815</v>
@@ -33306,10 +33313,10 @@
         <v>2399</v>
       </c>
       <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1135</v>
+        <v>3</v>
+      </c>
+      <c r="F11" t="s">
+        <v>3592</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -33546,7 +33553,7 @@
         <v>2411</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>1966</v>
@@ -33626,7 +33633,7 @@
         <v>318</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>701</v>
@@ -33686,7 +33693,7 @@
         <v>2416</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F30">
         <v>760</v>
@@ -33846,7 +33853,7 @@
         <v>2424</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F38">
         <v>1465</v>
@@ -34006,7 +34013,7 @@
         <v>779</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46">
         <v>1532</v>
@@ -34146,10 +34153,10 @@
         <v>2571</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F53">
-        <v>1752</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -34226,10 +34233,10 @@
         <v>2499</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>1378</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -34246,10 +34253,10 @@
         <v>2500</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>1787</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -34266,10 +34273,10 @@
         <v>2507</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F59">
-        <v>1886</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -34695,7 +34702,7 @@
         <v>1858</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F82">
         <v>593</v>
@@ -34715,7 +34722,7 @@
         <v>683</v>
       </c>
       <c r="E83">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F83">
         <v>368</v>
@@ -34922,7 +34929,10 @@
         <v>3562</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F94">
+        <v>1925</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -35990,7 +36000,7 @@
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F7" s="9"/>
     </row>
@@ -36080,7 +36090,7 @@
         <v>1465</v>
       </c>
       <c r="E12" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>2650</v>
@@ -37056,7 +37066,7 @@
         <v>778</v>
       </c>
       <c r="E66" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F66" s="9"/>
     </row>
@@ -37442,7 +37452,7 @@
         <v>897</v>
       </c>
       <c r="E85" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F85" s="9"/>
       <c r="G85" t="s">
@@ -38530,7 +38540,7 @@
         <v>1452</v>
       </c>
       <c r="E138" s="10">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F138" s="9"/>
     </row>
@@ -38737,7 +38747,7 @@
         <v>1185</v>
       </c>
       <c r="E148" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F148" s="9"/>
       <c r="G148" t="s">
@@ -39319,7 +39329,7 @@
         <v>1088</v>
       </c>
       <c r="E177" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F177" s="9"/>
       <c r="G177" t="s">
@@ -39814,7 +39824,7 @@
         <v>1379</v>
       </c>
       <c r="E201" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>2650</v>
@@ -42334,7 +42344,7 @@
         <v>2683</v>
       </c>
       <c r="E55" s="35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55" s="33">
         <v>3578</v>
@@ -42824,7 +42834,7 @@
       <c r="C84" s="33"/>
       <c r="D84" s="38"/>
       <c r="E84" s="35">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F84" s="33" t="s">
         <v>2595</v>
@@ -43393,7 +43403,7 @@
       </c>
       <c r="D117" s="38"/>
       <c r="E117" s="35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F117" s="33"/>
       <c r="H117" t="s">
@@ -45683,7 +45693,7 @@
       </c>
       <c r="D43" s="33"/>
       <c r="E43" s="35">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F43" s="33">
         <v>154</v>
@@ -46336,7 +46346,7 @@
       </c>
       <c r="D84" s="33"/>
       <c r="E84" s="35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F84" s="33"/>
     </row>
@@ -47117,7 +47127,7 @@
       </c>
       <c r="D132" s="33"/>
       <c r="E132" s="35">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F132" s="33">
         <v>247</v>
@@ -48424,7 +48434,7 @@
       </c>
       <c r="D211" s="33"/>
       <c r="E211" s="35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F211" s="33"/>
     </row>
@@ -49196,7 +49206,7 @@
       </c>
       <c r="D257" s="33"/>
       <c r="E257" s="35">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F257" s="33">
         <v>137</v>
@@ -49232,7 +49242,7 @@
         <v>2723</v>
       </c>
       <c r="E259" s="35">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F259" s="33">
         <v>327</v>
@@ -49710,7 +49720,7 @@
       </c>
       <c r="D288" s="33"/>
       <c r="E288" s="35">
-        <v>96</v>
+        <v>206</v>
       </c>
       <c r="F288" s="33"/>
     </row>
@@ -49762,7 +49772,7 @@
       </c>
       <c r="D291" s="33"/>
       <c r="E291" s="35">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F291" s="33">
         <v>356</v>
@@ -49834,7 +49844,7 @@
       </c>
       <c r="D295" s="33"/>
       <c r="E295" s="35">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F295" s="33">
         <v>696</v>
@@ -49870,7 +49880,7 @@
       </c>
       <c r="D297" s="33"/>
       <c r="E297" s="35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F297" s="33"/>
     </row>
@@ -51091,7 +51101,7 @@
       </c>
       <c r="D366" s="33"/>
       <c r="E366" s="35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F366" s="33">
         <v>1267</v>
@@ -51831,7 +51841,7 @@
         <v>2697</v>
       </c>
       <c r="E24" s="56">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="F24" s="35" t="s">
         <v>2819</v>
@@ -52384,7 +52394,7 @@
         <v>2697</v>
       </c>
       <c r="E57" s="56">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F57" s="35">
         <v>2075</v>
@@ -52404,7 +52414,7 @@
         <v>2700</v>
       </c>
       <c r="E58" s="56">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="F58" s="35" t="s">
         <v>3578</v>
@@ -52840,7 +52850,7 @@
         <v>2717</v>
       </c>
       <c r="E83" s="56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F83" s="35">
         <v>1036</v>
@@ -52990,7 +53000,7 @@
         <v>2707</v>
       </c>
       <c r="E91" s="56">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="F91" s="35">
         <v>855</v>
@@ -53623,7 +53633,7 @@
         <v>2703</v>
       </c>
       <c r="E127" s="56">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F127" s="35">
         <v>772</v>
@@ -53734,7 +53744,7 @@
         <v>2706</v>
       </c>
       <c r="E133" s="56">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F133" s="35" t="s">
         <v>3583</v>
@@ -53797,7 +53807,7 @@
         <v>518894</v>
       </c>
       <c r="E136" s="56">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F136" s="35" t="s">
         <v>3581</v>
@@ -53996,7 +54006,7 @@
         <v>2699</v>
       </c>
       <c r="E147" s="56">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="F147" s="35">
         <v>554</v>
@@ -54186,7 +54196,7 @@
         <v>2703</v>
       </c>
       <c r="E157" s="56">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F157" s="35">
         <v>3175</v>
@@ -54321,7 +54331,7 @@
         <v>1892</v>
       </c>
       <c r="E164" s="56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F164" s="35" t="s">
         <v>2732</v>
@@ -54523,7 +54533,7 @@
         <v>2703</v>
       </c>
       <c r="E175" s="56">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F175" s="56">
         <v>2310</v>
@@ -54561,7 +54571,7 @@
       </c>
       <c r="D177" s="33"/>
       <c r="E177" s="56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="35">
         <v>3293</v>
@@ -54581,7 +54591,7 @@
         <v>2703</v>
       </c>
       <c r="E178" s="56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F178" s="35">
         <v>1545</v>
@@ -54679,7 +54689,7 @@
         <v>2703</v>
       </c>
       <c r="E183" s="56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F183" s="35">
         <v>1485</v>
@@ -55186,7 +55196,7 @@
         <v>2190</v>
       </c>
       <c r="E210" s="56">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F210" s="35" t="s">
         <v>2734</v>
@@ -55206,7 +55216,7 @@
         <v>2703</v>
       </c>
       <c r="E211" s="56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F211" s="35">
         <v>1740</v>
@@ -55400,7 +55410,7 @@
       </c>
       <c r="D222" s="33"/>
       <c r="E222" s="56">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F222" s="35">
         <v>1321</v>
@@ -55489,7 +55499,7 @@
       </c>
       <c r="D227" s="33"/>
       <c r="E227" s="56">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F227" s="35">
         <v>2749</v>
@@ -57097,7 +57107,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:J293"/>
+  <dimension ref="A1:J294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -57173,7 +57183,7 @@
       </c>
       <c r="D4" s="33"/>
       <c r="E4" s="33">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="F4" s="35">
         <v>146</v>
@@ -57191,7 +57201,7 @@
       </c>
       <c r="D5" s="33"/>
       <c r="E5" s="33">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F5" s="35">
         <v>162</v>
@@ -57280,7 +57290,7 @@
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33">
-        <v>1001</v>
+        <v>941</v>
       </c>
       <c r="F10" s="35">
         <v>193</v>
@@ -57429,7 +57439,7 @@
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" s="35">
         <v>1301</v>
@@ -57537,7 +57547,7 @@
       </c>
       <c r="D24" s="33"/>
       <c r="E24" s="33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="35">
         <v>51</v>
@@ -57805,7 +57815,7 @@
         <v>3364</v>
       </c>
       <c r="E38" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="35">
         <v>1138</v>
@@ -57823,7 +57833,7 @@
       </c>
       <c r="D39" s="33"/>
       <c r="E39" s="33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F39" s="35">
         <v>2318</v>
@@ -58047,7 +58057,7 @@
       </c>
       <c r="D52" s="33"/>
       <c r="E52" s="33">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F52" s="35">
         <v>95</v>
@@ -58065,7 +58075,7 @@
       </c>
       <c r="D53" s="33"/>
       <c r="E53" s="33">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F53" s="35">
         <v>85</v>
@@ -58085,7 +58095,7 @@
         <v>3370</v>
       </c>
       <c r="E54" s="42">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F54" s="35">
         <v>211</v>
@@ -58139,7 +58149,7 @@
       </c>
       <c r="D57" s="33"/>
       <c r="E57" s="33">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F57" s="35">
         <v>260</v>
@@ -58227,7 +58237,7 @@
       </c>
       <c r="D62" s="33"/>
       <c r="E62" s="33">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="F62" s="35">
         <v>298</v>
@@ -58431,7 +58441,7 @@
         <v>3371</v>
       </c>
       <c r="E74" s="42">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F74" s="35">
         <v>415</v>
@@ -58469,7 +58479,7 @@
       </c>
       <c r="D76" s="33"/>
       <c r="E76" s="33">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F76" s="35">
         <v>239</v>
@@ -58505,7 +58515,7 @@
       </c>
       <c r="D78" s="33"/>
       <c r="E78" s="33">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="F78" s="35">
         <v>253</v>
@@ -58557,7 +58567,7 @@
         <v>3374</v>
       </c>
       <c r="E81" s="33">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F81" s="35">
         <v>537</v>
@@ -58629,7 +58639,7 @@
         <v>3376</v>
       </c>
       <c r="E85" s="33">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F85" s="35">
         <v>286</v>
@@ -58669,7 +58679,7 @@
         <v>3380</v>
       </c>
       <c r="E87" s="33">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F87" s="33">
         <v>330</v>
@@ -58775,7 +58785,7 @@
       </c>
       <c r="D93" s="33"/>
       <c r="E93" s="33">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F93" s="35">
         <v>1656</v>
@@ -58904,7 +58914,7 @@
         <v>1909</v>
       </c>
       <c r="E100" s="33">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F100" s="35" t="s">
         <v>2946</v>
@@ -58924,7 +58934,7 @@
         <v>1846</v>
       </c>
       <c r="E101" s="33">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F101" s="33">
         <v>372</v>
@@ -58962,7 +58972,7 @@
       </c>
       <c r="D103" s="33"/>
       <c r="E103" s="33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F103" s="35">
         <v>335</v>
@@ -59100,7 +59110,7 @@
         <v>1572</v>
       </c>
       <c r="E110" s="33">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F110" s="35">
         <v>494</v>
@@ -59150,7 +59160,7 @@
       </c>
       <c r="D113" s="33"/>
       <c r="E113" s="33">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F113" s="35">
         <v>746</v>
@@ -59170,7 +59180,7 @@
         <v>1688</v>
       </c>
       <c r="E114" s="33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F114" s="35">
         <v>396</v>
@@ -59432,313 +59442,313 @@
       <c r="F128" s="35"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="33">
-        <v>134</v>
-      </c>
+      <c r="A129" s="33"/>
       <c r="B129" s="33" t="s">
-        <v>2579</v>
+        <v>3593</v>
       </c>
       <c r="C129" s="33" t="s">
         <v>1279</v>
       </c>
-      <c r="D129" s="33"/>
+      <c r="D129" s="42"/>
       <c r="E129" s="33">
         <v>4</v>
       </c>
       <c r="F129" s="35">
-        <v>2752</v>
-      </c>
-      <c r="G129" s="12"/>
+        <v>2352</v>
+      </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="33">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>2226</v>
+        <v>2579</v>
       </c>
       <c r="C130" s="33" t="s">
         <v>1279</v>
       </c>
       <c r="D130" s="33"/>
       <c r="E130" s="33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F130" s="35">
-        <v>3546</v>
-      </c>
+        <v>2752</v>
+      </c>
+      <c r="G130" s="12"/>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="33">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B131" s="33" t="s">
-        <v>2244</v>
-      </c>
-      <c r="C131" s="33"/>
+        <v>2226</v>
+      </c>
+      <c r="C131" s="33" t="s">
+        <v>1279</v>
+      </c>
       <c r="D131" s="33"/>
       <c r="E131" s="33">
-        <v>7</v>
-      </c>
-      <c r="F131" s="35" t="s">
-        <v>2526</v>
+        <v>5</v>
+      </c>
+      <c r="F131" s="35">
+        <v>3546</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="33">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B132" s="33" t="s">
-        <v>2238</v>
-      </c>
-      <c r="C132" s="33" t="s">
-        <v>3388</v>
-      </c>
-      <c r="D132" s="33" t="s">
-        <v>3389</v>
-      </c>
+        <v>2244</v>
+      </c>
+      <c r="C132" s="33"/>
+      <c r="D132" s="33"/>
       <c r="E132" s="33">
-        <v>0</v>
-      </c>
-      <c r="F132" s="35">
-        <v>2838</v>
+        <v>7</v>
+      </c>
+      <c r="F132" s="35" t="s">
+        <v>2526</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="33">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B133" s="33" t="s">
-        <v>1285</v>
+        <v>2238</v>
       </c>
       <c r="C133" s="33" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D133" s="33"/>
+        <v>3388</v>
+      </c>
+      <c r="D133" s="33" t="s">
+        <v>3389</v>
+      </c>
       <c r="E133" s="33">
         <v>0</v>
       </c>
-      <c r="F133" s="35"/>
+      <c r="F133" s="35">
+        <v>2838</v>
+      </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="33">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B134" s="33" t="s">
-        <v>1407</v>
+        <v>1285</v>
       </c>
       <c r="C134" s="33" t="s">
-        <v>3390</v>
-      </c>
-      <c r="D134" s="33" t="s">
-        <v>3391</v>
-      </c>
+        <v>1279</v>
+      </c>
+      <c r="D134" s="33"/>
       <c r="E134" s="33">
-        <v>1</v>
-      </c>
-      <c r="F134" s="33">
-        <v>1478</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F134" s="35"/>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="33">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B135" s="33" t="s">
-        <v>2072</v>
+        <v>1407</v>
       </c>
       <c r="C135" s="33" t="s">
-        <v>1279</v>
+        <v>3390</v>
       </c>
       <c r="D135" s="33" t="s">
-        <v>3575</v>
+        <v>3391</v>
       </c>
       <c r="E135" s="33">
-        <v>7</v>
-      </c>
-      <c r="F135" s="35">
-        <v>1400</v>
+        <v>1</v>
+      </c>
+      <c r="F135" s="33">
+        <v>1478</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="33">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B136" s="33" t="s">
-        <v>1384</v>
+        <v>2072</v>
       </c>
       <c r="C136" s="33" t="s">
-        <v>1385</v>
-      </c>
-      <c r="D136" s="33"/>
+        <v>1279</v>
+      </c>
+      <c r="D136" s="33" t="s">
+        <v>3575</v>
+      </c>
       <c r="E136" s="33">
-        <v>0</v>
-      </c>
-      <c r="F136" s="33">
-        <v>1045</v>
+        <v>7</v>
+      </c>
+      <c r="F136" s="35">
+        <v>1400</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="33">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>1759</v>
+        <v>1384</v>
       </c>
       <c r="C137" s="33" t="s">
         <v>1385</v>
       </c>
       <c r="D137" s="33"/>
       <c r="E137" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F137" s="33">
-        <v>210</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="33">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B138" s="33" t="s">
-        <v>2869</v>
+        <v>1759</v>
       </c>
       <c r="C138" s="33" t="s">
-        <v>3388</v>
-      </c>
-      <c r="D138" s="33" t="s">
-        <v>3392</v>
-      </c>
+        <v>1385</v>
+      </c>
+      <c r="D138" s="33"/>
       <c r="E138" s="33">
-        <v>11</v>
-      </c>
-      <c r="F138" s="35">
-        <v>278</v>
-      </c>
-      <c r="H138" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="F138" s="33">
+        <v>210</v>
+      </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="33">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>2796</v>
+        <v>2869</v>
       </c>
       <c r="C139" s="33" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D139" s="33"/>
-      <c r="E139" s="35">
-        <v>0</v>
+        <v>3388</v>
+      </c>
+      <c r="D139" s="33" t="s">
+        <v>3392</v>
+      </c>
+      <c r="E139" s="33">
+        <v>11</v>
       </c>
       <c r="F139" s="35">
-        <v>950</v>
+        <v>278</v>
       </c>
       <c r="H139" s="4"/>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="33">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B140" s="33" t="s">
-        <v>1286</v>
+        <v>2796</v>
       </c>
       <c r="C140" s="33" t="s">
         <v>1279</v>
       </c>
-      <c r="D140" s="33" t="s">
-        <v>1683</v>
-      </c>
+      <c r="D140" s="33"/>
       <c r="E140" s="35">
         <v>0</v>
       </c>
-      <c r="F140" s="35"/>
+      <c r="F140" s="35">
+        <v>950</v>
+      </c>
       <c r="H140" s="4"/>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="33">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B141" s="33" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C141" s="33" t="s">
         <v>1279</v>
       </c>
       <c r="D141" s="33" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
       <c r="E141" s="35">
-        <v>1</v>
-      </c>
-      <c r="F141" s="35">
-        <v>564</v>
-      </c>
-      <c r="H141" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F141" s="35"/>
+      <c r="H141" s="4"/>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="33">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B142" s="33" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C142" s="33" t="s">
         <v>1279</v>
       </c>
       <c r="D142" s="33" t="s">
-        <v>3401</v>
+        <v>1686</v>
       </c>
       <c r="E142" s="35">
-        <v>8</v>
-      </c>
-      <c r="F142" s="33">
-        <v>1804</v>
+        <v>1</v>
+      </c>
+      <c r="F142" s="35">
+        <v>564</v>
       </c>
       <c r="H142" s="16"/>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="33">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B143" s="33" t="s">
-        <v>1483</v>
+        <v>1288</v>
       </c>
       <c r="C143" s="33" t="s">
         <v>1279</v>
       </c>
       <c r="D143" s="33" t="s">
-        <v>1858</v>
+        <v>3401</v>
       </c>
       <c r="E143" s="35">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F143" s="33">
-        <v>371</v>
-      </c>
+        <v>1804</v>
+      </c>
+      <c r="H143" s="16"/>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="33">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B144" s="33" t="s">
-        <v>1222</v>
+        <v>1483</v>
       </c>
       <c r="C144" s="33" t="s">
         <v>1279</v>
       </c>
-      <c r="D144" s="33"/>
-      <c r="E144" s="33">
-        <v>0</v>
-      </c>
-      <c r="F144" s="35"/>
+      <c r="D144" s="33" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E144" s="35">
+        <v>2</v>
+      </c>
+      <c r="F144" s="33">
+        <v>371</v>
+      </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="33">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B145" s="33" t="s">
-        <v>1289</v>
+        <v>1222</v>
       </c>
       <c r="C145" s="33" t="s">
         <v>1279</v>
@@ -59751,17 +59761,15 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="33">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B146" s="33" t="s">
-        <v>1749</v>
+        <v>1289</v>
       </c>
       <c r="C146" s="33" t="s">
         <v>1279</v>
       </c>
-      <c r="D146" s="33" t="s">
-        <v>1750</v>
-      </c>
+      <c r="D146" s="33"/>
       <c r="E146" s="33">
         <v>0</v>
       </c>
@@ -59769,7 +59777,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="33">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B147" s="33" t="s">
         <v>1749</v>
@@ -59778,7 +59786,7 @@
         <v>1279</v>
       </c>
       <c r="D147" s="33" t="s">
-        <v>3402</v>
+        <v>1750</v>
       </c>
       <c r="E147" s="33">
         <v>0</v>
@@ -59787,7 +59795,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="33">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B148" s="33" t="s">
         <v>1749</v>
@@ -59795,7 +59803,9 @@
       <c r="C148" s="33" t="s">
         <v>1279</v>
       </c>
-      <c r="D148" s="33"/>
+      <c r="D148" s="33" t="s">
+        <v>3402</v>
+      </c>
       <c r="E148" s="33">
         <v>0</v>
       </c>
@@ -59803,13 +59813,13 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="33">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B149" s="33" t="s">
-        <v>2580</v>
+        <v>1749</v>
       </c>
       <c r="C149" s="33" t="s">
-        <v>1385</v>
+        <v>1279</v>
       </c>
       <c r="D149" s="33"/>
       <c r="E149" s="33">
@@ -59819,79 +59829,79 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="33">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B150" s="33" t="s">
-        <v>2738</v>
+        <v>2580</v>
       </c>
       <c r="C150" s="33" t="s">
-        <v>3393</v>
-      </c>
-      <c r="D150" s="33" t="s">
-        <v>3394</v>
-      </c>
+        <v>1385</v>
+      </c>
+      <c r="D150" s="33"/>
       <c r="E150" s="33">
-        <v>1</v>
-      </c>
-      <c r="F150" s="35">
-        <v>4564</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F150" s="35"/>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="33">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B151" s="33" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
       <c r="C151" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D151" s="33" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="E151" s="33">
         <v>1</v>
       </c>
       <c r="F151" s="35">
+        <v>4564</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="33">
+        <v>157</v>
+      </c>
+      <c r="B152" s="33" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C152" s="33" t="s">
+        <v>3393</v>
+      </c>
+      <c r="D152" s="33" t="s">
+        <v>3395</v>
+      </c>
+      <c r="E152" s="33">
+        <v>1</v>
+      </c>
+      <c r="F152" s="35">
         <v>4839</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="21">
-      <c r="A152" s="33">
+    <row r="153" spans="1:7" ht="21">
+      <c r="A153" s="33">
         <v>165</v>
       </c>
-      <c r="B152" s="90" t="s">
+      <c r="B153" s="90" t="s">
         <v>1290</v>
       </c>
-      <c r="C152" s="90"/>
-      <c r="D152" s="90"/>
-      <c r="E152" s="90"/>
-      <c r="F152" s="90"/>
-      <c r="G152" s="58"/>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="A153" s="33">
-        <v>166</v>
-      </c>
-      <c r="B153" s="33" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C153" s="33" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D153" s="33"/>
-      <c r="E153" s="33">
-        <v>0</v>
-      </c>
-      <c r="F153" s="35"/>
+      <c r="C153" s="90"/>
+      <c r="D153" s="90"/>
+      <c r="E153" s="90"/>
+      <c r="F153" s="90"/>
+      <c r="G153" s="58"/>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="33">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B154" s="33" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C154" s="33" t="s">
         <v>1290</v>
@@ -59904,2703 +59914,2703 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="33">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B155" s="33" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C155" s="33" t="s">
-        <v>1202</v>
+        <v>1290</v>
       </c>
       <c r="D155" s="33"/>
-      <c r="E155" s="35">
-        <v>7</v>
-      </c>
-      <c r="F155" s="33">
-        <v>301</v>
-      </c>
+      <c r="E155" s="33">
+        <v>0</v>
+      </c>
+      <c r="F155" s="35"/>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="33">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B156" s="33" t="s">
-        <v>1559</v>
+        <v>1293</v>
       </c>
       <c r="C156" s="33" t="s">
-        <v>1469</v>
+        <v>1202</v>
       </c>
       <c r="D156" s="33"/>
       <c r="E156" s="35">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F156" s="33">
-        <v>143</v>
+        <v>301</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="33">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B157" s="33" t="s">
-        <v>1468</v>
+        <v>1559</v>
       </c>
       <c r="C157" s="33" t="s">
         <v>1469</v>
       </c>
       <c r="D157" s="33"/>
       <c r="E157" s="35">
+        <v>15</v>
+      </c>
+      <c r="F157" s="33">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" s="33">
+        <v>170</v>
+      </c>
+      <c r="B158" s="33" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C158" s="33" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D158" s="33"/>
+      <c r="E158" s="35">
         <v>17</v>
       </c>
-      <c r="F157" s="33">
+      <c r="F158" s="33">
         <v>150</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="21">
-      <c r="A158" s="33">
+    <row r="159" spans="1:7" ht="21">
+      <c r="A159" s="33">
         <v>175</v>
       </c>
-      <c r="B158" s="90" t="s">
+      <c r="B159" s="90" t="s">
         <v>3348</v>
       </c>
-      <c r="C158" s="90"/>
-      <c r="D158" s="90"/>
-      <c r="E158" s="90"/>
-      <c r="F158" s="90"/>
-    </row>
-    <row r="159" spans="1:7">
-      <c r="A159" s="33">
-        <v>178</v>
-      </c>
-      <c r="B159" s="33" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C159" s="33" t="s">
-        <v>3403</v>
-      </c>
-      <c r="D159" s="33" t="s">
-        <v>836</v>
-      </c>
-      <c r="E159" s="33">
-        <v>42</v>
-      </c>
-      <c r="F159" s="35">
-        <v>568</v>
-      </c>
+      <c r="C159" s="90"/>
+      <c r="D159" s="90"/>
+      <c r="E159" s="90"/>
+      <c r="F159" s="90"/>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="33">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B160" s="33" t="s">
-        <v>1814</v>
+        <v>2019</v>
       </c>
       <c r="C160" s="33" t="s">
-        <v>3344</v>
+        <v>3403</v>
       </c>
       <c r="D160" s="33" t="s">
-        <v>1858</v>
+        <v>836</v>
       </c>
       <c r="E160" s="33">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="F160" s="35">
-        <v>234</v>
+        <v>568</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="33">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B161" s="33" t="s">
-        <v>2105</v>
+        <v>1814</v>
       </c>
       <c r="C161" s="33" t="s">
         <v>3344</v>
       </c>
       <c r="D161" s="33" t="s">
-        <v>2422</v>
+        <v>1858</v>
       </c>
       <c r="E161" s="33">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="F161" s="35">
-        <v>300</v>
+        <v>234</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="33">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B162" s="33" t="s">
-        <v>2379</v>
-      </c>
-      <c r="C162" s="57" t="s">
-        <v>3404</v>
-      </c>
-      <c r="D162" s="57" t="s">
-        <v>3405</v>
+        <v>2105</v>
+      </c>
+      <c r="C162" s="33" t="s">
+        <v>3344</v>
+      </c>
+      <c r="D162" s="33" t="s">
+        <v>2422</v>
       </c>
       <c r="E162" s="33">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="F162" s="35">
-        <v>638</v>
+        <v>300</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="33">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B163" s="33" t="s">
-        <v>2000</v>
-      </c>
-      <c r="C163" s="33" t="s">
-        <v>3406</v>
-      </c>
-      <c r="D163" s="33" t="s">
-        <v>3407</v>
+        <v>2379</v>
+      </c>
+      <c r="C163" s="57" t="s">
+        <v>3404</v>
+      </c>
+      <c r="D163" s="57" t="s">
+        <v>3405</v>
       </c>
       <c r="E163" s="33">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="F163" s="35">
-        <v>686</v>
+        <v>638</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="33">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B164" s="33" t="s">
-        <v>2261</v>
+        <v>2000</v>
       </c>
       <c r="C164" s="33" t="s">
-        <v>3361</v>
+        <v>3406</v>
       </c>
       <c r="D164" s="33" t="s">
-        <v>3408</v>
-      </c>
-      <c r="E164" s="60">
-        <v>25</v>
-      </c>
-      <c r="F164" s="33">
-        <v>868</v>
+        <v>3407</v>
+      </c>
+      <c r="E164" s="33">
+        <v>83</v>
+      </c>
+      <c r="F164" s="35">
+        <v>686</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="33">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B165" s="33" t="s">
-        <v>2366</v>
+        <v>2261</v>
       </c>
       <c r="C165" s="33" t="s">
         <v>3361</v>
       </c>
       <c r="D165" s="33" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="E165" s="60">
-        <v>4</v>
-      </c>
-      <c r="F165" s="33" t="s">
-        <v>2546</v>
+        <v>25</v>
+      </c>
+      <c r="F165" s="33">
+        <v>868</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="33">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B166" s="33" t="s">
-        <v>1999</v>
+        <v>2366</v>
       </c>
       <c r="C166" s="33" t="s">
-        <v>3344</v>
+        <v>3361</v>
       </c>
       <c r="D166" s="33" t="s">
-        <v>3410</v>
-      </c>
-      <c r="E166" s="33">
-        <v>10</v>
-      </c>
-      <c r="F166" s="35" t="s">
-        <v>2848</v>
+        <v>3409</v>
+      </c>
+      <c r="E166" s="60">
+        <v>4</v>
+      </c>
+      <c r="F166" s="33" t="s">
+        <v>2546</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="33">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B167" s="33" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="C167" s="33" t="s">
         <v>3344</v>
       </c>
       <c r="D167" s="33" t="s">
-        <v>2552</v>
+        <v>3410</v>
       </c>
       <c r="E167" s="33">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F167" s="35" t="s">
-        <v>2935</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="33">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B168" s="33" t="s">
-        <v>1223</v>
+        <v>2001</v>
       </c>
       <c r="C168" s="33" t="s">
-        <v>3411</v>
+        <v>3344</v>
       </c>
       <c r="D168" s="33" t="s">
-        <v>3412</v>
+        <v>2552</v>
       </c>
       <c r="E168" s="33">
-        <v>18</v>
-      </c>
-      <c r="F168" s="35">
-        <v>451</v>
+        <v>34</v>
+      </c>
+      <c r="F168" s="35" t="s">
+        <v>2935</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="33">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B169" s="33" t="s">
-        <v>1941</v>
+        <v>1223</v>
       </c>
       <c r="C169" s="33" t="s">
-        <v>3413</v>
+        <v>3411</v>
       </c>
       <c r="D169" s="33" t="s">
-        <v>3414</v>
+        <v>3412</v>
       </c>
       <c r="E169" s="33">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F169" s="35">
-        <v>1454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="33">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B170" s="33" t="s">
-        <v>2339</v>
+        <v>1941</v>
       </c>
       <c r="C170" s="33" t="s">
-        <v>3415</v>
+        <v>3413</v>
       </c>
       <c r="D170" s="33" t="s">
-        <v>3416</v>
+        <v>3414</v>
       </c>
       <c r="E170" s="33">
-        <v>2</v>
-      </c>
-      <c r="F170" s="35" t="s">
-        <v>2826</v>
+        <v>25</v>
+      </c>
+      <c r="F170" s="35">
+        <v>1454</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="33">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B171" s="33" t="s">
-        <v>2325</v>
+        <v>2339</v>
       </c>
       <c r="C171" s="33" t="s">
         <v>3415</v>
       </c>
       <c r="D171" s="33" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="E171" s="33">
-        <v>9</v>
-      </c>
-      <c r="F171" s="35">
-        <v>1960</v>
+        <v>2</v>
+      </c>
+      <c r="F171" s="35" t="s">
+        <v>2826</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="33">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B172" s="33" t="s">
-        <v>2483</v>
+        <v>2325</v>
       </c>
       <c r="C172" s="33" t="s">
-        <v>3418</v>
+        <v>3415</v>
       </c>
       <c r="D172" s="33" t="s">
-        <v>3419</v>
+        <v>3417</v>
       </c>
       <c r="E172" s="33">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="F172" s="35">
-        <v>649</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="33">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B173" s="33" t="s">
-        <v>2487</v>
+        <v>2483</v>
       </c>
       <c r="C173" s="33" t="s">
         <v>3418</v>
       </c>
       <c r="D173" s="33" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="E173" s="33">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="F173" s="35">
-        <v>759</v>
+        <v>649</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="33">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B174" s="33" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>3421</v>
+        <v>3418</v>
       </c>
       <c r="D174" s="33" t="s">
-        <v>3422</v>
+        <v>3420</v>
       </c>
       <c r="E174" s="33">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="F174" s="35">
-        <v>605</v>
+        <v>759</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="33">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B175" s="33" t="s">
-        <v>2338</v>
+        <v>2486</v>
       </c>
       <c r="C175" s="33" t="s">
-        <v>3415</v>
+        <v>3421</v>
       </c>
       <c r="D175" s="33" t="s">
-        <v>2528</v>
+        <v>3422</v>
       </c>
       <c r="E175" s="33">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F175" s="35">
-        <v>1419</v>
+        <v>605</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="33">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B176" s="33" t="s">
-        <v>2645</v>
+        <v>2338</v>
       </c>
       <c r="C176" s="33" t="s">
-        <v>3423</v>
+        <v>3415</v>
       </c>
       <c r="D176" s="33" t="s">
-        <v>3424</v>
+        <v>2528</v>
       </c>
       <c r="E176" s="33">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="F176" s="35">
-        <v>282</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="33">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B177" s="33" t="s">
-        <v>2742</v>
+        <v>2645</v>
       </c>
       <c r="C177" s="33" t="s">
-        <v>3415</v>
+        <v>3423</v>
       </c>
       <c r="D177" s="33" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="E177" s="33">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="F177" s="35">
-        <v>1550</v>
+        <v>282</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="33">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B178" s="33" t="s">
-        <v>2647</v>
+        <v>2742</v>
       </c>
       <c r="C178" s="33" t="s">
-        <v>3418</v>
+        <v>3415</v>
       </c>
       <c r="D178" s="33" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="E178" s="33">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="F178" s="35">
-        <v>288</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="33">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B179" s="33" t="s">
-        <v>2959</v>
-      </c>
-      <c r="C179" s="33"/>
+        <v>2647</v>
+      </c>
+      <c r="C179" s="33" t="s">
+        <v>3418</v>
+      </c>
       <c r="D179" s="33" t="s">
-        <v>2960</v>
+        <v>3426</v>
       </c>
       <c r="E179" s="33">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F179" s="35">
-        <v>850</v>
+        <v>288</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="33">
+        <v>198</v>
+      </c>
+      <c r="B180" s="33" t="s">
+        <v>2959</v>
+      </c>
+      <c r="C180" s="33"/>
+      <c r="D180" s="33" t="s">
+        <v>2960</v>
+      </c>
+      <c r="E180" s="33">
+        <v>4</v>
+      </c>
+      <c r="F180" s="35">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" s="33">
         <v>199</v>
       </c>
-      <c r="B180" s="33" t="s">
+      <c r="B181" s="33" t="s">
         <v>2744</v>
       </c>
-      <c r="C180" s="33" t="s">
+      <c r="C181" s="33" t="s">
         <v>3415</v>
       </c>
-      <c r="D180" s="33" t="s">
+      <c r="D181" s="33" t="s">
         <v>3427</v>
       </c>
-      <c r="E180" s="33">
+      <c r="E181" s="33">
         <v>18</v>
       </c>
-      <c r="F180" s="35">
+      <c r="F181" s="35">
         <v>1004</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="21">
-      <c r="A181" s="33">
+    <row r="182" spans="1:6" ht="21">
+      <c r="A182" s="33">
         <v>203</v>
       </c>
-      <c r="B181" s="90" t="s">
+      <c r="B182" s="90" t="s">
         <v>3349</v>
       </c>
-      <c r="C181" s="90"/>
-      <c r="D181" s="90"/>
-      <c r="E181" s="90"/>
-      <c r="F181" s="90"/>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182" s="33">
-        <v>206</v>
-      </c>
-      <c r="B182" s="33" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C182" s="33" t="s">
-        <v>3373</v>
-      </c>
-      <c r="D182" s="33" t="s">
-        <v>3428</v>
-      </c>
-      <c r="E182" s="33">
-        <v>0</v>
-      </c>
-      <c r="F182" s="35">
-        <v>176</v>
-      </c>
+      <c r="C182" s="90"/>
+      <c r="D182" s="90"/>
+      <c r="E182" s="90"/>
+      <c r="F182" s="90"/>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="33">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B183" s="33" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C183" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D183" s="33" t="s">
-        <v>290</v>
+        <v>3428</v>
       </c>
       <c r="E183" s="33">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="F183" s="35">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="33">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B184" s="33" t="s">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="C184" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="E184" s="33">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="F184" s="35">
-        <v>186</v>
+        <v>170</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="33">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B185" s="33" t="s">
-        <v>1545</v>
+        <v>1264</v>
       </c>
       <c r="C185" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D185" s="33" t="s">
-        <v>3429</v>
+        <v>318</v>
       </c>
       <c r="E185" s="33">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="F185" s="35">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="33">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B186" s="33" t="s">
-        <v>1265</v>
+        <v>1545</v>
       </c>
       <c r="C186" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D186" s="33" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="E186" s="33">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F186" s="35">
-        <v>627</v>
+        <v>196</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="33">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B187" s="33" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C187" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D187" s="33" t="s">
-        <v>2422</v>
+        <v>3430</v>
       </c>
       <c r="E187" s="33">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F187" s="35">
-        <v>363</v>
+        <v>627</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="33">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B188" s="33" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C188" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D188" s="33" t="s">
-        <v>2246</v>
+        <v>2422</v>
       </c>
       <c r="E188" s="33">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="F188" s="35">
-        <v>229</v>
+        <v>363</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="33">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B189" s="33" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C189" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D189" s="33" t="s">
-        <v>3431</v>
+        <v>2246</v>
       </c>
       <c r="E189" s="33">
-        <v>48</v>
-      </c>
-      <c r="F189" s="35" t="s">
-        <v>2787</v>
+        <v>69</v>
+      </c>
+      <c r="F189" s="35">
+        <v>229</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="33">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B190" s="33" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C190" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D190" s="33" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="E190" s="33">
-        <v>168</v>
-      </c>
-      <c r="F190" s="33" t="s">
-        <v>3022</v>
+        <v>44</v>
+      </c>
+      <c r="F190" s="35" t="s">
+        <v>2787</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="33">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B191" s="33" t="s">
-        <v>1542</v>
+        <v>1270</v>
       </c>
       <c r="C191" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D191" s="33" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="E191" s="33">
-        <v>32</v>
-      </c>
-      <c r="F191" s="35">
-        <v>268</v>
+        <v>159</v>
+      </c>
+      <c r="F191" s="33" t="s">
+        <v>3022</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="33">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B192" s="33" t="s">
-        <v>1889</v>
+        <v>1542</v>
       </c>
       <c r="C192" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D192" s="33" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="E192" s="33">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F192" s="35">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="33">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B193" s="33" t="s">
-        <v>1273</v>
+        <v>1889</v>
       </c>
       <c r="C193" s="33" t="s">
         <v>3373</v>
       </c>
-      <c r="D193" s="33"/>
+      <c r="D193" s="33" t="s">
+        <v>3434</v>
+      </c>
       <c r="E193" s="33">
-        <v>4</v>
-      </c>
-      <c r="F193" s="53">
-        <v>628</v>
+        <v>30</v>
+      </c>
+      <c r="F193" s="35">
+        <v>267</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="33">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B194" s="33" t="s">
-        <v>1778</v>
+        <v>1273</v>
       </c>
       <c r="C194" s="33" t="s">
         <v>3373</v>
       </c>
-      <c r="D194" s="33" t="s">
-        <v>2799</v>
-      </c>
-      <c r="E194" s="42">
-        <v>241</v>
-      </c>
-      <c r="F194" s="35">
-        <v>170</v>
+      <c r="D194" s="33"/>
+      <c r="E194" s="33">
+        <v>4</v>
+      </c>
+      <c r="F194" s="53">
+        <v>628</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="33">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B195" s="33" t="s">
-        <v>1700</v>
+        <v>1778</v>
       </c>
       <c r="C195" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D195" s="33" t="s">
-        <v>3435</v>
+        <v>2799</v>
       </c>
       <c r="E195" s="42">
-        <v>30</v>
-      </c>
-      <c r="F195" s="35" t="s">
-        <v>3005</v>
+        <v>241</v>
+      </c>
+      <c r="F195" s="35">
+        <v>170</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="33">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B196" s="33" t="s">
-        <v>1429</v>
+        <v>1700</v>
       </c>
       <c r="C196" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D196" s="33" t="s">
-        <v>1859</v>
-      </c>
-      <c r="E196" s="60">
-        <v>5</v>
-      </c>
-      <c r="F196" s="35"/>
+        <v>3435</v>
+      </c>
+      <c r="E196" s="42">
+        <v>20</v>
+      </c>
+      <c r="F196" s="35" t="s">
+        <v>3005</v>
+      </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="33">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B197" s="33" t="s">
-        <v>1271</v>
+        <v>1429</v>
       </c>
       <c r="C197" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D197" s="33" t="s">
-        <v>3436</v>
-      </c>
-      <c r="E197" s="33">
-        <v>13</v>
-      </c>
-      <c r="F197" s="35">
-        <v>304</v>
-      </c>
+        <v>1859</v>
+      </c>
+      <c r="E197" s="60">
+        <v>5</v>
+      </c>
+      <c r="F197" s="35"/>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="33">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B198" s="33" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C198" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D198" s="33" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="E198" s="33">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F198" s="35">
-        <v>559</v>
+        <v>304</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="33">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B199" s="33" t="s">
-        <v>2790</v>
+        <v>1272</v>
       </c>
       <c r="C199" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D199" s="33" t="s">
-        <v>3143</v>
+        <v>3437</v>
       </c>
       <c r="E199" s="33">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F199" s="35">
-        <v>199</v>
+        <v>559</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="33">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B200" s="33" t="s">
-        <v>2002</v>
+        <v>2790</v>
       </c>
       <c r="C200" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D200" s="33" t="s">
-        <v>3438</v>
+        <v>3143</v>
       </c>
       <c r="E200" s="33">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="F200" s="35">
-        <v>155</v>
+        <v>199</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="33">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B201" s="33" t="s">
-        <v>2357</v>
+        <v>2002</v>
       </c>
       <c r="C201" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D201" s="33" t="s">
-        <v>2438</v>
+        <v>3438</v>
       </c>
       <c r="E201" s="33">
-        <v>30</v>
+        <v>107</v>
       </c>
       <c r="F201" s="35">
-        <v>200</v>
+        <v>155</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="33">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B202" s="33" t="s">
-        <v>2340</v>
+        <v>2357</v>
       </c>
       <c r="C202" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D202" s="33" t="s">
-        <v>3439</v>
+        <v>2438</v>
       </c>
       <c r="E202" s="33">
         <v>30</v>
       </c>
-      <c r="F202" s="35" t="s">
-        <v>2945</v>
+      <c r="F202" s="35">
+        <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="33">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B203" s="33" t="s">
-        <v>2326</v>
+        <v>2340</v>
       </c>
       <c r="C203" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D203" s="33" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="E203" s="33">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F203" s="35" t="s">
-        <v>2927</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="33">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B204" s="33" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="C204" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D204" s="33" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="E204" s="33">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F204" s="35" t="s">
-        <v>2328</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" s="33">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B205" s="33" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="C205" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D205" s="33" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="E205" s="33">
-        <v>8</v>
-      </c>
-      <c r="F205" s="35">
-        <v>622</v>
+        <v>3</v>
+      </c>
+      <c r="F205" s="35" t="s">
+        <v>2328</v>
       </c>
     </row>
     <row r="206" spans="1:6">
-      <c r="A206" s="33"/>
+      <c r="A206" s="33">
+        <v>229</v>
+      </c>
       <c r="B206" s="33" t="s">
-        <v>3585</v>
+        <v>2329</v>
       </c>
       <c r="C206" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D206" s="33" t="s">
-        <v>3586</v>
+        <v>3442</v>
       </c>
       <c r="E206" s="33">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F206" s="35">
-        <v>300</v>
+        <v>622</v>
       </c>
     </row>
     <row r="207" spans="1:6">
-      <c r="A207" s="33">
-        <v>230</v>
-      </c>
+      <c r="A207" s="33"/>
       <c r="B207" s="33" t="s">
-        <v>2330</v>
+        <v>3585</v>
       </c>
       <c r="C207" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D207" s="33" t="s">
-        <v>3443</v>
+        <v>3586</v>
       </c>
       <c r="E207" s="33">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F207" s="35">
-        <v>533</v>
+        <v>300</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="33">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B208" s="33" t="s">
-        <v>2558</v>
+        <v>2330</v>
       </c>
       <c r="C208" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D208" s="33" t="s">
-        <v>2408</v>
+        <v>3443</v>
       </c>
       <c r="E208" s="33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F208" s="35">
-        <v>278</v>
+        <v>533</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="33">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B209" s="33" t="s">
-        <v>2478</v>
+        <v>2558</v>
       </c>
       <c r="C209" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D209" s="33" t="s">
-        <v>3444</v>
+        <v>2408</v>
       </c>
       <c r="E209" s="33">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F209" s="35">
-        <v>198</v>
+        <v>278</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="33">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B210" s="33" t="s">
-        <v>2489</v>
+        <v>2478</v>
       </c>
       <c r="C210" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D210" s="33" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="E210" s="33">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F210" s="35">
-        <v>345</v>
+        <v>198</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="33">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B211" s="33" t="s">
-        <v>2239</v>
+        <v>2489</v>
       </c>
       <c r="C211" s="33" t="s">
         <v>3373</v>
       </c>
       <c r="D211" s="33" t="s">
+        <v>3445</v>
+      </c>
+      <c r="E211" s="33">
+        <v>22</v>
+      </c>
+      <c r="F211" s="35">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="33">
+        <v>234</v>
+      </c>
+      <c r="B212" s="33" t="s">
+        <v>2239</v>
+      </c>
+      <c r="C212" s="33" t="s">
+        <v>3373</v>
+      </c>
+      <c r="D212" s="33" t="s">
         <v>2839</v>
       </c>
-      <c r="E211" s="33">
+      <c r="E212" s="33">
         <v>2</v>
       </c>
-      <c r="F211" s="35"/>
-    </row>
-    <row r="212" spans="1:6" ht="21">
-      <c r="A212" s="33">
+      <c r="F212" s="35"/>
+    </row>
+    <row r="213" spans="1:6" ht="21">
+      <c r="A213" s="33">
         <v>237</v>
       </c>
-      <c r="B212" s="90" t="s">
+      <c r="B213" s="90" t="s">
         <v>3350</v>
       </c>
-      <c r="C212" s="90"/>
-      <c r="D212" s="90"/>
-      <c r="E212" s="90"/>
-      <c r="F212" s="90"/>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213" s="33">
-        <v>240</v>
-      </c>
-      <c r="B213" s="33" t="s">
-        <v>1970</v>
-      </c>
-      <c r="C213" s="33" t="s">
-        <v>3387</v>
-      </c>
-      <c r="D213" s="33" t="s">
-        <v>836</v>
-      </c>
-      <c r="E213" s="33">
-        <v>45</v>
-      </c>
-      <c r="F213" s="35">
-        <v>592</v>
-      </c>
+      <c r="C213" s="90"/>
+      <c r="D213" s="90"/>
+      <c r="E213" s="90"/>
+      <c r="F213" s="90"/>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" s="33">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B214" s="33" t="s">
-        <v>2367</v>
+        <v>1970</v>
       </c>
       <c r="C214" s="33" t="s">
         <v>3387</v>
       </c>
       <c r="D214" s="33" t="s">
-        <v>3446</v>
+        <v>836</v>
       </c>
       <c r="E214" s="33">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F214" s="35">
-        <v>833</v>
+        <v>592</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" s="33">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B215" s="33" t="s">
-        <v>2311</v>
+        <v>2367</v>
       </c>
       <c r="C215" s="33" t="s">
-        <v>3447</v>
+        <v>3387</v>
       </c>
       <c r="D215" s="33" t="s">
-        <v>3448</v>
+        <v>3446</v>
       </c>
       <c r="E215" s="33">
-        <v>18</v>
-      </c>
-      <c r="F215" s="33" t="s">
-        <v>2939</v>
+        <v>35</v>
+      </c>
+      <c r="F215" s="35">
+        <v>833</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="33">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B216" s="33" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="C216" s="33" t="s">
-        <v>3393</v>
+        <v>3447</v>
       </c>
       <c r="D216" s="33" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="E216" s="33">
-        <v>12</v>
-      </c>
-      <c r="F216" s="33">
-        <v>311</v>
+        <v>18</v>
+      </c>
+      <c r="F216" s="33" t="s">
+        <v>2939</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="33">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B217" s="33" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="C217" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D217" s="33" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="E217" s="33">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F217" s="33">
-        <v>330</v>
+        <v>311</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" s="33">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B218" s="33" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="C218" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D218" s="33" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="E218" s="33">
-        <v>3</v>
-      </c>
-      <c r="F218" s="33" t="s">
-        <v>2940</v>
+        <v>31</v>
+      </c>
+      <c r="F218" s="33">
+        <v>330</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" s="33">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B219" s="33" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="C219" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D219" s="33" t="s">
-        <v>2392</v>
+        <v>3451</v>
       </c>
       <c r="E219" s="33">
-        <v>10</v>
-      </c>
-      <c r="F219" s="33">
-        <v>244</v>
+        <v>1</v>
+      </c>
+      <c r="F219" s="33" t="s">
+        <v>2940</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="33">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B220" s="33" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="C220" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D220" s="33" t="s">
-        <v>3452</v>
+        <v>2392</v>
       </c>
       <c r="E220" s="33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F220" s="33">
-        <v>305</v>
+        <v>244</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="33">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B221" s="33" t="s">
-        <v>2469</v>
+        <v>2316</v>
       </c>
       <c r="C221" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D221" s="33" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="E221" s="33">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F221" s="33">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" s="33">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B222" s="33" t="s">
-        <v>2317</v>
+        <v>2469</v>
       </c>
       <c r="C222" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D222" s="33" t="s">
-        <v>2405</v>
+        <v>3453</v>
       </c>
       <c r="E222" s="33">
-        <v>6</v>
-      </c>
-      <c r="F222" s="33" t="s">
-        <v>2941</v>
+        <v>19</v>
+      </c>
+      <c r="F222" s="33">
+        <v>323</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="33">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B223" s="33" t="s">
-        <v>2358</v>
+        <v>2317</v>
       </c>
       <c r="C223" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D223" s="33" t="s">
-        <v>3454</v>
+        <v>2405</v>
       </c>
       <c r="E223" s="33">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F223" s="33" t="s">
-        <v>2827</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" s="33">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B224" s="33" t="s">
-        <v>2318</v>
+        <v>2358</v>
       </c>
       <c r="C224" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D224" s="33" t="s">
-        <v>3023</v>
+        <v>3454</v>
       </c>
       <c r="E224" s="33">
-        <v>31</v>
-      </c>
-      <c r="F224" s="33">
-        <v>340</v>
+        <v>16</v>
+      </c>
+      <c r="F224" s="33" t="s">
+        <v>2827</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="33">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B225" s="33" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="C225" s="33" t="s">
-        <v>3455</v>
+        <v>3393</v>
       </c>
       <c r="D225" s="33" t="s">
-        <v>3456</v>
+        <v>3023</v>
       </c>
       <c r="E225" s="33">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F225" s="33">
-        <v>237</v>
+        <v>340</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" s="33">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B226" s="33" t="s">
-        <v>2916</v>
+        <v>2319</v>
       </c>
       <c r="C226" s="33" t="s">
         <v>3455</v>
       </c>
       <c r="D226" s="33" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="E226" s="33">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F226" s="33">
-        <v>440</v>
+        <v>237</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" s="33">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B227" s="33" t="s">
-        <v>2320</v>
+        <v>2916</v>
       </c>
       <c r="C227" s="33" t="s">
-        <v>3393</v>
+        <v>3455</v>
       </c>
       <c r="D227" s="33" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="E227" s="33">
         <v>6</v>
       </c>
-      <c r="F227" s="33" t="s">
-        <v>2836</v>
+      <c r="F227" s="33">
+        <v>440</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" s="33">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B228" s="33" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="C228" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D228" s="33" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="E228" s="33">
-        <v>33</v>
-      </c>
-      <c r="F228" s="33">
-        <v>315</v>
+        <v>6</v>
+      </c>
+      <c r="F228" s="33" t="s">
+        <v>2836</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" s="33">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B229" s="33" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="C229" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D229" s="33" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="E229" s="33">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F229" s="33">
-        <v>650</v>
+        <v>315</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" s="33">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B230" s="33" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="C230" s="33" t="s">
-        <v>3455</v>
+        <v>3393</v>
       </c>
       <c r="D230" s="33" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="E230" s="33">
-        <v>18</v>
-      </c>
-      <c r="F230" s="35">
-        <v>309</v>
+        <v>0</v>
+      </c>
+      <c r="F230" s="33">
+        <v>650</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" s="33">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B231" s="33" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="C231" s="33" t="s">
         <v>3455</v>
       </c>
       <c r="D231" s="33" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="E231" s="33">
-        <v>33</v>
-      </c>
-      <c r="F231" s="35" t="s">
-        <v>2785</v>
+        <v>18</v>
+      </c>
+      <c r="F231" s="35">
+        <v>309</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" s="33">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B232" s="33" t="s">
-        <v>2333</v>
+        <v>2324</v>
       </c>
       <c r="C232" s="33" t="s">
-        <v>3393</v>
+        <v>3455</v>
       </c>
       <c r="D232" s="33" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="E232" s="33">
-        <v>7</v>
-      </c>
-      <c r="F232" s="35">
-        <v>1026</v>
+        <v>33</v>
+      </c>
+      <c r="F232" s="35" t="s">
+        <v>2785</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" s="33">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B233" s="33" t="s">
-        <v>1682</v>
+        <v>2333</v>
       </c>
       <c r="C233" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D233" s="33" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="E233" s="33">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F233" s="35">
-        <v>353</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" s="33">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B234" s="33" t="s">
-        <v>2345</v>
+        <v>1682</v>
       </c>
       <c r="C234" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D234" s="33" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="E234" s="33">
-        <v>15</v>
-      </c>
-      <c r="F234" s="35" t="s">
-        <v>2942</v>
+        <v>35</v>
+      </c>
+      <c r="F234" s="35">
+        <v>353</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" s="33">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B235" s="33" t="s">
-        <v>2365</v>
+        <v>2345</v>
       </c>
       <c r="C235" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D235" s="33" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="E235" s="33">
-        <v>35</v>
-      </c>
-      <c r="F235" s="35">
-        <v>273</v>
+        <v>15</v>
+      </c>
+      <c r="F235" s="35" t="s">
+        <v>2942</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" s="33">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B236" s="33" t="s">
-        <v>2346</v>
+        <v>2365</v>
       </c>
       <c r="C236" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D236" s="33" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="E236" s="33">
-        <v>49</v>
-      </c>
-      <c r="F236" s="35" t="s">
-        <v>2785</v>
+        <v>35</v>
+      </c>
+      <c r="F236" s="35">
+        <v>273</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" s="33">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B237" s="33" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="C237" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D237" s="33" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="E237" s="33">
-        <v>38</v>
-      </c>
-      <c r="F237" s="35">
-        <v>412</v>
+        <v>49</v>
+      </c>
+      <c r="F237" s="35" t="s">
+        <v>2785</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" s="33">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B238" s="33" t="s">
-        <v>2359</v>
+        <v>2347</v>
       </c>
       <c r="C238" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D238" s="33" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="E238" s="33">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F238" s="35">
-        <v>370</v>
+        <v>412</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" s="33">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B239" s="33" t="s">
-        <v>2481</v>
+        <v>2359</v>
       </c>
       <c r="C239" s="33" t="s">
-        <v>2983</v>
+        <v>3393</v>
       </c>
       <c r="D239" s="33" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="E239" s="33">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F239" s="35">
-        <v>494</v>
+        <v>370</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" s="33">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B240" s="33" t="s">
-        <v>2488</v>
+        <v>2481</v>
       </c>
       <c r="C240" s="33" t="s">
-        <v>3447</v>
+        <v>2983</v>
       </c>
       <c r="D240" s="33" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="E240" s="33">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F240" s="35">
-        <v>330</v>
+        <v>494</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" s="33">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B241" s="33" t="s">
-        <v>2930</v>
+        <v>2488</v>
       </c>
       <c r="C241" s="33" t="s">
         <v>3447</v>
       </c>
       <c r="D241" s="33" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="E241" s="33">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F241" s="35">
-        <v>404</v>
+        <v>330</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" s="33">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B242" s="33" t="s">
-        <v>2534</v>
+        <v>2930</v>
       </c>
       <c r="C242" s="33" t="s">
-        <v>3393</v>
+        <v>3447</v>
       </c>
       <c r="D242" s="33" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="E242" s="33">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F242" s="35">
-        <v>258</v>
+        <v>404</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" s="33">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B243" s="33" t="s">
-        <v>2653</v>
+        <v>2534</v>
       </c>
       <c r="C243" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D243" s="33" t="s">
-        <v>2438</v>
+        <v>3473</v>
       </c>
       <c r="E243" s="33">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F243" s="35">
-        <v>227</v>
+        <v>258</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" s="33">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B244" s="33" t="s">
-        <v>2735</v>
+        <v>2653</v>
       </c>
       <c r="C244" s="33" t="s">
-        <v>3474</v>
+        <v>3393</v>
       </c>
       <c r="D244" s="33" t="s">
-        <v>2423</v>
+        <v>2438</v>
       </c>
       <c r="E244" s="33">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F244" s="35">
-        <v>297</v>
+        <v>227</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" s="33">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B245" s="33" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
       <c r="C245" s="33" t="s">
-        <v>3393</v>
+        <v>3474</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>3475</v>
+        <v>2423</v>
       </c>
       <c r="E245" s="33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F245" s="35">
-        <v>390</v>
+        <v>297</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" s="33">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B246" s="33" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="C246" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="E246" s="33">
         <v>4</v>
       </c>
       <c r="F246" s="35">
-        <v>708</v>
+        <v>390</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" s="33">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B247" s="33" t="s">
-        <v>2740</v>
+        <v>2737</v>
       </c>
       <c r="C247" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D247" s="33" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="E247" s="33">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="F247" s="35">
-        <v>425</v>
+        <v>708</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" s="33">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B248" s="33" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="C248" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D248" s="33" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="E248" s="33">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F248" s="35">
-        <v>338</v>
+        <v>425</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" s="33">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B249" s="33" t="s">
-        <v>2743</v>
+        <v>2741</v>
       </c>
       <c r="C249" s="33" t="s">
         <v>3393</v>
       </c>
       <c r="D249" s="33" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="E249" s="33">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F249" s="35">
-        <v>830</v>
+        <v>338</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" s="33">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B250" s="33" t="s">
-        <v>2817</v>
+        <v>2743</v>
       </c>
       <c r="C250" s="33" t="s">
-        <v>2866</v>
-      </c>
-      <c r="D250" s="33"/>
+        <v>3393</v>
+      </c>
+      <c r="D250" s="33" t="s">
+        <v>3479</v>
+      </c>
       <c r="E250" s="33">
-        <v>5</v>
-      </c>
-      <c r="F250" s="35" t="s">
-        <v>2943</v>
+        <v>13</v>
+      </c>
+      <c r="F250" s="35">
+        <v>830</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" s="33">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B251" s="33" t="s">
-        <v>2871</v>
+        <v>2817</v>
       </c>
       <c r="C251" s="33" t="s">
         <v>2866</v>
       </c>
-      <c r="D251" s="33" t="s">
-        <v>2883</v>
-      </c>
+      <c r="D251" s="33"/>
       <c r="E251" s="33">
-        <v>3</v>
-      </c>
-      <c r="F251" s="35">
-        <v>613</v>
+        <v>5</v>
+      </c>
+      <c r="F251" s="35" t="s">
+        <v>2943</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" s="33">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B252" s="33" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="C252" s="33" t="s">
         <v>2866</v>
       </c>
       <c r="D252" s="33" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="E252" s="33">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F252" s="35">
-        <v>567</v>
+        <v>613</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" s="33">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B253" s="33" t="s">
-        <v>2876</v>
+        <v>2872</v>
       </c>
       <c r="C253" s="33" t="s">
         <v>2866</v>
       </c>
       <c r="D253" s="33" t="s">
-        <v>2882</v>
+        <v>2884</v>
       </c>
       <c r="E253" s="33">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F253" s="35">
-        <v>297</v>
+        <v>567</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" s="33">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B254" s="33" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="C254" s="33" t="s">
         <v>2866</v>
       </c>
       <c r="D254" s="33" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="E254" s="33">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F254" s="35">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" s="33">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B255" s="33" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="C255" s="33" t="s">
         <v>2866</v>
       </c>
       <c r="D255" s="33" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="E255" s="33">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F255" s="35">
-        <v>325</v>
+        <v>303</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" s="33">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B256" s="33" t="s">
-        <v>2894</v>
+        <v>2878</v>
       </c>
       <c r="C256" s="33" t="s">
         <v>2866</v>
       </c>
       <c r="D256" s="33" t="s">
-        <v>2424</v>
+        <v>2880</v>
       </c>
       <c r="E256" s="33">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F256" s="35">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257" s="33">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B257" s="33" t="s">
-        <v>2915</v>
+        <v>2894</v>
       </c>
       <c r="C257" s="33" t="s">
         <v>2866</v>
       </c>
       <c r="D257" s="33" t="s">
+        <v>2424</v>
+      </c>
+      <c r="E257" s="33">
+        <v>32</v>
+      </c>
+      <c r="F257" s="35">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="33">
+        <v>285</v>
+      </c>
+      <c r="B258" s="33" t="s">
+        <v>2915</v>
+      </c>
+      <c r="C258" s="33" t="s">
+        <v>2866</v>
+      </c>
+      <c r="D258" s="33" t="s">
         <v>3066</v>
       </c>
-      <c r="E257" s="33">
-        <v>29</v>
-      </c>
-      <c r="F257" s="35">
+      <c r="E258" s="33">
+        <v>23</v>
+      </c>
+      <c r="F258" s="35">
         <v>546</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
-      <c r="A258" s="33">
+    <row r="259" spans="1:6">
+      <c r="A259" s="33">
         <v>286</v>
       </c>
-      <c r="B258" s="33" t="s">
+      <c r="B259" s="33" t="s">
         <v>2982</v>
-      </c>
-      <c r="C258" s="33" t="s">
-        <v>2983</v>
-      </c>
-      <c r="D258" s="33"/>
-      <c r="E258" s="33">
-        <v>11</v>
-      </c>
-      <c r="F258" s="35">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
-      <c r="A259" s="33">
-        <v>287</v>
-      </c>
-      <c r="B259" s="33" t="s">
-        <v>2987</v>
       </c>
       <c r="C259" s="33" t="s">
         <v>2983</v>
       </c>
-      <c r="D259" s="33" t="s">
-        <v>2988</v>
-      </c>
+      <c r="D259" s="33"/>
       <c r="E259" s="33">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F259" s="35">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260" s="33">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B260" s="33" t="s">
-        <v>3053</v>
+        <v>2987</v>
       </c>
       <c r="C260" s="33" t="s">
         <v>2983</v>
       </c>
       <c r="D260" s="33" t="s">
-        <v>3068</v>
+        <v>2988</v>
       </c>
       <c r="E260" s="33">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F260" s="35">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
       <c r="A261" s="33">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B261" s="33" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="C261" s="33" t="s">
         <v>2983</v>
       </c>
       <c r="D261" s="33" t="s">
-        <v>3065</v>
+        <v>3068</v>
       </c>
       <c r="E261" s="33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F261" s="35">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262" s="33">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B262" s="33" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="C262" s="33" t="s">
         <v>2983</v>
       </c>
       <c r="D262" s="33" t="s">
-        <v>3069</v>
+        <v>3065</v>
       </c>
       <c r="E262" s="33">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F262" s="35">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
       <c r="A263" s="33">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B263" s="33" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="C263" s="33" t="s">
         <v>2983</v>
       </c>
       <c r="D263" s="33" t="s">
-        <v>3063</v>
+        <v>3069</v>
       </c>
       <c r="E263" s="33">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F263" s="35">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" s="33">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B264" s="33" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C264" s="33" t="s">
         <v>2983</v>
       </c>
       <c r="D264" s="33" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="E264" s="33">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F264" s="35">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
       <c r="A265" s="33">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B265" s="33" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="C265" s="33" t="s">
         <v>2983</v>
       </c>
       <c r="D265" s="33" t="s">
-        <v>3064</v>
+        <v>3067</v>
       </c>
       <c r="E265" s="33">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F265" s="35">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" s="33">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B266" s="33" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="C266" s="33" t="s">
         <v>2983</v>
       </c>
       <c r="D266" s="33" t="s">
-        <v>3062</v>
+        <v>3064</v>
       </c>
       <c r="E266" s="33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F266" s="35">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7">
-      <c r="A267" s="33"/>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="33">
+        <v>294</v>
+      </c>
       <c r="B267" s="33" t="s">
-        <v>3573</v>
+        <v>3059</v>
       </c>
       <c r="C267" s="33" t="s">
         <v>2983</v>
       </c>
       <c r="D267" s="33" t="s">
+        <v>3062</v>
+      </c>
+      <c r="E267" s="33">
+        <v>5</v>
+      </c>
+      <c r="F267" s="35">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="33"/>
+      <c r="B268" s="33" t="s">
+        <v>3573</v>
+      </c>
+      <c r="C268" s="33" t="s">
+        <v>2983</v>
+      </c>
+      <c r="D268" s="33" t="s">
         <v>3574</v>
       </c>
-      <c r="E267" s="33">
+      <c r="E268" s="33">
         <v>22</v>
       </c>
-      <c r="F267" s="35">
+      <c r="F268" s="35">
         <v>536</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
-      <c r="A268" s="33"/>
-      <c r="B268" s="33"/>
-      <c r="C268" s="33"/>
-      <c r="D268" s="33"/>
-      <c r="E268" s="33"/>
-      <c r="F268" s="35"/>
-    </row>
-    <row r="269" spans="1:7" ht="33" customHeight="1">
-      <c r="A269" s="33">
+    <row r="269" spans="1:6">
+      <c r="A269" s="33"/>
+      <c r="B269" s="33"/>
+      <c r="C269" s="33"/>
+      <c r="D269" s="33"/>
+      <c r="E269" s="33"/>
+      <c r="F269" s="35"/>
+    </row>
+    <row r="270" spans="1:6" ht="33" customHeight="1">
+      <c r="A270" s="33">
         <v>299</v>
       </c>
-      <c r="B269" s="90" t="s">
+      <c r="B270" s="90" t="s">
         <v>3351</v>
       </c>
-      <c r="C269" s="90"/>
-      <c r="D269" s="90"/>
-      <c r="E269" s="90"/>
-      <c r="F269" s="90"/>
-    </row>
-    <row r="270" spans="1:7">
-      <c r="A270" s="33">
+      <c r="C270" s="90"/>
+      <c r="D270" s="90"/>
+      <c r="E270" s="90"/>
+      <c r="F270" s="90"/>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="33">
         <v>302</v>
       </c>
-      <c r="B270" s="33" t="s">
+      <c r="B271" s="33" t="s">
         <v>2336</v>
-      </c>
-      <c r="C270" s="33" t="s">
-        <v>2380</v>
-      </c>
-      <c r="D270" s="33" t="s">
-        <v>3480</v>
-      </c>
-      <c r="E270" s="33">
-        <v>14</v>
-      </c>
-      <c r="F270" s="33">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7">
-      <c r="A271" s="33">
-        <v>303</v>
-      </c>
-      <c r="B271" s="33" t="s">
-        <v>2337</v>
       </c>
       <c r="C271" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D271" s="33" t="s">
-        <v>683</v>
+        <v>3480</v>
       </c>
       <c r="E271" s="33">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="F271" s="33">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
       <c r="A272" s="33">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B272" s="33" t="s">
-        <v>2360</v>
+        <v>2337</v>
       </c>
       <c r="C272" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D272" s="33" t="s">
-        <v>2405</v>
+        <v>683</v>
       </c>
       <c r="E272" s="33">
-        <v>22</v>
-      </c>
-      <c r="F272" s="33" t="s">
-        <v>2999</v>
-      </c>
-      <c r="G272" s="2">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6">
+        <v>43</v>
+      </c>
+      <c r="F272" s="33">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
       <c r="A273" s="33">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B273" s="33" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="C273" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D273" s="33" t="s">
-        <v>3417</v>
+        <v>2405</v>
       </c>
       <c r="E273" s="33">
-        <v>15</v>
-      </c>
-      <c r="F273" s="33">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6">
+        <v>22</v>
+      </c>
+      <c r="F273" s="33" t="s">
+        <v>2999</v>
+      </c>
+      <c r="G273" s="2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
       <c r="A274" s="33">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B274" s="33" t="s">
-        <v>2389</v>
+        <v>2361</v>
       </c>
       <c r="C274" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D274" s="33" t="s">
-        <v>3481</v>
+        <v>3417</v>
       </c>
       <c r="E274" s="33">
         <v>15</v>
       </c>
       <c r="F274" s="33">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
       <c r="A275" s="33">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B275" s="33" t="s">
-        <v>2362</v>
+        <v>2389</v>
       </c>
       <c r="C275" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D275" s="33" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="E275" s="33">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F275" s="33">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
       <c r="A276" s="33">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B276" s="33" t="s">
-        <v>2921</v>
+        <v>2362</v>
       </c>
       <c r="C276" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D276" s="33" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="E276" s="33">
         <v>9</v>
       </c>
       <c r="F276" s="33">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
       <c r="A277" s="33">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B277" s="33" t="s">
-        <v>2363</v>
+        <v>2921</v>
       </c>
       <c r="C277" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D277" s="33" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="E277" s="33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F277" s="33">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
       <c r="A278" s="33">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B278" s="33" t="s">
-        <v>2386</v>
+        <v>2363</v>
       </c>
       <c r="C278" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D278" s="33" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="E278" s="33">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F278" s="33">
-        <v>1712</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
       <c r="A279" s="33">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B279" s="33" t="s">
-        <v>2472</v>
+        <v>2386</v>
       </c>
       <c r="C279" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D279" s="33" t="s">
-        <v>2482</v>
+        <v>3485</v>
       </c>
       <c r="E279" s="33">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F279" s="33">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
       <c r="A280" s="33">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B280" s="33" t="s">
-        <v>2855</v>
+        <v>2472</v>
       </c>
       <c r="C280" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D280" s="33" t="s">
-        <v>2493</v>
+        <v>2482</v>
       </c>
       <c r="E280" s="33">
-        <v>5</v>
-      </c>
-      <c r="F280" s="33" t="s">
-        <v>2494</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6">
+        <v>30</v>
+      </c>
+      <c r="F280" s="33">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
       <c r="A281" s="33">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B281" s="33" t="s">
-        <v>2649</v>
+        <v>2855</v>
       </c>
       <c r="C281" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D281" s="33" t="s">
-        <v>2444</v>
+        <v>2493</v>
       </c>
       <c r="E281" s="33">
-        <v>41</v>
-      </c>
-      <c r="F281" s="35">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6">
+        <v>5</v>
+      </c>
+      <c r="F281" s="33" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
       <c r="A282" s="33">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B282" s="33" t="s">
-        <v>2675</v>
+        <v>2649</v>
       </c>
       <c r="C282" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D282" s="33" t="s">
-        <v>3486</v>
+        <v>2444</v>
       </c>
       <c r="E282" s="33">
-        <v>32</v>
-      </c>
-      <c r="F282" s="35" t="s">
-        <v>2944</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6">
+        <v>41</v>
+      </c>
+      <c r="F282" s="35">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
       <c r="A283" s="33">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B283" s="33" t="s">
-        <v>2841</v>
+        <v>2675</v>
       </c>
       <c r="C283" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D283" s="33" t="s">
-        <v>2889</v>
+        <v>3486</v>
       </c>
       <c r="E283" s="33">
-        <v>11</v>
-      </c>
-      <c r="F283" s="35">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6">
+        <v>32</v>
+      </c>
+      <c r="F283" s="35" t="s">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
       <c r="A284" s="33">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B284" s="33" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="C284" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D284" s="33" t="s">
-        <v>2863</v>
+        <v>2889</v>
       </c>
       <c r="E284" s="33">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F284" s="35">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
       <c r="A285" s="33">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B285" s="33" t="s">
-        <v>2873</v>
+        <v>2842</v>
       </c>
       <c r="C285" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D285" s="33" t="s">
-        <v>2885</v>
+        <v>2863</v>
       </c>
       <c r="E285" s="33">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F285" s="35">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
       <c r="A286" s="33">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B286" s="33" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="C286" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D286" s="33" t="s">
-        <v>2914</v>
+        <v>2885</v>
       </c>
       <c r="E286" s="33">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F286" s="35">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
       <c r="A287" s="33">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B287" s="33" t="s">
-        <v>2956</v>
+        <v>2874</v>
       </c>
       <c r="C287" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D287" s="33" t="s">
-        <v>3007</v>
+        <v>2914</v>
       </c>
       <c r="E287" s="33">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F287" s="35">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
       <c r="A288" s="33">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B288" s="33" t="s">
-        <v>2958</v>
+        <v>2956</v>
       </c>
       <c r="C288" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D288" s="33" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="E288" s="33">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F288" s="35">
-        <v>259</v>
+        <v>345</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" s="33">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B289" s="33" t="s">
-        <v>3060</v>
+        <v>2958</v>
       </c>
       <c r="C289" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D289" s="33" t="s">
-        <v>3070</v>
+        <v>3006</v>
       </c>
       <c r="E289" s="33">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F289" s="35">
-        <v>285</v>
+        <v>259</v>
       </c>
     </row>
     <row r="290" spans="1:6">
       <c r="A290" s="33">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B290" s="33" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="C290" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D290" s="33" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="E290" s="33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F290" s="35">
-        <v>209</v>
+        <v>285</v>
       </c>
     </row>
     <row r="291" spans="1:6">
       <c r="A291" s="33">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B291" s="33" t="s">
-        <v>3052</v>
+        <v>3061</v>
       </c>
       <c r="C291" s="33" t="s">
         <v>2380</v>
       </c>
       <c r="D291" s="33" t="s">
-        <v>2424</v>
+        <v>3071</v>
       </c>
       <c r="E291" s="33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F291" s="35">
-        <v>295</v>
+        <v>209</v>
       </c>
     </row>
     <row r="292" spans="1:6">
       <c r="A292" s="33">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B292" s="33" t="s">
-        <v>3074</v>
+        <v>3052</v>
       </c>
       <c r="C292" s="33" t="s">
         <v>2380</v>
       </c>
-      <c r="D292" s="33"/>
+      <c r="D292" s="33" t="s">
+        <v>2424</v>
+      </c>
       <c r="E292" s="33">
-        <v>5</v>
-      </c>
-      <c r="F292" s="35"/>
+        <v>10</v>
+      </c>
+      <c r="F292" s="35">
+        <v>295</v>
+      </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" s="33">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B293" s="33" t="s">
-        <v>3083</v>
+        <v>3074</v>
       </c>
       <c r="C293" s="33" t="s">
         <v>2380</v>
@@ -62611,9 +62621,25 @@
       </c>
       <c r="F293" s="35"/>
     </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="33">
+        <v>325</v>
+      </c>
+      <c r="B294" s="33" t="s">
+        <v>3083</v>
+      </c>
+      <c r="C294" s="33" t="s">
+        <v>2380</v>
+      </c>
+      <c r="D294" s="33"/>
+      <c r="E294" s="33">
+        <v>5</v>
+      </c>
+      <c r="F294" s="35"/>
+    </row>
   </sheetData>
   <sheetProtection password="CF21" sheet="1" objects="1" scenarios="1"/>
-  <autoFilter ref="A1:J293"/>
+  <autoFilter ref="A1:J294"/>
   <customSheetViews>
     <customSheetView guid="{8145F22A-AD74-4799-898B-BCECC4FA34F9}" scale="110" topLeftCell="A1045">
       <selection activeCell="D1055" sqref="D1055"/>
@@ -62623,11 +62649,11 @@
   </customSheetViews>
   <mergeCells count="8">
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B212:F212"/>
-    <mergeCell ref="B269:F269"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B213:F213"/>
+    <mergeCell ref="B270:F270"/>
+    <mergeCell ref="B153:F153"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B122:F122"/>
   </mergeCells>
@@ -63434,7 +63460,7 @@
         <v>372</v>
       </c>
       <c r="E44" s="62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F44" s="4">
         <v>1312</v>
@@ -63454,7 +63480,7 @@
         <v>2235</v>
       </c>
       <c r="E45" s="62">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F45" s="4">
         <v>1383</v>
@@ -63526,7 +63552,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="4">
         <v>11390</v>
@@ -63698,7 +63724,7 @@
         <v>399</v>
       </c>
       <c r="E58" s="62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="4">
         <v>2529</v>
@@ -63760,7 +63786,7 @@
         <v>344</v>
       </c>
       <c r="E61" s="62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="4">
         <v>2214</v>
@@ -63838,7 +63864,7 @@
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65" s="4">
         <v>4394</v>
@@ -64237,7 +64263,7 @@
         <v>290</v>
       </c>
       <c r="E3" s="35">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F3" s="33">
         <v>1465</v>
@@ -64535,7 +64561,7 @@
         <v>2965</v>
       </c>
       <c r="E19" s="35">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F19" s="33">
         <v>338</v>
@@ -64769,7 +64795,7 @@
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
       <c r="E32" s="35">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="F32" s="33"/>
     </row>
@@ -65201,7 +65227,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="35">
-        <v>740</v>
+        <v>710</v>
       </c>
       <c r="F12" s="33">
         <v>155</v>
@@ -65370,7 +65396,7 @@
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="35">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="F22" s="33">
         <v>79</v>
@@ -65391,7 +65417,7 @@
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="35">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F23" s="33">
         <v>105</v>
@@ -65447,7 +65473,7 @@
       </c>
       <c r="D26" s="33"/>
       <c r="E26" s="35">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F26" s="33">
         <v>18</v>
@@ -65988,7 +66014,7 @@
         <v>2669</v>
       </c>
       <c r="E57" s="35">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F57" s="33">
         <v>750</v>
@@ -66910,7 +66936,7 @@
       <c r="C115" s="33"/>
       <c r="D115" s="33"/>
       <c r="E115" s="35">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F115" s="33">
         <v>840</v>
@@ -66928,7 +66954,7 @@
       </c>
       <c r="D116" s="33"/>
       <c r="E116" s="35">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F116" s="33">
         <v>385</v>

--- a/backend/public/BOSCH_STOCK1.xlsx
+++ b/backend/public/BOSCH_STOCK1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730" firstSheet="10" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="ELEMENT" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5811" uniqueCount="3599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5810" uniqueCount="3598">
   <si>
     <t>0 433 175 443</t>
   </si>
@@ -10860,9 +10860,6 @@
   </si>
   <si>
     <t>285/262</t>
-  </si>
-  <si>
-    <t>2102/1937</t>
   </si>
   <si>
     <t>8125/7490</t>
@@ -14923,7 +14920,7 @@
       </c>
       <c r="D129" s="17"/>
       <c r="E129" s="19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F129" s="17"/>
       <c r="G129" s="17"/>
@@ -15644,7 +15641,7 @@
     <row r="165" spans="1:10" ht="15.75">
       <c r="A165" s="17"/>
       <c r="B165" s="17" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="C165" s="18" t="s">
         <v>3145</v>
@@ -16484,7 +16481,7 @@
         <v>70</v>
       </c>
       <c r="F16" s="74" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="G16" s="74"/>
       <c r="H16" s="74"/>
@@ -19861,10 +19858,10 @@
       </c>
       <c r="D189" s="74"/>
       <c r="E189" s="75">
-        <v>5</v>
-      </c>
-      <c r="F189" s="74" t="s">
-        <v>3570</v>
+        <v>7</v>
+      </c>
+      <c r="F189" s="74">
+        <v>2275</v>
       </c>
       <c r="G189" s="74"/>
       <c r="H189" s="74"/>
@@ -20458,7 +20455,7 @@
     <row r="220" spans="1:8" ht="21">
       <c r="A220" s="74"/>
       <c r="B220" s="74" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="C220" s="74" t="s">
         <v>598</v>
@@ -20576,7 +20573,7 @@
         <v>2</v>
       </c>
       <c r="F225" s="74" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="G225" s="74"/>
       <c r="H225" s="74"/>
@@ -20620,7 +20617,7 @@
         <v>1</v>
       </c>
       <c r="F227" s="74" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="G227" s="74"/>
       <c r="H227" s="74"/>
@@ -21050,7 +21047,7 @@
         <v>0</v>
       </c>
       <c r="F247" s="74" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G247" s="74"/>
       <c r="H247" s="74"/>
@@ -22037,7 +22034,7 @@
     </row>
     <row r="294" spans="1:8" ht="21">
       <c r="B294" s="90" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="C294" s="74" t="s">
         <v>843</v>
@@ -22502,7 +22499,7 @@
         <v>2604</v>
       </c>
       <c r="E18" s="71">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="F18" s="69">
         <v>392</v>
@@ -22568,7 +22565,7 @@
         <v>2227</v>
       </c>
       <c r="E21" s="71">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F21" s="69">
         <v>482</v>
@@ -31406,7 +31403,7 @@
         <v>1292</v>
       </c>
       <c r="E7" s="19">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F7" s="17">
         <v>3385</v>
@@ -32011,7 +32008,7 @@
         <v>2303</v>
       </c>
       <c r="E36" s="19">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="F36" s="17">
         <v>418</v>
@@ -32571,7 +32568,7 @@
         <v>3080</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.75">
@@ -33377,7 +33374,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -33854,10 +33851,10 @@
         <v>836</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -33974,7 +33971,7 @@
         <v>1747</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>953</v>
@@ -34317,7 +34314,7 @@
         <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -35049,7 +35046,7 @@
     </row>
     <row r="98" spans="1:6">
       <c r="B98" s="6" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="C98" t="s">
         <v>3546</v>
@@ -40198,7 +40195,7 @@
         <v>1542</v>
       </c>
       <c r="E217" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F217" s="9"/>
       <c r="G217" t="s">
@@ -41470,7 +41467,7 @@
       </c>
       <c r="D6" s="38"/>
       <c r="E6" s="35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="33"/>
       <c r="H6" t="s">
@@ -42716,7 +42713,7 @@
       <c r="C74" s="33"/>
       <c r="D74" s="38"/>
       <c r="E74" s="35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F74" s="33"/>
       <c r="H74" t="s">
@@ -45857,7 +45854,7 @@
       </c>
       <c r="D50" s="33"/>
       <c r="E50" s="35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F50" s="33"/>
     </row>
@@ -49256,7 +49253,7 @@
       </c>
       <c r="D257" s="33"/>
       <c r="E257" s="35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F257" s="33">
         <v>137</v>
@@ -49306,7 +49303,7 @@
         <v>1169</v>
       </c>
       <c r="C260" s="33" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="D260" s="33" t="s">
         <v>1170</v>
@@ -49448,7 +49445,7 @@
       <c r="C268" s="33"/>
       <c r="D268" s="33"/>
       <c r="E268" s="35">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F268" s="33"/>
     </row>
@@ -49770,7 +49767,7 @@
       </c>
       <c r="D288" s="33"/>
       <c r="E288" s="35">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F288" s="33"/>
     </row>
@@ -49876,7 +49873,7 @@
       </c>
       <c r="D294" s="33"/>
       <c r="E294" s="35">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F294" s="33">
         <v>696</v>
@@ -50257,7 +50254,7 @@
       </c>
       <c r="D316" s="33"/>
       <c r="E316" s="35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F316" s="33">
         <v>865</v>
@@ -50362,7 +50359,7 @@
         <v>1207</v>
       </c>
       <c r="D322" s="33" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="E322" s="35">
         <v>40</v>
@@ -50382,7 +50379,7 @@
         <v>1207</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="E323" s="35">
         <v>36</v>
@@ -50431,7 +50428,7 @@
         <v>3281</v>
       </c>
       <c r="C326" s="33" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="D326" s="33" t="s">
         <v>3314</v>
@@ -50506,7 +50503,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="33" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="C330" s="33" t="s">
         <v>3315</v>
@@ -51341,10 +51338,10 @@
     </row>
     <row r="377" spans="1:6">
       <c r="B377" s="34" t="s">
+        <v>3585</v>
+      </c>
+      <c r="C377" s="89" t="s">
         <v>3586</v>
-      </c>
-      <c r="C377" s="89" t="s">
-        <v>3587</v>
       </c>
       <c r="E377" s="1">
         <v>5</v>
@@ -53159,7 +53156,7 @@
         <v>4</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -53813,7 +53810,7 @@
         <v>8</v>
       </c>
       <c r="F133" s="35" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -53873,10 +53870,10 @@
         <v>518894</v>
       </c>
       <c r="E136" s="56">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F136" s="35" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -54242,7 +54239,7 @@
         <v>2700</v>
       </c>
       <c r="E156" s="56">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F156" s="35">
         <v>1092</v>
@@ -57331,7 +57328,7 @@
     <row r="9" spans="1:10">
       <c r="A9" s="33"/>
       <c r="B9" s="33" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1210</v>
@@ -57356,7 +57353,7 @@
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F10" s="35">
         <v>193</v>
@@ -58147,7 +58144,7 @@
       </c>
       <c r="D53" s="33"/>
       <c r="E53" s="33">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F53" s="35">
         <v>276</v>
@@ -58183,7 +58180,7 @@
       </c>
       <c r="D55" s="33"/>
       <c r="E55" s="33">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F55" s="35">
         <v>260</v>
@@ -59478,7 +59475,7 @@
     <row r="127" spans="1:8">
       <c r="A127" s="33"/>
       <c r="B127" s="33" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="C127" s="33" t="s">
         <v>1276</v>
@@ -60675,7 +60672,7 @@
         <v>39</v>
       </c>
       <c r="F190" s="35" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -60957,13 +60954,13 @@
     <row r="205" spans="1:6">
       <c r="A205" s="33"/>
       <c r="B205" s="33" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="C205" s="33" t="s">
         <v>3365</v>
       </c>
       <c r="D205" s="33" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="E205" s="33">
         <v>6</v>
@@ -61476,7 +61473,7 @@
         <v>3455</v>
       </c>
       <c r="E231" s="33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F231" s="35">
         <v>1026</v>
@@ -62450,7 +62447,7 @@
         <v>2377</v>
       </c>
       <c r="D281" s="33" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="E281" s="33">
         <v>27</v>
@@ -65506,7 +65503,7 @@
       </c>
       <c r="D26" s="33"/>
       <c r="E26" s="35">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F26" s="33">
         <v>18</v>
@@ -65556,7 +65553,7 @@
       </c>
       <c r="D29" s="33"/>
       <c r="E29" s="35">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="F29" s="33">
         <v>21</v>

--- a/backend/public/BOSCH_STOCK1.xlsx
+++ b/backend/public/BOSCH_STOCK1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730" firstSheet="10" activeTab="13"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730"/>
   </bookViews>
   <sheets>
     <sheet name="ELEMENT" sheetId="1" r:id="rId1"/>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="D74" s="17"/>
       <c r="E74" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" s="17"/>
       <c r="G74" s="17"/>
@@ -17540,7 +17540,7 @@
         <v>387</v>
       </c>
       <c r="E72" s="75">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F72" s="74">
         <v>2033</v>
@@ -19248,7 +19248,7 @@
       </c>
       <c r="D159" s="74"/>
       <c r="E159" s="75">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F159" s="74">
         <v>100</v>
@@ -22187,7 +22187,7 @@
         <v>3497</v>
       </c>
       <c r="E4" s="71">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F4" s="70">
         <v>287</v>
@@ -22209,7 +22209,7 @@
         <v>3498</v>
       </c>
       <c r="E5" s="71">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F5" s="70">
         <v>167</v>
@@ -22301,7 +22301,7 @@
         <v>3502</v>
       </c>
       <c r="E9" s="71">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F9" s="70">
         <v>219</v>
@@ -22347,7 +22347,7 @@
         <v>3504</v>
       </c>
       <c r="E11" s="71">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F11" s="70">
         <v>242</v>
@@ -22371,7 +22371,7 @@
         <v>3505</v>
       </c>
       <c r="E12" s="71">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="F12" s="70">
         <v>254</v>
@@ -22455,7 +22455,7 @@
         <v>2229</v>
       </c>
       <c r="E16" s="71">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="F16" s="69">
         <v>334</v>
@@ -22477,7 +22477,7 @@
         <v>2603</v>
       </c>
       <c r="E17" s="71">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="F17" s="69">
         <v>345</v>
@@ -22521,7 +22521,7 @@
         <v>2605</v>
       </c>
       <c r="E19" s="71">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F19" s="70">
         <v>420</v>
@@ -22543,7 +22543,7 @@
         <v>2228</v>
       </c>
       <c r="E20" s="71">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F20" s="69">
         <v>437</v>
@@ -31319,7 +31319,7 @@
         <v>1292</v>
       </c>
       <c r="E3" s="19">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="F3" s="17">
         <v>362</v>
@@ -31382,7 +31382,7 @@
         <v>1293</v>
       </c>
       <c r="E6" s="19">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F6" s="17">
         <v>2595</v>
@@ -31632,7 +31632,7 @@
         <v>1294</v>
       </c>
       <c r="E18" s="19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F18" s="17">
         <v>2881</v>
@@ -31882,7 +31882,7 @@
         <v>2369</v>
       </c>
       <c r="E30" s="19">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="F30" s="17">
         <v>1709</v>
@@ -32029,7 +32029,7 @@
         <v>2351</v>
       </c>
       <c r="E37" s="19">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F37" s="17">
         <v>1157</v>
@@ -49445,7 +49445,7 @@
       <c r="C268" s="33"/>
       <c r="D268" s="33"/>
       <c r="E268" s="35">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F268" s="33"/>
     </row>
@@ -49767,7 +49767,7 @@
       </c>
       <c r="D288" s="33"/>
       <c r="E288" s="35">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F288" s="33"/>
     </row>
@@ -52455,7 +52455,7 @@
         <v>2694</v>
       </c>
       <c r="E57" s="56">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F57" s="35">
         <v>2075</v>
@@ -53061,7 +53061,7 @@
         <v>2704</v>
       </c>
       <c r="E91" s="56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F91" s="35">
         <v>855</v>
@@ -53870,7 +53870,7 @@
         <v>518894</v>
       </c>
       <c r="E136" s="56">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F136" s="35" t="s">
         <v>3571</v>
@@ -54149,7 +54149,7 @@
         <v>2709</v>
       </c>
       <c r="E151" s="56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F151" s="35" t="s">
         <v>3118</v>
@@ -54815,7 +54815,7 @@
         <v>2705</v>
       </c>
       <c r="E186" s="56">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F186" s="35" t="s">
         <v>3114</v>
@@ -57228,7 +57228,7 @@
       </c>
       <c r="D3" s="33"/>
       <c r="E3" s="33">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F3" s="35">
         <v>161</v>
@@ -57246,7 +57246,7 @@
       </c>
       <c r="D4" s="33"/>
       <c r="E4" s="33">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F4" s="35">
         <v>146</v>
@@ -57319,7 +57319,7 @@
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="35">
         <v>121</v>
@@ -57353,7 +57353,7 @@
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="F10" s="35">
         <v>193</v>
@@ -57389,7 +57389,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="F12" s="35">
         <v>184</v>
@@ -57538,7 +57538,7 @@
       </c>
       <c r="D20" s="33"/>
       <c r="E20" s="33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="35">
         <v>1854</v>
@@ -58286,7 +58286,7 @@
       </c>
       <c r="D61" s="33"/>
       <c r="E61" s="33">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F61" s="35">
         <v>345</v>
@@ -58510,7 +58510,7 @@
       </c>
       <c r="D74" s="33"/>
       <c r="E74" s="33">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F74" s="35">
         <v>239</v>
@@ -58598,7 +58598,7 @@
         <v>3366</v>
       </c>
       <c r="E79" s="33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F79" s="35">
         <v>537</v>
@@ -58816,7 +58816,7 @@
       </c>
       <c r="D91" s="33"/>
       <c r="E91" s="33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F91" s="35">
         <v>1656</v>
@@ -58873,7 +58873,7 @@
       </c>
       <c r="D94" s="33"/>
       <c r="E94" s="33">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F94" s="35">
         <v>288</v>
@@ -59191,7 +59191,7 @@
       </c>
       <c r="D111" s="33"/>
       <c r="E111" s="33">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F111" s="35">
         <v>746</v>
@@ -59747,7 +59747,7 @@
         <v>3393</v>
       </c>
       <c r="E141" s="35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F141" s="33">
         <v>1804</v>
@@ -60039,7 +60039,7 @@
         <v>836</v>
       </c>
       <c r="E158" s="33">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F158" s="35">
         <v>568</v>
@@ -60059,7 +60059,7 @@
         <v>1855</v>
       </c>
       <c r="E159" s="33">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F159" s="35">
         <v>234</v>
@@ -60119,7 +60119,7 @@
         <v>3399</v>
       </c>
       <c r="E162" s="33">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F162" s="35">
         <v>686</v>
@@ -60569,7 +60569,7 @@
         <v>3422</v>
       </c>
       <c r="E185" s="33">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F185" s="35">
         <v>627</v>
@@ -66966,7 +66966,7 @@
       <c r="C115" s="33"/>
       <c r="D115" s="33"/>
       <c r="E115" s="35">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F115" s="33">
         <v>840</v>

--- a/backend/public/BOSCH_STOCK1.xlsx
+++ b/backend/public/BOSCH_STOCK1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730" firstSheet="10" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="ELEMENT" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5813" uniqueCount="3599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5819" uniqueCount="3605">
   <si>
     <t>0 433 175 443</t>
   </si>
@@ -9122,9 +9122,6 @@
     <t>NEXON</t>
   </si>
   <si>
-    <t>232/210</t>
-  </si>
-  <si>
     <t>ALTO/ WAGNR</t>
   </si>
   <si>
@@ -10947,6 +10944,27 @@
   </si>
   <si>
     <t>199/172</t>
+  </si>
+  <si>
+    <t>1330/1180</t>
+  </si>
+  <si>
+    <t>10729/9890</t>
+  </si>
+  <si>
+    <t>2688/2478</t>
+  </si>
+  <si>
+    <t>100/98</t>
+  </si>
+  <si>
+    <t>9170/8453</t>
+  </si>
+  <si>
+    <t>9 451 035 558</t>
+  </si>
+  <si>
+    <t>DOT 3</t>
   </si>
 </sst>
 </file>
@@ -12242,10 +12260,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -12262,7 +12280,7 @@
         <v>197</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="19">
@@ -12283,7 +12301,7 @@
         <v>1354</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="19">
@@ -12302,7 +12320,7 @@
         <v>198</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="19">
@@ -12323,7 +12341,7 @@
         <v>199</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="19">
@@ -12344,7 +12362,7 @@
         <v>200</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="19">
@@ -12365,7 +12383,7 @@
         <v>201</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="19">
@@ -12386,7 +12404,7 @@
         <v>202</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="19">
@@ -12409,7 +12427,7 @@
         <v>203</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="19">
@@ -12430,7 +12448,7 @@
         <v>204</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="19">
@@ -12449,7 +12467,7 @@
         <v>205</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="19">
@@ -12468,7 +12486,7 @@
         <v>206</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>1934</v>
@@ -12493,7 +12511,7 @@
         <v>207</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="19">
@@ -12514,7 +12532,7 @@
         <v>208</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="19">
@@ -12535,7 +12553,7 @@
         <v>209</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="19">
@@ -12556,7 +12574,7 @@
         <v>210</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="19">
@@ -12575,7 +12593,7 @@
         <v>211</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D17" s="17"/>
       <c r="E17" s="19">
@@ -12596,7 +12614,7 @@
         <v>212</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="19">
@@ -12617,7 +12635,7 @@
         <v>213</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="19">
@@ -12640,7 +12658,7 @@
         <v>214</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="19">
@@ -12661,7 +12679,7 @@
         <v>215</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D21" s="17"/>
       <c r="E21" s="19">
@@ -12680,7 +12698,7 @@
         <v>381</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D22" s="17"/>
       <c r="E22" s="19">
@@ -12701,7 +12719,7 @@
         <v>382</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="19">
@@ -12722,7 +12740,7 @@
         <v>383</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="19">
@@ -12743,7 +12761,7 @@
         <v>384</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D25" s="17"/>
       <c r="E25" s="19">
@@ -12764,7 +12782,7 @@
         <v>385</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D26" s="17"/>
       <c r="E26" s="19">
@@ -12787,7 +12805,7 @@
         <v>386</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D27" s="17"/>
       <c r="E27" s="19">
@@ -12808,11 +12826,11 @@
         <v>387</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
@@ -12829,7 +12847,7 @@
         <v>388</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="19">
@@ -12850,7 +12868,7 @@
         <v>389</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="19">
@@ -12871,7 +12889,7 @@
         <v>390</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="19">
@@ -12892,7 +12910,7 @@
         <v>391</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="19">
@@ -12913,7 +12931,7 @@
         <v>392</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="19">
@@ -12934,11 +12952,11 @@
         <v>393</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>2647</v>
@@ -12957,7 +12975,7 @@
         <v>394</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D35" s="17"/>
       <c r="E35" s="19">
@@ -12978,7 +12996,7 @@
         <v>395</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D36" s="17"/>
       <c r="E36" s="19">
@@ -12999,7 +13017,7 @@
         <v>1452</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D37" s="17"/>
       <c r="E37" s="19">
@@ -13020,11 +13038,11 @@
         <v>396</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D38" s="17"/>
       <c r="E38" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
@@ -13041,7 +13059,7 @@
         <v>397</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D39" s="17"/>
       <c r="E39" s="19">
@@ -13062,7 +13080,7 @@
         <v>455</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D40" s="17"/>
       <c r="E40" s="19">
@@ -13083,7 +13101,7 @@
         <v>1636</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D41" s="17"/>
       <c r="E41" s="19">
@@ -13102,7 +13120,7 @@
         <v>456</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="19">
@@ -13123,7 +13141,7 @@
         <v>1375</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="19">
@@ -13144,7 +13162,7 @@
         <v>457</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D44" s="17"/>
       <c r="E44" s="19">
@@ -13165,7 +13183,7 @@
         <v>1431</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D45" s="17"/>
       <c r="E45" s="19">
@@ -13186,7 +13204,7 @@
         <v>458</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="19">
@@ -13207,7 +13225,7 @@
         <v>459</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="19">
@@ -13228,7 +13246,7 @@
         <v>460</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="19">
@@ -13249,7 +13267,7 @@
         <v>461</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="19">
@@ -13268,7 +13286,7 @@
         <v>1478</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D50" s="17"/>
       <c r="E50" s="19">
@@ -13289,7 +13307,7 @@
         <v>462</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D51" s="17"/>
       <c r="E51" s="19">
@@ -13310,11 +13328,11 @@
         <v>463</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D52" s="17"/>
       <c r="E52" s="19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>2647</v>
@@ -13333,7 +13351,7 @@
         <v>464</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D53" s="17"/>
       <c r="E53" s="19">
@@ -13356,7 +13374,7 @@
         <v>465</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="19">
@@ -13377,7 +13395,7 @@
         <v>466</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D55" s="17"/>
       <c r="E55" s="19">
@@ -13398,7 +13416,7 @@
         <v>467</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D56" s="17"/>
       <c r="E56" s="19">
@@ -13419,7 +13437,7 @@
         <v>468</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="19">
@@ -13440,7 +13458,7 @@
         <v>469</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D58" s="17"/>
       <c r="E58" s="19">
@@ -13461,7 +13479,7 @@
         <v>470</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D59" s="17"/>
       <c r="E59" s="19">
@@ -13482,7 +13500,7 @@
         <v>471</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D60" s="17"/>
       <c r="E60" s="19">
@@ -13503,7 +13521,7 @@
         <v>472</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D61" s="17"/>
       <c r="E61" s="19">
@@ -13524,7 +13542,7 @@
         <v>473</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D62" s="17"/>
       <c r="E62" s="19">
@@ -13547,7 +13565,7 @@
         <v>474</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D63" s="17"/>
       <c r="E63" s="19">
@@ -13568,7 +13586,7 @@
         <v>475</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D64" s="17"/>
       <c r="E64" s="19">
@@ -13589,7 +13607,7 @@
         <v>476</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D65" s="17"/>
       <c r="E65" s="19">
@@ -13610,7 +13628,7 @@
         <v>477</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D66" s="17"/>
       <c r="E66" s="19">
@@ -13629,7 +13647,7 @@
         <v>478</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D67" s="17"/>
       <c r="E67" s="19">
@@ -13650,7 +13668,7 @@
         <v>479</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D68" s="17"/>
       <c r="E68" s="19">
@@ -13671,7 +13689,7 @@
         <v>480</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D69" s="17"/>
       <c r="E69" s="19">
@@ -13692,7 +13710,7 @@
         <v>2586</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D70" s="17"/>
       <c r="E70" s="19">
@@ -13713,7 +13731,7 @@
         <v>1613</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D71" s="17"/>
       <c r="E71" s="19">
@@ -13732,7 +13750,7 @@
         <v>481</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D72" s="17"/>
       <c r="E72" s="19">
@@ -13753,7 +13771,7 @@
         <v>1845</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D73" s="17"/>
       <c r="E73" s="19">
@@ -13772,7 +13790,7 @@
         <v>2032</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D74" s="17"/>
       <c r="E74" s="19">
@@ -13791,7 +13809,7 @@
         <v>482</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D75" s="17"/>
       <c r="E75" s="19">
@@ -13812,7 +13830,7 @@
         <v>1643</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D76" s="17"/>
       <c r="E76" s="19">
@@ -13831,7 +13849,7 @@
         <v>1743</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D77" s="17"/>
       <c r="E77" s="19">
@@ -13850,7 +13868,7 @@
         <v>1776</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D78" s="17"/>
       <c r="E78" s="19">
@@ -13869,7 +13887,7 @@
         <v>1826</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D79" s="17"/>
       <c r="E79" s="19">
@@ -13888,7 +13906,7 @@
         <v>2247</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D80" s="17"/>
       <c r="E80" s="19">
@@ -13907,7 +13925,7 @@
         <v>2135</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D81" s="17"/>
       <c r="E81" s="19">
@@ -13926,7 +13944,7 @@
         <v>2620</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D82" s="17"/>
       <c r="E82" s="19">
@@ -13945,7 +13963,7 @@
         <v>483</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D83" s="17"/>
       <c r="E83" s="19">
@@ -13966,7 +13984,7 @@
         <v>484</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D84" s="17"/>
       <c r="E84" s="19">
@@ -13989,7 +14007,7 @@
         <v>485</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D85" s="17"/>
       <c r="E85" s="19">
@@ -14012,7 +14030,7 @@
         <v>486</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D86" s="17"/>
       <c r="E86" s="19">
@@ -14033,11 +14051,11 @@
         <v>487</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D87" s="17"/>
       <c r="E87" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F87" s="17"/>
       <c r="G87" s="17"/>
@@ -14054,7 +14072,7 @@
         <v>488</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D88" s="17"/>
       <c r="E88" s="19">
@@ -14073,7 +14091,7 @@
         <v>489</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D89" s="17"/>
       <c r="E89" s="19">
@@ -14094,7 +14112,7 @@
         <v>490</v>
       </c>
       <c r="C90" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D90" s="17"/>
       <c r="E90" s="19">
@@ -14115,7 +14133,7 @@
         <v>491</v>
       </c>
       <c r="C91" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D91" s="17"/>
       <c r="E91" s="19">
@@ -14138,7 +14156,7 @@
         <v>492</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D92" s="17"/>
       <c r="E92" s="19">
@@ -14159,7 +14177,7 @@
         <v>493</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D93" s="17"/>
       <c r="E93" s="19">
@@ -14180,7 +14198,7 @@
         <v>494</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D94" s="17"/>
       <c r="E94" s="19">
@@ -14199,7 +14217,7 @@
         <v>495</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D95" s="17"/>
       <c r="E95" s="19">
@@ -14220,7 +14238,7 @@
         <v>496</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D96" s="17"/>
       <c r="E96" s="19">
@@ -14241,7 +14259,7 @@
         <v>497</v>
       </c>
       <c r="C97" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D97" s="17"/>
       <c r="E97" s="19">
@@ -14262,7 +14280,7 @@
         <v>498</v>
       </c>
       <c r="C98" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D98" s="17"/>
       <c r="E98" s="19">
@@ -14283,7 +14301,7 @@
         <v>499</v>
       </c>
       <c r="C99" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D99" s="17"/>
       <c r="E99" s="19">
@@ -14304,7 +14322,7 @@
         <v>500</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D100" s="17"/>
       <c r="E100" s="19">
@@ -14327,7 +14345,7 @@
         <v>501</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D101" s="17"/>
       <c r="E101" s="19">
@@ -14350,7 +14368,7 @@
         <v>502</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D102" s="17"/>
       <c r="E102" s="19">
@@ -14371,7 +14389,7 @@
         <v>503</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D103" s="17"/>
       <c r="E103" s="19">
@@ -14394,7 +14412,7 @@
         <v>2254</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D104" s="17"/>
       <c r="E104" s="19">
@@ -14413,7 +14431,7 @@
         <v>504</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D105" s="17"/>
       <c r="E105" s="19">
@@ -14434,7 +14452,7 @@
         <v>505</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D106" s="17"/>
       <c r="E106" s="19">
@@ -14455,7 +14473,7 @@
         <v>506</v>
       </c>
       <c r="C107" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D107" s="17"/>
       <c r="E107" s="19">
@@ -14478,7 +14496,7 @@
         <v>507</v>
       </c>
       <c r="C108" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D108" s="17"/>
       <c r="E108" s="19">
@@ -14499,7 +14517,7 @@
         <v>508</v>
       </c>
       <c r="C109" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D109" s="17"/>
       <c r="E109" s="19">
@@ -14522,7 +14540,7 @@
         <v>1736</v>
       </c>
       <c r="C110" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D110" s="17"/>
       <c r="E110" s="19">
@@ -14541,7 +14559,7 @@
         <v>509</v>
       </c>
       <c r="C111" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D111" s="17"/>
       <c r="E111" s="19">
@@ -14562,7 +14580,7 @@
         <v>510</v>
       </c>
       <c r="C112" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D112" s="17"/>
       <c r="E112" s="19">
@@ -14583,7 +14601,7 @@
         <v>511</v>
       </c>
       <c r="C113" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D113" s="17"/>
       <c r="E113" s="19">
@@ -14604,7 +14622,7 @@
         <v>1865</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D114" s="17"/>
       <c r="E114" s="19">
@@ -14623,7 +14641,7 @@
         <v>512</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D115" s="17"/>
       <c r="E115" s="19">
@@ -14644,7 +14662,7 @@
         <v>1457</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D116" s="17"/>
       <c r="E116" s="19">
@@ -14667,7 +14685,7 @@
         <v>513</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D117" s="17"/>
       <c r="E117" s="19">
@@ -14688,7 +14706,7 @@
         <v>514</v>
       </c>
       <c r="C118" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D118" s="17"/>
       <c r="E118" s="19">
@@ -14707,7 +14725,7 @@
         <v>515</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D119" s="17"/>
       <c r="E119" s="19">
@@ -14726,7 +14744,7 @@
         <v>516</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D120" s="17"/>
       <c r="E120" s="19">
@@ -14747,7 +14765,7 @@
         <v>517</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D121" s="17"/>
       <c r="E121" s="19">
@@ -14770,7 +14788,7 @@
         <v>518</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D122" s="17"/>
       <c r="E122" s="19">
@@ -14791,7 +14809,7 @@
         <v>519</v>
       </c>
       <c r="C123" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D123" s="17"/>
       <c r="E123" s="19">
@@ -14812,7 +14830,7 @@
         <v>520</v>
       </c>
       <c r="C124" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D124" s="17"/>
       <c r="E124" s="19">
@@ -14835,7 +14853,7 @@
         <v>521</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D125" s="17"/>
       <c r="E125" s="19">
@@ -14856,7 +14874,7 @@
         <v>522</v>
       </c>
       <c r="C126" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D126" s="17"/>
       <c r="E126" s="19">
@@ -14877,7 +14895,7 @@
         <v>523</v>
       </c>
       <c r="C127" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D127" s="17"/>
       <c r="E127" s="19">
@@ -14898,7 +14916,7 @@
         <v>524</v>
       </c>
       <c r="C128" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D128" s="17"/>
       <c r="E128" s="19">
@@ -14919,7 +14937,7 @@
         <v>525</v>
       </c>
       <c r="C129" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D129" s="17"/>
       <c r="E129" s="19">
@@ -14938,7 +14956,7 @@
         <v>526</v>
       </c>
       <c r="C130" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D130" s="17"/>
       <c r="E130" s="19">
@@ -14959,7 +14977,7 @@
         <v>527</v>
       </c>
       <c r="C131" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D131" s="17"/>
       <c r="E131" s="19">
@@ -14980,7 +14998,7 @@
         <v>528</v>
       </c>
       <c r="C132" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D132" s="17"/>
       <c r="E132" s="19">
@@ -15003,7 +15021,7 @@
         <v>529</v>
       </c>
       <c r="C133" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D133" s="17"/>
       <c r="E133" s="19">
@@ -15024,7 +15042,7 @@
         <v>530</v>
       </c>
       <c r="C134" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D134" s="17"/>
       <c r="E134" s="19">
@@ -15045,7 +15063,7 @@
         <v>531</v>
       </c>
       <c r="C135" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D135" s="17"/>
       <c r="E135" s="19">
@@ -15064,7 +15082,7 @@
         <v>532</v>
       </c>
       <c r="C136" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D136" s="17"/>
       <c r="E136" s="19">
@@ -15085,7 +15103,7 @@
         <v>533</v>
       </c>
       <c r="C137" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D137" s="17"/>
       <c r="E137" s="19">
@@ -15106,7 +15124,7 @@
         <v>534</v>
       </c>
       <c r="C138" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D138" s="17"/>
       <c r="E138" s="19">
@@ -15127,7 +15145,7 @@
         <v>536</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D139" s="17"/>
       <c r="E139" s="19">
@@ -15148,7 +15166,7 @@
         <v>537</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D140" s="17"/>
       <c r="E140" s="19">
@@ -15169,7 +15187,7 @@
         <v>2180</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D141" s="17"/>
       <c r="E141" s="19">
@@ -15188,7 +15206,7 @@
         <v>538</v>
       </c>
       <c r="C142" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D142" s="17"/>
       <c r="E142" s="19">
@@ -15209,11 +15227,11 @@
         <v>539</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D143" s="17"/>
       <c r="E143" s="19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F143" s="17"/>
       <c r="G143" s="17"/>
@@ -15230,7 +15248,7 @@
         <v>540</v>
       </c>
       <c r="C144" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D144" s="17"/>
       <c r="E144" s="19">
@@ -15251,7 +15269,7 @@
         <v>541</v>
       </c>
       <c r="C145" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D145" s="17"/>
       <c r="E145" s="19">
@@ -15272,7 +15290,7 @@
         <v>542</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D146" s="17"/>
       <c r="E146" s="19">
@@ -15293,7 +15311,7 @@
         <v>543</v>
       </c>
       <c r="C147" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D147" s="17"/>
       <c r="E147" s="19">
@@ -15312,7 +15330,7 @@
         <v>1516</v>
       </c>
       <c r="C148" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D148" s="17"/>
       <c r="E148" s="19">
@@ -15333,7 +15351,7 @@
         <v>2219</v>
       </c>
       <c r="C149" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D149" s="17"/>
       <c r="E149" s="19">
@@ -15352,7 +15370,7 @@
         <v>1455</v>
       </c>
       <c r="C150" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D150" s="17"/>
       <c r="E150" s="19">
@@ -15373,7 +15391,7 @@
         <v>1585</v>
       </c>
       <c r="C151" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D151" s="17"/>
       <c r="E151" s="19">
@@ -15392,7 +15410,7 @@
         <v>1481</v>
       </c>
       <c r="C152" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D152" s="17"/>
       <c r="E152" s="19">
@@ -15415,7 +15433,7 @@
         <v>1407</v>
       </c>
       <c r="C153" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D153" s="17"/>
       <c r="E153" s="19">
@@ -15436,7 +15454,7 @@
         <v>544</v>
       </c>
       <c r="C154" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D154" s="17"/>
       <c r="E154" s="19">
@@ -15455,7 +15473,7 @@
         <v>2590</v>
       </c>
       <c r="C155" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D155" s="17"/>
       <c r="E155" s="19">
@@ -15476,7 +15494,7 @@
         <v>1595</v>
       </c>
       <c r="C156" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D156" s="17"/>
       <c r="E156" s="19">
@@ -15495,7 +15513,7 @@
         <v>2040</v>
       </c>
       <c r="C157" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D157" s="17"/>
       <c r="E157" s="19">
@@ -15514,7 +15532,7 @@
         <v>545</v>
       </c>
       <c r="C158" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D158" s="17"/>
       <c r="E158" s="19">
@@ -15535,7 +15553,7 @@
         <v>2516</v>
       </c>
       <c r="C159" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D159" s="17"/>
       <c r="E159" s="19">
@@ -15554,7 +15572,7 @@
         <v>1828</v>
       </c>
       <c r="C160" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D160" s="17"/>
       <c r="E160" s="19">
@@ -15573,7 +15591,7 @@
         <v>2041</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D161" s="17"/>
       <c r="E161" s="19">
@@ -15592,7 +15610,7 @@
         <v>2042</v>
       </c>
       <c r="C162" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D162" s="17"/>
       <c r="E162" s="19">
@@ -15611,7 +15629,7 @@
         <v>2224</v>
       </c>
       <c r="C163" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D163" s="17"/>
       <c r="E163" s="19">
@@ -15630,7 +15648,7 @@
         <v>2078</v>
       </c>
       <c r="C164" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D164" s="17"/>
       <c r="E164" s="19">
@@ -15644,10 +15662,10 @@
     <row r="165" spans="1:10" ht="15.75">
       <c r="A165" s="17"/>
       <c r="B165" s="17" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="C165" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D165" s="17"/>
       <c r="E165" s="19">
@@ -15666,7 +15684,7 @@
         <v>2507</v>
       </c>
       <c r="C166" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D166" s="17"/>
       <c r="E166" s="19">
@@ -15685,7 +15703,7 @@
         <v>2761</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D167" s="17"/>
       <c r="E167" s="19">
@@ -15704,7 +15722,7 @@
         <v>2039</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D168" s="17" t="s">
         <v>2164</v>
@@ -15730,7 +15748,7 @@
         <v>2136</v>
       </c>
       <c r="C169" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D169" s="17"/>
       <c r="E169" s="19">
@@ -15749,7 +15767,7 @@
         <v>2188</v>
       </c>
       <c r="C170" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D170" s="17"/>
       <c r="E170" s="19">
@@ -15768,7 +15786,7 @@
         <v>2071</v>
       </c>
       <c r="C171" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D171" s="17"/>
       <c r="E171" s="19">
@@ -15787,7 +15805,7 @@
         <v>2618</v>
       </c>
       <c r="C172" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D172" s="17"/>
       <c r="E172" s="19">
@@ -15806,7 +15824,7 @@
         <v>2609</v>
       </c>
       <c r="C173" s="18" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="E173" s="10">
         <v>7</v>
@@ -16157,10 +16175,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -16246,7 +16264,7 @@
         <v>598</v>
       </c>
       <c r="D5" s="74" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="E5" s="75">
         <v>10</v>
@@ -16396,7 +16414,7 @@
         <v>2718</v>
       </c>
       <c r="D12" s="74" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="E12" s="75">
         <v>1</v>
@@ -16462,7 +16480,7 @@
         <v>102</v>
       </c>
       <c r="F15" s="74" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="G15" s="74"/>
       <c r="H15" s="74"/>
@@ -16484,7 +16502,7 @@
         <v>70</v>
       </c>
       <c r="F16" s="74" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="G16" s="74"/>
       <c r="H16" s="74"/>
@@ -17610,7 +17628,7 @@
         <v>9</v>
       </c>
       <c r="F75" s="74" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="G75" s="74"/>
       <c r="H75" s="74"/>
@@ -18615,10 +18633,10 @@
         <v>815</v>
       </c>
       <c r="E128" s="75">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F128" s="74">
-        <v>2948</v>
+        <v>2717</v>
       </c>
       <c r="G128" s="74"/>
       <c r="H128" s="74"/>
@@ -18655,10 +18673,10 @@
         <v>817</v>
       </c>
       <c r="E130" s="75">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F130" s="74" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="G130" s="74"/>
       <c r="H130" s="74"/>
@@ -18674,7 +18692,7 @@
         <v>625</v>
       </c>
       <c r="D131" s="74" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="E131" s="75">
         <v>2</v>
@@ -18696,7 +18714,7 @@
         <v>625</v>
       </c>
       <c r="D132" s="74" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="E132" s="75">
         <v>0</v>
@@ -18799,7 +18817,7 @@
         <v>2072</v>
       </c>
       <c r="E137" s="75">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F137" s="74" t="s">
         <v>2788</v>
@@ -18819,7 +18837,7 @@
       </c>
       <c r="D138" s="74"/>
       <c r="E138" s="75">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F138" s="74" t="s">
         <v>2757</v>
@@ -18899,10 +18917,10 @@
         <v>822</v>
       </c>
       <c r="E142" s="75">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="F142" s="74">
-        <v>746</v>
+        <v>687</v>
       </c>
       <c r="G142" s="74">
         <v>70050014</v>
@@ -19020,10 +19038,10 @@
         <v>825</v>
       </c>
       <c r="D148" s="74" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="E148" s="75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F148" s="74">
         <v>1515</v>
@@ -19060,7 +19078,7 @@
         <v>825</v>
       </c>
       <c r="D150" s="74" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="E150" s="75">
         <v>3</v>
@@ -19144,7 +19162,7 @@
         <v>598</v>
       </c>
       <c r="D154" s="74" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="E154" s="75">
         <v>7</v>
@@ -19182,7 +19200,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="74" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="C156" s="74" t="s">
         <v>825</v>
@@ -19208,7 +19226,7 @@
         <v>598</v>
       </c>
       <c r="D157" s="74" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="E157" s="75">
         <v>10</v>
@@ -19251,10 +19269,10 @@
       </c>
       <c r="D159" s="74"/>
       <c r="E159" s="75">
-        <v>240</v>
-      </c>
-      <c r="F159" s="74">
-        <v>100</v>
+        <v>480</v>
+      </c>
+      <c r="F159" s="74" t="s">
+        <v>3601</v>
       </c>
       <c r="G159" s="74"/>
       <c r="H159" s="74"/>
@@ -19399,10 +19417,10 @@
         <v>2651</v>
       </c>
       <c r="E167" s="75">
-        <v>2</v>
-      </c>
-      <c r="F167" s="74">
-        <v>2688</v>
+        <v>6</v>
+      </c>
+      <c r="F167" s="74" t="s">
+        <v>3600</v>
       </c>
       <c r="G167" s="74" t="s">
         <v>1553</v>
@@ -19510,7 +19528,7 @@
         <v>3</v>
       </c>
       <c r="F172" s="74" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="G172" s="74"/>
       <c r="H172" s="74"/>
@@ -20104,7 +20122,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="74" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="C202" s="74" t="s">
         <v>598</v>
@@ -20122,7 +20140,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="74" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="C203" s="74" t="s">
         <v>825</v>
@@ -20142,7 +20160,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="74" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="C204" s="74" t="s">
         <v>825</v>
@@ -20204,7 +20222,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="74" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="C207" s="74" t="s">
         <v>825</v>
@@ -20302,7 +20320,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="74" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="C212" s="74" t="s">
         <v>598</v>
@@ -20358,10 +20376,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="74" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C215" s="74" t="s">
         <v>3081</v>
-      </c>
-      <c r="C215" s="74" t="s">
-        <v>3082</v>
       </c>
       <c r="D215" s="74"/>
       <c r="E215" s="75">
@@ -20418,7 +20436,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="74" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="C218" s="74" t="s">
         <v>586</v>
@@ -20458,7 +20476,7 @@
     <row r="220" spans="1:8" ht="21">
       <c r="A220" s="74"/>
       <c r="B220" s="74" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="C220" s="74" t="s">
         <v>598</v>
@@ -20573,10 +20591,10 @@
         <v>1855</v>
       </c>
       <c r="E225" s="75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F225" s="74" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="G225" s="74"/>
       <c r="H225" s="74"/>
@@ -20620,7 +20638,7 @@
         <v>1</v>
       </c>
       <c r="F227" s="74" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="G227" s="74"/>
       <c r="H227" s="74"/>
@@ -20639,7 +20657,7 @@
         <v>2438</v>
       </c>
       <c r="E228" s="75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F228" s="74">
         <v>14552</v>
@@ -20727,7 +20745,7 @@
         <v>779</v>
       </c>
       <c r="E232" s="75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F232" s="74">
         <v>10597</v>
@@ -20959,10 +20977,10 @@
         <v>1855</v>
       </c>
       <c r="E243" s="75">
-        <v>1</v>
-      </c>
-      <c r="F243" s="74">
-        <v>9170</v>
+        <v>2</v>
+      </c>
+      <c r="F243" s="74" t="s">
+        <v>3602</v>
       </c>
       <c r="G243" s="74"/>
       <c r="H243" s="74"/>
@@ -21327,7 +21345,7 @@
         <v>2526</v>
       </c>
       <c r="C260" s="74" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="D260" s="74" t="s">
         <v>2553</v>
@@ -21336,7 +21354,7 @@
         <v>2</v>
       </c>
       <c r="F260" s="74" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="G260" s="74"/>
       <c r="H260" s="74"/>
@@ -21379,10 +21397,10 @@
         <v>1351</v>
       </c>
       <c r="E262" s="75">
-        <v>1</v>
-      </c>
-      <c r="F262" s="74">
-        <v>10729</v>
+        <v>2</v>
+      </c>
+      <c r="F262" s="74" t="s">
+        <v>3599</v>
       </c>
       <c r="G262" s="74"/>
       <c r="H262" s="74"/>
@@ -21445,10 +21463,10 @@
         <v>2902</v>
       </c>
       <c r="E265" s="75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F265" s="74">
-        <v>9962</v>
+        <v>9183</v>
       </c>
       <c r="G265" s="74"/>
       <c r="H265" s="74"/>
@@ -21575,10 +21593,10 @@
       </c>
       <c r="D271" s="74"/>
       <c r="E271" s="75">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F271" s="74">
-        <v>827</v>
+        <v>890</v>
       </c>
       <c r="G271" s="74"/>
       <c r="H271" s="74"/>
@@ -21716,7 +21734,7 @@
         <v>276</v>
       </c>
       <c r="B278" s="74" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="C278" s="74" t="s">
         <v>1966</v>
@@ -21904,7 +21922,7 @@
         <v>285</v>
       </c>
       <c r="B287" s="74" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="C287" s="74" t="s">
         <v>843</v>
@@ -21924,7 +21942,7 @@
         <v>286</v>
       </c>
       <c r="B288" s="74" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="C288" s="74" t="s">
         <v>843</v>
@@ -21942,7 +21960,7 @@
         <v>287</v>
       </c>
       <c r="B289" s="74" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="C289" s="74" t="s">
         <v>1966</v>
@@ -21962,7 +21980,7 @@
         <v>288</v>
       </c>
       <c r="B290" s="74" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="C290" s="74" t="s">
         <v>1966</v>
@@ -21980,7 +21998,7 @@
         <v>289</v>
       </c>
       <c r="B291" s="74" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="C291" s="74" t="s">
         <v>843</v>
@@ -22000,7 +22018,7 @@
         <v>290</v>
       </c>
       <c r="B292" s="74" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="C292" s="74" t="s">
         <v>843</v>
@@ -22020,7 +22038,7 @@
         <v>291</v>
       </c>
       <c r="B293" s="74" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="C293" s="74" t="s">
         <v>843</v>
@@ -22037,7 +22055,7 @@
     </row>
     <row r="294" spans="1:8" ht="21">
       <c r="B294" s="90" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="C294" s="74" t="s">
         <v>843</v>
@@ -22124,10 +22142,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -22143,7 +22161,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="97" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="C2" s="97"/>
       <c r="D2" s="97"/>
@@ -22160,13 +22178,13 @@
         <v>1629</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D3" s="69" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="E3" s="71">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="F3" s="70">
         <v>146</v>
@@ -22184,10 +22202,10 @@
         <v>1626</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="D4" s="69" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="E4" s="71">
         <v>220</v>
@@ -22206,10 +22224,10 @@
         <v>1980</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D5" s="69" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="E5" s="71">
         <v>138</v>
@@ -22228,10 +22246,10 @@
         <v>1981</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D6" s="69" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="E6" s="71">
         <v>725</v>
@@ -22252,10 +22270,10 @@
         <v>1982</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D7" s="69" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="E7" s="71">
         <v>295</v>
@@ -22276,10 +22294,10 @@
         <v>1983</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D8" s="69" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="E8" s="71">
         <v>262</v>
@@ -22298,10 +22316,10 @@
         <v>1984</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D9" s="69" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="E9" s="71">
         <v>341</v>
@@ -22320,10 +22338,10 @@
         <v>1985</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D10" s="69" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="E10" s="71">
         <v>208</v>
@@ -22344,13 +22362,13 @@
         <v>1986</v>
       </c>
       <c r="C11" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D11" s="69" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="E11" s="71">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="F11" s="70">
         <v>242</v>
@@ -22368,13 +22386,13 @@
         <v>1987</v>
       </c>
       <c r="C12" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D12" s="69" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="E12" s="71">
-        <v>952</v>
+        <v>922</v>
       </c>
       <c r="F12" s="70">
         <v>254</v>
@@ -22392,13 +22410,13 @@
         <v>1988</v>
       </c>
       <c r="C13" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D13" s="69" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="E13" s="71">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="F13" s="70">
         <v>288</v>
@@ -22416,10 +22434,10 @@
         <v>1989</v>
       </c>
       <c r="C14" s="69" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D14" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="E14" s="71">
         <v>240</v>
@@ -22435,7 +22453,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="98" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="C15" s="98"/>
       <c r="D15" s="98"/>
@@ -22452,7 +22470,7 @@
         <v>690</v>
       </c>
       <c r="C16" s="69" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="D16" s="69" t="s">
         <v>2229</v>
@@ -22474,7 +22492,7 @@
         <v>2064</v>
       </c>
       <c r="C17" s="69" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="D17" s="69" t="s">
         <v>2603</v>
@@ -22496,7 +22514,7 @@
         <v>691</v>
       </c>
       <c r="C18" s="69" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="D18" s="69" t="s">
         <v>2604</v>
@@ -22518,7 +22536,7 @@
         <v>692</v>
       </c>
       <c r="C19" s="69" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="D19" s="69" t="s">
         <v>2605</v>
@@ -22540,7 +22558,7 @@
         <v>693</v>
       </c>
       <c r="C20" s="69" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="D20" s="69" t="s">
         <v>2228</v>
@@ -22562,7 +22580,7 @@
         <v>694</v>
       </c>
       <c r="C21" s="69" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="D21" s="69" t="s">
         <v>2227</v>
@@ -22581,7 +22599,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="98" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="C22" s="98"/>
       <c r="D22" s="98"/>
@@ -22598,7 +22616,7 @@
         <v>2612</v>
       </c>
       <c r="C23" s="69" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="D23" s="69" t="s">
         <v>2606</v>
@@ -22620,7 +22638,7 @@
         <v>2045</v>
       </c>
       <c r="C24" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D24" s="69" t="s">
         <v>2049</v>
@@ -22642,7 +22660,7 @@
         <v>2090</v>
       </c>
       <c r="C25" s="69" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="D25" s="69" t="s">
         <v>2091</v>
@@ -22664,7 +22682,7 @@
         <v>2677</v>
       </c>
       <c r="C26" s="69" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="D26" s="69" t="s">
         <v>1720</v>
@@ -22686,7 +22704,7 @@
         <v>2065</v>
       </c>
       <c r="C27" s="69" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="D27" s="69" t="s">
         <v>2066</v>
@@ -22708,7 +22726,7 @@
         <v>2050</v>
       </c>
       <c r="C28" s="69" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="D28" s="69" t="s">
         <v>2051</v>
@@ -22730,7 +22748,7 @@
         <v>2607</v>
       </c>
       <c r="C29" s="69" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="D29" s="69" t="s">
         <v>2608</v>
@@ -31274,10 +31292,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -31322,7 +31340,7 @@
         <v>1292</v>
       </c>
       <c r="E3" s="19">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F3" s="17">
         <v>362</v>
@@ -31385,7 +31403,7 @@
         <v>1293</v>
       </c>
       <c r="E6" s="19">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F6" s="17">
         <v>2595</v>
@@ -31406,7 +31424,7 @@
         <v>1292</v>
       </c>
       <c r="E7" s="19">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F7" s="17">
         <v>3385</v>
@@ -31509,7 +31527,7 @@
         <v>1300</v>
       </c>
       <c r="E12" s="19">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F12" s="17">
         <v>2698</v>
@@ -31696,7 +31714,7 @@
         <v>1314</v>
       </c>
       <c r="E21" s="19">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="F21" s="17">
         <v>418</v>
@@ -32011,7 +32029,7 @@
         <v>2303</v>
       </c>
       <c r="E36" s="19">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="F36" s="17">
         <v>418</v>
@@ -32053,7 +32071,7 @@
         <v>2351</v>
       </c>
       <c r="E38" s="19">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F38" s="17">
         <v>395</v>
@@ -32238,7 +32256,7 @@
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47" s="17"/>
       <c r="G47" s="32"/>
@@ -32358,14 +32376,14 @@
         <v>2530</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="E54" s="19">
         <v>0</v>
       </c>
       <c r="F54" s="17"/>
       <c r="G54" s="32" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="H54" s="8" t="s">
         <v>2838</v>
@@ -32382,7 +32400,7 @@
         <v>2530</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="E55" s="19">
         <v>0</v>
@@ -32397,13 +32415,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>2530</v>
+        <v>3604</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="E56" s="19">
         <v>0</v>
@@ -32412,10 +32430,10 @@
         <v>50</v>
       </c>
       <c r="G56" s="32" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15.75">
@@ -32518,7 +32536,7 @@
         <v>2830</v>
       </c>
       <c r="E61" s="84">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F61" s="32">
         <v>2492</v>
@@ -32541,7 +32559,7 @@
         <v>2634</v>
       </c>
       <c r="E62" s="84">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F62" s="32">
         <v>228</v>
@@ -32562,16 +32580,16 @@
       </c>
       <c r="D63" s="32"/>
       <c r="E63" s="84">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="F63" s="32">
         <v>115</v>
       </c>
       <c r="G63" s="32" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.75">
@@ -33168,10 +33186,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -33188,7 +33206,7 @@
         <v>417</v>
       </c>
       <c r="C2" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D2" t="s">
         <v>293</v>
@@ -33208,7 +33226,7 @@
         <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D3" t="s">
         <v>2388</v>
@@ -33228,7 +33246,7 @@
         <v>831</v>
       </c>
       <c r="C4" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D4" t="s">
         <v>2389</v>
@@ -33248,7 +33266,7 @@
         <v>2392</v>
       </c>
       <c r="C5" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D5" t="s">
         <v>2390</v>
@@ -33268,7 +33286,7 @@
         <v>2391</v>
       </c>
       <c r="C6" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D6" t="s">
         <v>2243</v>
@@ -33288,7 +33306,7 @@
         <v>402</v>
       </c>
       <c r="C7" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D7" t="s">
         <v>2429</v>
@@ -33308,10 +33326,10 @@
         <v>834</v>
       </c>
       <c r="C8" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D8" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -33328,7 +33346,7 @@
         <v>2393</v>
       </c>
       <c r="C9" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D9" t="s">
         <v>2394</v>
@@ -33348,7 +33366,7 @@
         <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D10" t="s">
         <v>2395</v>
@@ -33368,7 +33386,7 @@
         <v>183</v>
       </c>
       <c r="C11" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D11" t="s">
         <v>2396</v>
@@ -33377,7 +33395,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -33388,7 +33406,7 @@
         <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D12" t="s">
         <v>2397</v>
@@ -33408,7 +33426,7 @@
         <v>186</v>
       </c>
       <c r="C13" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D13" t="s">
         <v>2398</v>
@@ -33428,7 +33446,7 @@
         <v>2399</v>
       </c>
       <c r="C14" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D14" t="s">
         <v>2400</v>
@@ -33448,7 +33466,7 @@
         <v>2401</v>
       </c>
       <c r="C15" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D15" t="s">
         <v>2447</v>
@@ -33468,7 +33486,7 @@
         <v>835</v>
       </c>
       <c r="C16" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D16" t="s">
         <v>2402</v>
@@ -33488,7 +33506,7 @@
         <v>641</v>
       </c>
       <c r="C17" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D17" t="s">
         <v>2403</v>
@@ -33508,10 +33526,10 @@
         <v>410</v>
       </c>
       <c r="C18" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D18" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="E18">
         <v>4</v>
@@ -33528,7 +33546,7 @@
         <v>640</v>
       </c>
       <c r="C19" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D19" t="s">
         <v>2404</v>
@@ -33548,7 +33566,7 @@
         <v>609</v>
       </c>
       <c r="C20" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D20" t="s">
         <v>2405</v>
@@ -33568,7 +33586,7 @@
         <v>525</v>
       </c>
       <c r="C21" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D21" t="s">
         <v>2598</v>
@@ -33588,7 +33606,7 @@
         <v>649</v>
       </c>
       <c r="C22" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D22" t="s">
         <v>2407</v>
@@ -33608,7 +33626,7 @@
         <v>2406</v>
       </c>
       <c r="C23" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D23" t="s">
         <v>2408</v>
@@ -33628,7 +33646,7 @@
         <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D24" t="s">
         <v>2409</v>
@@ -33648,7 +33666,7 @@
         <v>605</v>
       </c>
       <c r="C25" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D25" t="s">
         <v>2410</v>
@@ -33668,7 +33686,7 @@
         <v>403</v>
       </c>
       <c r="C26" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D26" t="s">
         <v>2411</v>
@@ -33688,7 +33706,7 @@
         <v>406</v>
       </c>
       <c r="C27" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D27" t="s">
         <v>318</v>
@@ -33708,7 +33726,7 @@
         <v>401</v>
       </c>
       <c r="C28" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D28" t="s">
         <v>2414</v>
@@ -33728,7 +33746,7 @@
         <v>638</v>
       </c>
       <c r="C29" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D29" t="s">
         <v>2412</v>
@@ -33748,7 +33766,7 @@
         <v>650</v>
       </c>
       <c r="C30" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D30" t="s">
         <v>2413</v>
@@ -33768,10 +33786,10 @@
         <v>832</v>
       </c>
       <c r="C31" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D31" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -33788,7 +33806,7 @@
         <v>185</v>
       </c>
       <c r="C32" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D32" t="s">
         <v>2415</v>
@@ -33797,7 +33815,7 @@
         <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -33808,7 +33826,7 @@
         <v>836</v>
       </c>
       <c r="C33" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D33" t="s">
         <v>2416</v>
@@ -33828,7 +33846,7 @@
         <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D34" t="s">
         <v>2417</v>
@@ -33848,7 +33866,7 @@
         <v>2418</v>
       </c>
       <c r="C35" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D35" t="s">
         <v>836</v>
@@ -33857,7 +33875,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -33868,7 +33886,7 @@
         <v>197</v>
       </c>
       <c r="C36" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D36" t="s">
         <v>2420</v>
@@ -33877,7 +33895,7 @@
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -33888,7 +33906,7 @@
         <v>198</v>
       </c>
       <c r="C37" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D37" t="s">
         <v>2421</v>
@@ -33908,7 +33926,7 @@
         <v>999</v>
       </c>
       <c r="C38" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D38" t="s">
         <v>2423</v>
@@ -33928,7 +33946,7 @@
         <v>2422</v>
       </c>
       <c r="C39" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D39" t="s">
         <v>2419</v>
@@ -33948,7 +33966,7 @@
         <v>2424</v>
       </c>
       <c r="C40" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D40" t="s">
         <v>2502</v>
@@ -33968,7 +33986,7 @@
         <v>683</v>
       </c>
       <c r="C41" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D41" t="s">
         <v>1747</v>
@@ -33988,7 +34006,7 @@
         <v>983</v>
       </c>
       <c r="C42" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D42" t="s">
         <v>2402</v>
@@ -34008,7 +34026,7 @@
         <v>652</v>
       </c>
       <c r="C43" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D43" t="s">
         <v>2425</v>
@@ -34028,7 +34046,7 @@
         <v>828</v>
       </c>
       <c r="C44" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D44" t="s">
         <v>2426</v>
@@ -34048,7 +34066,7 @@
         <v>2427</v>
       </c>
       <c r="C45" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D45" t="s">
         <v>779</v>
@@ -34068,7 +34086,7 @@
         <v>188</v>
       </c>
       <c r="C46" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D46" t="s">
         <v>2435</v>
@@ -34088,7 +34106,7 @@
         <v>187</v>
       </c>
       <c r="C47" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D47" t="s">
         <v>2436</v>
@@ -34108,10 +34126,10 @@
         <v>189</v>
       </c>
       <c r="C48" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D48" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="E48">
         <v>5</v>
@@ -34128,7 +34146,7 @@
         <v>2566</v>
       </c>
       <c r="C49" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D49" t="s">
         <v>2470</v>
@@ -34148,7 +34166,7 @@
         <v>2473</v>
       </c>
       <c r="C50" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D50" t="s">
         <v>2567</v>
@@ -34168,7 +34186,7 @@
         <v>2808</v>
       </c>
       <c r="C51" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D51" t="s">
         <v>2441</v>
@@ -34188,7 +34206,7 @@
         <v>684</v>
       </c>
       <c r="C52" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D52" t="s">
         <v>2568</v>
@@ -34208,10 +34226,10 @@
         <v>103</v>
       </c>
       <c r="C53" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D53" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="E53">
         <v>2</v>
@@ -34228,7 +34246,7 @@
         <v>653</v>
       </c>
       <c r="C54" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D54" t="s">
         <v>2493</v>
@@ -34248,7 +34266,7 @@
         <v>447</v>
       </c>
       <c r="C55" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D55" t="s">
         <v>2494</v>
@@ -34268,7 +34286,7 @@
         <v>2495</v>
       </c>
       <c r="C56" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D56" t="s">
         <v>2496</v>
@@ -34288,7 +34306,7 @@
         <v>2498</v>
       </c>
       <c r="C57" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D57" t="s">
         <v>2497</v>
@@ -34308,7 +34326,7 @@
         <v>438</v>
       </c>
       <c r="C58" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D58" t="s">
         <v>2504</v>
@@ -34317,7 +34335,7 @@
         <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -34328,7 +34346,7 @@
         <v>2503</v>
       </c>
       <c r="C59" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D59" t="s">
         <v>2505</v>
@@ -34348,7 +34366,7 @@
         <v>448</v>
       </c>
       <c r="C60" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D60" t="s">
         <v>2506</v>
@@ -34368,7 +34386,7 @@
         <v>639</v>
       </c>
       <c r="C61" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D61" t="s">
         <v>2525</v>
@@ -34388,7 +34406,7 @@
         <v>607</v>
       </c>
       <c r="C62" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -34402,7 +34420,7 @@
         <v>2930</v>
       </c>
       <c r="C63" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D63" t="s">
         <v>2931</v>
@@ -34422,10 +34440,10 @@
         <v>190</v>
       </c>
       <c r="C64" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D64" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -34439,13 +34457,13 @@
         <v>66</v>
       </c>
       <c r="B65" s="6" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C65" t="s">
+        <v>3524</v>
+      </c>
+      <c r="D65" t="s">
         <v>3016</v>
-      </c>
-      <c r="C65" t="s">
-        <v>3525</v>
-      </c>
-      <c r="D65" t="s">
-        <v>3017</v>
       </c>
       <c r="E65">
         <v>2</v>
@@ -34459,13 +34477,13 @@
         <v>67</v>
       </c>
       <c r="B66" s="6" t="s">
+        <v>3017</v>
+      </c>
+      <c r="C66" t="s">
+        <v>3524</v>
+      </c>
+      <c r="D66" t="s">
         <v>3018</v>
-      </c>
-      <c r="C66" t="s">
-        <v>3525</v>
-      </c>
-      <c r="D66" t="s">
-        <v>3019</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -34482,10 +34500,10 @@
         <v>442</v>
       </c>
       <c r="C67" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D67" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -34496,13 +34514,13 @@
         <v>69</v>
       </c>
       <c r="B68" s="6" t="s">
+        <v>3121</v>
+      </c>
+      <c r="C68" t="s">
+        <v>3524</v>
+      </c>
+      <c r="D68" t="s">
         <v>3122</v>
-      </c>
-      <c r="C68" t="s">
-        <v>3525</v>
-      </c>
-      <c r="D68" t="s">
-        <v>3123</v>
       </c>
       <c r="E68">
         <v>2</v>
@@ -34519,7 +34537,7 @@
         <v>430</v>
       </c>
       <c r="C69" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -34536,10 +34554,10 @@
         <v>100</v>
       </c>
       <c r="C70" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="D70" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -34550,13 +34568,13 @@
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="6" t="s">
+        <v>3556</v>
+      </c>
+      <c r="C71" t="s">
+        <v>3524</v>
+      </c>
+      <c r="D71" t="s">
         <v>3557</v>
-      </c>
-      <c r="C71" t="s">
-        <v>3525</v>
-      </c>
-      <c r="D71" t="s">
-        <v>3558</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -34583,10 +34601,10 @@
         <v>378</v>
       </c>
       <c r="C73" t="s">
+        <v>3525</v>
+      </c>
+      <c r="D73" t="s">
         <v>3526</v>
-      </c>
-      <c r="D73" t="s">
-        <v>3527</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -34603,10 +34621,10 @@
         <v>892</v>
       </c>
       <c r="C74" t="s">
+        <v>3527</v>
+      </c>
+      <c r="D74" t="s">
         <v>3528</v>
-      </c>
-      <c r="D74" t="s">
-        <v>3529</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -34623,10 +34641,10 @@
         <v>202</v>
       </c>
       <c r="C75" t="s">
+        <v>3529</v>
+      </c>
+      <c r="D75" t="s">
         <v>3530</v>
-      </c>
-      <c r="D75" t="s">
-        <v>3531</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -34643,10 +34661,10 @@
         <v>28</v>
       </c>
       <c r="C76" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="D76" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="E76">
         <v>2</v>
@@ -34663,10 +34681,10 @@
         <v>2628</v>
       </c>
       <c r="C77" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="D77" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -34680,7 +34698,7 @@
         <v>318026</v>
       </c>
       <c r="C78" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D78" t="s">
         <v>836</v>
@@ -34697,13 +34715,13 @@
         <v>79</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="C79" t="s">
+        <v>3534</v>
+      </c>
+      <c r="D79" t="s">
         <v>3535</v>
-      </c>
-      <c r="D79" t="s">
-        <v>3536</v>
       </c>
       <c r="E79">
         <v>2</v>
@@ -34720,10 +34738,10 @@
         <v>2855</v>
       </c>
       <c r="C80" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="D80" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="E80">
         <v>4</v>
@@ -34740,7 +34758,7 @@
         <v>2920</v>
       </c>
       <c r="C81" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D81" t="s">
         <v>1855</v>
@@ -34757,10 +34775,10 @@
         <v>82</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="C82" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D82" t="s">
         <v>683</v>
@@ -34790,10 +34808,10 @@
         <v>2623</v>
       </c>
       <c r="C84" t="s">
+        <v>3538</v>
+      </c>
+      <c r="D84" t="s">
         <v>3539</v>
-      </c>
-      <c r="D84" t="s">
-        <v>3540</v>
       </c>
       <c r="E84">
         <v>21</v>
@@ -34810,10 +34828,10 @@
         <v>963</v>
       </c>
       <c r="C85" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D85" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="E85">
         <v>1</v>
@@ -34830,10 +34848,10 @@
         <v>671</v>
       </c>
       <c r="C86" t="s">
+        <v>3541</v>
+      </c>
+      <c r="D86" t="s">
         <v>3542</v>
-      </c>
-      <c r="D86" t="s">
-        <v>3543</v>
       </c>
       <c r="E86">
         <v>10</v>
@@ -34850,7 +34868,7 @@
         <v>2826</v>
       </c>
       <c r="C87" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D87" t="s">
         <v>2417</v>
@@ -34867,10 +34885,10 @@
         <v>88</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C88" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="D88" t="s">
         <v>836</v>
@@ -34887,13 +34905,13 @@
         <v>89</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="C89" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="D89" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="E89">
         <v>9</v>
@@ -34907,13 +34925,13 @@
         <v>90</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="C90" t="s">
+        <v>3544</v>
+      </c>
+      <c r="D90" t="s">
         <v>3545</v>
-      </c>
-      <c r="D90" t="s">
-        <v>3546</v>
       </c>
       <c r="E90">
         <v>1</v>
@@ -34930,10 +34948,10 @@
         <v>8001</v>
       </c>
       <c r="C91" t="s">
+        <v>3546</v>
+      </c>
+      <c r="D91" t="s">
         <v>3547</v>
-      </c>
-      <c r="D91" t="s">
-        <v>3548</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -34944,13 +34962,13 @@
         <v>92</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="C92" t="s">
+        <v>3548</v>
+      </c>
+      <c r="D92" t="s">
         <v>3549</v>
-      </c>
-      <c r="D92" t="s">
-        <v>3550</v>
       </c>
       <c r="E92">
         <v>10</v>
@@ -34964,13 +34982,13 @@
         <v>93</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="C93" t="s">
+        <v>3550</v>
+      </c>
+      <c r="D93" t="s">
         <v>3551</v>
-      </c>
-      <c r="D93" t="s">
-        <v>3552</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -34987,7 +35005,7 @@
         <v>689</v>
       </c>
       <c r="C94" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -35001,7 +35019,7 @@
         <v>663</v>
       </c>
       <c r="C95" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="E95">
         <v>6</v>
@@ -35018,7 +35036,7 @@
         <v>821</v>
       </c>
       <c r="C96" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="E96">
         <v>6</v>
@@ -35035,10 +35053,10 @@
         <v>2569</v>
       </c>
       <c r="C97" t="s">
+        <v>3552</v>
+      </c>
+      <c r="D97" t="s">
         <v>3553</v>
-      </c>
-      <c r="D97" t="s">
-        <v>3554</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -35049,10 +35067,10 @@
     </row>
     <row r="98" spans="1:6">
       <c r="B98" s="6" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="C98" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
     </row>
   </sheetData>
@@ -35520,7 +35538,7 @@
     </row>
     <row r="28" spans="2:11">
       <c r="B28" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -35940,10 +35958,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -36634,7 +36652,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>2616</v>
@@ -37931,7 +37949,7 @@
         <v>1329</v>
       </c>
       <c r="E106" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F106" s="9"/>
       <c r="G106" t="s">
@@ -38776,7 +38794,7 @@
         <v>574</v>
       </c>
       <c r="E147" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F147" s="9"/>
       <c r="G147" t="s">
@@ -39001,7 +39019,7 @@
         <v>4</v>
       </c>
       <c r="F158" s="9" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="G158" t="s">
         <v>1485</v>
@@ -39526,7 +39544,7 @@
         <v>1150</v>
       </c>
       <c r="E184" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F184" s="9"/>
     </row>
@@ -39623,7 +39641,7 @@
         <v>1180</v>
       </c>
       <c r="E189" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F189" s="9"/>
       <c r="G189" t="s">
@@ -39999,7 +40017,7 @@
         <v>1397</v>
       </c>
       <c r="E207" s="10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F207" s="9"/>
       <c r="G207" t="s">
@@ -40046,7 +40064,7 @@
         <v>3</v>
       </c>
       <c r="F209" s="9" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -41215,7 +41233,7 @@
         <v>5544</v>
       </c>
       <c r="E269" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>2647</v>
@@ -41368,10 +41386,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -41429,7 +41447,7 @@
       </c>
       <c r="D4" s="38"/>
       <c r="E4" s="35">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F4" s="33">
         <v>1233</v>
@@ -41480,13 +41498,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>847</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="E7" s="35">
         <v>0</v>
@@ -41514,13 +41532,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
+        <v>3144</v>
+      </c>
+      <c r="C9" s="33" t="s">
         <v>3145</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="D9" s="41" t="s">
         <v>3146</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>3147</v>
       </c>
       <c r="E9" s="35">
         <v>0</v>
@@ -41532,13 +41550,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
+        <v>3147</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>3145</v>
+      </c>
+      <c r="D10" s="41" t="s">
         <v>3148</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>3146</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>3149</v>
       </c>
       <c r="E10" s="35">
         <v>0</v>
@@ -41550,13 +41568,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>1895</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="E11" s="35">
         <v>0</v>
@@ -41571,13 +41589,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>1895</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="E12" s="35">
         <v>0</v>
@@ -41592,13 +41610,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="C13" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="E13" s="35">
         <v>0</v>
@@ -41619,7 +41637,7 @@
         <v>1863</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="E14" s="35">
         <v>0</v>
@@ -41634,13 +41652,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="E15" s="35">
         <v>0</v>
@@ -41652,13 +41670,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="C16" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="E16" s="44">
         <v>1</v>
@@ -41674,7 +41692,7 @@
       </c>
       <c r="C17" s="42"/>
       <c r="D17" s="43" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="E17" s="35">
         <v>0</v>
@@ -41692,7 +41710,7 @@
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="43" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="E18" s="44">
         <v>0</v>
@@ -41704,13 +41722,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="C19" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="E19" s="44">
         <v>0</v>
@@ -41725,13 +41743,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="C20" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="E20" s="35">
         <v>0</v>
@@ -41746,13 +41764,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="C21" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="E21" s="44">
         <v>0</v>
@@ -41771,7 +41789,7 @@
       </c>
       <c r="C22" s="42"/>
       <c r="D22" s="43" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="E22" s="44">
         <v>2</v>
@@ -41788,13 +41806,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="C23" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="E23" s="44">
         <v>0</v>
@@ -41809,13 +41827,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="C24" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="E24" s="35">
         <v>0</v>
@@ -41831,7 +41849,7 @@
       </c>
       <c r="C25" s="42"/>
       <c r="D25" s="43" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="E25" s="35">
         <v>0</v>
@@ -41843,13 +41861,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="C26" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="E26" s="44">
         <v>1</v>
@@ -41861,13 +41879,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="42" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="C27" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="E27" s="44">
         <v>0</v>
@@ -41881,13 +41899,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="C28" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="E28" s="44">
         <v>1</v>
@@ -41899,13 +41917,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="C29" s="33" t="s">
         <v>1895</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="E29" s="44">
         <v>0</v>
@@ -41920,13 +41938,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="42" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="C30" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="E30" s="35">
         <v>0</v>
@@ -41940,13 +41958,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="C31" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="E31" s="44">
         <v>0</v>
@@ -41958,13 +41976,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="42" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="C32" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D32" s="43" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="E32" s="44">
         <v>0</v>
@@ -41976,19 +41994,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="42" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="C33" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="E33" s="44">
         <v>1</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="38.25">
@@ -41996,13 +42014,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="42" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="C34" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D34" s="43" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="E34" s="44">
         <v>1</v>
@@ -42016,13 +42034,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="42" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="C35" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D35" s="43" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="E35" s="35">
         <v>0</v>
@@ -42034,13 +42052,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="42" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="C36" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="E36" s="44">
         <v>0</v>
@@ -42052,13 +42070,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="42" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="C37" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="E37" s="44">
         <v>0</v>
@@ -42070,13 +42088,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="42" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="C38" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="E38" s="35">
         <v>0</v>
@@ -42088,13 +42106,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="42" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="C39" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="E39" s="35">
         <v>0</v>
@@ -42110,7 +42128,7 @@
       </c>
       <c r="C40" s="42"/>
       <c r="D40" s="43" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="E40" s="35">
         <v>0</v>
@@ -42122,13 +42140,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="42" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="C41" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="E41" s="44">
         <v>2</v>
@@ -42137,7 +42155,7 @@
         <v>1914</v>
       </c>
       <c r="H41" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="38.25">
@@ -42145,13 +42163,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="42" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="C42" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="E42" s="35">
         <v>0</v>
@@ -42163,13 +42181,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="42" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="C43" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="E43" s="44">
         <v>0</v>
@@ -42181,13 +42199,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="42" t="s">
+        <v>3210</v>
+      </c>
+      <c r="C44" s="42" t="s">
         <v>3211</v>
       </c>
-      <c r="C44" s="42" t="s">
-        <v>3212</v>
-      </c>
       <c r="D44" s="43" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="E44" s="35">
         <v>0</v>
@@ -42199,13 +42217,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="42" t="s">
+        <v>3212</v>
+      </c>
+      <c r="C45" s="42" t="s">
         <v>3213</v>
       </c>
-      <c r="C45" s="42" t="s">
-        <v>3214</v>
-      </c>
       <c r="D45" s="43" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="E45" s="44">
         <v>0</v>
@@ -42217,13 +42235,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="C46" s="42" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="E46" s="44">
         <v>0</v>
@@ -42235,13 +42253,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="42" t="s">
+        <v>3215</v>
+      </c>
+      <c r="C47" s="42" t="s">
         <v>3216</v>
       </c>
-      <c r="C47" s="42" t="s">
-        <v>3217</v>
-      </c>
       <c r="D47" s="43" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="E47" s="44">
         <v>0</v>
@@ -42253,13 +42271,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="42" t="s">
+        <v>3217</v>
+      </c>
+      <c r="C48" s="42" t="s">
         <v>3218</v>
       </c>
-      <c r="C48" s="42" t="s">
-        <v>3219</v>
-      </c>
       <c r="D48" s="43" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="E48" s="35">
         <v>0</v>
@@ -42271,13 +42289,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="42" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="C49" s="42" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E49" s="35">
         <v>0</v>
@@ -42289,7 +42307,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="C50" s="33" t="s">
         <v>1895</v>
@@ -42307,7 +42325,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="C51" s="33" t="s">
         <v>1895</v>
@@ -42325,7 +42343,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="33" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="C52" s="48" t="s">
         <v>1895</v>
@@ -42343,7 +42361,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="C53" s="48" t="s">
         <v>1895</v>
@@ -42363,7 +42381,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="C54" s="48" t="s">
         <v>1895</v>
@@ -42383,10 +42401,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="33" t="s">
+        <v>3225</v>
+      </c>
+      <c r="C55" s="48" t="s">
         <v>3226</v>
-      </c>
-      <c r="C55" s="48" t="s">
-        <v>3227</v>
       </c>
       <c r="D55" s="38" t="s">
         <v>2680</v>
@@ -42403,10 +42421,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="C56" s="48" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="D56" s="38" t="s">
         <v>2681</v>
@@ -42423,10 +42441,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="33" t="s">
+        <v>3228</v>
+      </c>
+      <c r="C57" s="48" t="s">
         <v>3229</v>
-      </c>
-      <c r="C57" s="48" t="s">
-        <v>3230</v>
       </c>
       <c r="D57" s="38" t="s">
         <v>2905</v>
@@ -42441,10 +42459,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="33" t="s">
+        <v>3230</v>
+      </c>
+      <c r="C58" s="48" t="s">
         <v>3231</v>
-      </c>
-      <c r="C58" s="48" t="s">
-        <v>3232</v>
       </c>
       <c r="D58" s="38" t="s">
         <v>2682</v>
@@ -42461,10 +42479,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="C59" s="48" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="D59" s="38" t="s">
         <v>2681</v>
@@ -42481,10 +42499,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="C60" s="48" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="D60" s="38" t="s">
         <v>2906</v>
@@ -42499,7 +42517,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="C61" s="33" t="s">
         <v>1895</v>
@@ -43361,7 +43379,7 @@
       <c r="C112" s="33"/>
       <c r="D112" s="38"/>
       <c r="E112" s="35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F112" s="33" t="s">
         <v>2647</v>
@@ -43449,7 +43467,7 @@
       </c>
       <c r="D117" s="38"/>
       <c r="E117" s="35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F117" s="33"/>
       <c r="H117" t="s">
@@ -43558,10 +43576,10 @@
         <v>1663</v>
       </c>
       <c r="C124" s="33" t="s">
+        <v>3234</v>
+      </c>
+      <c r="D124" s="38" t="s">
         <v>3235</v>
-      </c>
-      <c r="D124" s="38" t="s">
-        <v>3236</v>
       </c>
       <c r="E124" s="35">
         <v>2</v>
@@ -45032,10 +45050,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -45052,10 +45070,10 @@
         <v>1709</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="D2" s="51" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="E2" s="35">
         <v>0</v>
@@ -45088,7 +45106,7 @@
         <v>1762</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="D4" s="33" t="s">
         <v>1763</v>
@@ -45180,7 +45198,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1438</v>
@@ -45196,10 +45214,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
+        <v>3239</v>
+      </c>
+      <c r="C10" s="33" t="s">
         <v>3240</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>3241</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="35">
@@ -45212,10 +45230,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
+        <v>3241</v>
+      </c>
+      <c r="C11" s="33" t="s">
         <v>3242</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>3243</v>
       </c>
       <c r="D11" s="33"/>
       <c r="E11" s="35">
@@ -45228,10 +45246,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
+        <v>3243</v>
+      </c>
+      <c r="C12" s="33" t="s">
         <v>3244</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>3245</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="35">
@@ -45244,10 +45262,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
+        <v>3245</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>3246</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>3247</v>
       </c>
       <c r="D13" s="33"/>
       <c r="E13" s="35">
@@ -45260,10 +45278,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
+        <v>3247</v>
+      </c>
+      <c r="C14" s="33" t="s">
         <v>3248</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>3249</v>
       </c>
       <c r="D14" s="33" t="s">
         <v>177</v>
@@ -45278,10 +45296,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="33" t="s">
+        <v>3249</v>
+      </c>
+      <c r="C15" s="33" t="s">
         <v>3250</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>3251</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="35">
@@ -45294,10 +45312,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="33" t="s">
+        <v>3251</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>3252</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>3253</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="35">
@@ -45310,10 +45328,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="33" t="s">
+        <v>3253</v>
+      </c>
+      <c r="C17" s="33" t="s">
         <v>3254</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>3255</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="35">
@@ -45326,10 +45344,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="33" t="s">
+        <v>3255</v>
+      </c>
+      <c r="C18" s="33" t="s">
         <v>3256</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>3257</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="35">
@@ -45342,10 +45360,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="33" t="s">
+        <v>3257</v>
+      </c>
+      <c r="C19" s="33" t="s">
         <v>3258</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>3259</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="35">
@@ -45358,10 +45376,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="33" t="s">
+        <v>3259</v>
+      </c>
+      <c r="C20" s="33" t="s">
         <v>3260</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>3261</v>
       </c>
       <c r="D20" s="33"/>
       <c r="E20" s="35">
@@ -45374,10 +45392,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
+        <v>3261</v>
+      </c>
+      <c r="C21" s="33" t="s">
         <v>3262</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>3263</v>
       </c>
       <c r="D21" s="33"/>
       <c r="E21" s="35">
@@ -45390,10 +45408,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="35">
@@ -45406,10 +45424,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="35">
@@ -45422,10 +45440,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
+        <v>3265</v>
+      </c>
+      <c r="C24" s="33" t="s">
         <v>3266</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>3267</v>
       </c>
       <c r="D24" s="33"/>
       <c r="E24" s="35">
@@ -45438,10 +45456,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
+        <v>3267</v>
+      </c>
+      <c r="C25" s="33" t="s">
         <v>3268</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>3269</v>
       </c>
       <c r="D25" s="33"/>
       <c r="E25" s="35">
@@ -45454,10 +45472,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
+        <v>3269</v>
+      </c>
+      <c r="C26" s="33" t="s">
         <v>3270</v>
-      </c>
-      <c r="C26" s="33" t="s">
-        <v>3271</v>
       </c>
       <c r="D26" s="33"/>
       <c r="E26" s="35">
@@ -45470,10 +45488,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
+        <v>3271</v>
+      </c>
+      <c r="C27" s="33" t="s">
         <v>3272</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>3273</v>
       </c>
       <c r="D27" s="33"/>
       <c r="E27" s="35">
@@ -45486,10 +45504,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
+        <v>3273</v>
+      </c>
+      <c r="C28" s="33" t="s">
         <v>3274</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>3275</v>
       </c>
       <c r="D28" s="33"/>
       <c r="E28" s="35">
@@ -45853,7 +45871,7 @@
       </c>
       <c r="D50" s="33"/>
       <c r="E50" s="35">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F50" s="33"/>
     </row>
@@ -45876,10 +45894,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="33" t="s">
+        <v>3275</v>
+      </c>
+      <c r="C52" s="33" t="s">
         <v>3276</v>
-      </c>
-      <c r="C52" s="33" t="s">
-        <v>3277</v>
       </c>
       <c r="D52" s="33"/>
       <c r="E52" s="35">
@@ -47712,7 +47730,7 @@
       </c>
       <c r="D165" s="33"/>
       <c r="E165" s="35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F165" s="33"/>
     </row>
@@ -47893,13 +47911,13 @@
         <v>176</v>
       </c>
       <c r="B177" s="33" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="C177" s="33" t="s">
         <v>1075</v>
       </c>
       <c r="D177" s="33" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="E177" s="35">
         <v>7</v>
@@ -47998,7 +48016,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="33" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="C183" s="33" t="s">
         <v>1077</v>
@@ -48976,7 +48994,7 @@
         <v>1772</v>
       </c>
       <c r="C241" s="33" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="D241" s="33" t="s">
         <v>1569</v>
@@ -49302,7 +49320,7 @@
         <v>1169</v>
       </c>
       <c r="C260" s="33" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="D260" s="33" t="s">
         <v>1170</v>
@@ -49439,12 +49457,12 @@
         <v>267</v>
       </c>
       <c r="B268" s="33" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="C268" s="33"/>
       <c r="D268" s="33"/>
       <c r="E268" s="35">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F268" s="33"/>
     </row>
@@ -49766,7 +49784,7 @@
       </c>
       <c r="D288" s="33"/>
       <c r="E288" s="35">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F288" s="33"/>
     </row>
@@ -50358,10 +50376,10 @@
         <v>1207</v>
       </c>
       <c r="D322" s="33" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="E322" s="35">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F322" s="33" t="s">
         <v>2928</v>
@@ -50378,7 +50396,7 @@
         <v>1207</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="E323" s="35">
         <v>36</v>
@@ -50424,13 +50442,13 @@
         <v>325</v>
       </c>
       <c r="B326" s="33" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="C326" s="33" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="D326" s="33" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="E326" s="35">
         <v>0</v>
@@ -50444,7 +50462,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="33" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="C327" s="33" t="s">
         <v>2250</v>
@@ -50462,7 +50480,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="33" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="C328" s="33" t="s">
         <v>2253</v>
@@ -50482,7 +50500,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="33" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="C329" s="33" t="s">
         <v>2253</v>
@@ -50502,10 +50520,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="33" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="C330" s="33" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="D330" s="33" t="s">
         <v>1747</v>
@@ -50522,7 +50540,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="33" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="C331" s="33" t="s">
         <v>2279</v>
@@ -50540,7 +50558,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="33" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="C332" s="33" t="s">
         <v>2292</v>
@@ -50560,7 +50578,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="33" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="C333" s="33" t="s">
         <v>2293</v>
@@ -50580,7 +50598,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="33" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="C334" s="33"/>
       <c r="D334" s="33"/>
@@ -50594,7 +50612,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="33" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="C335" s="33" t="s">
         <v>2292</v>
@@ -50632,7 +50650,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="33" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="C337" s="33" t="s">
         <v>2292</v>
@@ -50650,13 +50668,13 @@
         <v>337</v>
       </c>
       <c r="B338" s="33" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="C338" s="33" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D338" s="33" t="s">
         <v>3315</v>
-      </c>
-      <c r="D338" s="33" t="s">
-        <v>3316</v>
       </c>
       <c r="E338" s="35">
         <v>1</v>
@@ -50670,7 +50688,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="33" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="C339" s="33" t="s">
         <v>2602</v>
@@ -50688,13 +50706,13 @@
         <v>339</v>
       </c>
       <c r="B340" s="52" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="C340" s="33" t="s">
         <v>2692</v>
       </c>
       <c r="D340" s="33" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="E340" s="35">
         <v>6</v>
@@ -50708,7 +50726,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="33" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="C341" s="33" t="s">
         <v>2298</v>
@@ -50724,7 +50742,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="33" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="C342" s="33" t="s">
         <v>2614</v>
@@ -50742,7 +50760,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="33" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="C343" s="33"/>
       <c r="D343" s="33"/>
@@ -50756,13 +50774,13 @@
         <v>343</v>
       </c>
       <c r="B344" s="33" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="C344" s="33" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D344" s="33" t="s">
         <v>3318</v>
-      </c>
-      <c r="D344" s="33" t="s">
-        <v>3319</v>
       </c>
       <c r="E344" s="35">
         <v>1</v>
@@ -50776,7 +50794,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="33" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="C345" s="33" t="s">
         <v>2614</v>
@@ -50794,7 +50812,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="33" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="C346" s="33" t="s">
         <v>2614</v>
@@ -50812,7 +50830,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="33" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="C347" s="33" t="s">
         <v>2614</v>
@@ -50830,7 +50848,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="33" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="C348" s="33" t="s">
         <v>2692</v>
@@ -50846,7 +50864,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="33" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="C349" s="33" t="s">
         <v>2692</v>
@@ -50864,7 +50882,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="33" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="C350" s="33" t="s">
         <v>2751</v>
@@ -50918,7 +50936,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="33" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="C353" s="33"/>
       <c r="D353" s="33"/>
@@ -50982,7 +51000,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="53" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="C357" s="53" t="s">
         <v>2856</v>
@@ -50998,7 +51016,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="33" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="C358" s="53" t="s">
         <v>2865</v>
@@ -51016,7 +51034,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="33" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="C359" s="53" t="s">
         <v>2890</v>
@@ -51034,7 +51052,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="33" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="C360" s="33" t="s">
         <v>2943</v>
@@ -51053,7 +51071,7 @@
         <v>2954</v>
       </c>
       <c r="C361" s="33" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="D361" s="33" t="s">
         <v>1855</v>
@@ -51068,7 +51086,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="33" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="C362" s="33" t="s">
         <v>2614</v>
@@ -51230,14 +51248,14 @@
         <v>370</v>
       </c>
       <c r="B371" s="33" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="C371" s="33" t="s">
         <v>2292</v>
       </c>
       <c r="D371" s="33"/>
       <c r="E371" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F371" s="33">
         <v>3867</v>
@@ -51248,10 +51266,10 @@
         <v>371</v>
       </c>
       <c r="B372" s="33" t="s">
+        <v>3040</v>
+      </c>
+      <c r="C372" s="33" t="s">
         <v>3041</v>
-      </c>
-      <c r="C372" s="33" t="s">
-        <v>3042</v>
       </c>
       <c r="D372" s="33"/>
       <c r="E372" s="35">
@@ -51266,7 +51284,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="33" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="C373" s="33" t="s">
         <v>257</v>
@@ -51284,10 +51302,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="33" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="C374" s="33" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="D374" s="33" t="s">
         <v>1747</v>
@@ -51304,7 +51322,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="33" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="C375" s="33" t="s">
         <v>2923</v>
@@ -51322,7 +51340,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="33" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="C376" s="33" t="s">
         <v>2923</v>
@@ -51337,16 +51355,27 @@
     </row>
     <row r="377" spans="1:6">
       <c r="B377" s="34" t="s">
+        <v>3582</v>
+      </c>
+      <c r="C377" s="89" t="s">
         <v>3583</v>
-      </c>
-      <c r="C377" s="89" t="s">
-        <v>3584</v>
       </c>
       <c r="E377" s="1">
         <v>5</v>
       </c>
       <c r="F377" s="89">
         <v>1750</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="B378" s="34" t="s">
+        <v>3603</v>
+      </c>
+      <c r="E378" s="1">
+        <v>4</v>
+      </c>
+      <c r="F378" s="89">
+        <v>520</v>
       </c>
     </row>
     <row r="461" spans="2:5">
@@ -51509,10 +51538,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -51798,7 +51827,7 @@
         <v>2716</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="56">
@@ -51863,7 +51892,7 @@
         <v>5</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="G22" t="s">
         <v>2700</v>
@@ -51881,7 +51910,7 @@
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" s="35">
         <v>584</v>
@@ -52091,7 +52120,7 @@
       </c>
       <c r="C35" s="33"/>
       <c r="D35" s="33" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="E35" s="56">
         <v>0</v>
@@ -52454,7 +52483,7 @@
         <v>2694</v>
       </c>
       <c r="E57" s="56">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F57" s="35">
         <v>2075</v>
@@ -52474,10 +52503,10 @@
         <v>2697</v>
       </c>
       <c r="E58" s="56">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="F58" s="35" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -52887,7 +52916,7 @@
         <v>482201</v>
       </c>
       <c r="E82" s="56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F82" s="35">
         <v>1260</v>
@@ -53034,10 +53063,10 @@
         <v>741</v>
       </c>
       <c r="C90" s="33" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D90" s="33" t="s">
         <v>3324</v>
-      </c>
-      <c r="D90" s="33" t="s">
-        <v>3325</v>
       </c>
       <c r="E90" s="56">
         <v>1</v>
@@ -53060,7 +53089,7 @@
         <v>2704</v>
       </c>
       <c r="E91" s="56">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="F91" s="35">
         <v>855</v>
@@ -53074,10 +53103,10 @@
         <v>743</v>
       </c>
       <c r="C92" s="33" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D92" s="33" t="s">
         <v>3326</v>
-      </c>
-      <c r="D92" s="33" t="s">
-        <v>3327</v>
       </c>
       <c r="E92" s="56">
         <v>10</v>
@@ -53155,7 +53184,7 @@
         <v>3</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -53186,7 +53215,7 @@
         <v>2700</v>
       </c>
       <c r="E98" s="56">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F98" s="56">
         <v>1320</v>
@@ -53212,7 +53241,7 @@
         <v>11</v>
       </c>
       <c r="F99" s="35" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -53323,10 +53352,10 @@
       </c>
       <c r="D106" s="33"/>
       <c r="E106" s="56">
-        <v>9</v>
-      </c>
-      <c r="F106" s="35">
-        <v>1330</v>
+        <v>21</v>
+      </c>
+      <c r="F106" s="35" t="s">
+        <v>3598</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -53338,7 +53367,7 @@
       </c>
       <c r="C107" s="33"/>
       <c r="D107" s="33" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="E107" s="56">
         <v>7</v>
@@ -53395,7 +53424,7 @@
         <v>2700</v>
       </c>
       <c r="E110" s="56">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F110" s="35">
         <v>986</v>
@@ -53429,7 +53458,7 @@
         <v>2701</v>
       </c>
       <c r="E112" s="56">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F112" s="35" t="s">
         <v>2992</v>
@@ -53771,7 +53800,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="35" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -53806,10 +53835,10 @@
         <v>2703</v>
       </c>
       <c r="E133" s="56">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F133" s="35" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -53826,7 +53855,7 @@
         <v>2700</v>
       </c>
       <c r="E134" s="56">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F134" s="35">
         <v>1507</v>
@@ -53869,10 +53898,10 @@
         <v>518894</v>
       </c>
       <c r="E136" s="56">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="F136" s="35" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -53907,7 +53936,7 @@
         <v>1859</v>
       </c>
       <c r="D138" s="33" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="E138" s="56">
         <v>8</v>
@@ -54068,7 +54097,7 @@
         <v>2696</v>
       </c>
       <c r="E147" s="56">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F147" s="35">
         <v>554</v>
@@ -54128,7 +54157,7 @@
         <v>2699</v>
       </c>
       <c r="E150" s="56">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="F150" s="35">
         <v>893</v>
@@ -54151,7 +54180,7 @@
         <v>6</v>
       </c>
       <c r="F151" s="35" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -54162,10 +54191,10 @@
         <v>794</v>
       </c>
       <c r="C152" s="33" t="s">
+        <v>3329</v>
+      </c>
+      <c r="D152" s="33" t="s">
         <v>3330</v>
-      </c>
-      <c r="D152" s="33" t="s">
-        <v>3331</v>
       </c>
       <c r="E152" s="56">
         <v>0</v>
@@ -54338,13 +54367,13 @@
         <v>586</v>
       </c>
       <c r="D161" s="33" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="E161" s="56">
         <v>6</v>
       </c>
       <c r="F161" s="35" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -54817,7 +54846,7 @@
         <v>9</v>
       </c>
       <c r="F186" s="35" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -54841,14 +54870,14 @@
         <v>187</v>
       </c>
       <c r="B188" s="33" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="C188" s="33" t="s">
         <v>268</v>
       </c>
       <c r="D188" s="33"/>
       <c r="E188" s="56">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F188" s="35">
         <v>1457</v>
@@ -54904,7 +54933,7 @@
         <v>2700</v>
       </c>
       <c r="E191" s="56">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F191" s="35">
         <v>1106</v>
@@ -55013,7 +55042,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="33" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="C197" s="33" t="s">
         <v>1546</v>
@@ -55052,10 +55081,10 @@
         <v>1713</v>
       </c>
       <c r="C199" s="33" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D199" s="33" t="s">
         <v>3333</v>
-      </c>
-      <c r="D199" s="33" t="s">
-        <v>3334</v>
       </c>
       <c r="E199" s="56">
         <v>12</v>
@@ -55078,7 +55107,7 @@
         <v>2694</v>
       </c>
       <c r="E200" s="56">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F200" s="35">
         <v>1399</v>
@@ -55089,7 +55118,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="33" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="C201" s="33"/>
       <c r="D201" s="33"/>
@@ -55189,7 +55218,7 @@
         <v>13</v>
       </c>
       <c r="F206" s="35" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -55209,7 +55238,7 @@
         <v>42</v>
       </c>
       <c r="F207" s="35" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -55433,12 +55462,14 @@
       <c r="B220" s="33" t="s">
         <v>2670</v>
       </c>
-      <c r="C220" s="33"/>
+      <c r="C220" s="33" t="s">
+        <v>268</v>
+      </c>
       <c r="D220" s="33" t="s">
         <v>2700</v>
       </c>
       <c r="E220" s="56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220" s="35">
         <v>2866</v>
@@ -55624,7 +55655,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="33" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="C231" s="33"/>
       <c r="D231" s="33"/>
@@ -55632,7 +55663,7 @@
         <v>4</v>
       </c>
       <c r="F231" s="35" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="333" spans="2:5">
@@ -57189,10 +57220,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -57227,7 +57258,7 @@
       </c>
       <c r="D3" s="33"/>
       <c r="E3" s="33">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F3" s="35">
         <v>161</v>
@@ -57245,7 +57276,7 @@
       </c>
       <c r="D4" s="33"/>
       <c r="E4" s="33">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F4" s="35">
         <v>146</v>
@@ -57327,7 +57358,7 @@
     <row r="9" spans="1:10">
       <c r="A9" s="33"/>
       <c r="B9" s="33" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1210</v>
@@ -57352,7 +57383,7 @@
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="F10" s="35">
         <v>193</v>
@@ -57384,11 +57415,11 @@
         <v>2222</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33">
-        <v>432</v>
+        <v>398</v>
       </c>
       <c r="F12" s="35">
         <v>184</v>
@@ -57420,10 +57451,10 @@
         <v>1212</v>
       </c>
       <c r="C14" s="33" t="s">
+        <v>3334</v>
+      </c>
+      <c r="D14" s="33" t="s">
         <v>3335</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>3336</v>
       </c>
       <c r="E14" s="42">
         <v>6</v>
@@ -57441,13 +57472,13 @@
         <v>1213</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="E15" s="42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" s="35" t="s">
         <v>2763</v>
@@ -57465,7 +57496,7 @@
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F16" s="35">
         <v>400</v>
@@ -57483,7 +57514,7 @@
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F17" s="35">
         <v>396</v>
@@ -57501,7 +57532,7 @@
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" s="35">
         <v>1301</v>
@@ -57515,7 +57546,7 @@
         <v>1216</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="33">
@@ -57551,10 +57582,10 @@
         <v>2508</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="E21" s="33">
         <v>5</v>
@@ -57571,7 +57602,7 @@
         <v>1450</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="33">
@@ -57609,7 +57640,7 @@
       </c>
       <c r="D24" s="33"/>
       <c r="E24" s="33">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="F24" s="35">
         <v>51</v>
@@ -57657,10 +57688,10 @@
         <v>2678</v>
       </c>
       <c r="C27" s="33" t="s">
+        <v>3342</v>
+      </c>
+      <c r="D27" s="33" t="s">
         <v>3343</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>3344</v>
       </c>
       <c r="E27" s="53">
         <v>9</v>
@@ -57677,10 +57708,10 @@
         <v>2052</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="E28" s="60">
         <v>52</v>
@@ -57697,10 +57728,10 @@
         <v>2103</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="E29" s="60">
         <v>42</v>
@@ -57717,10 +57748,10 @@
         <v>2575</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="E30" s="60">
         <v>56</v>
@@ -57737,10 +57768,10 @@
         <v>2053</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="E31" s="60">
         <v>20</v>
@@ -57757,10 +57788,10 @@
         <v>2684</v>
       </c>
       <c r="C32" s="33" t="s">
+        <v>3348</v>
+      </c>
+      <c r="D32" s="33" t="s">
         <v>3349</v>
-      </c>
-      <c r="D32" s="33" t="s">
-        <v>3350</v>
       </c>
       <c r="E32" s="60">
         <v>4</v>
@@ -57798,7 +57829,7 @@
         <v>2142</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="E34" s="60">
         <v>28</v>
@@ -57815,7 +57846,7 @@
         <v>2442</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="D35" s="33">
         <v>239</v>
@@ -57835,10 +57866,10 @@
         <v>2661</v>
       </c>
       <c r="C36" s="33" t="s">
+        <v>3352</v>
+      </c>
+      <c r="D36" s="33" t="s">
         <v>3353</v>
-      </c>
-      <c r="D36" s="33" t="s">
-        <v>3354</v>
       </c>
       <c r="E36" s="33">
         <v>5</v>
@@ -57855,10 +57886,10 @@
         <v>2853</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="D37" s="33" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="E37" s="33">
         <v>1</v>
@@ -57900,7 +57931,7 @@
         <v>4</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -57978,7 +58009,7 @@
         <v>15</v>
       </c>
       <c r="F43" s="35" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -58004,13 +58035,13 @@
         <v>45</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="E45" s="60">
         <v>95</v>
@@ -58024,11 +58055,11 @@
         <v>46</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C46" s="33"/>
       <c r="D46" s="33" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="E46" s="60">
         <v>2</v>
@@ -58042,11 +58073,11 @@
         <v>47</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="C47" s="33"/>
       <c r="D47" s="33" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="E47" s="60">
         <v>0</v>
@@ -58058,7 +58089,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="C48" s="33"/>
       <c r="D48" s="33"/>
@@ -58131,7 +58162,7 @@
         <v>1223</v>
       </c>
       <c r="D52" s="33" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="E52" s="42">
         <v>32</v>
@@ -58188,7 +58219,7 @@
       </c>
       <c r="D55" s="33"/>
       <c r="E55" s="33">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F55" s="35">
         <v>260</v>
@@ -58205,7 +58236,7 @@
         <v>2378</v>
       </c>
       <c r="D56" s="33" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="E56" s="42">
         <v>8</v>
@@ -58477,10 +58508,10 @@
         <v>2378</v>
       </c>
       <c r="D72" s="33" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="E72" s="42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F72" s="35">
         <v>415</v>
@@ -58497,7 +58528,7 @@
         <v>1223</v>
       </c>
       <c r="D73" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="E73" s="42">
         <v>3</v>
@@ -58518,7 +58549,7 @@
       </c>
       <c r="D74" s="33"/>
       <c r="E74" s="33">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="F74" s="35">
         <v>239</v>
@@ -58536,7 +58567,7 @@
       </c>
       <c r="D75" s="33"/>
       <c r="E75" s="42">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F75" s="35">
         <v>124</v>
@@ -58554,7 +58585,7 @@
       </c>
       <c r="D76" s="33"/>
       <c r="E76" s="33">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F76" s="35">
         <v>253</v>
@@ -58600,13 +58631,13 @@
         <v>1255</v>
       </c>
       <c r="C79" s="33" t="s">
+        <v>3363</v>
+      </c>
+      <c r="D79" s="33" t="s">
         <v>3364</v>
       </c>
-      <c r="D79" s="33" t="s">
-        <v>3365</v>
-      </c>
       <c r="E79" s="33">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F79" s="35">
         <v>537</v>
@@ -58655,7 +58686,7 @@
         <v>2378</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="E82" s="33">
         <v>4</v>
@@ -58672,13 +58703,13 @@
         <v>1259</v>
       </c>
       <c r="C83" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D83" s="33" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="E83" s="33">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F83" s="35">
         <v>286</v>
@@ -58692,10 +58723,10 @@
         <v>2748</v>
       </c>
       <c r="C84" s="33" t="s">
+        <v>3367</v>
+      </c>
+      <c r="D84" s="33" t="s">
         <v>3368</v>
-      </c>
-      <c r="D84" s="33" t="s">
-        <v>3369</v>
       </c>
       <c r="E84" s="33">
         <v>0</v>
@@ -58712,13 +58743,13 @@
         <v>1260</v>
       </c>
       <c r="C85" s="33" t="s">
+        <v>3369</v>
+      </c>
+      <c r="D85" s="33" t="s">
         <v>3370</v>
       </c>
-      <c r="D85" s="33" t="s">
-        <v>3371</v>
-      </c>
       <c r="E85" s="33">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F85" s="33">
         <v>330</v>
@@ -58735,7 +58766,7 @@
         <v>2378</v>
       </c>
       <c r="D86" s="33" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="E86" s="33">
         <v>0</v>
@@ -58844,10 +58875,10 @@
         <v>19644</v>
       </c>
       <c r="E92" s="33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F92" s="61" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -58861,7 +58892,7 @@
         <v>1223</v>
       </c>
       <c r="D93" s="33" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="E93" s="33">
         <v>3</v>
@@ -58881,7 +58912,7 @@
       </c>
       <c r="D94" s="33"/>
       <c r="E94" s="33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F94" s="35">
         <v>288</v>
@@ -58908,13 +58939,13 @@
         <v>99</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="C96" s="33" t="s">
         <v>1223</v>
       </c>
       <c r="D96" s="33" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="E96" s="33">
         <v>0</v>
@@ -58973,7 +59004,7 @@
         <v>1843</v>
       </c>
       <c r="E99" s="33">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F99" s="33">
         <v>372</v>
@@ -58993,7 +59024,7 @@
         <v>240</v>
       </c>
       <c r="E100" s="33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F100" s="35">
         <v>407</v>
@@ -59025,10 +59056,10 @@
         <v>2173</v>
       </c>
       <c r="C102" s="33" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="D102" s="33" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="E102" s="33">
         <v>13</v>
@@ -59045,10 +59076,10 @@
         <v>2208</v>
       </c>
       <c r="C103" s="33" t="s">
+        <v>3373</v>
+      </c>
+      <c r="D103" s="33" t="s">
         <v>3374</v>
-      </c>
-      <c r="D103" s="33" t="s">
-        <v>3375</v>
       </c>
       <c r="E103" s="60">
         <v>5</v>
@@ -59065,13 +59096,13 @@
         <v>2079</v>
       </c>
       <c r="C104" s="33" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="D104" s="33" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="E104" s="60">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F104" s="35">
         <v>396</v>
@@ -59085,7 +59116,7 @@
         <v>1969</v>
       </c>
       <c r="C105" s="33" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="D105" s="33" t="s">
         <v>1517</v>
@@ -59126,10 +59157,10 @@
         <v>2477</v>
       </c>
       <c r="D107" s="33" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="E107" s="33">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F107" s="35">
         <v>247</v>
@@ -59199,7 +59230,7 @@
       </c>
       <c r="D111" s="33"/>
       <c r="E111" s="33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F111" s="35">
         <v>746</v>
@@ -59236,7 +59267,7 @@
         <v>2171</v>
       </c>
       <c r="D113" s="33" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="E113" s="33">
         <v>3</v>
@@ -59323,7 +59354,7 @@
         <v>2940</v>
       </c>
       <c r="C118" s="33" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="D118" s="33" t="s">
         <v>1569</v>
@@ -59377,7 +59408,7 @@
       </c>
       <c r="D121" s="33"/>
       <c r="E121" s="33">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F121" s="35">
         <v>197</v>
@@ -59412,7 +59443,7 @@
         <v>1276</v>
       </c>
       <c r="D123" s="57" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="E123" s="33">
         <v>3</v>
@@ -59452,10 +59483,10 @@
         <v>1280</v>
       </c>
       <c r="C125" s="33" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="D125" s="42" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="E125" s="33">
         <v>0</v>
@@ -59483,7 +59514,7 @@
     <row r="127" spans="1:8">
       <c r="A127" s="33"/>
       <c r="B127" s="33" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="C127" s="33" t="s">
         <v>1276</v>
@@ -59560,10 +59591,10 @@
         <v>2235</v>
       </c>
       <c r="C131" s="33" t="s">
+        <v>3378</v>
+      </c>
+      <c r="D131" s="33" t="s">
         <v>3379</v>
-      </c>
-      <c r="D131" s="33" t="s">
-        <v>3380</v>
       </c>
       <c r="E131" s="33">
         <v>0</v>
@@ -59596,10 +59627,10 @@
         <v>1404</v>
       </c>
       <c r="C133" s="33" t="s">
+        <v>3380</v>
+      </c>
+      <c r="D133" s="33" t="s">
         <v>3381</v>
-      </c>
-      <c r="D133" s="33" t="s">
-        <v>3382</v>
       </c>
       <c r="E133" s="33">
         <v>0</v>
@@ -59619,10 +59650,10 @@
         <v>1276</v>
       </c>
       <c r="D134" s="33" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="E134" s="33">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F134" s="35">
         <v>1400</v>
@@ -59658,7 +59689,7 @@
       </c>
       <c r="D136" s="33"/>
       <c r="E136" s="33">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F136" s="33">
         <v>210</v>
@@ -59672,10 +59703,10 @@
         <v>2864</v>
       </c>
       <c r="C137" s="33" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="D137" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="E137" s="33">
         <v>11</v>
@@ -59755,7 +59786,7 @@
         <v>1276</v>
       </c>
       <c r="D141" s="33" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="E141" s="35">
         <v>4</v>
@@ -59779,7 +59810,7 @@
         <v>1855</v>
       </c>
       <c r="E142" s="35">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F142" s="33">
         <v>371</v>
@@ -59846,7 +59877,7 @@
         <v>1276</v>
       </c>
       <c r="D146" s="33" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="E146" s="33">
         <v>0</v>
@@ -59893,10 +59924,10 @@
         <v>2735</v>
       </c>
       <c r="C149" s="33" t="s">
+        <v>3383</v>
+      </c>
+      <c r="D149" s="33" t="s">
         <v>3384</v>
-      </c>
-      <c r="D149" s="33" t="s">
-        <v>3385</v>
       </c>
       <c r="E149" s="33">
         <v>1</v>
@@ -59913,10 +59944,10 @@
         <v>2736</v>
       </c>
       <c r="C150" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D150" s="33" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="E150" s="33">
         <v>1</v>
@@ -60029,7 +60060,7 @@
         <v>175</v>
       </c>
       <c r="B157" s="95" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="C157" s="95"/>
       <c r="D157" s="95"/>
@@ -60044,7 +60075,7 @@
         <v>2016</v>
       </c>
       <c r="C158" s="33" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D158" s="33" t="s">
         <v>836</v>
@@ -60064,13 +60095,13 @@
         <v>1811</v>
       </c>
       <c r="C159" s="33" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="D159" s="33" t="s">
         <v>1855</v>
       </c>
       <c r="E159" s="33">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="F159" s="35">
         <v>234</v>
@@ -60084,7 +60115,7 @@
         <v>2102</v>
       </c>
       <c r="C160" s="33" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="D160" s="33" t="s">
         <v>2419</v>
@@ -60104,10 +60135,10 @@
         <v>2376</v>
       </c>
       <c r="C161" s="57" t="s">
+        <v>3394</v>
+      </c>
+      <c r="D161" s="57" t="s">
         <v>3395</v>
-      </c>
-      <c r="D161" s="57" t="s">
-        <v>3396</v>
       </c>
       <c r="E161" s="33">
         <v>41</v>
@@ -60124,13 +60155,13 @@
         <v>1997</v>
       </c>
       <c r="C162" s="33" t="s">
+        <v>3396</v>
+      </c>
+      <c r="D162" s="33" t="s">
         <v>3397</v>
       </c>
-      <c r="D162" s="33" t="s">
-        <v>3398</v>
-      </c>
       <c r="E162" s="33">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="F162" s="35">
         <v>686</v>
@@ -60144,10 +60175,10 @@
         <v>2258</v>
       </c>
       <c r="C163" s="33" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="D163" s="33" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="E163" s="60">
         <v>22</v>
@@ -60164,10 +60195,10 @@
         <v>2363</v>
       </c>
       <c r="C164" s="33" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="D164" s="33" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="E164" s="60">
         <v>4</v>
@@ -60184,10 +60215,10 @@
         <v>1996</v>
       </c>
       <c r="C165" s="33" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="D165" s="33" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="E165" s="33">
         <v>5</v>
@@ -60204,7 +60235,7 @@
         <v>1998</v>
       </c>
       <c r="C166" s="33" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="D166" s="33" t="s">
         <v>2549</v>
@@ -60224,10 +60255,10 @@
         <v>1221</v>
       </c>
       <c r="C167" s="33" t="s">
+        <v>3401</v>
+      </c>
+      <c r="D167" s="33" t="s">
         <v>3402</v>
-      </c>
-      <c r="D167" s="33" t="s">
-        <v>3403</v>
       </c>
       <c r="E167" s="33">
         <v>14</v>
@@ -60244,10 +60275,10 @@
         <v>1938</v>
       </c>
       <c r="C168" s="33" t="s">
+        <v>3403</v>
+      </c>
+      <c r="D168" s="33" t="s">
         <v>3404</v>
-      </c>
-      <c r="D168" s="33" t="s">
-        <v>3405</v>
       </c>
       <c r="E168" s="33">
         <v>16</v>
@@ -60264,10 +60295,10 @@
         <v>2336</v>
       </c>
       <c r="C169" s="33" t="s">
+        <v>3405</v>
+      </c>
+      <c r="D169" s="33" t="s">
         <v>3406</v>
-      </c>
-      <c r="D169" s="33" t="s">
-        <v>3407</v>
       </c>
       <c r="E169" s="33">
         <v>2</v>
@@ -60284,10 +60315,10 @@
         <v>2322</v>
       </c>
       <c r="C170" s="33" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="D170" s="33" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="E170" s="33">
         <v>6</v>
@@ -60304,10 +60335,10 @@
         <v>2480</v>
       </c>
       <c r="C171" s="33" t="s">
+        <v>3408</v>
+      </c>
+      <c r="D171" s="33" t="s">
         <v>3409</v>
-      </c>
-      <c r="D171" s="33" t="s">
-        <v>3410</v>
       </c>
       <c r="E171" s="33">
         <v>60</v>
@@ -60324,13 +60355,13 @@
         <v>2484</v>
       </c>
       <c r="C172" s="33" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="D172" s="33" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="E172" s="33">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F172" s="35">
         <v>759</v>
@@ -60344,13 +60375,13 @@
         <v>2483</v>
       </c>
       <c r="C173" s="33" t="s">
+        <v>3411</v>
+      </c>
+      <c r="D173" s="33" t="s">
         <v>3412</v>
       </c>
-      <c r="D173" s="33" t="s">
-        <v>3413</v>
-      </c>
       <c r="E173" s="33">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F173" s="35">
         <v>605</v>
@@ -60364,7 +60395,7 @@
         <v>2335</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="D174" s="33" t="s">
         <v>2525</v>
@@ -60384,10 +60415,10 @@
         <v>2642</v>
       </c>
       <c r="C175" s="33" t="s">
+        <v>3413</v>
+      </c>
+      <c r="D175" s="33" t="s">
         <v>3414</v>
-      </c>
-      <c r="D175" s="33" t="s">
-        <v>3415</v>
       </c>
       <c r="E175" s="33">
         <v>20</v>
@@ -60404,10 +60435,10 @@
         <v>2739</v>
       </c>
       <c r="C176" s="33" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="D176" s="33" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="E176" s="33">
         <v>3</v>
@@ -60424,10 +60455,10 @@
         <v>2644</v>
       </c>
       <c r="C177" s="33" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="D177" s="33" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="E177" s="33">
         <v>62</v>
@@ -60462,10 +60493,10 @@
         <v>2741</v>
       </c>
       <c r="C179" s="33" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="D179" s="33" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="E179" s="33">
         <v>17</v>
@@ -60479,7 +60510,7 @@
         <v>203</v>
       </c>
       <c r="B180" s="95" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="C180" s="95"/>
       <c r="D180" s="95"/>
@@ -60494,10 +60525,10 @@
         <v>1251</v>
       </c>
       <c r="C181" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D181" s="33" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="E181" s="33">
         <v>0</v>
@@ -60514,7 +60545,7 @@
         <v>1252</v>
       </c>
       <c r="C182" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D182" s="33" t="s">
         <v>290</v>
@@ -60534,13 +60565,13 @@
         <v>1261</v>
       </c>
       <c r="C183" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D183" s="33" t="s">
         <v>318</v>
       </c>
       <c r="E183" s="33">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F183" s="35">
         <v>186</v>
@@ -60554,10 +60585,10 @@
         <v>1542</v>
       </c>
       <c r="C184" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="E184" s="33">
         <v>18</v>
@@ -60574,10 +60605,10 @@
         <v>1262</v>
       </c>
       <c r="C185" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D185" s="33" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="E185" s="33">
         <v>21</v>
@@ -60594,7 +60625,7 @@
         <v>1263</v>
       </c>
       <c r="C186" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D186" s="33" t="s">
         <v>2419</v>
@@ -60614,7 +60645,7 @@
         <v>1265</v>
       </c>
       <c r="C187" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D187" s="33" t="s">
         <v>2243</v>
@@ -60634,10 +60665,10 @@
         <v>1266</v>
       </c>
       <c r="C188" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D188" s="33" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="E188" s="33">
         <v>62</v>
@@ -60654,16 +60685,16 @@
         <v>1267</v>
       </c>
       <c r="C189" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D189" s="33" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="E189" s="33">
-        <v>25</v>
-      </c>
-      <c r="F189" s="33" t="s">
-        <v>3014</v>
+        <v>120</v>
+      </c>
+      <c r="F189" s="33">
+        <v>210</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -60674,16 +60705,16 @@
         <v>1539</v>
       </c>
       <c r="C190" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D190" s="33" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="E190" s="33">
         <v>39</v>
       </c>
       <c r="F190" s="35" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -60694,10 +60725,10 @@
         <v>1886</v>
       </c>
       <c r="C191" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D191" s="33" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="E191" s="33">
         <v>27</v>
@@ -60714,7 +60745,7 @@
         <v>1270</v>
       </c>
       <c r="C192" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D192" s="33"/>
       <c r="E192" s="33">
@@ -60732,13 +60763,13 @@
         <v>1775</v>
       </c>
       <c r="C193" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D193" s="33" t="s">
         <v>2795</v>
       </c>
       <c r="E193" s="42">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F193" s="35">
         <v>170</v>
@@ -60752,13 +60783,13 @@
         <v>1697</v>
       </c>
       <c r="C194" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D194" s="33" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="E194" s="42">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F194" s="35" t="s">
         <v>2997</v>
@@ -60772,7 +60803,7 @@
         <v>1426</v>
       </c>
       <c r="C195" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D195" s="33" t="s">
         <v>1856</v>
@@ -60790,10 +60821,10 @@
         <v>1268</v>
       </c>
       <c r="C196" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D196" s="33" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="E196" s="33">
         <v>13</v>
@@ -60810,10 +60841,10 @@
         <v>1269</v>
       </c>
       <c r="C197" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D197" s="33" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="E197" s="33">
         <v>0</v>
@@ -60830,10 +60861,10 @@
         <v>2786</v>
       </c>
       <c r="C198" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D198" s="33" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="E198" s="33">
         <v>22</v>
@@ -60850,10 +60881,10 @@
         <v>1999</v>
       </c>
       <c r="C199" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D199" s="33" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="E199" s="33">
         <v>131</v>
@@ -60870,7 +60901,7 @@
         <v>2354</v>
       </c>
       <c r="C200" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D200" s="33" t="s">
         <v>2435</v>
@@ -60890,10 +60921,10 @@
         <v>2337</v>
       </c>
       <c r="C201" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D201" s="33" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="E201" s="33">
         <v>30</v>
@@ -60910,10 +60941,10 @@
         <v>2323</v>
       </c>
       <c r="C202" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D202" s="33" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="E202" s="33">
         <v>10</v>
@@ -60930,10 +60961,10 @@
         <v>2324</v>
       </c>
       <c r="C203" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D203" s="33" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="E203" s="33">
         <v>3</v>
@@ -60950,10 +60981,10 @@
         <v>2326</v>
       </c>
       <c r="C204" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D204" s="33" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="E204" s="33">
         <v>6</v>
@@ -60965,13 +60996,13 @@
     <row r="205" spans="1:6">
       <c r="A205" s="33"/>
       <c r="B205" s="33" t="s">
+        <v>3572</v>
+      </c>
+      <c r="C205" s="33" t="s">
+        <v>3363</v>
+      </c>
+      <c r="D205" s="33" t="s">
         <v>3573</v>
-      </c>
-      <c r="C205" s="33" t="s">
-        <v>3364</v>
-      </c>
-      <c r="D205" s="33" t="s">
-        <v>3574</v>
       </c>
       <c r="E205" s="33">
         <v>6</v>
@@ -60988,10 +61019,10 @@
         <v>2327</v>
       </c>
       <c r="C206" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D206" s="33" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="E206" s="33">
         <v>16</v>
@@ -61008,7 +61039,7 @@
         <v>2555</v>
       </c>
       <c r="C207" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D207" s="33" t="s">
         <v>2405</v>
@@ -61028,10 +61059,10 @@
         <v>2475</v>
       </c>
       <c r="C208" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D208" s="33" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="E208" s="33">
         <v>17</v>
@@ -61048,10 +61079,10 @@
         <v>2486</v>
       </c>
       <c r="C209" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D209" s="33" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="E209" s="33">
         <v>114</v>
@@ -61068,7 +61099,7 @@
         <v>2236</v>
       </c>
       <c r="C210" s="33" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D210" s="33" t="s">
         <v>2834</v>
@@ -61083,7 +61114,7 @@
         <v>237</v>
       </c>
       <c r="B211" s="95" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="C211" s="95"/>
       <c r="D211" s="95"/>
@@ -61098,7 +61129,7 @@
         <v>1967</v>
       </c>
       <c r="C212" s="33" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="D212" s="33" t="s">
         <v>836</v>
@@ -61118,10 +61149,10 @@
         <v>2364</v>
       </c>
       <c r="C213" s="33" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="D213" s="33" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="E213" s="33">
         <v>30</v>
@@ -61138,10 +61169,10 @@
         <v>2308</v>
       </c>
       <c r="C214" s="33" t="s">
+        <v>3437</v>
+      </c>
+      <c r="D214" s="33" t="s">
         <v>3438</v>
-      </c>
-      <c r="D214" s="33" t="s">
-        <v>3439</v>
       </c>
       <c r="E214" s="33">
         <v>18</v>
@@ -61158,10 +61189,10 @@
         <v>2309</v>
       </c>
       <c r="C215" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D215" s="33" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="E215" s="33">
         <v>10</v>
@@ -61178,10 +61209,10 @@
         <v>2310</v>
       </c>
       <c r="C216" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D216" s="33" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="E216" s="33">
         <v>24</v>
@@ -61198,10 +61229,10 @@
         <v>2311</v>
       </c>
       <c r="C217" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D217" s="33" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="E217" s="33">
         <v>17</v>
@@ -61218,7 +61249,7 @@
         <v>2312</v>
       </c>
       <c r="C218" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D218" s="33" t="s">
         <v>2389</v>
@@ -61238,10 +61269,10 @@
         <v>2313</v>
       </c>
       <c r="C219" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D219" s="33" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="E219" s="33">
         <v>9</v>
@@ -61258,10 +61289,10 @@
         <v>2466</v>
       </c>
       <c r="C220" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D220" s="33" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="E220" s="33">
         <v>17</v>
@@ -61278,7 +61309,7 @@
         <v>2314</v>
       </c>
       <c r="C221" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D221" s="33" t="s">
         <v>2402</v>
@@ -61298,10 +61329,10 @@
         <v>2355</v>
       </c>
       <c r="C222" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D222" s="33" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="E222" s="33">
         <v>12</v>
@@ -61318,10 +61349,10 @@
         <v>2315</v>
       </c>
       <c r="C223" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D223" s="33" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="E223" s="33">
         <v>22</v>
@@ -61338,10 +61369,10 @@
         <v>2316</v>
       </c>
       <c r="C224" s="33" t="s">
+        <v>3445</v>
+      </c>
+      <c r="D224" s="33" t="s">
         <v>3446</v>
-      </c>
-      <c r="D224" s="33" t="s">
-        <v>3447</v>
       </c>
       <c r="E224" s="33">
         <v>12</v>
@@ -61358,10 +61389,10 @@
         <v>2911</v>
       </c>
       <c r="C225" s="33" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="D225" s="33" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="E225" s="33">
         <v>6</v>
@@ -61378,10 +61409,10 @@
         <v>2317</v>
       </c>
       <c r="C226" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D226" s="33" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="E226" s="33">
         <v>24</v>
@@ -61398,10 +61429,10 @@
         <v>2318</v>
       </c>
       <c r="C227" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D227" s="33" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="E227" s="33">
         <v>31</v>
@@ -61418,10 +61449,10 @@
         <v>2319</v>
       </c>
       <c r="C228" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D228" s="33" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="E228" s="33">
         <v>0</v>
@@ -61438,10 +61469,10 @@
         <v>2320</v>
       </c>
       <c r="C229" s="33" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="D229" s="33" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="E229" s="33">
         <v>17</v>
@@ -61458,10 +61489,10 @@
         <v>2321</v>
       </c>
       <c r="C230" s="33" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="D230" s="33" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="E230" s="33">
         <v>32</v>
@@ -61478,10 +61509,10 @@
         <v>2330</v>
       </c>
       <c r="C231" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D231" s="33" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="E231" s="33">
         <v>7</v>
@@ -61498,10 +61529,10 @@
         <v>1679</v>
       </c>
       <c r="C232" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D232" s="33" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="E232" s="33">
         <v>27</v>
@@ -61518,10 +61549,10 @@
         <v>2342</v>
       </c>
       <c r="C233" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D233" s="33" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="E233" s="33">
         <v>12</v>
@@ -61538,10 +61569,10 @@
         <v>2362</v>
       </c>
       <c r="C234" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D234" s="33" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="E234" s="33">
         <v>29</v>
@@ -61558,10 +61589,10 @@
         <v>2343</v>
       </c>
       <c r="C235" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D235" s="33" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="E235" s="33">
         <v>48</v>
@@ -61578,10 +61609,10 @@
         <v>2344</v>
       </c>
       <c r="C236" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D236" s="33" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="E236" s="33">
         <v>36</v>
@@ -61598,10 +61629,10 @@
         <v>2356</v>
       </c>
       <c r="C237" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D237" s="33" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="E237" s="33">
         <v>26</v>
@@ -61621,7 +61652,7 @@
         <v>2976</v>
       </c>
       <c r="D238" s="33" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="E238" s="33">
         <v>22</v>
@@ -61638,10 +61669,10 @@
         <v>2485</v>
       </c>
       <c r="C239" s="33" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="D239" s="33" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="E239" s="33">
         <v>13</v>
@@ -61658,10 +61689,10 @@
         <v>2924</v>
       </c>
       <c r="C240" s="33" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="D240" s="33" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="E240" s="33">
         <v>7</v>
@@ -61678,10 +61709,10 @@
         <v>2531</v>
       </c>
       <c r="C241" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D241" s="33" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="E241" s="33">
         <v>20</v>
@@ -61698,7 +61729,7 @@
         <v>2650</v>
       </c>
       <c r="C242" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D242" s="33" t="s">
         <v>2435</v>
@@ -61718,7 +61749,7 @@
         <v>2732</v>
       </c>
       <c r="C243" s="33" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="D243" s="33" t="s">
         <v>2420</v>
@@ -61738,10 +61769,10 @@
         <v>2733</v>
       </c>
       <c r="C244" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D244" s="33" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="E244" s="33">
         <v>4</v>
@@ -61758,10 +61789,10 @@
         <v>2734</v>
       </c>
       <c r="C245" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="E245" s="33">
         <v>4</v>
@@ -61778,10 +61809,10 @@
         <v>2737</v>
       </c>
       <c r="C246" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="E246" s="33">
         <v>63</v>
@@ -61798,10 +61829,10 @@
         <v>2738</v>
       </c>
       <c r="C247" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D247" s="33" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="E247" s="33">
         <v>10</v>
@@ -61818,10 +61849,10 @@
         <v>2740</v>
       </c>
       <c r="C248" s="33" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D248" s="33" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="E248" s="33">
         <v>6</v>
@@ -61979,7 +62010,7 @@
         <v>2861</v>
       </c>
       <c r="D256" s="33" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="E256" s="33">
         <v>27</v>
@@ -62031,13 +62062,13 @@
         <v>288</v>
       </c>
       <c r="B259" s="33" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="C259" s="33" t="s">
         <v>2976</v>
       </c>
       <c r="D259" s="33" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="E259" s="33">
         <v>4</v>
@@ -62051,13 +62082,13 @@
         <v>289</v>
       </c>
       <c r="B260" s="33" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="C260" s="33" t="s">
         <v>2976</v>
       </c>
       <c r="D260" s="33" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="E260" s="33">
         <v>22</v>
@@ -62071,13 +62102,13 @@
         <v>290</v>
       </c>
       <c r="B261" s="33" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="C261" s="33" t="s">
         <v>2976</v>
       </c>
       <c r="D261" s="33" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="E261" s="33">
         <v>3</v>
@@ -62091,13 +62122,13 @@
         <v>291</v>
       </c>
       <c r="B262" s="33" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C262" s="33" t="s">
         <v>2976</v>
       </c>
       <c r="D262" s="33" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="E262" s="33">
         <v>0</v>
@@ -62111,13 +62142,13 @@
         <v>292</v>
       </c>
       <c r="B263" s="33" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="C263" s="33" t="s">
         <v>2976</v>
       </c>
       <c r="D263" s="33" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="E263" s="33">
         <v>1</v>
@@ -62131,13 +62162,13 @@
         <v>293</v>
       </c>
       <c r="B264" s="33" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="C264" s="33" t="s">
         <v>2976</v>
       </c>
       <c r="D264" s="33" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="E264" s="33">
         <v>13</v>
@@ -62151,13 +62182,13 @@
         <v>294</v>
       </c>
       <c r="B265" s="33" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C265" s="33" t="s">
         <v>2976</v>
       </c>
       <c r="D265" s="33" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="E265" s="33">
         <v>5</v>
@@ -62169,13 +62200,13 @@
     <row r="266" spans="1:7">
       <c r="A266" s="33"/>
       <c r="B266" s="33" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="C266" s="33" t="s">
         <v>2976</v>
       </c>
       <c r="D266" s="33" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="E266" s="33">
         <v>17</v>
@@ -62197,7 +62228,7 @@
         <v>299</v>
       </c>
       <c r="B268" s="95" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="C268" s="95"/>
       <c r="D268" s="95"/>
@@ -62215,7 +62246,7 @@
         <v>2377</v>
       </c>
       <c r="D269" s="33" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="E269" s="33">
         <v>9</v>
@@ -62278,10 +62309,10 @@
         <v>2377</v>
       </c>
       <c r="D272" s="33" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="E272" s="33">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F272" s="33">
         <v>299</v>
@@ -62298,7 +62329,7 @@
         <v>2377</v>
       </c>
       <c r="D273" s="33" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="E273" s="33">
         <v>13</v>
@@ -62318,7 +62349,7 @@
         <v>2377</v>
       </c>
       <c r="D274" s="33" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="E274" s="33">
         <v>7</v>
@@ -62338,7 +62369,7 @@
         <v>2377</v>
       </c>
       <c r="D275" s="33" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="E275" s="33">
         <v>18</v>
@@ -62358,7 +62389,7 @@
         <v>2377</v>
       </c>
       <c r="D276" s="33" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="E276" s="33">
         <v>10</v>
@@ -62378,7 +62409,7 @@
         <v>2377</v>
       </c>
       <c r="D277" s="33" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="E277" s="33">
         <v>5</v>
@@ -62458,7 +62489,7 @@
         <v>2377</v>
       </c>
       <c r="D281" s="33" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="E281" s="33">
         <v>27</v>
@@ -62561,7 +62592,7 @@
         <v>2999</v>
       </c>
       <c r="E286" s="33">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F286" s="35">
         <v>345</v>
@@ -62592,13 +62623,13 @@
         <v>321</v>
       </c>
       <c r="B288" s="33" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="C288" s="33" t="s">
         <v>2377</v>
       </c>
       <c r="D288" s="33" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="E288" s="33">
         <v>5</v>
@@ -62612,13 +62643,13 @@
         <v>322</v>
       </c>
       <c r="B289" s="33" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="C289" s="33" t="s">
         <v>2377</v>
       </c>
       <c r="D289" s="33" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="E289" s="33">
         <v>9</v>
@@ -62632,7 +62663,7 @@
         <v>323</v>
       </c>
       <c r="B290" s="33" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="C290" s="33" t="s">
         <v>2377</v>
@@ -62652,7 +62683,7 @@
         <v>324</v>
       </c>
       <c r="B291" s="33" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C291" s="33" t="s">
         <v>2377</v>
@@ -62668,7 +62699,7 @@
         <v>325</v>
       </c>
       <c r="B292" s="33" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="C292" s="33" t="s">
         <v>2377</v>
@@ -62723,10 +62754,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -63624,7 +63655,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -63787,7 +63818,7 @@
         <v>1939</v>
       </c>
       <c r="E59" s="62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" s="4">
         <v>2470</v>
@@ -63827,7 +63858,7 @@
         <v>344</v>
       </c>
       <c r="E61" s="62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="4">
         <v>2214</v>
@@ -63966,7 +63997,7 @@
     <row r="69" spans="1:8">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -64258,10 +64289,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -64304,7 +64335,7 @@
         <v>290</v>
       </c>
       <c r="E3" s="35">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F3" s="33">
         <v>1465</v>
@@ -64546,7 +64577,7 @@
         <v>2501</v>
       </c>
       <c r="E16" s="35">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F16" s="33">
         <v>182</v>
@@ -64569,7 +64600,7 @@
         <v>48</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -64602,7 +64633,7 @@
         <v>2958</v>
       </c>
       <c r="E19" s="35">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F19" s="33">
         <v>338</v>
@@ -64639,7 +64670,7 @@
         <v>1903</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="E21" s="35">
         <v>78</v>
@@ -64693,7 +64724,7 @@
         <v>49</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="C24" s="33" t="s">
         <v>296</v>
@@ -64736,7 +64767,7 @@
         <v>300</v>
       </c>
       <c r="E26" s="35">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F26" s="33">
         <v>350</v>
@@ -64831,7 +64862,7 @@
         <v>66</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
@@ -64929,13 +64960,13 @@
         <v>82</v>
       </c>
       <c r="B38" s="33" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="E38" s="35">
         <v>10</v>
@@ -64949,10 +64980,10 @@
         <v>83</v>
       </c>
       <c r="B39" s="33" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="D39" s="33" t="s">
         <v>3013</v>
@@ -64969,13 +65000,13 @@
         <v>84</v>
       </c>
       <c r="B40" s="33" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="C40" s="33" t="s">
+        <v>3129</v>
+      </c>
+      <c r="D40" s="33" t="s">
         <v>3130</v>
-      </c>
-      <c r="D40" s="33" t="s">
-        <v>3131</v>
       </c>
       <c r="E40" s="35">
         <v>65</v>
@@ -64989,7 +65020,7 @@
         <v>85</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="C41" s="33"/>
       <c r="D41" s="33"/>
@@ -65003,13 +65034,13 @@
         <v>86</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="E42" s="35">
         <v>10</v>
@@ -65023,7 +65054,7 @@
         <v>87</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="C43" s="33"/>
       <c r="D43" s="33"/>
@@ -65067,10 +65098,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3141</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3142</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3143</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -65102,10 +65133,10 @@
         <v>410</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="E3" s="35">
         <v>0</v>
@@ -65140,7 +65171,7 @@
         <v>412</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="D5" s="33"/>
       <c r="E5" s="35">
@@ -65268,7 +65299,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="35">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F12" s="33">
         <v>155</v>
@@ -65289,7 +65320,7 @@
       </c>
       <c r="D13" s="33"/>
       <c r="E13" s="35">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F13" s="33">
         <v>195</v>
@@ -65437,7 +65468,7 @@
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="35">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="F22" s="33">
         <v>79</v>
@@ -65458,7 +65489,7 @@
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="35">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="F23" s="33">
         <v>105</v>
@@ -65472,13 +65503,13 @@
         <v>430</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="D24" s="33" t="s">
         <v>3005</v>
       </c>
       <c r="E24" s="35">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F24" s="33">
         <v>262</v>
@@ -65492,7 +65523,7 @@
         <v>431</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="D25" s="33" t="s">
         <v>432</v>
@@ -65510,11 +65541,11 @@
         <v>433</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="D26" s="33"/>
       <c r="E26" s="35">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="F26" s="33">
         <v>18</v>
@@ -65544,7 +65575,7 @@
         <v>434</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="D28" s="33"/>
       <c r="E28" s="35">
@@ -65560,7 +65591,7 @@
         <v>435</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="D29" s="33"/>
       <c r="E29" s="35">
@@ -65578,7 +65609,7 @@
         <v>436</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="D30" s="33"/>
       <c r="E30" s="35">
@@ -65596,7 +65627,7 @@
         <v>1552</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="D31" s="33"/>
       <c r="E31" s="35">
@@ -65646,7 +65677,7 @@
         <v>437</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="D34" s="33"/>
       <c r="E34" s="35">
@@ -65664,7 +65695,7 @@
         <v>438</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="D35" s="33"/>
       <c r="E35" s="35">
@@ -65929,7 +65960,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="96" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="C50" s="96"/>
       <c r="D50" s="96"/>

--- a/backend/public/BOSCH_STOCK1.xlsx
+++ b/backend/public/BOSCH_STOCK1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730" firstSheet="10" activeTab="12"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="730"/>
   </bookViews>
   <sheets>
     <sheet name="ELEMENT" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5819" uniqueCount="3605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5822" uniqueCount="3608">
   <si>
     <t>0 433 175 443</t>
   </si>
@@ -8564,9 +8564,6 @@
     <t>870/888</t>
   </si>
   <si>
-    <t>NET- 1360</t>
-  </si>
-  <si>
     <t>F 002 H24 667</t>
   </si>
   <si>
@@ -10965,6 +10962,18 @@
   </si>
   <si>
     <t>DOT 3</t>
+  </si>
+  <si>
+    <t>828/763</t>
+  </si>
+  <si>
+    <t>1199/1105</t>
+  </si>
+  <si>
+    <t>1245/1147</t>
+  </si>
+  <si>
+    <t>NET- 1400</t>
   </si>
 </sst>
 </file>
@@ -12260,10 +12269,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -12280,7 +12289,7 @@
         <v>197</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="19">
@@ -12301,7 +12310,7 @@
         <v>1354</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="19">
@@ -12320,7 +12329,7 @@
         <v>198</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="19">
@@ -12341,7 +12350,7 @@
         <v>199</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="19">
@@ -12362,7 +12371,7 @@
         <v>200</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="19">
@@ -12383,7 +12392,7 @@
         <v>201</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="19">
@@ -12404,7 +12413,7 @@
         <v>202</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="19">
@@ -12427,7 +12436,7 @@
         <v>203</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="19">
@@ -12448,7 +12457,7 @@
         <v>204</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="19">
@@ -12467,7 +12476,7 @@
         <v>205</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="19">
@@ -12486,7 +12495,7 @@
         <v>206</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>1934</v>
@@ -12511,7 +12520,7 @@
         <v>207</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="19">
@@ -12532,7 +12541,7 @@
         <v>208</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="19">
@@ -12553,7 +12562,7 @@
         <v>209</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="19">
@@ -12574,7 +12583,7 @@
         <v>210</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="19">
@@ -12593,7 +12602,7 @@
         <v>211</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D17" s="17"/>
       <c r="E17" s="19">
@@ -12614,7 +12623,7 @@
         <v>212</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="19">
@@ -12635,7 +12644,7 @@
         <v>213</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="19">
@@ -12658,7 +12667,7 @@
         <v>214</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="19">
@@ -12679,7 +12688,7 @@
         <v>215</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D21" s="17"/>
       <c r="E21" s="19">
@@ -12698,7 +12707,7 @@
         <v>381</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D22" s="17"/>
       <c r="E22" s="19">
@@ -12719,7 +12728,7 @@
         <v>382</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="19">
@@ -12740,7 +12749,7 @@
         <v>383</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="19">
@@ -12761,7 +12770,7 @@
         <v>384</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D25" s="17"/>
       <c r="E25" s="19">
@@ -12782,7 +12791,7 @@
         <v>385</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D26" s="17"/>
       <c r="E26" s="19">
@@ -12805,7 +12814,7 @@
         <v>386</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D27" s="17"/>
       <c r="E27" s="19">
@@ -12826,7 +12835,7 @@
         <v>387</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="19">
@@ -12847,7 +12856,7 @@
         <v>388</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="19">
@@ -12868,7 +12877,7 @@
         <v>389</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="19">
@@ -12889,7 +12898,7 @@
         <v>390</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="19">
@@ -12910,7 +12919,7 @@
         <v>391</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="19">
@@ -12931,7 +12940,7 @@
         <v>392</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="19">
@@ -12952,7 +12961,7 @@
         <v>393</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="19">
@@ -12975,7 +12984,7 @@
         <v>394</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D35" s="17"/>
       <c r="E35" s="19">
@@ -12996,7 +13005,7 @@
         <v>395</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D36" s="17"/>
       <c r="E36" s="19">
@@ -13017,7 +13026,7 @@
         <v>1452</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D37" s="17"/>
       <c r="E37" s="19">
@@ -13038,7 +13047,7 @@
         <v>396</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D38" s="17"/>
       <c r="E38" s="19">
@@ -13059,7 +13068,7 @@
         <v>397</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D39" s="17"/>
       <c r="E39" s="19">
@@ -13080,7 +13089,7 @@
         <v>455</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D40" s="17"/>
       <c r="E40" s="19">
@@ -13101,7 +13110,7 @@
         <v>1636</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D41" s="17"/>
       <c r="E41" s="19">
@@ -13120,7 +13129,7 @@
         <v>456</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="19">
@@ -13141,7 +13150,7 @@
         <v>1375</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="19">
@@ -13162,7 +13171,7 @@
         <v>457</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D44" s="17"/>
       <c r="E44" s="19">
@@ -13183,7 +13192,7 @@
         <v>1431</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D45" s="17"/>
       <c r="E45" s="19">
@@ -13204,7 +13213,7 @@
         <v>458</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D46" s="17"/>
       <c r="E46" s="19">
@@ -13225,7 +13234,7 @@
         <v>459</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="19">
@@ -13246,7 +13255,7 @@
         <v>460</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D48" s="17"/>
       <c r="E48" s="19">
@@ -13267,7 +13276,7 @@
         <v>461</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D49" s="17"/>
       <c r="E49" s="19">
@@ -13286,7 +13295,7 @@
         <v>1478</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D50" s="17"/>
       <c r="E50" s="19">
@@ -13307,7 +13316,7 @@
         <v>462</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D51" s="17"/>
       <c r="E51" s="19">
@@ -13328,7 +13337,7 @@
         <v>463</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D52" s="17"/>
       <c r="E52" s="19">
@@ -13351,7 +13360,7 @@
         <v>464</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D53" s="17"/>
       <c r="E53" s="19">
@@ -13374,7 +13383,7 @@
         <v>465</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D54" s="17"/>
       <c r="E54" s="19">
@@ -13395,7 +13404,7 @@
         <v>466</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D55" s="17"/>
       <c r="E55" s="19">
@@ -13416,7 +13425,7 @@
         <v>467</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D56" s="17"/>
       <c r="E56" s="19">
@@ -13437,7 +13446,7 @@
         <v>468</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="19">
@@ -13458,7 +13467,7 @@
         <v>469</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D58" s="17"/>
       <c r="E58" s="19">
@@ -13479,7 +13488,7 @@
         <v>470</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D59" s="17"/>
       <c r="E59" s="19">
@@ -13500,7 +13509,7 @@
         <v>471</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D60" s="17"/>
       <c r="E60" s="19">
@@ -13521,7 +13530,7 @@
         <v>472</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D61" s="17"/>
       <c r="E61" s="19">
@@ -13542,7 +13551,7 @@
         <v>473</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D62" s="17"/>
       <c r="E62" s="19">
@@ -13565,7 +13574,7 @@
         <v>474</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D63" s="17"/>
       <c r="E63" s="19">
@@ -13586,7 +13595,7 @@
         <v>475</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D64" s="17"/>
       <c r="E64" s="19">
@@ -13607,7 +13616,7 @@
         <v>476</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D65" s="17"/>
       <c r="E65" s="19">
@@ -13628,7 +13637,7 @@
         <v>477</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D66" s="17"/>
       <c r="E66" s="19">
@@ -13647,7 +13656,7 @@
         <v>478</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D67" s="17"/>
       <c r="E67" s="19">
@@ -13668,7 +13677,7 @@
         <v>479</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D68" s="17"/>
       <c r="E68" s="19">
@@ -13689,7 +13698,7 @@
         <v>480</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D69" s="17"/>
       <c r="E69" s="19">
@@ -13710,7 +13719,7 @@
         <v>2586</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D70" s="17"/>
       <c r="E70" s="19">
@@ -13731,7 +13740,7 @@
         <v>1613</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D71" s="17"/>
       <c r="E71" s="19">
@@ -13750,7 +13759,7 @@
         <v>481</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D72" s="17"/>
       <c r="E72" s="19">
@@ -13771,7 +13780,7 @@
         <v>1845</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D73" s="17"/>
       <c r="E73" s="19">
@@ -13790,7 +13799,7 @@
         <v>2032</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D74" s="17"/>
       <c r="E74" s="19">
@@ -13809,7 +13818,7 @@
         <v>482</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D75" s="17"/>
       <c r="E75" s="19">
@@ -13830,7 +13839,7 @@
         <v>1643</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D76" s="17"/>
       <c r="E76" s="19">
@@ -13849,7 +13858,7 @@
         <v>1743</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D77" s="17"/>
       <c r="E77" s="19">
@@ -13868,7 +13877,7 @@
         <v>1776</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D78" s="17"/>
       <c r="E78" s="19">
@@ -13887,7 +13896,7 @@
         <v>1826</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D79" s="17"/>
       <c r="E79" s="19">
@@ -13906,7 +13915,7 @@
         <v>2247</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D80" s="17"/>
       <c r="E80" s="19">
@@ -13925,7 +13934,7 @@
         <v>2135</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D81" s="17"/>
       <c r="E81" s="19">
@@ -13944,7 +13953,7 @@
         <v>2620</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D82" s="17"/>
       <c r="E82" s="19">
@@ -13963,7 +13972,7 @@
         <v>483</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D83" s="17"/>
       <c r="E83" s="19">
@@ -13984,7 +13993,7 @@
         <v>484</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D84" s="17"/>
       <c r="E84" s="19">
@@ -14007,7 +14016,7 @@
         <v>485</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D85" s="17"/>
       <c r="E85" s="19">
@@ -14030,7 +14039,7 @@
         <v>486</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D86" s="17"/>
       <c r="E86" s="19">
@@ -14051,7 +14060,7 @@
         <v>487</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D87" s="17"/>
       <c r="E87" s="19">
@@ -14072,7 +14081,7 @@
         <v>488</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D88" s="17"/>
       <c r="E88" s="19">
@@ -14091,7 +14100,7 @@
         <v>489</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D89" s="17"/>
       <c r="E89" s="19">
@@ -14112,7 +14121,7 @@
         <v>490</v>
       </c>
       <c r="C90" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D90" s="17"/>
       <c r="E90" s="19">
@@ -14133,7 +14142,7 @@
         <v>491</v>
       </c>
       <c r="C91" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D91" s="17"/>
       <c r="E91" s="19">
@@ -14156,7 +14165,7 @@
         <v>492</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D92" s="17"/>
       <c r="E92" s="19">
@@ -14177,7 +14186,7 @@
         <v>493</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D93" s="17"/>
       <c r="E93" s="19">
@@ -14198,7 +14207,7 @@
         <v>494</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D94" s="17"/>
       <c r="E94" s="19">
@@ -14217,7 +14226,7 @@
         <v>495</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D95" s="17"/>
       <c r="E95" s="19">
@@ -14238,7 +14247,7 @@
         <v>496</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D96" s="17"/>
       <c r="E96" s="19">
@@ -14259,7 +14268,7 @@
         <v>497</v>
       </c>
       <c r="C97" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D97" s="17"/>
       <c r="E97" s="19">
@@ -14280,7 +14289,7 @@
         <v>498</v>
       </c>
       <c r="C98" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D98" s="17"/>
       <c r="E98" s="19">
@@ -14301,7 +14310,7 @@
         <v>499</v>
       </c>
       <c r="C99" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D99" s="17"/>
       <c r="E99" s="19">
@@ -14322,7 +14331,7 @@
         <v>500</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D100" s="17"/>
       <c r="E100" s="19">
@@ -14345,7 +14354,7 @@
         <v>501</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D101" s="17"/>
       <c r="E101" s="19">
@@ -14368,7 +14377,7 @@
         <v>502</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D102" s="17"/>
       <c r="E102" s="19">
@@ -14389,7 +14398,7 @@
         <v>503</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D103" s="17"/>
       <c r="E103" s="19">
@@ -14412,7 +14421,7 @@
         <v>2254</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D104" s="17"/>
       <c r="E104" s="19">
@@ -14431,7 +14440,7 @@
         <v>504</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D105" s="17"/>
       <c r="E105" s="19">
@@ -14452,7 +14461,7 @@
         <v>505</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D106" s="17"/>
       <c r="E106" s="19">
@@ -14473,7 +14482,7 @@
         <v>506</v>
       </c>
       <c r="C107" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D107" s="17"/>
       <c r="E107" s="19">
@@ -14496,7 +14505,7 @@
         <v>507</v>
       </c>
       <c r="C108" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D108" s="17"/>
       <c r="E108" s="19">
@@ -14517,7 +14526,7 @@
         <v>508</v>
       </c>
       <c r="C109" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D109" s="17"/>
       <c r="E109" s="19">
@@ -14540,7 +14549,7 @@
         <v>1736</v>
       </c>
       <c r="C110" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D110" s="17"/>
       <c r="E110" s="19">
@@ -14559,7 +14568,7 @@
         <v>509</v>
       </c>
       <c r="C111" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D111" s="17"/>
       <c r="E111" s="19">
@@ -14580,7 +14589,7 @@
         <v>510</v>
       </c>
       <c r="C112" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D112" s="17"/>
       <c r="E112" s="19">
@@ -14601,7 +14610,7 @@
         <v>511</v>
       </c>
       <c r="C113" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D113" s="17"/>
       <c r="E113" s="19">
@@ -14622,7 +14631,7 @@
         <v>1865</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D114" s="17"/>
       <c r="E114" s="19">
@@ -14641,7 +14650,7 @@
         <v>512</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D115" s="17"/>
       <c r="E115" s="19">
@@ -14662,7 +14671,7 @@
         <v>1457</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D116" s="17"/>
       <c r="E116" s="19">
@@ -14685,7 +14694,7 @@
         <v>513</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D117" s="17"/>
       <c r="E117" s="19">
@@ -14706,7 +14715,7 @@
         <v>514</v>
       </c>
       <c r="C118" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D118" s="17"/>
       <c r="E118" s="19">
@@ -14725,7 +14734,7 @@
         <v>515</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D119" s="17"/>
       <c r="E119" s="19">
@@ -14744,7 +14753,7 @@
         <v>516</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D120" s="17"/>
       <c r="E120" s="19">
@@ -14765,7 +14774,7 @@
         <v>517</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D121" s="17"/>
       <c r="E121" s="19">
@@ -14788,7 +14797,7 @@
         <v>518</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D122" s="17"/>
       <c r="E122" s="19">
@@ -14809,7 +14818,7 @@
         <v>519</v>
       </c>
       <c r="C123" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D123" s="17"/>
       <c r="E123" s="19">
@@ -14830,7 +14839,7 @@
         <v>520</v>
       </c>
       <c r="C124" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D124" s="17"/>
       <c r="E124" s="19">
@@ -14853,7 +14862,7 @@
         <v>521</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D125" s="17"/>
       <c r="E125" s="19">
@@ -14874,7 +14883,7 @@
         <v>522</v>
       </c>
       <c r="C126" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D126" s="17"/>
       <c r="E126" s="19">
@@ -14895,7 +14904,7 @@
         <v>523</v>
       </c>
       <c r="C127" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D127" s="17"/>
       <c r="E127" s="19">
@@ -14916,7 +14925,7 @@
         <v>524</v>
       </c>
       <c r="C128" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D128" s="17"/>
       <c r="E128" s="19">
@@ -14937,7 +14946,7 @@
         <v>525</v>
       </c>
       <c r="C129" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D129" s="17"/>
       <c r="E129" s="19">
@@ -14956,7 +14965,7 @@
         <v>526</v>
       </c>
       <c r="C130" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D130" s="17"/>
       <c r="E130" s="19">
@@ -14977,7 +14986,7 @@
         <v>527</v>
       </c>
       <c r="C131" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D131" s="17"/>
       <c r="E131" s="19">
@@ -14998,7 +15007,7 @@
         <v>528</v>
       </c>
       <c r="C132" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D132" s="17"/>
       <c r="E132" s="19">
@@ -15021,7 +15030,7 @@
         <v>529</v>
       </c>
       <c r="C133" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D133" s="17"/>
       <c r="E133" s="19">
@@ -15042,7 +15051,7 @@
         <v>530</v>
       </c>
       <c r="C134" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D134" s="17"/>
       <c r="E134" s="19">
@@ -15063,7 +15072,7 @@
         <v>531</v>
       </c>
       <c r="C135" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D135" s="17"/>
       <c r="E135" s="19">
@@ -15082,7 +15091,7 @@
         <v>532</v>
       </c>
       <c r="C136" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D136" s="17"/>
       <c r="E136" s="19">
@@ -15103,7 +15112,7 @@
         <v>533</v>
       </c>
       <c r="C137" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D137" s="17"/>
       <c r="E137" s="19">
@@ -15124,7 +15133,7 @@
         <v>534</v>
       </c>
       <c r="C138" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D138" s="17"/>
       <c r="E138" s="19">
@@ -15145,7 +15154,7 @@
         <v>536</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D139" s="17"/>
       <c r="E139" s="19">
@@ -15166,7 +15175,7 @@
         <v>537</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D140" s="17"/>
       <c r="E140" s="19">
@@ -15187,7 +15196,7 @@
         <v>2180</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D141" s="17"/>
       <c r="E141" s="19">
@@ -15206,7 +15215,7 @@
         <v>538</v>
       </c>
       <c r="C142" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D142" s="17"/>
       <c r="E142" s="19">
@@ -15227,7 +15236,7 @@
         <v>539</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D143" s="17"/>
       <c r="E143" s="19">
@@ -15248,7 +15257,7 @@
         <v>540</v>
       </c>
       <c r="C144" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D144" s="17"/>
       <c r="E144" s="19">
@@ -15269,7 +15278,7 @@
         <v>541</v>
       </c>
       <c r="C145" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D145" s="17"/>
       <c r="E145" s="19">
@@ -15290,7 +15299,7 @@
         <v>542</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D146" s="17"/>
       <c r="E146" s="19">
@@ -15311,7 +15320,7 @@
         <v>543</v>
       </c>
       <c r="C147" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D147" s="17"/>
       <c r="E147" s="19">
@@ -15330,7 +15339,7 @@
         <v>1516</v>
       </c>
       <c r="C148" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D148" s="17"/>
       <c r="E148" s="19">
@@ -15351,7 +15360,7 @@
         <v>2219</v>
       </c>
       <c r="C149" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D149" s="17"/>
       <c r="E149" s="19">
@@ -15370,7 +15379,7 @@
         <v>1455</v>
       </c>
       <c r="C150" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D150" s="17"/>
       <c r="E150" s="19">
@@ -15391,7 +15400,7 @@
         <v>1585</v>
       </c>
       <c r="C151" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D151" s="17"/>
       <c r="E151" s="19">
@@ -15410,7 +15419,7 @@
         <v>1481</v>
       </c>
       <c r="C152" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D152" s="17"/>
       <c r="E152" s="19">
@@ -15433,7 +15442,7 @@
         <v>1407</v>
       </c>
       <c r="C153" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D153" s="17"/>
       <c r="E153" s="19">
@@ -15454,7 +15463,7 @@
         <v>544</v>
       </c>
       <c r="C154" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D154" s="17"/>
       <c r="E154" s="19">
@@ -15473,7 +15482,7 @@
         <v>2590</v>
       </c>
       <c r="C155" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D155" s="17"/>
       <c r="E155" s="19">
@@ -15494,7 +15503,7 @@
         <v>1595</v>
       </c>
       <c r="C156" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D156" s="17"/>
       <c r="E156" s="19">
@@ -15513,7 +15522,7 @@
         <v>2040</v>
       </c>
       <c r="C157" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D157" s="17"/>
       <c r="E157" s="19">
@@ -15532,7 +15541,7 @@
         <v>545</v>
       </c>
       <c r="C158" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D158" s="17"/>
       <c r="E158" s="19">
@@ -15553,7 +15562,7 @@
         <v>2516</v>
       </c>
       <c r="C159" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D159" s="17"/>
       <c r="E159" s="19">
@@ -15572,7 +15581,7 @@
         <v>1828</v>
       </c>
       <c r="C160" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D160" s="17"/>
       <c r="E160" s="19">
@@ -15591,7 +15600,7 @@
         <v>2041</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D161" s="17"/>
       <c r="E161" s="19">
@@ -15610,7 +15619,7 @@
         <v>2042</v>
       </c>
       <c r="C162" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D162" s="17"/>
       <c r="E162" s="19">
@@ -15629,7 +15638,7 @@
         <v>2224</v>
       </c>
       <c r="C163" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D163" s="17"/>
       <c r="E163" s="19">
@@ -15648,7 +15657,7 @@
         <v>2078</v>
       </c>
       <c r="C164" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D164" s="17"/>
       <c r="E164" s="19">
@@ -15662,10 +15671,10 @@
     <row r="165" spans="1:10" ht="15.75">
       <c r="A165" s="17"/>
       <c r="B165" s="17" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="C165" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D165" s="17"/>
       <c r="E165" s="19">
@@ -15684,7 +15693,7 @@
         <v>2507</v>
       </c>
       <c r="C166" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D166" s="17"/>
       <c r="E166" s="19">
@@ -15703,7 +15712,7 @@
         <v>2761</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D167" s="17"/>
       <c r="E167" s="19">
@@ -15722,7 +15731,7 @@
         <v>2039</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D168" s="17" t="s">
         <v>2164</v>
@@ -15748,7 +15757,7 @@
         <v>2136</v>
       </c>
       <c r="C169" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D169" s="17"/>
       <c r="E169" s="19">
@@ -15767,7 +15776,7 @@
         <v>2188</v>
       </c>
       <c r="C170" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D170" s="17"/>
       <c r="E170" s="19">
@@ -15786,7 +15795,7 @@
         <v>2071</v>
       </c>
       <c r="C171" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D171" s="17"/>
       <c r="E171" s="19">
@@ -15805,7 +15814,7 @@
         <v>2618</v>
       </c>
       <c r="C172" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D172" s="17"/>
       <c r="E172" s="19">
@@ -15824,7 +15833,7 @@
         <v>2609</v>
       </c>
       <c r="C173" s="18" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="E173" s="10">
         <v>7</v>
@@ -16175,10 +16184,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -16264,10 +16273,10 @@
         <v>598</v>
       </c>
       <c r="D5" s="74" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="E5" s="75">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" s="74">
         <v>2443</v>
@@ -16315,7 +16324,7 @@
         <v>2700</v>
       </c>
       <c r="E7" s="75">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F7" s="75">
         <v>2412</v>
@@ -16372,7 +16381,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="74" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="C10" s="74" t="s">
         <v>598</v>
@@ -16414,7 +16423,7 @@
         <v>2718</v>
       </c>
       <c r="D12" s="74" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="E12" s="75">
         <v>1</v>
@@ -16480,7 +16489,7 @@
         <v>102</v>
       </c>
       <c r="F15" s="74" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="G15" s="74"/>
       <c r="H15" s="74"/>
@@ -16502,7 +16511,7 @@
         <v>70</v>
       </c>
       <c r="F16" s="74" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="G16" s="74"/>
       <c r="H16" s="74"/>
@@ -16512,7 +16521,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="74" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="C17" s="74" t="s">
         <v>598</v>
@@ -17256,7 +17265,7 @@
         <v>3</v>
       </c>
       <c r="F56" s="74" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="G56" s="74"/>
       <c r="H56" s="74"/>
@@ -17628,7 +17637,7 @@
         <v>9</v>
       </c>
       <c r="F75" s="74" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="G75" s="74"/>
       <c r="H75" s="74"/>
@@ -17817,7 +17826,7 @@
         <v>2700</v>
       </c>
       <c r="E85" s="75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F85" s="74">
         <v>2122</v>
@@ -18286,7 +18295,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="74" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="C111" s="74"/>
       <c r="D111" s="74" t="s">
@@ -18440,7 +18449,7 @@
         <v>37</v>
       </c>
       <c r="F118" s="74" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="G118" s="74" t="s">
         <v>1778</v>
@@ -18676,7 +18685,7 @@
         <v>10</v>
       </c>
       <c r="F130" s="74" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="G130" s="74"/>
       <c r="H130" s="74"/>
@@ -18692,13 +18701,13 @@
         <v>625</v>
       </c>
       <c r="D131" s="74" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="E131" s="75">
         <v>2</v>
       </c>
       <c r="F131" s="74" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="G131" s="74"/>
       <c r="H131" s="74"/>
@@ -18714,7 +18723,7 @@
         <v>625</v>
       </c>
       <c r="D132" s="74" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="E132" s="75">
         <v>0</v>
@@ -18917,7 +18926,7 @@
         <v>822</v>
       </c>
       <c r="E142" s="75">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F142" s="74">
         <v>687</v>
@@ -19038,10 +19047,10 @@
         <v>825</v>
       </c>
       <c r="D148" s="74" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="E148" s="75">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F148" s="74">
         <v>1515</v>
@@ -19078,7 +19087,7 @@
         <v>825</v>
       </c>
       <c r="D150" s="74" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="E150" s="75">
         <v>3</v>
@@ -19136,7 +19145,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="74" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="C153" s="74" t="s">
         <v>2819</v>
@@ -19162,7 +19171,7 @@
         <v>598</v>
       </c>
       <c r="D154" s="74" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="E154" s="75">
         <v>7</v>
@@ -19200,7 +19209,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="74" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="C156" s="74" t="s">
         <v>825</v>
@@ -19226,7 +19235,7 @@
         <v>598</v>
       </c>
       <c r="D157" s="74" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="E157" s="75">
         <v>10</v>
@@ -19269,10 +19278,10 @@
       </c>
       <c r="D159" s="74"/>
       <c r="E159" s="75">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="F159" s="74" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="G159" s="74"/>
       <c r="H159" s="74"/>
@@ -19420,7 +19429,7 @@
         <v>6</v>
       </c>
       <c r="F167" s="74" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="G167" s="74" t="s">
         <v>1553</v>
@@ -19528,7 +19537,7 @@
         <v>3</v>
       </c>
       <c r="F172" s="74" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="G172" s="74"/>
       <c r="H172" s="74"/>
@@ -19684,7 +19693,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="74" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="C180" s="74" t="s">
         <v>825</v>
@@ -19912,7 +19921,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="74" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C191" s="74" t="s">
         <v>825</v>
@@ -19930,7 +19939,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="74" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="C192" s="74" t="s">
         <v>586</v>
@@ -19950,7 +19959,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="74" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="C193" s="74"/>
       <c r="D193" s="74"/>
@@ -19968,7 +19977,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="74" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="C194" s="74"/>
       <c r="D194" s="74"/>
@@ -19986,7 +19995,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="74" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="C195" s="74" t="s">
         <v>598</v>
@@ -20044,7 +20053,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="74" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="C198" s="74" t="s">
         <v>598</v>
@@ -20102,7 +20111,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="74" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="C201" s="74" t="s">
         <v>598</v>
@@ -20122,7 +20131,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="74" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="C202" s="74" t="s">
         <v>598</v>
@@ -20140,7 +20149,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="74" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="C203" s="74" t="s">
         <v>825</v>
@@ -20160,14 +20169,14 @@
         <v>203</v>
       </c>
       <c r="B204" s="74" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="C204" s="74" t="s">
         <v>825</v>
       </c>
       <c r="D204" s="74"/>
       <c r="E204" s="75">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F204" s="74">
         <v>2434</v>
@@ -20222,7 +20231,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="74" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="C207" s="74" t="s">
         <v>825</v>
@@ -20240,7 +20249,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="74" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="C208" s="74" t="s">
         <v>825</v>
@@ -20284,7 +20293,7 @@
         <v>625</v>
       </c>
       <c r="D210" s="74" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="E210" s="75">
         <v>3</v>
@@ -20307,7 +20316,7 @@
       </c>
       <c r="D211" s="74"/>
       <c r="E211" s="75">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F211" s="74">
         <v>2360</v>
@@ -20320,7 +20329,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="74" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="C212" s="74" t="s">
         <v>598</v>
@@ -20340,7 +20349,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="74" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="C213" s="74" t="s">
         <v>586</v>
@@ -20376,10 +20385,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="74" t="s">
+        <v>3079</v>
+      </c>
+      <c r="C215" s="74" t="s">
         <v>3080</v>
-      </c>
-      <c r="C215" s="74" t="s">
-        <v>3081</v>
       </c>
       <c r="D215" s="74"/>
       <c r="E215" s="75">
@@ -20396,7 +20405,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="74" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="C216" s="74" t="s">
         <v>825</v>
@@ -20416,7 +20425,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="74" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="C217" s="74" t="s">
         <v>625</v>
@@ -20436,7 +20445,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="74" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="C218" s="74" t="s">
         <v>586</v>
@@ -20456,13 +20465,13 @@
         <v>218</v>
       </c>
       <c r="B219" s="74" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="C219" s="74" t="s">
         <v>598</v>
       </c>
       <c r="D219" s="74" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="E219" s="75">
         <v>2</v>
@@ -20476,7 +20485,7 @@
     <row r="220" spans="1:8" ht="21">
       <c r="A220" s="74"/>
       <c r="B220" s="74" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="C220" s="74" t="s">
         <v>598</v>
@@ -20594,7 +20603,7 @@
         <v>4</v>
       </c>
       <c r="F225" s="74" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="G225" s="74"/>
       <c r="H225" s="74"/>
@@ -20635,10 +20644,10 @@
         <v>289</v>
       </c>
       <c r="E227" s="75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F227" s="74" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="G227" s="74"/>
       <c r="H227" s="74"/>
@@ -20679,7 +20688,7 @@
         <v>2439</v>
       </c>
       <c r="E229" s="75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F229" s="74">
         <v>11764</v>
@@ -20770,7 +20779,7 @@
         <v>2</v>
       </c>
       <c r="F233" s="74" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="G233" s="74"/>
       <c r="H233" s="74"/>
@@ -20846,7 +20855,7 @@
         <v>843</v>
       </c>
       <c r="D237" s="74" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="E237" s="75">
         <v>1</v>
@@ -20933,7 +20942,7 @@
         <v>2438</v>
       </c>
       <c r="E241" s="75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F241" s="74">
         <v>12511</v>
@@ -20955,10 +20964,10 @@
         <v>2036</v>
       </c>
       <c r="E242" s="75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F242" s="78">
-        <v>11142</v>
+        <v>11650</v>
       </c>
       <c r="G242" s="74"/>
       <c r="H242" s="74"/>
@@ -20980,7 +20989,7 @@
         <v>2</v>
       </c>
       <c r="F243" s="74" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="G243" s="74"/>
       <c r="H243" s="74"/>
@@ -20999,7 +21008,7 @@
         <v>2547</v>
       </c>
       <c r="E244" s="75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F244" s="74">
         <v>12026</v>
@@ -21345,7 +21354,7 @@
         <v>2526</v>
       </c>
       <c r="C260" s="74" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="D260" s="74" t="s">
         <v>2553</v>
@@ -21354,7 +21363,7 @@
         <v>2</v>
       </c>
       <c r="F260" s="74" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="G260" s="74"/>
       <c r="H260" s="74"/>
@@ -21400,7 +21409,7 @@
         <v>2</v>
       </c>
       <c r="F262" s="74" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="G262" s="74"/>
       <c r="H262" s="74"/>
@@ -21460,7 +21469,7 @@
         <v>843</v>
       </c>
       <c r="D265" s="74" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="E265" s="75">
         <v>1</v>
@@ -21482,7 +21491,7 @@
         <v>843</v>
       </c>
       <c r="D266" s="74" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="E266" s="75">
         <v>1</v>
@@ -21504,7 +21513,7 @@
         <v>843</v>
       </c>
       <c r="D267" s="74" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="E267" s="75">
         <v>1</v>
@@ -21548,7 +21557,7 @@
         <v>843</v>
       </c>
       <c r="D269" s="74" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="E269" s="75">
         <v>1</v>
@@ -21635,7 +21644,7 @@
         <v>1569</v>
       </c>
       <c r="E273" s="75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F273" s="74">
         <v>9474</v>
@@ -21648,13 +21657,13 @@
         <v>272</v>
       </c>
       <c r="B274" s="74" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="C274" s="74" t="s">
         <v>1966</v>
       </c>
       <c r="D274" s="74" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="E274" s="75">
         <v>2</v>
@@ -21670,7 +21679,7 @@
         <v>273</v>
       </c>
       <c r="B275" s="74" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="C275" s="74" t="s">
         <v>843</v>
@@ -21690,13 +21699,13 @@
         <v>274</v>
       </c>
       <c r="B276" s="74" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="C276" s="74" t="s">
         <v>843</v>
       </c>
       <c r="D276" s="74" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="E276" s="75">
         <v>1</v>
@@ -21712,13 +21721,13 @@
         <v>275</v>
       </c>
       <c r="B277" s="74" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="C277" s="74" t="s">
         <v>1966</v>
       </c>
       <c r="D277" s="74" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E277" s="75">
         <v>1</v>
@@ -21734,7 +21743,7 @@
         <v>276</v>
       </c>
       <c r="B278" s="74" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="C278" s="74" t="s">
         <v>1966</v>
@@ -21754,13 +21763,13 @@
         <v>277</v>
       </c>
       <c r="B279" s="74" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="C279" s="74" t="s">
         <v>1966</v>
       </c>
       <c r="D279" s="74" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="E279" s="75">
         <v>0</v>
@@ -21776,13 +21785,13 @@
         <v>278</v>
       </c>
       <c r="B280" s="74" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="C280" s="74" t="s">
         <v>843</v>
       </c>
       <c r="D280" s="74" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="E280" s="75">
         <v>0</v>
@@ -21796,7 +21805,7 @@
         <v>279</v>
       </c>
       <c r="B281" s="74" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="C281" s="74" t="s">
         <v>1966</v>
@@ -21818,7 +21827,7 @@
         <v>280</v>
       </c>
       <c r="B282" s="74" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="C282" s="74" t="s">
         <v>843</v>
@@ -21838,7 +21847,7 @@
         <v>281</v>
       </c>
       <c r="B283" s="74" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="C283" s="74" t="s">
         <v>1966</v>
@@ -21858,13 +21867,13 @@
         <v>282</v>
       </c>
       <c r="B284" s="74" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="C284" s="74" t="s">
         <v>843</v>
       </c>
       <c r="D284" s="74" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="E284" s="75">
         <v>2</v>
@@ -21880,16 +21889,16 @@
         <v>283</v>
       </c>
       <c r="B285" s="74" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="C285" s="74" t="s">
         <v>1966</v>
       </c>
       <c r="D285" s="74" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="E285" s="75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F285" s="74">
         <v>9660</v>
@@ -21902,7 +21911,7 @@
         <v>284</v>
       </c>
       <c r="B286" s="74" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="C286" s="74" t="s">
         <v>1966</v>
@@ -21922,7 +21931,7 @@
         <v>285</v>
       </c>
       <c r="B287" s="74" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="C287" s="74" t="s">
         <v>843</v>
@@ -21942,7 +21951,7 @@
         <v>286</v>
       </c>
       <c r="B288" s="74" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="C288" s="74" t="s">
         <v>843</v>
@@ -21960,7 +21969,7 @@
         <v>287</v>
       </c>
       <c r="B289" s="74" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="C289" s="74" t="s">
         <v>1966</v>
@@ -21980,7 +21989,7 @@
         <v>288</v>
       </c>
       <c r="B290" s="74" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="C290" s="74" t="s">
         <v>1966</v>
@@ -21998,7 +22007,7 @@
         <v>289</v>
       </c>
       <c r="B291" s="74" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="C291" s="74" t="s">
         <v>843</v>
@@ -22018,7 +22027,7 @@
         <v>290</v>
       </c>
       <c r="B292" s="74" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="C292" s="74" t="s">
         <v>843</v>
@@ -22038,7 +22047,7 @@
         <v>291</v>
       </c>
       <c r="B293" s="74" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="C293" s="74" t="s">
         <v>843</v>
@@ -22055,7 +22064,7 @@
     </row>
     <row r="294" spans="1:8" ht="21">
       <c r="B294" s="90" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="C294" s="74" t="s">
         <v>843</v>
@@ -22142,10 +22151,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -22161,7 +22170,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="97" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="C2" s="97"/>
       <c r="D2" s="97"/>
@@ -22178,10 +22187,10 @@
         <v>1629</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="D3" s="69" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="E3" s="71">
         <v>195</v>
@@ -22190,7 +22199,7 @@
         <v>146</v>
       </c>
       <c r="G3" s="69" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="H3" s="71"/>
     </row>
@@ -22202,10 +22211,10 @@
         <v>1626</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="D4" s="69" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="E4" s="71">
         <v>220</v>
@@ -22224,10 +22233,10 @@
         <v>1980</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="D5" s="69" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="E5" s="71">
         <v>138</v>
@@ -22246,10 +22255,10 @@
         <v>1981</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="D6" s="69" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="E6" s="71">
         <v>725</v>
@@ -22270,10 +22279,10 @@
         <v>1982</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="D7" s="69" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="E7" s="71">
         <v>295</v>
@@ -22294,10 +22303,10 @@
         <v>1983</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="D8" s="69" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="E8" s="71">
         <v>262</v>
@@ -22316,10 +22325,10 @@
         <v>1984</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="D9" s="69" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="E9" s="71">
         <v>341</v>
@@ -22338,10 +22347,10 @@
         <v>1985</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="D10" s="69" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="E10" s="71">
         <v>208</v>
@@ -22362,13 +22371,13 @@
         <v>1986</v>
       </c>
       <c r="C11" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="D11" s="69" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="E11" s="71">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="F11" s="70">
         <v>242</v>
@@ -22386,13 +22395,13 @@
         <v>1987</v>
       </c>
       <c r="C12" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="D12" s="69" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="E12" s="71">
-        <v>922</v>
+        <v>912</v>
       </c>
       <c r="F12" s="70">
         <v>254</v>
@@ -22410,10 +22419,10 @@
         <v>1988</v>
       </c>
       <c r="C13" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="D13" s="69" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="E13" s="71">
         <v>192</v>
@@ -22434,10 +22443,10 @@
         <v>1989</v>
       </c>
       <c r="C14" s="69" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="D14" s="69" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="E14" s="71">
         <v>240</v>
@@ -22453,7 +22462,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="98" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="C15" s="98"/>
       <c r="D15" s="98"/>
@@ -22470,7 +22479,7 @@
         <v>690</v>
       </c>
       <c r="C16" s="69" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="D16" s="69" t="s">
         <v>2229</v>
@@ -22492,7 +22501,7 @@
         <v>2064</v>
       </c>
       <c r="C17" s="69" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="D17" s="69" t="s">
         <v>2603</v>
@@ -22514,7 +22523,7 @@
         <v>691</v>
       </c>
       <c r="C18" s="69" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="D18" s="69" t="s">
         <v>2604</v>
@@ -22536,7 +22545,7 @@
         <v>692</v>
       </c>
       <c r="C19" s="69" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="D19" s="69" t="s">
         <v>2605</v>
@@ -22558,7 +22567,7 @@
         <v>693</v>
       </c>
       <c r="C20" s="69" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="D20" s="69" t="s">
         <v>2228</v>
@@ -22580,7 +22589,7 @@
         <v>694</v>
       </c>
       <c r="C21" s="69" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="D21" s="69" t="s">
         <v>2227</v>
@@ -22599,7 +22608,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="98" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="C22" s="98"/>
       <c r="D22" s="98"/>
@@ -22616,7 +22625,7 @@
         <v>2612</v>
       </c>
       <c r="C23" s="69" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="D23" s="69" t="s">
         <v>2606</v>
@@ -22638,7 +22647,7 @@
         <v>2045</v>
       </c>
       <c r="C24" s="69" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="D24" s="69" t="s">
         <v>2049</v>
@@ -22660,7 +22669,7 @@
         <v>2090</v>
       </c>
       <c r="C25" s="69" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="D25" s="69" t="s">
         <v>2091</v>
@@ -22682,7 +22691,7 @@
         <v>2677</v>
       </c>
       <c r="C26" s="69" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="D26" s="69" t="s">
         <v>1720</v>
@@ -22704,7 +22713,7 @@
         <v>2065</v>
       </c>
       <c r="C27" s="69" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="D27" s="69" t="s">
         <v>2066</v>
@@ -22726,7 +22735,7 @@
         <v>2050</v>
       </c>
       <c r="C28" s="69" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="D28" s="69" t="s">
         <v>2051</v>
@@ -22748,7 +22757,7 @@
         <v>2607</v>
       </c>
       <c r="C29" s="69" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="D29" s="69" t="s">
         <v>2608</v>
@@ -22776,7 +22785,7 @@
         <v>1719</v>
       </c>
       <c r="E30" s="71">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F30" s="70">
         <v>360</v>
@@ -22944,7 +22953,7 @@
         <v>2460</v>
       </c>
       <c r="C39" s="69" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="D39" s="71"/>
       <c r="E39" s="71">
@@ -31281,7 +31290,9 @@
     <col min="3" max="3" width="15.28515625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="8"/>
+    <col min="6" max="6" width="9.140625" style="8"/>
+    <col min="7" max="7" width="11.5703125" style="8" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75">
@@ -31292,10 +31303,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -31403,7 +31414,7 @@
         <v>1293</v>
       </c>
       <c r="E6" s="19">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F6" s="17">
         <v>2595</v>
@@ -31424,7 +31435,7 @@
         <v>1292</v>
       </c>
       <c r="E7" s="19">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F7" s="17">
         <v>3385</v>
@@ -31527,7 +31538,7 @@
         <v>1300</v>
       </c>
       <c r="E12" s="19">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F12" s="17">
         <v>2698</v>
@@ -31653,7 +31664,7 @@
         <v>1294</v>
       </c>
       <c r="E18" s="19">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F18" s="17">
         <v>2881</v>
@@ -31684,7 +31695,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>1329</v>
@@ -31714,7 +31725,7 @@
         <v>1314</v>
       </c>
       <c r="E21" s="19">
-        <v>126</v>
+        <v>276</v>
       </c>
       <c r="F21" s="17">
         <v>418</v>
@@ -31903,7 +31914,7 @@
         <v>2369</v>
       </c>
       <c r="E30" s="19">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F30" s="17">
         <v>1709</v>
@@ -32062,7 +32073,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>1296</v>
@@ -32356,13 +32367,13 @@
         <v>2522</v>
       </c>
       <c r="E53" s="19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F53" s="17">
         <v>1804</v>
       </c>
       <c r="G53" s="32" t="s">
-        <v>2828</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75">
@@ -32376,17 +32387,17 @@
         <v>2530</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="E54" s="19">
         <v>0</v>
       </c>
       <c r="F54" s="17"/>
       <c r="G54" s="32" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15.75">
@@ -32400,7 +32411,7 @@
         <v>2530</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="E55" s="19">
         <v>0</v>
@@ -32415,13 +32426,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="E56" s="19">
         <v>0</v>
@@ -32430,10 +32441,10 @@
         <v>50</v>
       </c>
       <c r="G56" s="32" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15.75">
@@ -32483,13 +32494,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="C59" s="32" t="s">
         <v>1296</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="E59" s="84">
         <v>75</v>
@@ -32504,13 +32515,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="32" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="C60" s="32" t="s">
         <v>1358</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="E60" s="84">
         <v>92</v>
@@ -32519,7 +32530,7 @@
         <v>1998</v>
       </c>
       <c r="G60" s="32" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15.75">
@@ -32527,13 +32538,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="32" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="C61" s="32" t="s">
         <v>1297</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="E61" s="84">
         <v>52</v>
@@ -32542,7 +32553,7 @@
         <v>2492</v>
       </c>
       <c r="G61" s="32" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.75">
@@ -32565,7 +32576,7 @@
         <v>228</v>
       </c>
       <c r="G62" s="32" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15.75">
@@ -32580,16 +32591,16 @@
       </c>
       <c r="D63" s="32"/>
       <c r="E63" s="84">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="F63" s="32">
         <v>115</v>
       </c>
       <c r="G63" s="32" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.75">
@@ -32597,13 +32608,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="C64" s="17" t="s">
         <v>1920</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="E64" s="84">
         <v>73</v>
@@ -32618,16 +32629,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="C65" s="17" t="s">
         <v>1920</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="E65" s="84">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F65" s="32">
         <v>251</v>
@@ -32639,13 +32650,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="C66" s="17" t="s">
+        <v>2881</v>
+      </c>
+      <c r="D66" s="17" t="s">
         <v>2882</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>2883</v>
       </c>
       <c r="E66" s="84">
         <v>15</v>
@@ -33186,10 +33197,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -33206,7 +33217,7 @@
         <v>417</v>
       </c>
       <c r="C2" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D2" t="s">
         <v>293</v>
@@ -33226,7 +33237,7 @@
         <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D3" t="s">
         <v>2388</v>
@@ -33246,7 +33257,7 @@
         <v>831</v>
       </c>
       <c r="C4" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D4" t="s">
         <v>2389</v>
@@ -33266,7 +33277,7 @@
         <v>2392</v>
       </c>
       <c r="C5" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D5" t="s">
         <v>2390</v>
@@ -33286,7 +33297,7 @@
         <v>2391</v>
       </c>
       <c r="C6" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D6" t="s">
         <v>2243</v>
@@ -33306,7 +33317,7 @@
         <v>402</v>
       </c>
       <c r="C7" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D7" t="s">
         <v>2429</v>
@@ -33326,10 +33337,10 @@
         <v>834</v>
       </c>
       <c r="C8" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D8" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -33346,7 +33357,7 @@
         <v>2393</v>
       </c>
       <c r="C9" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D9" t="s">
         <v>2394</v>
@@ -33366,7 +33377,7 @@
         <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D10" t="s">
         <v>2395</v>
@@ -33386,7 +33397,7 @@
         <v>183</v>
       </c>
       <c r="C11" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D11" t="s">
         <v>2396</v>
@@ -33395,7 +33406,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -33406,7 +33417,7 @@
         <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D12" t="s">
         <v>2397</v>
@@ -33426,7 +33437,7 @@
         <v>186</v>
       </c>
       <c r="C13" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D13" t="s">
         <v>2398</v>
@@ -33446,7 +33457,7 @@
         <v>2399</v>
       </c>
       <c r="C14" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D14" t="s">
         <v>2400</v>
@@ -33466,13 +33477,13 @@
         <v>2401</v>
       </c>
       <c r="C15" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D15" t="s">
         <v>2447</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F15">
         <v>935</v>
@@ -33486,7 +33497,7 @@
         <v>835</v>
       </c>
       <c r="C16" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D16" t="s">
         <v>2402</v>
@@ -33506,7 +33517,7 @@
         <v>641</v>
       </c>
       <c r="C17" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D17" t="s">
         <v>2403</v>
@@ -33526,13 +33537,13 @@
         <v>410</v>
       </c>
       <c r="C18" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D18" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F18">
         <v>628</v>
@@ -33546,7 +33557,7 @@
         <v>640</v>
       </c>
       <c r="C19" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D19" t="s">
         <v>2404</v>
@@ -33566,7 +33577,7 @@
         <v>609</v>
       </c>
       <c r="C20" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D20" t="s">
         <v>2405</v>
@@ -33586,7 +33597,7 @@
         <v>525</v>
       </c>
       <c r="C21" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D21" t="s">
         <v>2598</v>
@@ -33606,7 +33617,7 @@
         <v>649</v>
       </c>
       <c r="C22" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D22" t="s">
         <v>2407</v>
@@ -33626,7 +33637,7 @@
         <v>2406</v>
       </c>
       <c r="C23" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D23" t="s">
         <v>2408</v>
@@ -33646,7 +33657,7 @@
         <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D24" t="s">
         <v>2409</v>
@@ -33666,7 +33677,7 @@
         <v>605</v>
       </c>
       <c r="C25" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D25" t="s">
         <v>2410</v>
@@ -33686,7 +33697,7 @@
         <v>403</v>
       </c>
       <c r="C26" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D26" t="s">
         <v>2411</v>
@@ -33706,13 +33717,13 @@
         <v>406</v>
       </c>
       <c r="C27" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D27" t="s">
         <v>318</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>701</v>
@@ -33726,7 +33737,7 @@
         <v>401</v>
       </c>
       <c r="C28" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D28" t="s">
         <v>2414</v>
@@ -33746,7 +33757,7 @@
         <v>638</v>
       </c>
       <c r="C29" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D29" t="s">
         <v>2412</v>
@@ -33766,13 +33777,13 @@
         <v>650</v>
       </c>
       <c r="C30" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D30" t="s">
         <v>2413</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F30">
         <v>760</v>
@@ -33786,10 +33797,10 @@
         <v>832</v>
       </c>
       <c r="C31" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D31" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -33806,7 +33817,7 @@
         <v>185</v>
       </c>
       <c r="C32" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D32" t="s">
         <v>2415</v>
@@ -33815,7 +33826,7 @@
         <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -33826,7 +33837,7 @@
         <v>836</v>
       </c>
       <c r="C33" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D33" t="s">
         <v>2416</v>
@@ -33846,7 +33857,7 @@
         <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D34" t="s">
         <v>2417</v>
@@ -33866,7 +33877,7 @@
         <v>2418</v>
       </c>
       <c r="C35" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D35" t="s">
         <v>836</v>
@@ -33875,7 +33886,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -33886,7 +33897,7 @@
         <v>197</v>
       </c>
       <c r="C36" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D36" t="s">
         <v>2420</v>
@@ -33895,7 +33906,7 @@
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -33906,7 +33917,7 @@
         <v>198</v>
       </c>
       <c r="C37" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D37" t="s">
         <v>2421</v>
@@ -33926,7 +33937,7 @@
         <v>999</v>
       </c>
       <c r="C38" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D38" t="s">
         <v>2423</v>
@@ -33946,7 +33957,7 @@
         <v>2422</v>
       </c>
       <c r="C39" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D39" t="s">
         <v>2419</v>
@@ -33966,7 +33977,7 @@
         <v>2424</v>
       </c>
       <c r="C40" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D40" t="s">
         <v>2502</v>
@@ -33986,7 +33997,7 @@
         <v>683</v>
       </c>
       <c r="C41" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D41" t="s">
         <v>1747</v>
@@ -34006,7 +34017,7 @@
         <v>983</v>
       </c>
       <c r="C42" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D42" t="s">
         <v>2402</v>
@@ -34026,7 +34037,7 @@
         <v>652</v>
       </c>
       <c r="C43" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D43" t="s">
         <v>2425</v>
@@ -34046,7 +34057,7 @@
         <v>828</v>
       </c>
       <c r="C44" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D44" t="s">
         <v>2426</v>
@@ -34066,7 +34077,7 @@
         <v>2427</v>
       </c>
       <c r="C45" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D45" t="s">
         <v>779</v>
@@ -34086,13 +34097,13 @@
         <v>188</v>
       </c>
       <c r="C46" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D46" t="s">
         <v>2435</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46">
         <v>956</v>
@@ -34106,7 +34117,7 @@
         <v>187</v>
       </c>
       <c r="C47" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D47" t="s">
         <v>2436</v>
@@ -34126,10 +34137,10 @@
         <v>189</v>
       </c>
       <c r="C48" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D48" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="E48">
         <v>5</v>
@@ -34146,7 +34157,7 @@
         <v>2566</v>
       </c>
       <c r="C49" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D49" t="s">
         <v>2470</v>
@@ -34166,7 +34177,7 @@
         <v>2473</v>
       </c>
       <c r="C50" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D50" t="s">
         <v>2567</v>
@@ -34186,7 +34197,7 @@
         <v>2808</v>
       </c>
       <c r="C51" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D51" t="s">
         <v>2441</v>
@@ -34206,7 +34217,7 @@
         <v>684</v>
       </c>
       <c r="C52" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D52" t="s">
         <v>2568</v>
@@ -34226,10 +34237,10 @@
         <v>103</v>
       </c>
       <c r="C53" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D53" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="E53">
         <v>2</v>
@@ -34246,13 +34257,13 @@
         <v>653</v>
       </c>
       <c r="C54" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D54" t="s">
         <v>2493</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54">
         <v>1193</v>
@@ -34266,7 +34277,7 @@
         <v>447</v>
       </c>
       <c r="C55" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D55" t="s">
         <v>2494</v>
@@ -34286,7 +34297,7 @@
         <v>2495</v>
       </c>
       <c r="C56" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D56" t="s">
         <v>2496</v>
@@ -34306,7 +34317,7 @@
         <v>2498</v>
       </c>
       <c r="C57" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D57" t="s">
         <v>2497</v>
@@ -34326,7 +34337,7 @@
         <v>438</v>
       </c>
       <c r="C58" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D58" t="s">
         <v>2504</v>
@@ -34335,7 +34346,7 @@
         <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -34346,7 +34357,7 @@
         <v>2503</v>
       </c>
       <c r="C59" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D59" t="s">
         <v>2505</v>
@@ -34366,7 +34377,7 @@
         <v>448</v>
       </c>
       <c r="C60" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D60" t="s">
         <v>2506</v>
@@ -34386,7 +34397,7 @@
         <v>639</v>
       </c>
       <c r="C61" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D61" t="s">
         <v>2525</v>
@@ -34406,7 +34417,7 @@
         <v>607</v>
       </c>
       <c r="C62" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -34417,13 +34428,13 @@
         <v>64</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>2929</v>
+      </c>
+      <c r="C63" t="s">
+        <v>3523</v>
+      </c>
+      <c r="D63" t="s">
         <v>2930</v>
-      </c>
-      <c r="C63" t="s">
-        <v>3524</v>
-      </c>
-      <c r="D63" t="s">
-        <v>2931</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -34440,10 +34451,10 @@
         <v>190</v>
       </c>
       <c r="C64" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D64" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -34457,13 +34468,13 @@
         <v>66</v>
       </c>
       <c r="B65" s="6" t="s">
+        <v>3014</v>
+      </c>
+      <c r="C65" t="s">
+        <v>3523</v>
+      </c>
+      <c r="D65" t="s">
         <v>3015</v>
-      </c>
-      <c r="C65" t="s">
-        <v>3524</v>
-      </c>
-      <c r="D65" t="s">
-        <v>3016</v>
       </c>
       <c r="E65">
         <v>2</v>
@@ -34477,13 +34488,13 @@
         <v>67</v>
       </c>
       <c r="B66" s="6" t="s">
+        <v>3016</v>
+      </c>
+      <c r="C66" t="s">
+        <v>3523</v>
+      </c>
+      <c r="D66" t="s">
         <v>3017</v>
-      </c>
-      <c r="C66" t="s">
-        <v>3524</v>
-      </c>
-      <c r="D66" t="s">
-        <v>3018</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -34500,10 +34511,10 @@
         <v>442</v>
       </c>
       <c r="C67" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D67" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -34514,13 +34525,13 @@
         <v>69</v>
       </c>
       <c r="B68" s="6" t="s">
+        <v>3120</v>
+      </c>
+      <c r="C68" t="s">
+        <v>3523</v>
+      </c>
+      <c r="D68" t="s">
         <v>3121</v>
-      </c>
-      <c r="C68" t="s">
-        <v>3524</v>
-      </c>
-      <c r="D68" t="s">
-        <v>3122</v>
       </c>
       <c r="E68">
         <v>2</v>
@@ -34537,7 +34548,7 @@
         <v>430</v>
       </c>
       <c r="C69" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -34554,10 +34565,10 @@
         <v>100</v>
       </c>
       <c r="C70" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D70" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -34568,13 +34579,13 @@
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="6" t="s">
+        <v>3555</v>
+      </c>
+      <c r="C71" t="s">
+        <v>3523</v>
+      </c>
+      <c r="D71" t="s">
         <v>3556</v>
-      </c>
-      <c r="C71" t="s">
-        <v>3524</v>
-      </c>
-      <c r="D71" t="s">
-        <v>3557</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -34601,10 +34612,10 @@
         <v>378</v>
       </c>
       <c r="C73" t="s">
+        <v>3524</v>
+      </c>
+      <c r="D73" t="s">
         <v>3525</v>
-      </c>
-      <c r="D73" t="s">
-        <v>3526</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -34621,10 +34632,10 @@
         <v>892</v>
       </c>
       <c r="C74" t="s">
+        <v>3526</v>
+      </c>
+      <c r="D74" t="s">
         <v>3527</v>
-      </c>
-      <c r="D74" t="s">
-        <v>3528</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -34641,10 +34652,10 @@
         <v>202</v>
       </c>
       <c r="C75" t="s">
+        <v>3528</v>
+      </c>
+      <c r="D75" t="s">
         <v>3529</v>
-      </c>
-      <c r="D75" t="s">
-        <v>3530</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -34661,10 +34672,10 @@
         <v>28</v>
       </c>
       <c r="C76" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="D76" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="E76">
         <v>2</v>
@@ -34681,10 +34692,10 @@
         <v>2628</v>
       </c>
       <c r="C77" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="D77" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -34698,7 +34709,7 @@
         <v>318026</v>
       </c>
       <c r="C78" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="D78" t="s">
         <v>836</v>
@@ -34715,13 +34726,13 @@
         <v>79</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="C79" t="s">
+        <v>3533</v>
+      </c>
+      <c r="D79" t="s">
         <v>3534</v>
-      </c>
-      <c r="D79" t="s">
-        <v>3535</v>
       </c>
       <c r="E79">
         <v>2</v>
@@ -34735,13 +34746,13 @@
         <v>80</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="C80" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D80" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="E80">
         <v>4</v>
@@ -34755,10 +34766,10 @@
         <v>81</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="C81" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="D81" t="s">
         <v>1855</v>
@@ -34775,10 +34786,10 @@
         <v>82</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="C82" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="D82" t="s">
         <v>683</v>
@@ -34808,10 +34819,10 @@
         <v>2623</v>
       </c>
       <c r="C84" t="s">
+        <v>3537</v>
+      </c>
+      <c r="D84" t="s">
         <v>3538</v>
-      </c>
-      <c r="D84" t="s">
-        <v>3539</v>
       </c>
       <c r="E84">
         <v>21</v>
@@ -34828,10 +34839,10 @@
         <v>963</v>
       </c>
       <c r="C85" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D85" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="E85">
         <v>1</v>
@@ -34848,10 +34859,10 @@
         <v>671</v>
       </c>
       <c r="C86" t="s">
+        <v>3540</v>
+      </c>
+      <c r="D86" t="s">
         <v>3541</v>
-      </c>
-      <c r="D86" t="s">
-        <v>3542</v>
       </c>
       <c r="E86">
         <v>10</v>
@@ -34868,7 +34879,7 @@
         <v>2826</v>
       </c>
       <c r="C87" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D87" t="s">
         <v>2417</v>
@@ -34885,10 +34896,10 @@
         <v>88</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="C88" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="D88" t="s">
         <v>836</v>
@@ -34905,13 +34916,13 @@
         <v>89</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C89" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="D89" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="E89">
         <v>9</v>
@@ -34925,13 +34936,13 @@
         <v>90</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="C90" t="s">
+        <v>3543</v>
+      </c>
+      <c r="D90" t="s">
         <v>3544</v>
-      </c>
-      <c r="D90" t="s">
-        <v>3545</v>
       </c>
       <c r="E90">
         <v>1</v>
@@ -34948,10 +34959,10 @@
         <v>8001</v>
       </c>
       <c r="C91" t="s">
+        <v>3545</v>
+      </c>
+      <c r="D91" t="s">
         <v>3546</v>
-      </c>
-      <c r="D91" t="s">
-        <v>3547</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -34962,13 +34973,13 @@
         <v>92</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="C92" t="s">
+        <v>3547</v>
+      </c>
+      <c r="D92" t="s">
         <v>3548</v>
-      </c>
-      <c r="D92" t="s">
-        <v>3549</v>
       </c>
       <c r="E92">
         <v>10</v>
@@ -34982,13 +34993,13 @@
         <v>93</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="C93" t="s">
+        <v>3549</v>
+      </c>
+      <c r="D93" t="s">
         <v>3550</v>
-      </c>
-      <c r="D93" t="s">
-        <v>3551</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -35005,7 +35016,7 @@
         <v>689</v>
       </c>
       <c r="C94" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -35019,7 +35030,7 @@
         <v>663</v>
       </c>
       <c r="C95" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="E95">
         <v>6</v>
@@ -35036,7 +35047,7 @@
         <v>821</v>
       </c>
       <c r="C96" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="E96">
         <v>6</v>
@@ -35053,10 +35064,10 @@
         <v>2569</v>
       </c>
       <c r="C97" t="s">
+        <v>3551</v>
+      </c>
+      <c r="D97" t="s">
         <v>3552</v>
-      </c>
-      <c r="D97" t="s">
-        <v>3553</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -35067,10 +35078,10 @@
     </row>
     <row r="98" spans="1:6">
       <c r="B98" s="6" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
       <c r="C98" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
     </row>
   </sheetData>
@@ -35538,7 +35549,7 @@
     </row>
     <row r="28" spans="2:11">
       <c r="B28" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -35958,10 +35969,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -36095,7 +36106,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>2616</v>
@@ -36652,7 +36663,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>2616</v>
@@ -37973,7 +37984,7 @@
         <v>3</v>
       </c>
       <c r="F107" s="9" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -39019,7 +39030,7 @@
         <v>4</v>
       </c>
       <c r="F158" s="9" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="G158" t="s">
         <v>1485</v>
@@ -39768,7 +39779,7 @@
         <v>9</v>
       </c>
       <c r="F195" s="9" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="G195" t="s">
         <v>1485</v>
@@ -39892,7 +39903,7 @@
         <v>1379</v>
       </c>
       <c r="E201" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>2647</v>
@@ -40064,7 +40075,7 @@
         <v>3</v>
       </c>
       <c r="F209" s="9" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -41386,10 +41397,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -41465,7 +41476,7 @@
       </c>
       <c r="D5" s="38"/>
       <c r="E5" s="35">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5" s="33" t="s">
         <v>2647</v>
@@ -41498,13 +41509,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>847</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="E7" s="35">
         <v>0</v>
@@ -41532,13 +41543,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C9" s="33" t="s">
         <v>3144</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="D9" s="41" t="s">
         <v>3145</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>3146</v>
       </c>
       <c r="E9" s="35">
         <v>0</v>
@@ -41550,13 +41561,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
+        <v>3146</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>3144</v>
+      </c>
+      <c r="D10" s="41" t="s">
         <v>3147</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>3145</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>3148</v>
       </c>
       <c r="E10" s="35">
         <v>0</v>
@@ -41568,13 +41579,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>1895</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="E11" s="35">
         <v>0</v>
@@ -41589,13 +41600,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>1895</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="E12" s="35">
         <v>0</v>
@@ -41610,13 +41621,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="C13" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="E13" s="35">
         <v>0</v>
@@ -41637,7 +41648,7 @@
         <v>1863</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="E14" s="35">
         <v>0</v>
@@ -41652,13 +41663,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="E15" s="35">
         <v>0</v>
@@ -41670,13 +41681,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="C16" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="E16" s="44">
         <v>1</v>
@@ -41692,7 +41703,7 @@
       </c>
       <c r="C17" s="42"/>
       <c r="D17" s="43" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="E17" s="35">
         <v>0</v>
@@ -41710,7 +41721,7 @@
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="43" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="E18" s="44">
         <v>0</v>
@@ -41722,13 +41733,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="C19" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="E19" s="44">
         <v>0</v>
@@ -41743,13 +41754,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="C20" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="E20" s="35">
         <v>0</v>
@@ -41764,13 +41775,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="C21" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="E21" s="44">
         <v>0</v>
@@ -41789,7 +41800,7 @@
       </c>
       <c r="C22" s="42"/>
       <c r="D22" s="43" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="E22" s="44">
         <v>2</v>
@@ -41806,13 +41817,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="C23" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="E23" s="44">
         <v>0</v>
@@ -41827,13 +41838,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="C24" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="E24" s="35">
         <v>0</v>
@@ -41849,7 +41860,7 @@
       </c>
       <c r="C25" s="42"/>
       <c r="D25" s="43" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="E25" s="35">
         <v>0</v>
@@ -41861,13 +41872,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="C26" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="E26" s="44">
         <v>1</v>
@@ -41879,13 +41890,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="42" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="C27" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="E27" s="44">
         <v>0</v>
@@ -41899,13 +41910,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="C28" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="E28" s="44">
         <v>1</v>
@@ -41917,13 +41928,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="C29" s="33" t="s">
         <v>1895</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="E29" s="44">
         <v>0</v>
@@ -41938,13 +41949,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="42" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="C30" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="E30" s="35">
         <v>0</v>
@@ -41958,13 +41969,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="C31" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="E31" s="44">
         <v>0</v>
@@ -41976,13 +41987,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="42" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="C32" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D32" s="43" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="E32" s="44">
         <v>0</v>
@@ -41994,19 +42005,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="42" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="C33" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="E33" s="44">
         <v>1</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="38.25">
@@ -42014,13 +42025,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="42" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="C34" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D34" s="43" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="E34" s="44">
         <v>1</v>
@@ -42034,13 +42045,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="42" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="C35" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D35" s="43" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="E35" s="35">
         <v>0</v>
@@ -42052,13 +42063,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="42" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="C36" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="E36" s="44">
         <v>0</v>
@@ -42070,13 +42081,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="42" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="C37" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="E37" s="44">
         <v>0</v>
@@ -42088,13 +42099,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="42" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="C38" s="46" t="s">
         <v>1895</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="E38" s="35">
         <v>0</v>
@@ -42106,13 +42117,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="42" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="C39" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="E39" s="35">
         <v>0</v>
@@ -42128,7 +42139,7 @@
       </c>
       <c r="C40" s="42"/>
       <c r="D40" s="43" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="E40" s="35">
         <v>0</v>
@@ -42140,13 +42151,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="42" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="C41" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="E41" s="44">
         <v>2</v>
@@ -42155,7 +42166,7 @@
         <v>1914</v>
       </c>
       <c r="H41" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="38.25">
@@ -42163,13 +42174,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="42" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="C42" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="E42" s="35">
         <v>0</v>
@@ -42181,13 +42192,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="42" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="C43" s="42" t="s">
         <v>1895</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="E43" s="44">
         <v>0</v>
@@ -42199,13 +42210,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="42" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C44" s="42" t="s">
         <v>3210</v>
       </c>
-      <c r="C44" s="42" t="s">
-        <v>3211</v>
-      </c>
       <c r="D44" s="43" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="E44" s="35">
         <v>0</v>
@@ -42217,13 +42228,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="42" t="s">
+        <v>3211</v>
+      </c>
+      <c r="C45" s="42" t="s">
         <v>3212</v>
       </c>
-      <c r="C45" s="42" t="s">
-        <v>3213</v>
-      </c>
       <c r="D45" s="43" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="E45" s="44">
         <v>0</v>
@@ -42235,13 +42246,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="C46" s="42" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="E46" s="44">
         <v>0</v>
@@ -42253,13 +42264,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="42" t="s">
+        <v>3214</v>
+      </c>
+      <c r="C47" s="42" t="s">
         <v>3215</v>
       </c>
-      <c r="C47" s="42" t="s">
-        <v>3216</v>
-      </c>
       <c r="D47" s="43" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="E47" s="44">
         <v>0</v>
@@ -42271,13 +42282,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="42" t="s">
+        <v>3216</v>
+      </c>
+      <c r="C48" s="42" t="s">
         <v>3217</v>
       </c>
-      <c r="C48" s="42" t="s">
-        <v>3218</v>
-      </c>
       <c r="D48" s="43" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="E48" s="35">
         <v>0</v>
@@ -42289,13 +42300,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="42" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="C49" s="42" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="E49" s="35">
         <v>0</v>
@@ -42307,7 +42318,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="C50" s="33" t="s">
         <v>1895</v>
@@ -42325,7 +42336,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="C51" s="33" t="s">
         <v>1895</v>
@@ -42343,7 +42354,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="33" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="C52" s="48" t="s">
         <v>1895</v>
@@ -42361,7 +42372,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="C53" s="48" t="s">
         <v>1895</v>
@@ -42381,13 +42392,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="C54" s="48" t="s">
         <v>1895</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="E54" s="35">
         <v>3</v>
@@ -42401,10 +42412,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="33" t="s">
+        <v>3224</v>
+      </c>
+      <c r="C55" s="48" t="s">
         <v>3225</v>
-      </c>
-      <c r="C55" s="48" t="s">
-        <v>3226</v>
       </c>
       <c r="D55" s="38" t="s">
         <v>2680</v>
@@ -42421,10 +42432,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="C56" s="48" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="D56" s="38" t="s">
         <v>2681</v>
@@ -42441,13 +42452,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="33" t="s">
+        <v>3227</v>
+      </c>
+      <c r="C57" s="48" t="s">
         <v>3228</v>
       </c>
-      <c r="C57" s="48" t="s">
-        <v>3229</v>
-      </c>
       <c r="D57" s="38" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="E57" s="35">
         <v>1</v>
@@ -42459,10 +42470,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="33" t="s">
+        <v>3229</v>
+      </c>
+      <c r="C58" s="48" t="s">
         <v>3230</v>
-      </c>
-      <c r="C58" s="48" t="s">
-        <v>3231</v>
       </c>
       <c r="D58" s="38" t="s">
         <v>2682</v>
@@ -42479,10 +42490,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="C59" s="48" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="D59" s="38" t="s">
         <v>2681</v>
@@ -42499,13 +42510,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="C60" s="48" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="E60" s="35">
         <v>1</v>
@@ -42517,7 +42528,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="C61" s="33" t="s">
         <v>1895</v>
@@ -42585,13 +42596,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="C65" s="33" t="s">
         <v>2021</v>
       </c>
       <c r="D65" s="50" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="E65" s="35">
         <v>0</v>
@@ -43036,7 +43047,7 @@
       <c r="C92" s="33"/>
       <c r="D92" s="38"/>
       <c r="E92" s="35">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F92" s="33"/>
       <c r="H92" t="s">
@@ -43534,7 +43545,7 @@
       <c r="C121" s="33"/>
       <c r="D121" s="38"/>
       <c r="E121" s="35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F121" s="33" t="s">
         <v>2588</v>
@@ -43576,10 +43587,10 @@
         <v>1663</v>
       </c>
       <c r="C124" s="33" t="s">
+        <v>3233</v>
+      </c>
+      <c r="D124" s="38" t="s">
         <v>3234</v>
-      </c>
-      <c r="D124" s="38" t="s">
-        <v>3235</v>
       </c>
       <c r="E124" s="35">
         <v>2</v>
@@ -45050,10 +45061,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -45070,10 +45081,10 @@
         <v>1709</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="D2" s="51" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="E2" s="35">
         <v>0</v>
@@ -45106,7 +45117,7 @@
         <v>1762</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="D4" s="33" t="s">
         <v>1763</v>
@@ -45198,7 +45209,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1438</v>
@@ -45214,10 +45225,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
+        <v>3238</v>
+      </c>
+      <c r="C10" s="33" t="s">
         <v>3239</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>3240</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="35">
@@ -45230,10 +45241,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
+        <v>3240</v>
+      </c>
+      <c r="C11" s="33" t="s">
         <v>3241</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>3242</v>
       </c>
       <c r="D11" s="33"/>
       <c r="E11" s="35">
@@ -45246,10 +45257,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
+        <v>3242</v>
+      </c>
+      <c r="C12" s="33" t="s">
         <v>3243</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>3244</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="35">
@@ -45262,10 +45273,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
+        <v>3244</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>3245</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>3246</v>
       </c>
       <c r="D13" s="33"/>
       <c r="E13" s="35">
@@ -45278,10 +45289,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
+        <v>3246</v>
+      </c>
+      <c r="C14" s="33" t="s">
         <v>3247</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>3248</v>
       </c>
       <c r="D14" s="33" t="s">
         <v>177</v>
@@ -45296,10 +45307,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="33" t="s">
+        <v>3248</v>
+      </c>
+      <c r="C15" s="33" t="s">
         <v>3249</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>3250</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="35">
@@ -45312,10 +45323,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="33" t="s">
+        <v>3250</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>3251</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>3252</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="35">
@@ -45328,10 +45339,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="33" t="s">
+        <v>3252</v>
+      </c>
+      <c r="C17" s="33" t="s">
         <v>3253</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>3254</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="35">
@@ -45344,10 +45355,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="33" t="s">
+        <v>3254</v>
+      </c>
+      <c r="C18" s="33" t="s">
         <v>3255</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>3256</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="35">
@@ -45360,10 +45371,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="33" t="s">
+        <v>3256</v>
+      </c>
+      <c r="C19" s="33" t="s">
         <v>3257</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>3258</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="35">
@@ -45376,10 +45387,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="33" t="s">
+        <v>3258</v>
+      </c>
+      <c r="C20" s="33" t="s">
         <v>3259</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>3260</v>
       </c>
       <c r="D20" s="33"/>
       <c r="E20" s="35">
@@ -45392,10 +45403,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
+        <v>3260</v>
+      </c>
+      <c r="C21" s="33" t="s">
         <v>3261</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>3262</v>
       </c>
       <c r="D21" s="33"/>
       <c r="E21" s="35">
@@ -45408,10 +45419,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="35">
@@ -45424,10 +45435,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="35">
@@ -45440,10 +45451,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
+        <v>3264</v>
+      </c>
+      <c r="C24" s="33" t="s">
         <v>3265</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>3266</v>
       </c>
       <c r="D24" s="33"/>
       <c r="E24" s="35">
@@ -45456,10 +45467,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
+        <v>3266</v>
+      </c>
+      <c r="C25" s="33" t="s">
         <v>3267</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>3268</v>
       </c>
       <c r="D25" s="33"/>
       <c r="E25" s="35">
@@ -45472,10 +45483,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
+        <v>3268</v>
+      </c>
+      <c r="C26" s="33" t="s">
         <v>3269</v>
-      </c>
-      <c r="C26" s="33" t="s">
-        <v>3270</v>
       </c>
       <c r="D26" s="33"/>
       <c r="E26" s="35">
@@ -45488,10 +45499,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
+        <v>3270</v>
+      </c>
+      <c r="C27" s="33" t="s">
         <v>3271</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>3272</v>
       </c>
       <c r="D27" s="33"/>
       <c r="E27" s="35">
@@ -45504,10 +45515,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
+        <v>3272</v>
+      </c>
+      <c r="C28" s="33" t="s">
         <v>3273</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>3274</v>
       </c>
       <c r="D28" s="33"/>
       <c r="E28" s="35">
@@ -45894,10 +45905,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="33" t="s">
+        <v>3274</v>
+      </c>
+      <c r="C52" s="33" t="s">
         <v>3275</v>
-      </c>
-      <c r="C52" s="33" t="s">
-        <v>3276</v>
       </c>
       <c r="D52" s="33"/>
       <c r="E52" s="35">
@@ -47414,7 +47425,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="33" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="C146" s="33" t="s">
         <v>1044</v>
@@ -47911,13 +47922,13 @@
         <v>176</v>
       </c>
       <c r="B177" s="33" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="C177" s="33" t="s">
         <v>1075</v>
       </c>
       <c r="D177" s="33" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="E177" s="35">
         <v>7</v>
@@ -48016,14 +48027,14 @@
         <v>182</v>
       </c>
       <c r="B183" s="33" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="C183" s="33" t="s">
         <v>1077</v>
       </c>
       <c r="D183" s="33"/>
       <c r="E183" s="35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F183" s="33"/>
     </row>
@@ -48059,7 +48070,7 @@
       </c>
       <c r="F185" s="33"/>
       <c r="G185" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -48994,7 +49005,7 @@
         <v>1772</v>
       </c>
       <c r="C241" s="33" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="D241" s="33" t="s">
         <v>1569</v>
@@ -49320,7 +49331,7 @@
         <v>1169</v>
       </c>
       <c r="C260" s="33" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="D260" s="33" t="s">
         <v>1170</v>
@@ -49457,7 +49468,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="33" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="C268" s="33"/>
       <c r="D268" s="33"/>
@@ -49969,20 +49980,20 @@
         <v>298</v>
       </c>
       <c r="B299" s="33" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="C299" s="33" t="s">
         <v>1809</v>
       </c>
       <c r="D299" s="33" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="E299" s="1">
         <v>0</v>
       </c>
       <c r="F299" s="33"/>
       <c r="G299" s="35" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -50076,7 +50087,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="33" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="C305" s="33" t="s">
         <v>1991</v>
@@ -50309,10 +50320,10 @@
         <v>1204</v>
       </c>
       <c r="E318" s="35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F318" s="33">
-        <v>1029</v>
+        <v>968</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -50376,13 +50387,13 @@
         <v>1207</v>
       </c>
       <c r="D322" s="33" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="E322" s="35">
         <v>33</v>
       </c>
       <c r="F322" s="33" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -50396,10 +50407,10 @@
         <v>1207</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="E323" s="35">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F323" s="33">
         <v>1050</v>
@@ -50442,13 +50453,13 @@
         <v>325</v>
       </c>
       <c r="B326" s="33" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="C326" s="33" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="D326" s="33" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="E326" s="35">
         <v>0</v>
@@ -50462,7 +50473,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="33" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="C327" s="33" t="s">
         <v>2250</v>
@@ -50472,7 +50483,7 @@
         <v>12</v>
       </c>
       <c r="F327" s="33" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -50480,7 +50491,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="33" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="C328" s="33" t="s">
         <v>2253</v>
@@ -50489,7 +50500,7 @@
         <v>2295</v>
       </c>
       <c r="E328" s="35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F328" s="33">
         <v>7770</v>
@@ -50500,7 +50511,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="33" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="C329" s="33" t="s">
         <v>2253</v>
@@ -50509,7 +50520,7 @@
         <v>2416</v>
       </c>
       <c r="E329" s="35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F329" s="33">
         <v>6204</v>
@@ -50520,10 +50531,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="33" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="C330" s="33" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="D330" s="33" t="s">
         <v>1747</v>
@@ -50540,7 +50551,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="33" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="C331" s="33" t="s">
         <v>2279</v>
@@ -50558,7 +50569,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="33" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="C332" s="33" t="s">
         <v>2292</v>
@@ -50578,7 +50589,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="33" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="C333" s="33" t="s">
         <v>2293</v>
@@ -50598,7 +50609,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="33" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="C334" s="33"/>
       <c r="D334" s="33"/>
@@ -50612,7 +50623,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="33" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="C335" s="33" t="s">
         <v>2292</v>
@@ -50650,7 +50661,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="33" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="C337" s="33" t="s">
         <v>2292</v>
@@ -50668,13 +50679,13 @@
         <v>337</v>
       </c>
       <c r="B338" s="33" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="C338" s="33" t="s">
+        <v>3313</v>
+      </c>
+      <c r="D338" s="33" t="s">
         <v>3314</v>
-      </c>
-      <c r="D338" s="33" t="s">
-        <v>3315</v>
       </c>
       <c r="E338" s="35">
         <v>1</v>
@@ -50688,14 +50699,14 @@
         <v>338</v>
       </c>
       <c r="B339" s="33" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="C339" s="33" t="s">
         <v>2602</v>
       </c>
       <c r="D339" s="33"/>
       <c r="E339" s="35" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="F339" s="33">
         <v>6944</v>
@@ -50706,13 +50717,13 @@
         <v>339</v>
       </c>
       <c r="B340" s="52" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="C340" s="33" t="s">
         <v>2692</v>
       </c>
       <c r="D340" s="33" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="E340" s="35">
         <v>6</v>
@@ -50726,7 +50737,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="33" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="C341" s="33" t="s">
         <v>2298</v>
@@ -50742,7 +50753,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="33" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="C342" s="33" t="s">
         <v>2614</v>
@@ -50760,7 +50771,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="33" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="C343" s="33"/>
       <c r="D343" s="33"/>
@@ -50774,13 +50785,13 @@
         <v>343</v>
       </c>
       <c r="B344" s="33" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="C344" s="33" t="s">
+        <v>3316</v>
+      </c>
+      <c r="D344" s="33" t="s">
         <v>3317</v>
-      </c>
-      <c r="D344" s="33" t="s">
-        <v>3318</v>
       </c>
       <c r="E344" s="35">
         <v>1</v>
@@ -50794,7 +50805,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="33" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="C345" s="33" t="s">
         <v>2614</v>
@@ -50812,7 +50823,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="33" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="C346" s="33" t="s">
         <v>2614</v>
@@ -50830,7 +50841,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="33" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="C347" s="33" t="s">
         <v>2614</v>
@@ -50848,7 +50859,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="33" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="C348" s="33" t="s">
         <v>2692</v>
@@ -50864,7 +50875,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="33" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="C349" s="33" t="s">
         <v>2692</v>
@@ -50882,7 +50893,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="33" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="C350" s="33" t="s">
         <v>2751</v>
@@ -50925,7 +50936,7 @@
       </c>
       <c r="D352" s="33"/>
       <c r="E352" s="35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F352" s="33">
         <v>1433</v>
@@ -50936,7 +50947,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="33" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="C353" s="33"/>
       <c r="D353" s="33"/>
@@ -50984,7 +50995,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="42" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="C356" s="53" t="s">
         <v>2614</v>
@@ -51000,10 +51011,10 @@
         <v>356</v>
       </c>
       <c r="B357" s="53" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="C357" s="53" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="D357" s="33"/>
       <c r="E357" s="35">
@@ -51016,10 +51027,10 @@
         <v>357</v>
       </c>
       <c r="B358" s="33" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="C358" s="53" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="D358" s="33"/>
       <c r="E358" s="35">
@@ -51034,10 +51045,10 @@
         <v>358</v>
       </c>
       <c r="B359" s="33" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="C359" s="53" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="D359" s="33"/>
       <c r="E359" s="35">
@@ -51052,10 +51063,10 @@
         <v>359</v>
       </c>
       <c r="B360" s="33" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="C360" s="33" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="D360" s="33"/>
       <c r="E360" s="35">
@@ -51068,10 +51079,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="33" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="C361" s="33" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="D361" s="33" t="s">
         <v>1855</v>
@@ -51086,7 +51097,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="33" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="C362" s="33" t="s">
         <v>2614</v>
@@ -51104,7 +51115,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="33" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="C363" s="33" t="s">
         <v>2292</v>
@@ -51122,10 +51133,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="33" t="s">
+        <v>2963</v>
+      </c>
+      <c r="C364" s="33" t="s">
         <v>2964</v>
-      </c>
-      <c r="C364" s="33" t="s">
-        <v>2965</v>
       </c>
       <c r="D364" s="33"/>
       <c r="E364" s="35">
@@ -51140,10 +51151,10 @@
         <v>364</v>
       </c>
       <c r="B365" s="33" t="s">
+        <v>2965</v>
+      </c>
+      <c r="C365" s="33" t="s">
         <v>2966</v>
-      </c>
-      <c r="C365" s="33" t="s">
-        <v>2967</v>
       </c>
       <c r="D365" s="33"/>
       <c r="E365" s="35">
@@ -51158,10 +51169,10 @@
         <v>365</v>
       </c>
       <c r="B366" s="33" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="C366" s="33" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="D366" s="33"/>
       <c r="E366" s="35">
@@ -51176,7 +51187,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="33" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="C367" s="33" t="s">
         <v>2614</v>
@@ -51194,10 +51205,10 @@
         <v>367</v>
       </c>
       <c r="B368" s="33" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="C368" s="33" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="D368" s="33"/>
       <c r="E368" s="35">
@@ -51212,10 +51223,10 @@
         <v>368</v>
       </c>
       <c r="B369" s="33" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="C369" s="33" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="D369" s="33"/>
       <c r="E369" s="35">
@@ -51230,10 +51241,10 @@
         <v>369</v>
       </c>
       <c r="B370" s="33" t="s">
+        <v>2994</v>
+      </c>
+      <c r="C370" s="33" t="s">
         <v>2995</v>
-      </c>
-      <c r="C370" s="33" t="s">
-        <v>2996</v>
       </c>
       <c r="D370" s="33"/>
       <c r="E370" s="35">
@@ -51248,7 +51259,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="33" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="C371" s="33" t="s">
         <v>2292</v>
@@ -51266,10 +51277,10 @@
         <v>371</v>
       </c>
       <c r="B372" s="33" t="s">
+        <v>3039</v>
+      </c>
+      <c r="C372" s="33" t="s">
         <v>3040</v>
-      </c>
-      <c r="C372" s="33" t="s">
-        <v>3041</v>
       </c>
       <c r="D372" s="33"/>
       <c r="E372" s="35">
@@ -51284,7 +51295,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="33" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C373" s="33" t="s">
         <v>257</v>
@@ -51302,10 +51313,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="33" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="C374" s="33" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="D374" s="33" t="s">
         <v>1747</v>
@@ -51322,10 +51333,10 @@
         <v>374</v>
       </c>
       <c r="B375" s="33" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="C375" s="33" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="D375" s="33"/>
       <c r="E375" s="35">
@@ -51340,10 +51351,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="33" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="C376" s="33" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="D376" s="33"/>
       <c r="E376" s="35">
@@ -51355,10 +51366,10 @@
     </row>
     <row r="377" spans="1:6">
       <c r="B377" s="34" t="s">
+        <v>3581</v>
+      </c>
+      <c r="C377" s="89" t="s">
         <v>3582</v>
-      </c>
-      <c r="C377" s="89" t="s">
-        <v>3583</v>
       </c>
       <c r="E377" s="1">
         <v>5</v>
@@ -51369,7 +51380,7 @@
     </row>
     <row r="378" spans="1:6">
       <c r="B378" s="34" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="E378" s="1">
         <v>4</v>
@@ -51538,10 +51549,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -51827,7 +51838,7 @@
         <v>2716</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="56">
@@ -51892,7 +51903,7 @@
         <v>5</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="G22" t="s">
         <v>2700</v>
@@ -52120,7 +52131,7 @@
       </c>
       <c r="C35" s="33"/>
       <c r="D35" s="33" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="E35" s="56">
         <v>0</v>
@@ -52369,7 +52380,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C51" s="33" t="s">
         <v>1628</v>
@@ -52506,7 +52517,7 @@
         <v>97</v>
       </c>
       <c r="F58" s="35" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -53063,10 +53074,10 @@
         <v>741</v>
       </c>
       <c r="C90" s="33" t="s">
+        <v>3322</v>
+      </c>
+      <c r="D90" s="33" t="s">
         <v>3323</v>
-      </c>
-      <c r="D90" s="33" t="s">
-        <v>3324</v>
       </c>
       <c r="E90" s="56">
         <v>1</v>
@@ -53103,10 +53114,10 @@
         <v>743</v>
       </c>
       <c r="C92" s="33" t="s">
+        <v>3324</v>
+      </c>
+      <c r="D92" s="33" t="s">
         <v>3325</v>
-      </c>
-      <c r="D92" s="33" t="s">
-        <v>3326</v>
       </c>
       <c r="E92" s="56">
         <v>10</v>
@@ -53184,7 +53195,7 @@
         <v>3</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -53215,7 +53226,7 @@
         <v>2700</v>
       </c>
       <c r="E98" s="56">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F98" s="56">
         <v>1320</v>
@@ -53241,7 +53252,7 @@
         <v>11</v>
       </c>
       <c r="F99" s="35" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -53355,7 +53366,7 @@
         <v>21</v>
       </c>
       <c r="F106" s="35" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -53367,7 +53378,7 @@
       </c>
       <c r="C107" s="33"/>
       <c r="D107" s="33" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="E107" s="56">
         <v>7</v>
@@ -53424,7 +53435,7 @@
         <v>2700</v>
       </c>
       <c r="E110" s="56">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F110" s="35">
         <v>986</v>
@@ -53458,10 +53469,10 @@
         <v>2701</v>
       </c>
       <c r="E112" s="56">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F112" s="35" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -53770,14 +53781,14 @@
         <v>129</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="C130" s="33" t="s">
         <v>1953</v>
       </c>
       <c r="D130" s="33"/>
       <c r="E130" s="56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" s="35">
         <v>1423</v>
@@ -53797,10 +53808,10 @@
         <v>2695</v>
       </c>
       <c r="E131" s="56">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F131" s="35" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -53838,7 +53849,7 @@
         <v>27</v>
       </c>
       <c r="F133" s="35" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -53855,7 +53866,7 @@
         <v>2700</v>
       </c>
       <c r="E134" s="56">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F134" s="35">
         <v>1507</v>
@@ -53898,10 +53909,10 @@
         <v>518894</v>
       </c>
       <c r="E136" s="56">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="F136" s="35" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -53936,7 +53947,7 @@
         <v>1859</v>
       </c>
       <c r="D138" s="33" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="E138" s="56">
         <v>8</v>
@@ -54117,7 +54128,7 @@
         <v>2753</v>
       </c>
       <c r="E148" s="56">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F148" s="35">
         <v>2493</v>
@@ -54180,7 +54191,7 @@
         <v>6</v>
       </c>
       <c r="F151" s="35" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -54191,10 +54202,10 @@
         <v>794</v>
       </c>
       <c r="C152" s="33" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D152" s="33" t="s">
         <v>3329</v>
-      </c>
-      <c r="D152" s="33" t="s">
-        <v>3330</v>
       </c>
       <c r="E152" s="56">
         <v>0</v>
@@ -54267,7 +54278,7 @@
         <v>2700</v>
       </c>
       <c r="E156" s="56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F156" s="35">
         <v>1092</v>
@@ -54367,13 +54378,13 @@
         <v>586</v>
       </c>
       <c r="D161" s="33" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="E161" s="56">
         <v>6</v>
       </c>
       <c r="F161" s="35" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -54499,7 +54510,7 @@
         <v>3</v>
       </c>
       <c r="F168" s="35" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -54548,7 +54559,7 @@
         <v>2702</v>
       </c>
       <c r="E171" s="56">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F171" s="35">
         <v>1186</v>
@@ -54655,7 +54666,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="33" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="C177" s="33" t="s">
         <v>1546</v>
@@ -54682,7 +54693,7 @@
         <v>2700</v>
       </c>
       <c r="E178" s="56">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F178" s="35">
         <v>1545</v>
@@ -54722,10 +54733,10 @@
         <v>2700</v>
       </c>
       <c r="E180" s="56">
-        <v>1</v>
-      </c>
-      <c r="F180" s="35">
-        <v>1245</v>
+        <v>4</v>
+      </c>
+      <c r="F180" s="35" t="s">
+        <v>3606</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -54846,7 +54857,7 @@
         <v>9</v>
       </c>
       <c r="F186" s="35" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -54870,7 +54881,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="33" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="C188" s="33" t="s">
         <v>268</v>
@@ -55042,7 +55053,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="33" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="C197" s="33" t="s">
         <v>1546</v>
@@ -55081,10 +55092,10 @@
         <v>1713</v>
       </c>
       <c r="C199" s="33" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D199" s="33" t="s">
         <v>3332</v>
-      </c>
-      <c r="D199" s="33" t="s">
-        <v>3333</v>
       </c>
       <c r="E199" s="56">
         <v>12</v>
@@ -55118,7 +55129,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="33" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="C201" s="33"/>
       <c r="D201" s="33"/>
@@ -55132,7 +55143,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="33" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="C202" s="33"/>
       <c r="D202" s="33"/>
@@ -55195,10 +55206,10 @@
         <v>2700</v>
       </c>
       <c r="E205" s="56">
-        <v>2</v>
-      </c>
-      <c r="F205" s="35">
-        <v>1199</v>
+        <v>4</v>
+      </c>
+      <c r="F205" s="35" t="s">
+        <v>3605</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -55218,7 +55229,7 @@
         <v>13</v>
       </c>
       <c r="F206" s="35" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -55235,10 +55246,10 @@
         <v>2711</v>
       </c>
       <c r="E207" s="56">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F207" s="35" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -55307,7 +55318,7 @@
         <v>2700</v>
       </c>
       <c r="E211" s="56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F211" s="35">
         <v>1740</v>
@@ -55355,10 +55366,10 @@
         <v>2707</v>
       </c>
       <c r="E214" s="56">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F214" s="35">
-        <v>2525</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -55384,7 +55395,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="33" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="C216" s="33" t="s">
         <v>1953</v>
@@ -55621,10 +55632,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="33" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C229" s="33" t="s">
         <v>2845</v>
-      </c>
-      <c r="C229" s="33" t="s">
-        <v>2846</v>
       </c>
       <c r="D229" s="33"/>
       <c r="E229" s="56">
@@ -55644,10 +55655,10 @@
       <c r="C230" s="33"/>
       <c r="D230" s="33"/>
       <c r="E230" s="56">
-        <v>7</v>
-      </c>
-      <c r="F230" s="35">
-        <v>828</v>
+        <v>17</v>
+      </c>
+      <c r="F230" s="35" t="s">
+        <v>3604</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -55655,7 +55666,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="33" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="C231" s="33"/>
       <c r="D231" s="33"/>
@@ -55663,7 +55674,7 @@
         <v>4</v>
       </c>
       <c r="F231" s="35" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="333" spans="2:5">
@@ -57220,10 +57231,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -57276,7 +57287,7 @@
       </c>
       <c r="D4" s="33"/>
       <c r="E4" s="33">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="F4" s="35">
         <v>146</v>
@@ -57358,7 +57369,7 @@
     <row r="9" spans="1:10">
       <c r="A9" s="33"/>
       <c r="B9" s="33" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1210</v>
@@ -57383,7 +57394,7 @@
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33">
-        <v>122</v>
+        <v>212</v>
       </c>
       <c r="F10" s="35">
         <v>193</v>
@@ -57415,7 +57426,7 @@
         <v>2222</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33">
@@ -57451,10 +57462,10 @@
         <v>1212</v>
       </c>
       <c r="C14" s="33" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D14" s="33" t="s">
         <v>3334</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>3335</v>
       </c>
       <c r="E14" s="42">
         <v>6</v>
@@ -57472,10 +57483,10 @@
         <v>1213</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="E15" s="42">
         <v>7</v>
@@ -57496,7 +57507,7 @@
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F16" s="35">
         <v>400</v>
@@ -57546,7 +57557,7 @@
         <v>1216</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="33">
@@ -57582,10 +57593,10 @@
         <v>2508</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="E21" s="33">
         <v>5</v>
@@ -57602,7 +57613,7 @@
         <v>1450</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="33">
@@ -57674,7 +57685,7 @@
       </c>
       <c r="D26" s="33"/>
       <c r="E26" s="53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F26" s="35">
         <v>1118</v>
@@ -57688,10 +57699,10 @@
         <v>2678</v>
       </c>
       <c r="C27" s="33" t="s">
+        <v>3341</v>
+      </c>
+      <c r="D27" s="33" t="s">
         <v>3342</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>3343</v>
       </c>
       <c r="E27" s="53">
         <v>9</v>
@@ -57708,10 +57719,10 @@
         <v>2052</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="E28" s="60">
         <v>52</v>
@@ -57728,10 +57739,10 @@
         <v>2103</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="E29" s="60">
         <v>42</v>
@@ -57748,10 +57759,10 @@
         <v>2575</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="E30" s="60">
         <v>56</v>
@@ -57768,10 +57779,10 @@
         <v>2053</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="E31" s="60">
         <v>20</v>
@@ -57788,10 +57799,10 @@
         <v>2684</v>
       </c>
       <c r="C32" s="33" t="s">
+        <v>3347</v>
+      </c>
+      <c r="D32" s="33" t="s">
         <v>3348</v>
-      </c>
-      <c r="D32" s="33" t="s">
-        <v>3349</v>
       </c>
       <c r="E32" s="60">
         <v>4</v>
@@ -57829,7 +57840,7 @@
         <v>2142</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="E34" s="60">
         <v>28</v>
@@ -57846,7 +57857,7 @@
         <v>2442</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="D35" s="33">
         <v>239</v>
@@ -57866,10 +57877,10 @@
         <v>2661</v>
       </c>
       <c r="C36" s="33" t="s">
+        <v>3351</v>
+      </c>
+      <c r="D36" s="33" t="s">
         <v>3352</v>
-      </c>
-      <c r="D36" s="33" t="s">
-        <v>3353</v>
       </c>
       <c r="E36" s="33">
         <v>5</v>
@@ -57883,13 +57894,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="D37" s="33" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="E37" s="33">
         <v>1</v>
@@ -57931,7 +57942,7 @@
         <v>4</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -58009,7 +58020,7 @@
         <v>15</v>
       </c>
       <c r="F43" s="35" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -58035,13 +58046,13 @@
         <v>45</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="E45" s="60">
         <v>95</v>
@@ -58055,11 +58066,11 @@
         <v>46</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="C46" s="33"/>
       <c r="D46" s="33" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="E46" s="60">
         <v>2</v>
@@ -58073,11 +58084,11 @@
         <v>47</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="C47" s="33"/>
       <c r="D47" s="33" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="E47" s="60">
         <v>0</v>
@@ -58089,7 +58100,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="C48" s="33"/>
       <c r="D48" s="33"/>
@@ -58162,7 +58173,7 @@
         <v>1223</v>
       </c>
       <c r="D52" s="33" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="E52" s="42">
         <v>32</v>
@@ -58236,7 +58247,7 @@
         <v>2378</v>
       </c>
       <c r="D56" s="33" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="E56" s="42">
         <v>8</v>
@@ -58508,7 +58519,7 @@
         <v>2378</v>
       </c>
       <c r="D72" s="33" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="E72" s="42">
         <v>8</v>
@@ -58528,7 +58539,7 @@
         <v>1223</v>
       </c>
       <c r="D73" s="33" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="E73" s="42">
         <v>3</v>
@@ -58631,10 +58642,10 @@
         <v>1255</v>
       </c>
       <c r="C79" s="33" t="s">
+        <v>3362</v>
+      </c>
+      <c r="D79" s="33" t="s">
         <v>3363</v>
-      </c>
-      <c r="D79" s="33" t="s">
-        <v>3364</v>
       </c>
       <c r="E79" s="33">
         <v>17</v>
@@ -58686,7 +58697,7 @@
         <v>2378</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="E82" s="33">
         <v>4</v>
@@ -58703,10 +58714,10 @@
         <v>1259</v>
       </c>
       <c r="C83" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D83" s="33" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="E83" s="33">
         <v>39</v>
@@ -58723,13 +58734,13 @@
         <v>2748</v>
       </c>
       <c r="C84" s="33" t="s">
+        <v>3366</v>
+      </c>
+      <c r="D84" s="33" t="s">
         <v>3367</v>
       </c>
-      <c r="D84" s="33" t="s">
-        <v>3368</v>
-      </c>
       <c r="E84" s="33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F84" s="35">
         <v>410</v>
@@ -58743,10 +58754,10 @@
         <v>1260</v>
       </c>
       <c r="C85" s="33" t="s">
+        <v>3368</v>
+      </c>
+      <c r="D85" s="33" t="s">
         <v>3369</v>
-      </c>
-      <c r="D85" s="33" t="s">
-        <v>3370</v>
       </c>
       <c r="E85" s="33">
         <v>104</v>
@@ -58766,7 +58777,7 @@
         <v>2378</v>
       </c>
       <c r="D86" s="33" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="E86" s="33">
         <v>0</v>
@@ -58878,7 +58889,7 @@
         <v>3</v>
       </c>
       <c r="F92" s="61" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -58892,7 +58903,7 @@
         <v>1223</v>
       </c>
       <c r="D93" s="33" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="E93" s="33">
         <v>3</v>
@@ -58939,16 +58950,16 @@
         <v>99</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="C96" s="33" t="s">
         <v>1223</v>
       </c>
       <c r="D96" s="33" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="E96" s="33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F96" s="35">
         <v>746</v>
@@ -58987,7 +58998,7 @@
         <v>35</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -59056,10 +59067,10 @@
         <v>2173</v>
       </c>
       <c r="C102" s="33" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="D102" s="33" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="E102" s="33">
         <v>13</v>
@@ -59076,13 +59087,13 @@
         <v>2208</v>
       </c>
       <c r="C103" s="33" t="s">
+        <v>3372</v>
+      </c>
+      <c r="D103" s="33" t="s">
         <v>3373</v>
       </c>
-      <c r="D103" s="33" t="s">
-        <v>3374</v>
-      </c>
       <c r="E103" s="60">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F103" s="33">
         <v>401</v>
@@ -59096,10 +59107,10 @@
         <v>2079</v>
       </c>
       <c r="C104" s="33" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="D104" s="33" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="E104" s="60">
         <v>16</v>
@@ -59116,7 +59127,7 @@
         <v>1969</v>
       </c>
       <c r="C105" s="33" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="D105" s="33" t="s">
         <v>1517</v>
@@ -59157,7 +59168,7 @@
         <v>2477</v>
       </c>
       <c r="D107" s="33" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="E107" s="33">
         <v>9</v>
@@ -59250,7 +59261,7 @@
         <v>1685</v>
       </c>
       <c r="E112" s="33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F112" s="35">
         <v>396</v>
@@ -59267,7 +59278,7 @@
         <v>2171</v>
       </c>
       <c r="D113" s="33" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="E113" s="33">
         <v>3</v>
@@ -59351,10 +59362,10 @@
         <v>122</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="C118" s="33" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="D118" s="33" t="s">
         <v>1569</v>
@@ -59443,7 +59454,7 @@
         <v>1276</v>
       </c>
       <c r="D123" s="57" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="E123" s="33">
         <v>3</v>
@@ -59483,10 +59494,10 @@
         <v>1280</v>
       </c>
       <c r="C125" s="33" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="D125" s="42" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="E125" s="33">
         <v>0</v>
@@ -59514,7 +59525,7 @@
     <row r="127" spans="1:8">
       <c r="A127" s="33"/>
       <c r="B127" s="33" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="C127" s="33" t="s">
         <v>1276</v>
@@ -59591,10 +59602,10 @@
         <v>2235</v>
       </c>
       <c r="C131" s="33" t="s">
+        <v>3377</v>
+      </c>
+      <c r="D131" s="33" t="s">
         <v>3378</v>
-      </c>
-      <c r="D131" s="33" t="s">
-        <v>3379</v>
       </c>
       <c r="E131" s="33">
         <v>0</v>
@@ -59627,13 +59638,13 @@
         <v>1404</v>
       </c>
       <c r="C133" s="33" t="s">
+        <v>3379</v>
+      </c>
+      <c r="D133" s="33" t="s">
         <v>3380</v>
       </c>
-      <c r="D133" s="33" t="s">
-        <v>3381</v>
-      </c>
       <c r="E133" s="33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F133" s="33">
         <v>1478</v>
@@ -59650,7 +59661,7 @@
         <v>1276</v>
       </c>
       <c r="D134" s="33" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="E134" s="33">
         <v>10</v>
@@ -59700,13 +59711,13 @@
         <v>144</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="C137" s="33" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="D137" s="33" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="E137" s="33">
         <v>11</v>
@@ -59786,7 +59797,7 @@
         <v>1276</v>
       </c>
       <c r="D141" s="33" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="E141" s="35">
         <v>4</v>
@@ -59810,7 +59821,7 @@
         <v>1855</v>
       </c>
       <c r="E142" s="35">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="F142" s="33">
         <v>371</v>
@@ -59877,7 +59888,7 @@
         <v>1276</v>
       </c>
       <c r="D146" s="33" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="E146" s="33">
         <v>0</v>
@@ -59924,10 +59935,10 @@
         <v>2735</v>
       </c>
       <c r="C149" s="33" t="s">
+        <v>3382</v>
+      </c>
+      <c r="D149" s="33" t="s">
         <v>3383</v>
-      </c>
-      <c r="D149" s="33" t="s">
-        <v>3384</v>
       </c>
       <c r="E149" s="33">
         <v>1</v>
@@ -59944,10 +59955,10 @@
         <v>2736</v>
       </c>
       <c r="C150" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D150" s="33" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="E150" s="33">
         <v>1</v>
@@ -60060,7 +60071,7 @@
         <v>175</v>
       </c>
       <c r="B157" s="95" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="C157" s="95"/>
       <c r="D157" s="95"/>
@@ -60075,7 +60086,7 @@
         <v>2016</v>
       </c>
       <c r="C158" s="33" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="D158" s="33" t="s">
         <v>836</v>
@@ -60095,7 +60106,7 @@
         <v>1811</v>
       </c>
       <c r="C159" s="33" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="D159" s="33" t="s">
         <v>1855</v>
@@ -60115,7 +60126,7 @@
         <v>2102</v>
       </c>
       <c r="C160" s="33" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="D160" s="33" t="s">
         <v>2419</v>
@@ -60135,10 +60146,10 @@
         <v>2376</v>
       </c>
       <c r="C161" s="57" t="s">
+        <v>3393</v>
+      </c>
+      <c r="D161" s="57" t="s">
         <v>3394</v>
-      </c>
-      <c r="D161" s="57" t="s">
-        <v>3395</v>
       </c>
       <c r="E161" s="33">
         <v>41</v>
@@ -60155,10 +60166,10 @@
         <v>1997</v>
       </c>
       <c r="C162" s="33" t="s">
+        <v>3395</v>
+      </c>
+      <c r="D162" s="33" t="s">
         <v>3396</v>
-      </c>
-      <c r="D162" s="33" t="s">
-        <v>3397</v>
       </c>
       <c r="E162" s="33">
         <v>149</v>
@@ -60175,10 +60186,10 @@
         <v>2258</v>
       </c>
       <c r="C163" s="33" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="D163" s="33" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="E163" s="60">
         <v>22</v>
@@ -60195,10 +60206,10 @@
         <v>2363</v>
       </c>
       <c r="C164" s="33" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="D164" s="33" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="E164" s="60">
         <v>4</v>
@@ -60215,16 +60226,16 @@
         <v>1996</v>
       </c>
       <c r="C165" s="33" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="D165" s="33" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="E165" s="33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F165" s="35" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -60235,16 +60246,16 @@
         <v>1998</v>
       </c>
       <c r="C166" s="33" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="D166" s="33" t="s">
         <v>2549</v>
       </c>
       <c r="E166" s="33">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F166" s="35" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -60255,13 +60266,13 @@
         <v>1221</v>
       </c>
       <c r="C167" s="33" t="s">
+        <v>3400</v>
+      </c>
+      <c r="D167" s="33" t="s">
         <v>3401</v>
       </c>
-      <c r="D167" s="33" t="s">
-        <v>3402</v>
-      </c>
       <c r="E167" s="33">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F167" s="35">
         <v>451</v>
@@ -60275,10 +60286,10 @@
         <v>1938</v>
       </c>
       <c r="C168" s="33" t="s">
+        <v>3402</v>
+      </c>
+      <c r="D168" s="33" t="s">
         <v>3403</v>
-      </c>
-      <c r="D168" s="33" t="s">
-        <v>3404</v>
       </c>
       <c r="E168" s="33">
         <v>16</v>
@@ -60295,10 +60306,10 @@
         <v>2336</v>
       </c>
       <c r="C169" s="33" t="s">
+        <v>3404</v>
+      </c>
+      <c r="D169" s="33" t="s">
         <v>3405</v>
-      </c>
-      <c r="D169" s="33" t="s">
-        <v>3406</v>
       </c>
       <c r="E169" s="33">
         <v>2</v>
@@ -60315,10 +60326,10 @@
         <v>2322</v>
       </c>
       <c r="C170" s="33" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="D170" s="33" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="E170" s="33">
         <v>6</v>
@@ -60335,10 +60346,10 @@
         <v>2480</v>
       </c>
       <c r="C171" s="33" t="s">
+        <v>3407</v>
+      </c>
+      <c r="D171" s="33" t="s">
         <v>3408</v>
-      </c>
-      <c r="D171" s="33" t="s">
-        <v>3409</v>
       </c>
       <c r="E171" s="33">
         <v>60</v>
@@ -60355,13 +60366,13 @@
         <v>2484</v>
       </c>
       <c r="C172" s="33" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="D172" s="33" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="E172" s="33">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F172" s="35">
         <v>759</v>
@@ -60375,10 +60386,10 @@
         <v>2483</v>
       </c>
       <c r="C173" s="33" t="s">
+        <v>3410</v>
+      </c>
+      <c r="D173" s="33" t="s">
         <v>3411</v>
-      </c>
-      <c r="D173" s="33" t="s">
-        <v>3412</v>
       </c>
       <c r="E173" s="33">
         <v>18</v>
@@ -60395,7 +60406,7 @@
         <v>2335</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="D174" s="33" t="s">
         <v>2525</v>
@@ -60415,10 +60426,10 @@
         <v>2642</v>
       </c>
       <c r="C175" s="33" t="s">
+        <v>3412</v>
+      </c>
+      <c r="D175" s="33" t="s">
         <v>3413</v>
-      </c>
-      <c r="D175" s="33" t="s">
-        <v>3414</v>
       </c>
       <c r="E175" s="33">
         <v>20</v>
@@ -60435,10 +60446,10 @@
         <v>2739</v>
       </c>
       <c r="C176" s="33" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="D176" s="33" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="E176" s="33">
         <v>3</v>
@@ -60455,10 +60466,10 @@
         <v>2644</v>
       </c>
       <c r="C177" s="33" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="D177" s="33" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="E177" s="33">
         <v>62</v>
@@ -60472,11 +60483,11 @@
         <v>198</v>
       </c>
       <c r="B178" s="33" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="C178" s="33"/>
       <c r="D178" s="33" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="E178" s="33">
         <v>4</v>
@@ -60493,10 +60504,10 @@
         <v>2741</v>
       </c>
       <c r="C179" s="33" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="D179" s="33" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="E179" s="33">
         <v>17</v>
@@ -60510,7 +60521,7 @@
         <v>203</v>
       </c>
       <c r="B180" s="95" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="C180" s="95"/>
       <c r="D180" s="95"/>
@@ -60525,10 +60536,10 @@
         <v>1251</v>
       </c>
       <c r="C181" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D181" s="33" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="E181" s="33">
         <v>0</v>
@@ -60545,7 +60556,7 @@
         <v>1252</v>
       </c>
       <c r="C182" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D182" s="33" t="s">
         <v>290</v>
@@ -60565,7 +60576,7 @@
         <v>1261</v>
       </c>
       <c r="C183" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D183" s="33" t="s">
         <v>318</v>
@@ -60585,10 +60596,10 @@
         <v>1542</v>
       </c>
       <c r="C184" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="E184" s="33">
         <v>18</v>
@@ -60605,10 +60616,10 @@
         <v>1262</v>
       </c>
       <c r="C185" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D185" s="33" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="E185" s="33">
         <v>21</v>
@@ -60625,7 +60636,7 @@
         <v>1263</v>
       </c>
       <c r="C186" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D186" s="33" t="s">
         <v>2419</v>
@@ -60645,7 +60656,7 @@
         <v>1265</v>
       </c>
       <c r="C187" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D187" s="33" t="s">
         <v>2243</v>
@@ -60665,10 +60676,10 @@
         <v>1266</v>
       </c>
       <c r="C188" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D188" s="33" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="E188" s="33">
         <v>62</v>
@@ -60685,10 +60696,10 @@
         <v>1267</v>
       </c>
       <c r="C189" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D189" s="33" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="E189" s="33">
         <v>120</v>
@@ -60705,16 +60716,16 @@
         <v>1539</v>
       </c>
       <c r="C190" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D190" s="33" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="E190" s="33">
         <v>39</v>
       </c>
       <c r="F190" s="35" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -60725,10 +60736,10 @@
         <v>1886</v>
       </c>
       <c r="C191" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D191" s="33" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="E191" s="33">
         <v>27</v>
@@ -60745,7 +60756,7 @@
         <v>1270</v>
       </c>
       <c r="C192" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D192" s="33"/>
       <c r="E192" s="33">
@@ -60763,13 +60774,13 @@
         <v>1775</v>
       </c>
       <c r="C193" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D193" s="33" t="s">
         <v>2795</v>
       </c>
       <c r="E193" s="42">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F193" s="35">
         <v>170</v>
@@ -60783,16 +60794,16 @@
         <v>1697</v>
       </c>
       <c r="C194" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D194" s="33" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="E194" s="42">
         <v>82</v>
       </c>
       <c r="F194" s="35" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -60803,7 +60814,7 @@
         <v>1426</v>
       </c>
       <c r="C195" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D195" s="33" t="s">
         <v>1856</v>
@@ -60821,10 +60832,10 @@
         <v>1268</v>
       </c>
       <c r="C196" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D196" s="33" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="E196" s="33">
         <v>13</v>
@@ -60841,10 +60852,10 @@
         <v>1269</v>
       </c>
       <c r="C197" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D197" s="33" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="E197" s="33">
         <v>0</v>
@@ -60861,10 +60872,10 @@
         <v>2786</v>
       </c>
       <c r="C198" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D198" s="33" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="E198" s="33">
         <v>22</v>
@@ -60881,13 +60892,13 @@
         <v>1999</v>
       </c>
       <c r="C199" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D199" s="33" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="E199" s="33">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F199" s="35">
         <v>155</v>
@@ -60901,7 +60912,7 @@
         <v>2354</v>
       </c>
       <c r="C200" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D200" s="33" t="s">
         <v>2435</v>
@@ -60921,16 +60932,16 @@
         <v>2337</v>
       </c>
       <c r="C201" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D201" s="33" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="E201" s="33">
         <v>30</v>
       </c>
       <c r="F201" s="35" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -60941,16 +60952,16 @@
         <v>2323</v>
       </c>
       <c r="C202" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D202" s="33" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="E202" s="33">
         <v>10</v>
       </c>
       <c r="F202" s="35" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -60961,10 +60972,10 @@
         <v>2324</v>
       </c>
       <c r="C203" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D203" s="33" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="E203" s="33">
         <v>3</v>
@@ -60981,10 +60992,10 @@
         <v>2326</v>
       </c>
       <c r="C204" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D204" s="33" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="E204" s="33">
         <v>6</v>
@@ -60996,16 +61007,16 @@
     <row r="205" spans="1:6">
       <c r="A205" s="33"/>
       <c r="B205" s="33" t="s">
+        <v>3571</v>
+      </c>
+      <c r="C205" s="33" t="s">
+        <v>3362</v>
+      </c>
+      <c r="D205" s="33" t="s">
         <v>3572</v>
       </c>
-      <c r="C205" s="33" t="s">
-        <v>3363</v>
-      </c>
-      <c r="D205" s="33" t="s">
-        <v>3573</v>
-      </c>
       <c r="E205" s="33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F205" s="35">
         <v>300</v>
@@ -61019,10 +61030,10 @@
         <v>2327</v>
       </c>
       <c r="C206" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D206" s="33" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="E206" s="33">
         <v>16</v>
@@ -61039,7 +61050,7 @@
         <v>2555</v>
       </c>
       <c r="C207" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D207" s="33" t="s">
         <v>2405</v>
@@ -61059,10 +61070,10 @@
         <v>2475</v>
       </c>
       <c r="C208" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D208" s="33" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="E208" s="33">
         <v>17</v>
@@ -61079,13 +61090,13 @@
         <v>2486</v>
       </c>
       <c r="C209" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D209" s="33" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="E209" s="33">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F209" s="35">
         <v>345</v>
@@ -61099,10 +61110,10 @@
         <v>2236</v>
       </c>
       <c r="C210" s="33" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D210" s="33" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="E210" s="33">
         <v>2</v>
@@ -61114,7 +61125,7 @@
         <v>237</v>
       </c>
       <c r="B211" s="95" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="C211" s="95"/>
       <c r="D211" s="95"/>
@@ -61129,7 +61140,7 @@
         <v>1967</v>
       </c>
       <c r="C212" s="33" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="D212" s="33" t="s">
         <v>836</v>
@@ -61149,10 +61160,10 @@
         <v>2364</v>
       </c>
       <c r="C213" s="33" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="D213" s="33" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="E213" s="33">
         <v>30</v>
@@ -61169,16 +61180,16 @@
         <v>2308</v>
       </c>
       <c r="C214" s="33" t="s">
+        <v>3436</v>
+      </c>
+      <c r="D214" s="33" t="s">
         <v>3437</v>
-      </c>
-      <c r="D214" s="33" t="s">
-        <v>3438</v>
       </c>
       <c r="E214" s="33">
         <v>18</v>
       </c>
       <c r="F214" s="33" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -61189,10 +61200,10 @@
         <v>2309</v>
       </c>
       <c r="C215" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D215" s="33" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="E215" s="33">
         <v>10</v>
@@ -61209,10 +61220,10 @@
         <v>2310</v>
       </c>
       <c r="C216" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D216" s="33" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="E216" s="33">
         <v>24</v>
@@ -61229,10 +61240,10 @@
         <v>2311</v>
       </c>
       <c r="C217" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D217" s="33" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="E217" s="33">
         <v>17</v>
@@ -61249,7 +61260,7 @@
         <v>2312</v>
       </c>
       <c r="C218" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D218" s="33" t="s">
         <v>2389</v>
@@ -61269,10 +61280,10 @@
         <v>2313</v>
       </c>
       <c r="C219" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D219" s="33" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="E219" s="33">
         <v>9</v>
@@ -61289,10 +61300,10 @@
         <v>2466</v>
       </c>
       <c r="C220" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D220" s="33" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="E220" s="33">
         <v>17</v>
@@ -61309,7 +61320,7 @@
         <v>2314</v>
       </c>
       <c r="C221" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D221" s="33" t="s">
         <v>2402</v>
@@ -61318,7 +61329,7 @@
         <v>8</v>
       </c>
       <c r="F221" s="33" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -61329,10 +61340,10 @@
         <v>2355</v>
       </c>
       <c r="C222" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D222" s="33" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="E222" s="33">
         <v>12</v>
@@ -61349,10 +61360,10 @@
         <v>2315</v>
       </c>
       <c r="C223" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D223" s="33" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="E223" s="33">
         <v>22</v>
@@ -61369,10 +61380,10 @@
         <v>2316</v>
       </c>
       <c r="C224" s="33" t="s">
+        <v>3444</v>
+      </c>
+      <c r="D224" s="33" t="s">
         <v>3445</v>
-      </c>
-      <c r="D224" s="33" t="s">
-        <v>3446</v>
       </c>
       <c r="E224" s="33">
         <v>12</v>
@@ -61386,13 +61397,13 @@
         <v>253</v>
       </c>
       <c r="B225" s="33" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="C225" s="33" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="D225" s="33" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="E225" s="33">
         <v>6</v>
@@ -61409,10 +61420,10 @@
         <v>2317</v>
       </c>
       <c r="C226" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D226" s="33" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="E226" s="33">
         <v>24</v>
@@ -61429,10 +61440,10 @@
         <v>2318</v>
       </c>
       <c r="C227" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D227" s="33" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="E227" s="33">
         <v>31</v>
@@ -61449,10 +61460,10 @@
         <v>2319</v>
       </c>
       <c r="C228" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D228" s="33" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="E228" s="33">
         <v>0</v>
@@ -61469,10 +61480,10 @@
         <v>2320</v>
       </c>
       <c r="C229" s="33" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="D229" s="33" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="E229" s="33">
         <v>17</v>
@@ -61489,10 +61500,10 @@
         <v>2321</v>
       </c>
       <c r="C230" s="33" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="D230" s="33" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="E230" s="33">
         <v>32</v>
@@ -61509,10 +61520,10 @@
         <v>2330</v>
       </c>
       <c r="C231" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D231" s="33" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="E231" s="33">
         <v>7</v>
@@ -61529,10 +61540,10 @@
         <v>1679</v>
       </c>
       <c r="C232" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D232" s="33" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="E232" s="33">
         <v>27</v>
@@ -61549,16 +61560,16 @@
         <v>2342</v>
       </c>
       <c r="C233" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D233" s="33" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="E233" s="33">
         <v>12</v>
       </c>
       <c r="F233" s="35" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -61569,10 +61580,10 @@
         <v>2362</v>
       </c>
       <c r="C234" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D234" s="33" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="E234" s="33">
         <v>29</v>
@@ -61589,10 +61600,10 @@
         <v>2343</v>
       </c>
       <c r="C235" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D235" s="33" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="E235" s="33">
         <v>48</v>
@@ -61609,10 +61620,10 @@
         <v>2344</v>
       </c>
       <c r="C236" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D236" s="33" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="E236" s="33">
         <v>36</v>
@@ -61629,10 +61640,10 @@
         <v>2356</v>
       </c>
       <c r="C237" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D237" s="33" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="E237" s="33">
         <v>26</v>
@@ -61649,10 +61660,10 @@
         <v>2478</v>
       </c>
       <c r="C238" s="33" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="D238" s="33" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="E238" s="33">
         <v>22</v>
@@ -61669,10 +61680,10 @@
         <v>2485</v>
       </c>
       <c r="C239" s="33" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="D239" s="33" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="E239" s="33">
         <v>13</v>
@@ -61686,13 +61697,13 @@
         <v>268</v>
       </c>
       <c r="B240" s="33" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="C240" s="33" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="D240" s="33" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="E240" s="33">
         <v>7</v>
@@ -61709,10 +61720,10 @@
         <v>2531</v>
       </c>
       <c r="C241" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D241" s="33" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="E241" s="33">
         <v>20</v>
@@ -61729,7 +61740,7 @@
         <v>2650</v>
       </c>
       <c r="C242" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D242" s="33" t="s">
         <v>2435</v>
@@ -61749,7 +61760,7 @@
         <v>2732</v>
       </c>
       <c r="C243" s="33" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="D243" s="33" t="s">
         <v>2420</v>
@@ -61769,10 +61780,10 @@
         <v>2733</v>
       </c>
       <c r="C244" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D244" s="33" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="E244" s="33">
         <v>4</v>
@@ -61789,10 +61800,10 @@
         <v>2734</v>
       </c>
       <c r="C245" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="E245" s="33">
         <v>4</v>
@@ -61809,10 +61820,10 @@
         <v>2737</v>
       </c>
       <c r="C246" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="E246" s="33">
         <v>63</v>
@@ -61829,13 +61840,13 @@
         <v>2738</v>
       </c>
       <c r="C247" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D247" s="33" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="E247" s="33">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F247" s="35">
         <v>338</v>
@@ -61849,10 +61860,10 @@
         <v>2740</v>
       </c>
       <c r="C248" s="33" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D248" s="33" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="E248" s="33">
         <v>6</v>
@@ -61869,14 +61880,14 @@
         <v>2813</v>
       </c>
       <c r="C249" s="33" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="D249" s="33"/>
       <c r="E249" s="33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F249" s="35" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -61884,13 +61895,13 @@
         <v>279</v>
       </c>
       <c r="B250" s="33" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="C250" s="33" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="D250" s="33" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="E250" s="33">
         <v>10</v>
@@ -61904,13 +61915,13 @@
         <v>280</v>
       </c>
       <c r="B251" s="33" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="C251" s="33" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="D251" s="33" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="E251" s="33">
         <v>18</v>
@@ -61924,13 +61935,13 @@
         <v>281</v>
       </c>
       <c r="B252" s="33" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="C252" s="33" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="D252" s="33" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="E252" s="33">
         <v>8</v>
@@ -61944,13 +61955,13 @@
         <v>282</v>
       </c>
       <c r="B253" s="33" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="C253" s="33" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="D253" s="33" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="E253" s="33">
         <v>12</v>
@@ -61964,13 +61975,13 @@
         <v>283</v>
       </c>
       <c r="B254" s="33" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="C254" s="33" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="D254" s="33" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="E254" s="33">
         <v>10</v>
@@ -61984,10 +61995,10 @@
         <v>284</v>
       </c>
       <c r="B255" s="33" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="C255" s="33" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="D255" s="33" t="s">
         <v>2421</v>
@@ -62004,13 +62015,13 @@
         <v>285</v>
       </c>
       <c r="B256" s="33" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="C256" s="33" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="D256" s="33" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="E256" s="33">
         <v>27</v>
@@ -62024,10 +62035,10 @@
         <v>286</v>
       </c>
       <c r="B257" s="33" t="s">
+        <v>2974</v>
+      </c>
+      <c r="C257" s="33" t="s">
         <v>2975</v>
-      </c>
-      <c r="C257" s="33" t="s">
-        <v>2976</v>
       </c>
       <c r="D257" s="33"/>
       <c r="E257" s="33">
@@ -62042,13 +62053,13 @@
         <v>287</v>
       </c>
       <c r="B258" s="33" t="s">
+        <v>2979</v>
+      </c>
+      <c r="C258" s="33" t="s">
+        <v>2975</v>
+      </c>
+      <c r="D258" s="33" t="s">
         <v>2980</v>
-      </c>
-      <c r="C258" s="33" t="s">
-        <v>2976</v>
-      </c>
-      <c r="D258" s="33" t="s">
-        <v>2981</v>
       </c>
       <c r="E258" s="33">
         <v>16</v>
@@ -62062,13 +62073,13 @@
         <v>288</v>
       </c>
       <c r="B259" s="33" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="C259" s="33" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="D259" s="33" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="E259" s="33">
         <v>4</v>
@@ -62082,13 +62093,13 @@
         <v>289</v>
       </c>
       <c r="B260" s="33" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="C260" s="33" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="D260" s="33" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="E260" s="33">
         <v>22</v>
@@ -62102,13 +62113,13 @@
         <v>290</v>
       </c>
       <c r="B261" s="33" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="C261" s="33" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="D261" s="33" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="E261" s="33">
         <v>3</v>
@@ -62122,13 +62133,13 @@
         <v>291</v>
       </c>
       <c r="B262" s="33" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="C262" s="33" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="D262" s="33" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="E262" s="33">
         <v>0</v>
@@ -62142,13 +62153,13 @@
         <v>292</v>
       </c>
       <c r="B263" s="33" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C263" s="33" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="D263" s="33" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="E263" s="33">
         <v>1</v>
@@ -62162,13 +62173,13 @@
         <v>293</v>
       </c>
       <c r="B264" s="33" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="C264" s="33" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="D264" s="33" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="E264" s="33">
         <v>13</v>
@@ -62182,13 +62193,13 @@
         <v>294</v>
       </c>
       <c r="B265" s="33" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="C265" s="33" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="D265" s="33" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="E265" s="33">
         <v>5</v>
@@ -62200,13 +62211,13 @@
     <row r="266" spans="1:7">
       <c r="A266" s="33"/>
       <c r="B266" s="33" t="s">
+        <v>3561</v>
+      </c>
+      <c r="C266" s="33" t="s">
+        <v>2975</v>
+      </c>
+      <c r="D266" s="33" t="s">
         <v>3562</v>
-      </c>
-      <c r="C266" s="33" t="s">
-        <v>2976</v>
-      </c>
-      <c r="D266" s="33" t="s">
-        <v>3563</v>
       </c>
       <c r="E266" s="33">
         <v>17</v>
@@ -62228,7 +62239,7 @@
         <v>299</v>
       </c>
       <c r="B268" s="95" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="C268" s="95"/>
       <c r="D268" s="95"/>
@@ -62246,7 +62257,7 @@
         <v>2377</v>
       </c>
       <c r="D269" s="33" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="E269" s="33">
         <v>9</v>
@@ -62292,7 +62303,7 @@
         <v>12</v>
       </c>
       <c r="F271" s="33" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="G271" s="2">
         <v>399</v>
@@ -62309,7 +62320,7 @@
         <v>2377</v>
       </c>
       <c r="D272" s="33" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="E272" s="33">
         <v>17</v>
@@ -62329,7 +62340,7 @@
         <v>2377</v>
       </c>
       <c r="D273" s="33" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="E273" s="33">
         <v>13</v>
@@ -62349,7 +62360,7 @@
         <v>2377</v>
       </c>
       <c r="D274" s="33" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="E274" s="33">
         <v>7</v>
@@ -62363,13 +62374,13 @@
         <v>308</v>
       </c>
       <c r="B275" s="33" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="C275" s="33" t="s">
         <v>2377</v>
       </c>
       <c r="D275" s="33" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="E275" s="33">
         <v>18</v>
@@ -62389,10 +62400,10 @@
         <v>2377</v>
       </c>
       <c r="D276" s="33" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="E276" s="33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F276" s="33">
         <v>260</v>
@@ -62409,7 +62420,7 @@
         <v>2377</v>
       </c>
       <c r="D277" s="33" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="E277" s="33">
         <v>5</v>
@@ -62443,7 +62454,7 @@
         <v>312</v>
       </c>
       <c r="B279" s="33" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="C279" s="33" t="s">
         <v>2377</v>
@@ -62489,13 +62500,13 @@
         <v>2377</v>
       </c>
       <c r="D281" s="33" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="E281" s="33">
         <v>27</v>
       </c>
       <c r="F281" s="35" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -62503,13 +62514,13 @@
         <v>315</v>
       </c>
       <c r="B282" s="33" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="C282" s="33" t="s">
         <v>2377</v>
       </c>
       <c r="D282" s="33" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="E282" s="33">
         <v>9</v>
@@ -62523,13 +62534,13 @@
         <v>316</v>
       </c>
       <c r="B283" s="33" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="C283" s="33" t="s">
         <v>2377</v>
       </c>
       <c r="D283" s="33" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="E283" s="33">
         <v>14</v>
@@ -62543,13 +62554,13 @@
         <v>317</v>
       </c>
       <c r="B284" s="33" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="C284" s="33" t="s">
         <v>2377</v>
       </c>
       <c r="D284" s="33" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="E284" s="33">
         <v>7</v>
@@ -62563,13 +62574,13 @@
         <v>318</v>
       </c>
       <c r="B285" s="33" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="C285" s="33" t="s">
         <v>2377</v>
       </c>
       <c r="D285" s="33" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="E285" s="33">
         <v>17</v>
@@ -62583,13 +62594,13 @@
         <v>319</v>
       </c>
       <c r="B286" s="33" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="C286" s="33" t="s">
         <v>2377</v>
       </c>
       <c r="D286" s="33" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="E286" s="33">
         <v>8</v>
@@ -62603,13 +62614,13 @@
         <v>320</v>
       </c>
       <c r="B287" s="33" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="C287" s="33" t="s">
         <v>2377</v>
       </c>
       <c r="D287" s="33" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="E287" s="33">
         <v>0</v>
@@ -62623,13 +62634,13 @@
         <v>321</v>
       </c>
       <c r="B288" s="33" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C288" s="33" t="s">
         <v>2377</v>
       </c>
       <c r="D288" s="33" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="E288" s="33">
         <v>5</v>
@@ -62643,13 +62654,13 @@
         <v>322</v>
       </c>
       <c r="B289" s="33" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="C289" s="33" t="s">
         <v>2377</v>
       </c>
       <c r="D289" s="33" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="E289" s="33">
         <v>9</v>
@@ -62663,7 +62674,7 @@
         <v>323</v>
       </c>
       <c r="B290" s="33" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="C290" s="33" t="s">
         <v>2377</v>
@@ -62683,7 +62694,7 @@
         <v>324</v>
       </c>
       <c r="B291" s="33" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="C291" s="33" t="s">
         <v>2377</v>
@@ -62699,7 +62710,7 @@
         <v>325</v>
       </c>
       <c r="B292" s="33" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="C292" s="33" t="s">
         <v>2377</v>
@@ -62754,10 +62765,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -63637,7 +63648,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -63655,7 +63666,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -63997,7 +64008,7 @@
     <row r="69" spans="1:8">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -64289,10 +64300,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -64335,7 +64346,7 @@
         <v>290</v>
       </c>
       <c r="E3" s="35">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F3" s="33">
         <v>1465</v>
@@ -64508,13 +64519,13 @@
         <v>23</v>
       </c>
       <c r="B13" s="33" t="s">
+        <v>2893</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>2894</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="D13" s="33" t="s">
         <v>2895</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>2896</v>
       </c>
       <c r="E13" s="35">
         <v>37</v>
@@ -64528,13 +64539,13 @@
         <v>25</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="C14" s="33" t="s">
+        <v>2945</v>
+      </c>
+      <c r="D14" s="33" t="s">
         <v>2946</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>2947</v>
       </c>
       <c r="E14" s="35">
         <v>10</v>
@@ -64548,13 +64559,13 @@
         <v>27</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>1903</v>
       </c>
       <c r="D15" s="63" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="E15" s="35">
         <v>60</v>
@@ -64577,7 +64588,7 @@
         <v>2501</v>
       </c>
       <c r="E16" s="35">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F16" s="33">
         <v>182</v>
@@ -64588,7 +64599,7 @@
         <v>31</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="C17" s="33" t="s">
         <v>2500</v>
@@ -64600,7 +64611,7 @@
         <v>48</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -64630,10 +64641,10 @@
         <v>1903</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="E19" s="35">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F19" s="33">
         <v>338</v>
@@ -64650,7 +64661,7 @@
         <v>1903</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="E20" s="35">
         <v>57</v>
@@ -64670,7 +64681,7 @@
         <v>1903</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="E21" s="35">
         <v>78</v>
@@ -64690,7 +64701,7 @@
         <v>1902</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="E22" s="35">
         <v>89</v>
@@ -64710,7 +64721,7 @@
         <v>1902</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="E23" s="35">
         <v>11</v>
@@ -64724,7 +64735,7 @@
         <v>49</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="C24" s="33" t="s">
         <v>296</v>
@@ -64862,7 +64873,7 @@
         <v>66</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
@@ -64894,7 +64905,7 @@
         <v>71</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C34" s="33" t="s">
         <v>1510</v>
@@ -64946,7 +64957,7 @@
         <v>80</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="C37" s="33"/>
       <c r="D37" s="33"/>
@@ -64960,13 +64971,13 @@
         <v>82</v>
       </c>
       <c r="B38" s="33" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="E38" s="35">
         <v>10</v>
@@ -64980,13 +64991,13 @@
         <v>83</v>
       </c>
       <c r="B39" s="33" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="E39" s="35">
         <v>15</v>
@@ -65000,13 +65011,13 @@
         <v>84</v>
       </c>
       <c r="B40" s="33" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="C40" s="33" t="s">
+        <v>3128</v>
+      </c>
+      <c r="D40" s="33" t="s">
         <v>3129</v>
-      </c>
-      <c r="D40" s="33" t="s">
-        <v>3130</v>
       </c>
       <c r="E40" s="35">
         <v>65</v>
@@ -65020,7 +65031,7 @@
         <v>85</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="C41" s="33"/>
       <c r="D41" s="33"/>
@@ -65034,13 +65045,13 @@
         <v>86</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="E42" s="35">
         <v>10</v>
@@ -65054,7 +65065,7 @@
         <v>87</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="C43" s="33"/>
       <c r="D43" s="33"/>
@@ -65098,10 +65109,10 @@
         <v>2374</v>
       </c>
       <c r="C1" s="85" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D1" s="85" t="s">
         <v>3141</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>3142</v>
       </c>
       <c r="E1" s="86" t="s">
         <v>1978</v>
@@ -65133,10 +65144,10 @@
         <v>410</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="E3" s="35">
         <v>0</v>
@@ -65154,7 +65165,7 @@
         <v>2192</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="E4" s="35">
         <v>10</v>
@@ -65171,7 +65182,7 @@
         <v>412</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="D5" s="33"/>
       <c r="E5" s="35">
@@ -65226,7 +65237,7 @@
         <v>2192</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="E8" s="35">
         <v>3</v>
@@ -65262,7 +65273,7 @@
         <v>2192</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="E10" s="35">
         <v>1</v>
@@ -65503,10 +65514,10 @@
         <v>430</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="E24" s="35">
         <v>36</v>
@@ -65523,7 +65534,7 @@
         <v>431</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="D25" s="33" t="s">
         <v>432</v>
@@ -65541,7 +65552,7 @@
         <v>433</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="D26" s="33"/>
       <c r="E26" s="35">
@@ -65575,7 +65586,7 @@
         <v>434</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="D28" s="33"/>
       <c r="E28" s="35">
@@ -65591,7 +65602,7 @@
         <v>435</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="D29" s="33"/>
       <c r="E29" s="35">
@@ -65609,7 +65620,7 @@
         <v>436</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="D30" s="33"/>
       <c r="E30" s="35">
@@ -65627,7 +65638,7 @@
         <v>1552</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="D31" s="33"/>
       <c r="E31" s="35">
@@ -65677,7 +65688,7 @@
         <v>437</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="D34" s="33"/>
       <c r="E34" s="35">
@@ -65695,7 +65706,7 @@
         <v>438</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="D35" s="33"/>
       <c r="E35" s="35">
@@ -65929,7 +65940,7 @@
         <v>2353</v>
       </c>
       <c r="E48" s="35">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F48" s="33">
         <v>420</v>
@@ -65952,7 +65963,7 @@
         <v>44</v>
       </c>
       <c r="F49" s="33" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="23.25">
@@ -65960,7 +65971,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="96" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="C50" s="96"/>
       <c r="D50" s="96"/>
@@ -67008,7 +67019,7 @@
       <c r="C115" s="33"/>
       <c r="D115" s="33"/>
       <c r="E115" s="35">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F115" s="33">
         <v>840</v>

--- a/backend/public/BOSCH_STOCK1.xlsx
+++ b/backend/public/BOSCH_STOCK1.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5822" uniqueCount="3608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5826" uniqueCount="3612">
   <si>
     <t>0 433 175 443</t>
   </si>
@@ -10886,9 +10886,6 @@
     <t xml:space="preserve"> crank senssor 026121032</t>
   </si>
   <si>
-    <t>1135/1046</t>
-  </si>
-  <si>
     <t>F 002 H23 561</t>
   </si>
   <si>
@@ -10974,6 +10971,21 @@
   </si>
   <si>
     <t>NET- 1400</t>
+  </si>
+  <si>
+    <t>935/862</t>
+  </si>
+  <si>
+    <t>1465/1350</t>
+  </si>
+  <si>
+    <t>1739/1603</t>
+  </si>
+  <si>
+    <t>1399/1289</t>
+  </si>
+  <si>
+    <t>1092/1006</t>
   </si>
 </sst>
 </file>
@@ -14593,7 +14605,7 @@
       </c>
       <c r="D112" s="17"/>
       <c r="E112" s="19">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F112" s="17"/>
       <c r="G112" s="17"/>
@@ -15671,7 +15683,7 @@
     <row r="165" spans="1:10" ht="15.75">
       <c r="A165" s="17"/>
       <c r="B165" s="17" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="C165" s="18" t="s">
         <v>3142</v>
@@ -15737,7 +15749,7 @@
         <v>2164</v>
       </c>
       <c r="E168" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F168" s="17" t="s">
         <v>2163</v>
@@ -16489,7 +16501,7 @@
         <v>102</v>
       </c>
       <c r="F15" s="74" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="G15" s="74"/>
       <c r="H15" s="74"/>
@@ -16511,7 +16523,7 @@
         <v>70</v>
       </c>
       <c r="F16" s="74" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="G16" s="74"/>
       <c r="H16" s="74"/>
@@ -17634,7 +17646,7 @@
         <v>1790</v>
       </c>
       <c r="E75" s="75">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F75" s="74" t="s">
         <v>3110</v>
@@ -18322,7 +18334,7 @@
         <v>2719</v>
       </c>
       <c r="E112" s="75">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F112" s="75">
         <v>1246</v>
@@ -18826,7 +18838,7 @@
         <v>2072</v>
       </c>
       <c r="E137" s="75">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F137" s="74" t="s">
         <v>2788</v>
@@ -18926,7 +18938,7 @@
         <v>822</v>
       </c>
       <c r="E142" s="75">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F142" s="74">
         <v>687</v>
@@ -19281,7 +19293,7 @@
         <v>460</v>
       </c>
       <c r="F159" s="74" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="G159" s="74"/>
       <c r="H159" s="74"/>
@@ -19429,7 +19441,7 @@
         <v>6</v>
       </c>
       <c r="F167" s="74" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="G167" s="74" t="s">
         <v>1553</v>
@@ -20603,7 +20615,7 @@
         <v>4</v>
       </c>
       <c r="F225" s="74" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="G225" s="74"/>
       <c r="H225" s="74"/>
@@ -20647,7 +20659,7 @@
         <v>2</v>
       </c>
       <c r="F227" s="74" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="G227" s="74"/>
       <c r="H227" s="74"/>
@@ -20986,10 +20998,10 @@
         <v>1855</v>
       </c>
       <c r="E243" s="75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F243" s="74" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="G243" s="74"/>
       <c r="H243" s="74"/>
@@ -21409,7 +21421,7 @@
         <v>2</v>
       </c>
       <c r="F262" s="74" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="G262" s="74"/>
       <c r="H262" s="74"/>
@@ -21772,10 +21784,10 @@
         <v>2897</v>
       </c>
       <c r="E279" s="75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F279" s="74">
-        <v>9794</v>
+        <v>9890</v>
       </c>
       <c r="G279" s="74"/>
       <c r="H279" s="74"/>
@@ -21854,7 +21866,7 @@
       </c>
       <c r="D283" s="74"/>
       <c r="E283" s="75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F283" s="74">
         <v>11455</v>
@@ -22064,7 +22076,7 @@
     </row>
     <row r="294" spans="1:8" ht="21">
       <c r="B294" s="90" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="C294" s="74" t="s">
         <v>843</v>
@@ -22261,7 +22273,7 @@
         <v>3496</v>
       </c>
       <c r="E6" s="71">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="F6" s="70">
         <v>182</v>
@@ -22449,7 +22461,7 @@
         <v>3504</v>
       </c>
       <c r="E14" s="71">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="F14" s="70">
         <v>351</v>
@@ -22595,7 +22607,7 @@
         <v>2227</v>
       </c>
       <c r="E21" s="71">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F21" s="69">
         <v>482</v>
@@ -22785,7 +22797,7 @@
         <v>1719</v>
       </c>
       <c r="E30" s="71">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F30" s="70">
         <v>360</v>
@@ -31393,7 +31405,7 @@
         <v>1292</v>
       </c>
       <c r="E5" s="19">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F5" s="17">
         <v>1098</v>
@@ -31475,7 +31487,7 @@
         <v>1300</v>
       </c>
       <c r="E9" s="19">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="F9" s="17">
         <v>378</v>
@@ -31746,7 +31758,7 @@
         <v>1314</v>
       </c>
       <c r="E22" s="19">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F22" s="17">
         <v>2056</v>
@@ -32373,7 +32385,7 @@
         <v>1804</v>
       </c>
       <c r="G53" s="32" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75">
@@ -32429,7 +32441,7 @@
         <v>3106</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="D56" s="17" t="s">
         <v>3105</v>
@@ -32591,7 +32603,7 @@
       </c>
       <c r="D63" s="32"/>
       <c r="E63" s="84">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F63" s="32">
         <v>115</v>
@@ -32600,7 +32612,7 @@
         <v>3077</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.75">
@@ -33403,10 +33415,10 @@
         <v>2396</v>
       </c>
       <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
-        <v>3578</v>
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>1135</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -33483,10 +33495,10 @@
         <v>2447</v>
       </c>
       <c r="E15">
-        <v>9</v>
-      </c>
-      <c r="F15">
-        <v>935</v>
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>3607</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -33543,7 +33555,7 @@
         <v>3013</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F18">
         <v>628</v>
@@ -33883,10 +33895,10 @@
         <v>836</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -33923,10 +33935,10 @@
         <v>2421</v>
       </c>
       <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>1465</v>
+        <v>6</v>
+      </c>
+      <c r="F37" t="s">
+        <v>3608</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -34003,10 +34015,10 @@
         <v>1747</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>953</v>
+        <v>906</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -34346,7 +34358,7 @@
         <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -38043,7 +38055,7 @@
         <v>1353</v>
       </c>
       <c r="E110" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F110" s="9"/>
       <c r="G110" t="s">
@@ -47741,7 +47753,7 @@
       </c>
       <c r="D165" s="33"/>
       <c r="E165" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165" s="33"/>
     </row>
@@ -48405,7 +48417,7 @@
         <v>2562</v>
       </c>
       <c r="E205" s="35">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F205" s="33"/>
       <c r="G205" t="s">
@@ -49331,7 +49343,7 @@
         <v>1169</v>
       </c>
       <c r="C260" s="33" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="D260" s="33" t="s">
         <v>1170</v>
@@ -49473,7 +49485,7 @@
       <c r="C268" s="33"/>
       <c r="D268" s="33"/>
       <c r="E268" s="35">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F268" s="33"/>
     </row>
@@ -49795,7 +49807,7 @@
       </c>
       <c r="D288" s="33"/>
       <c r="E288" s="35">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F288" s="33"/>
     </row>
@@ -49901,7 +49913,7 @@
       </c>
       <c r="D294" s="33"/>
       <c r="E294" s="35">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F294" s="33">
         <v>696</v>
@@ -49919,7 +49931,7 @@
       </c>
       <c r="D295" s="33"/>
       <c r="E295" s="35">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F295" s="33">
         <v>696</v>
@@ -50282,7 +50294,7 @@
       </c>
       <c r="D316" s="33"/>
       <c r="E316" s="35">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F316" s="33">
         <v>865</v>
@@ -51366,10 +51378,10 @@
     </row>
     <row r="377" spans="1:6">
       <c r="B377" s="34" t="s">
+        <v>3580</v>
+      </c>
+      <c r="C377" s="89" t="s">
         <v>3581</v>
-      </c>
-      <c r="C377" s="89" t="s">
-        <v>3582</v>
       </c>
       <c r="E377" s="1">
         <v>5</v>
@@ -51380,7 +51392,7 @@
     </row>
     <row r="378" spans="1:6">
       <c r="B378" s="34" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="E378" s="1">
         <v>4</v>
@@ -52630,7 +52642,7 @@
         <v>2700</v>
       </c>
       <c r="E65" s="56">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F65" s="35" t="s">
         <v>2760</v>
@@ -53100,7 +53112,7 @@
         <v>2704</v>
       </c>
       <c r="E91" s="56">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F91" s="35">
         <v>855</v>
@@ -53195,7 +53207,7 @@
         <v>3</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -53366,7 +53378,7 @@
         <v>21</v>
       </c>
       <c r="F106" s="35" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -53846,7 +53858,7 @@
         <v>2703</v>
       </c>
       <c r="E133" s="56">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F133" s="35" t="s">
         <v>3569</v>
@@ -53866,7 +53878,7 @@
         <v>2700</v>
       </c>
       <c r="E134" s="56">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F134" s="35">
         <v>1507</v>
@@ -53909,7 +53921,7 @@
         <v>518894</v>
       </c>
       <c r="E136" s="56">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F136" s="35" t="s">
         <v>3567</v>
@@ -54108,7 +54120,7 @@
         <v>2696</v>
       </c>
       <c r="E147" s="56">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="F147" s="35">
         <v>554</v>
@@ -54168,7 +54180,7 @@
         <v>2699</v>
       </c>
       <c r="E150" s="56">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F150" s="35">
         <v>893</v>
@@ -54278,10 +54290,10 @@
         <v>2700</v>
       </c>
       <c r="E156" s="56">
-        <v>3</v>
-      </c>
-      <c r="F156" s="35">
-        <v>1092</v>
+        <v>5</v>
+      </c>
+      <c r="F156" s="35" t="s">
+        <v>3611</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -54559,7 +54571,7 @@
         <v>2702</v>
       </c>
       <c r="E171" s="56">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F171" s="35">
         <v>1186</v>
@@ -54736,7 +54748,7 @@
         <v>4</v>
       </c>
       <c r="F180" s="35" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -54811,10 +54823,10 @@
         <v>2706</v>
       </c>
       <c r="E184" s="56">
-        <v>2</v>
-      </c>
-      <c r="F184" s="35">
-        <v>1739</v>
+        <v>6</v>
+      </c>
+      <c r="F184" s="35" t="s">
+        <v>3609</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -55118,10 +55130,10 @@
         <v>2694</v>
       </c>
       <c r="E200" s="56">
-        <v>8</v>
-      </c>
-      <c r="F200" s="35">
-        <v>1399</v>
+        <v>17</v>
+      </c>
+      <c r="F200" s="35" t="s">
+        <v>3610</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -55209,7 +55221,7 @@
         <v>4</v>
       </c>
       <c r="F205" s="35" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -55249,7 +55261,7 @@
         <v>40</v>
       </c>
       <c r="F207" s="35" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -55658,7 +55670,7 @@
         <v>17</v>
       </c>
       <c r="F230" s="35" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -57394,7 +57406,7 @@
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="F10" s="35">
         <v>193</v>
@@ -57412,7 +57424,7 @@
       </c>
       <c r="D11" s="33"/>
       <c r="E11" s="33">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F11" s="35">
         <v>184</v>
@@ -57430,7 +57442,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="F12" s="35">
         <v>184</v>
@@ -57617,7 +57629,7 @@
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="33">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F22" s="35">
         <v>363</v>
@@ -57843,7 +57855,7 @@
         <v>3349</v>
       </c>
       <c r="E34" s="60">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F34" s="35">
         <v>1118</v>
@@ -58578,7 +58590,7 @@
       </c>
       <c r="D75" s="33"/>
       <c r="E75" s="42">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F75" s="35">
         <v>124</v>
@@ -58700,7 +58712,7 @@
         <v>3364</v>
       </c>
       <c r="E82" s="33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F82" s="35">
         <v>417</v>
@@ -58923,7 +58935,7 @@
       </c>
       <c r="D94" s="33"/>
       <c r="E94" s="33">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F94" s="35">
         <v>288</v>
@@ -59525,7 +59537,7 @@
     <row r="127" spans="1:8">
       <c r="A127" s="33"/>
       <c r="B127" s="33" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="C127" s="33" t="s">
         <v>1276</v>
@@ -59569,7 +59581,7 @@
       </c>
       <c r="D129" s="33"/>
       <c r="E129" s="33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F129" s="35">
         <v>3546</v>
@@ -59821,7 +59833,7 @@
         <v>1855</v>
       </c>
       <c r="E142" s="35">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F142" s="33">
         <v>371</v>
@@ -60060,7 +60072,7 @@
       </c>
       <c r="D156" s="33"/>
       <c r="E156" s="35">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="F156" s="33">
         <v>150</v>
@@ -60172,7 +60184,7 @@
         <v>3396</v>
       </c>
       <c r="E162" s="33">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F162" s="35">
         <v>686</v>
@@ -60272,7 +60284,7 @@
         <v>3401</v>
       </c>
       <c r="E167" s="33">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="F167" s="35">
         <v>451</v>
@@ -60352,7 +60364,7 @@
         <v>3408</v>
       </c>
       <c r="E171" s="33">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F171" s="35">
         <v>649</v>
@@ -60372,7 +60384,7 @@
         <v>3409</v>
       </c>
       <c r="E172" s="33">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F172" s="35">
         <v>759</v>
@@ -60562,7 +60574,7 @@
         <v>290</v>
       </c>
       <c r="E182" s="33">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="F182" s="35">
         <v>170</v>
@@ -60582,7 +60594,7 @@
         <v>318</v>
       </c>
       <c r="E183" s="33">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F183" s="35">
         <v>186</v>
@@ -60622,7 +60634,7 @@
         <v>3419</v>
       </c>
       <c r="E185" s="33">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F185" s="35">
         <v>627</v>
@@ -60702,7 +60714,7 @@
         <v>3421</v>
       </c>
       <c r="E189" s="33">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="F189" s="33">
         <v>210</v>
@@ -60725,7 +60737,7 @@
         <v>39</v>
       </c>
       <c r="F190" s="35" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -60898,7 +60910,7 @@
         <v>3427</v>
       </c>
       <c r="E199" s="33">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="F199" s="35">
         <v>155</v>
@@ -61486,7 +61498,7 @@
         <v>3450</v>
       </c>
       <c r="E229" s="33">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F229" s="35">
         <v>309</v>
@@ -62024,7 +62036,7 @@
         <v>3056</v>
       </c>
       <c r="E256" s="33">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F256" s="35">
         <v>546</v>
@@ -62220,7 +62232,7 @@
         <v>3562</v>
       </c>
       <c r="E266" s="33">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F266" s="35">
         <v>536</v>
@@ -62500,7 +62512,7 @@
         <v>2377</v>
       </c>
       <c r="D281" s="33" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="E281" s="33">
         <v>27</v>
@@ -62623,7 +62635,7 @@
         <v>2997</v>
       </c>
       <c r="E287" s="33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F287" s="35">
         <v>259</v>
@@ -63543,7 +63555,7 @@
         <v>372</v>
       </c>
       <c r="E44" s="62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F44" s="4">
         <v>1312</v>
@@ -63869,7 +63881,7 @@
         <v>344</v>
       </c>
       <c r="E61" s="62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="4">
         <v>2214</v>
@@ -64472,7 +64484,7 @@
         <v>2243</v>
       </c>
       <c r="E10" s="35">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F10" s="33">
         <v>641</v>
@@ -64611,7 +64623,7 @@
         <v>48</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -64644,7 +64656,7 @@
         <v>2957</v>
       </c>
       <c r="E19" s="35">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F19" s="33">
         <v>338</v>
@@ -65256,7 +65268,7 @@
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="35">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="F9" s="33" t="s">
         <v>2810</v>
@@ -65310,7 +65322,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="35">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="F12" s="33">
         <v>155</v>
@@ -67019,7 +67031,7 @@
       <c r="C115" s="33"/>
       <c r="D115" s="33"/>
       <c r="E115" s="35">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F115" s="33">
         <v>840</v>

--- a/backend/public/BOSCH_STOCK1.xlsx
+++ b/backend/public/BOSCH_STOCK1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="741"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="12240" windowHeight="9240" tabRatio="741" firstSheet="9" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="ELEMENT" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5828" uniqueCount="3612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5829" uniqueCount="3613">
   <si>
     <t>0 433 175 443</t>
   </si>
@@ -10986,6 +10986,9 @@
   </si>
   <si>
     <t>1 004 011 602</t>
+  </si>
+  <si>
+    <t>**</t>
   </si>
 </sst>
 </file>
@@ -15749,7 +15752,7 @@
         <v>2164</v>
       </c>
       <c r="E168" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F168" s="17" t="s">
         <v>2163</v>
@@ -16498,7 +16501,7 @@
         <v>2700</v>
       </c>
       <c r="E15" s="75">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F15" s="74" t="s">
         <v>3593</v>
@@ -17604,7 +17607,7 @@
         <v>412</v>
       </c>
       <c r="E73" s="75">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F73" s="74">
         <v>1530</v>
@@ -19290,7 +19293,7 @@
       </c>
       <c r="D159" s="74"/>
       <c r="E159" s="75">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F159" s="74" t="s">
         <v>3598</v>
@@ -20678,7 +20681,7 @@
         <v>2438</v>
       </c>
       <c r="E228" s="75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F228" s="74">
         <v>14552</v>
@@ -22103,35 +22106,35 @@
     </customSheetView>
   </customSheetViews>
   <conditionalFormatting sqref="D144">
-    <cfRule type="duplicateValues" dxfId="31" priority="17" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="18" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="19" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="20" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="21" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="22" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="17" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="18" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="19" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="22" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="duplicateValues" dxfId="24" priority="8" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="9" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="10" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="11" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="12" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="13" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="9" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="10" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="11" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="13" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G50">
-    <cfRule type="duplicateValues" dxfId="17" priority="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="3" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="4" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="5" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="6" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G62">
-    <cfRule type="duplicateValues" dxfId="10" priority="15" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -22969,12 +22972,14 @@
       </c>
       <c r="D39" s="71"/>
       <c r="E39" s="71">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="F39" s="70">
         <v>408</v>
       </c>
-      <c r="G39" s="69"/>
+      <c r="G39" s="69" t="s">
+        <v>3612</v>
+      </c>
       <c r="H39" s="69"/>
     </row>
     <row r="40" spans="1:8" ht="21">
@@ -31363,7 +31368,7 @@
         <v>1292</v>
       </c>
       <c r="E3" s="19">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="F3" s="17">
         <v>362</v>
@@ -31384,7 +31389,7 @@
         <v>1292</v>
       </c>
       <c r="E4" s="19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" s="17">
         <v>1772</v>
@@ -31426,7 +31431,7 @@
         <v>1293</v>
       </c>
       <c r="E6" s="19">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="F6" s="17">
         <v>2595</v>
@@ -31447,7 +31452,7 @@
         <v>1292</v>
       </c>
       <c r="E7" s="19">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F7" s="17">
         <v>3385</v>
@@ -31508,7 +31513,7 @@
         <v>1300</v>
       </c>
       <c r="E10" s="19">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F10" s="17">
         <v>1100</v>
@@ -31550,7 +31555,7 @@
         <v>1300</v>
       </c>
       <c r="E12" s="19">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="F12" s="17">
         <v>2698</v>
@@ -31737,7 +31742,7 @@
         <v>1314</v>
       </c>
       <c r="E21" s="19">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="F21" s="17">
         <v>418</v>
@@ -31758,7 +31763,7 @@
         <v>1314</v>
       </c>
       <c r="E22" s="19">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F22" s="17">
         <v>2056</v>
@@ -31800,7 +31805,7 @@
         <v>1311</v>
       </c>
       <c r="E24" s="19">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="F24" s="17">
         <v>446</v>
@@ -31926,7 +31931,7 @@
         <v>2369</v>
       </c>
       <c r="E30" s="19">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="F30" s="17">
         <v>1709</v>
@@ -32031,7 +32036,7 @@
         <v>2303</v>
       </c>
       <c r="E35" s="19">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F35" s="17">
         <v>216</v>
@@ -32094,7 +32099,7 @@
         <v>2351</v>
       </c>
       <c r="E38" s="19">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F38" s="17">
         <v>395</v>
@@ -32218,7 +32223,7 @@
         <v>1328</v>
       </c>
       <c r="E44" s="19">
-        <v>0</v>
+        <v>1305</v>
       </c>
       <c r="F44" s="17">
         <v>247</v>
@@ -32379,7 +32384,7 @@
         <v>2522</v>
       </c>
       <c r="E53" s="19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F53" s="17">
         <v>1804</v>
@@ -32603,7 +32608,7 @@
       </c>
       <c r="D63" s="32"/>
       <c r="E63" s="84">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F63" s="32">
         <v>115</v>
@@ -32629,7 +32634,7 @@
         <v>2859</v>
       </c>
       <c r="E64" s="84">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="F64" s="32">
         <v>251</v>
@@ -33335,7 +33340,7 @@
         <v>2429</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F7">
         <v>1170</v>
@@ -33355,7 +33360,7 @@
         <v>3038</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>1587</v>
@@ -33495,7 +33500,7 @@
         <v>2447</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s">
         <v>3606</v>
@@ -34837,7 +34842,7 @@
         <v>3537</v>
       </c>
       <c r="E84">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F84">
         <v>365</v>
@@ -38633,7 +38638,7 @@
         <v>1449</v>
       </c>
       <c r="E138" s="10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F138" s="9"/>
     </row>
@@ -39246,7 +39251,7 @@
         <v>1026</v>
       </c>
       <c r="E168" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F168" s="9"/>
       <c r="G168" t="s">
@@ -39399,7 +39404,7 @@
         <v>1082</v>
       </c>
       <c r="E176" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="9"/>
       <c r="G176" t="s">
@@ -47623,7 +47628,7 @@
       </c>
       <c r="D157" s="33"/>
       <c r="E157" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F157" s="33"/>
     </row>
@@ -49293,7 +49298,7 @@
       </c>
       <c r="D257" s="33"/>
       <c r="E257" s="35">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F257" s="33">
         <v>137</v>
@@ -49329,7 +49334,7 @@
         <v>2720</v>
       </c>
       <c r="E259" s="35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F259" s="33">
         <v>327</v>
@@ -49807,7 +49812,7 @@
       </c>
       <c r="D288" s="33"/>
       <c r="E288" s="35">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="F288" s="33"/>
     </row>
@@ -50294,7 +50299,7 @@
       </c>
       <c r="D316" s="33"/>
       <c r="E316" s="35">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F316" s="33">
         <v>865</v>
@@ -50492,7 +50497,7 @@
       </c>
       <c r="D327" s="33"/>
       <c r="E327" s="35">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F327" s="33" t="s">
         <v>2834</v>
@@ -50512,7 +50517,7 @@
         <v>2295</v>
       </c>
       <c r="E328" s="35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F328" s="33">
         <v>7770</v>
@@ -50948,7 +50953,7 @@
       </c>
       <c r="D352" s="33"/>
       <c r="E352" s="35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F352" s="33">
         <v>1433</v>
@@ -52540,7 +52545,7 @@
         <v>2697</v>
       </c>
       <c r="E59" s="56">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="F59" s="35" t="s">
         <v>3565</v>
@@ -53218,7 +53223,7 @@
         <v>2700</v>
       </c>
       <c r="E97" s="56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" s="35" t="s">
         <v>3581</v>
@@ -53834,7 +53839,7 @@
         <v>2695</v>
       </c>
       <c r="E132" s="56">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F132" s="35" t="s">
         <v>3117</v>
@@ -57217,17 +57222,17 @@
     </customSheetView>
   </customSheetViews>
   <conditionalFormatting sqref="G99">
-    <cfRule type="duplicateValues" dxfId="8" priority="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="3" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="5" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="6" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="2" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="4" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="5" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="6" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G138">
-    <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="9" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="9" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -57420,7 +57425,7 @@
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F10" s="35">
         <v>193</v>
@@ -57456,7 +57461,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33">
-        <v>365</v>
+        <v>325</v>
       </c>
       <c r="F12" s="35">
         <v>184</v>
@@ -57569,7 +57574,7 @@
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" s="35">
         <v>1301</v>
@@ -57643,7 +57648,7 @@
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="33">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F22" s="35">
         <v>363</v>
@@ -57849,7 +57854,7 @@
       </c>
       <c r="D33" s="33"/>
       <c r="E33" s="53">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F33" s="35">
         <v>392</v>
@@ -58182,7 +58187,7 @@
       </c>
       <c r="D51" s="33"/>
       <c r="E51" s="33">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F51" s="35">
         <v>85</v>
@@ -58238,7 +58243,7 @@
       </c>
       <c r="D54" s="33"/>
       <c r="E54" s="33">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="F54" s="35">
         <v>120</v>
@@ -58276,7 +58281,7 @@
         <v>3384</v>
       </c>
       <c r="E56" s="42">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F56" s="35">
         <v>408</v>
@@ -58528,7 +58533,7 @@
       </c>
       <c r="D71" s="33"/>
       <c r="E71" s="42">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F71" s="35">
         <v>295</v>
@@ -58548,7 +58553,7 @@
         <v>3359</v>
       </c>
       <c r="E72" s="42">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F72" s="35">
         <v>415</v>
@@ -58912,7 +58917,7 @@
         <v>19644</v>
       </c>
       <c r="E92" s="33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F92" s="61" t="s">
         <v>3556</v>
@@ -59061,7 +59066,7 @@
         <v>240</v>
       </c>
       <c r="E100" s="33">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F100" s="35">
         <v>407</v>
@@ -59139,7 +59144,7 @@
         <v>3373</v>
       </c>
       <c r="E104" s="60">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F104" s="35">
         <v>396</v>
@@ -59690,7 +59695,7 @@
         <v>3562</v>
       </c>
       <c r="E134" s="33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F134" s="35">
         <v>1400</v>
@@ -60050,7 +60055,7 @@
       </c>
       <c r="D154" s="33"/>
       <c r="E154" s="35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F154" s="33">
         <v>301</v>
@@ -60086,7 +60091,7 @@
       </c>
       <c r="D156" s="33"/>
       <c r="E156" s="35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F156" s="33">
         <v>150</v>
@@ -60138,7 +60143,7 @@
         <v>1855</v>
       </c>
       <c r="E159" s="33">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F159" s="35">
         <v>234</v>
@@ -60198,7 +60203,7 @@
         <v>3395</v>
       </c>
       <c r="E162" s="33">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F162" s="35">
         <v>686</v>
@@ -60218,7 +60223,7 @@
         <v>3396</v>
       </c>
       <c r="E163" s="60">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F163" s="33">
         <v>868</v>
@@ -60278,7 +60283,7 @@
         <v>2549</v>
       </c>
       <c r="E166" s="33">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F166" s="35" t="s">
         <v>2928</v>
@@ -60318,7 +60323,7 @@
         <v>3402</v>
       </c>
       <c r="E168" s="33">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F168" s="35">
         <v>1454</v>
@@ -60398,7 +60403,7 @@
         <v>3408</v>
       </c>
       <c r="E172" s="33">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F172" s="35">
         <v>759</v>
@@ -60418,7 +60423,7 @@
         <v>3410</v>
       </c>
       <c r="E173" s="33">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F173" s="35">
         <v>605</v>
@@ -60478,7 +60483,7 @@
         <v>3413</v>
       </c>
       <c r="E176" s="33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F176" s="35">
         <v>1550</v>
@@ -60498,7 +60503,7 @@
         <v>3414</v>
       </c>
       <c r="E177" s="33">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F177" s="35">
         <v>288</v>
@@ -60608,7 +60613,7 @@
         <v>318</v>
       </c>
       <c r="E183" s="33">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F183" s="35">
         <v>186</v>
@@ -60806,7 +60811,7 @@
         <v>2795</v>
       </c>
       <c r="E193" s="42">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F193" s="35">
         <v>170</v>
@@ -60924,7 +60929,7 @@
         <v>3426</v>
       </c>
       <c r="E199" s="33">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F199" s="35">
         <v>155</v>
@@ -61024,7 +61029,7 @@
         <v>3430</v>
       </c>
       <c r="E204" s="33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F204" s="35">
         <v>622</v>
@@ -61312,7 +61317,7 @@
         <v>3440</v>
       </c>
       <c r="E219" s="33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F219" s="33">
         <v>305</v>
@@ -61392,7 +61397,7 @@
         <v>3013</v>
       </c>
       <c r="E223" s="33">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F223" s="33">
         <v>340</v>
@@ -61592,7 +61597,7 @@
         <v>3453</v>
       </c>
       <c r="E233" s="33">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F233" s="35" t="s">
         <v>2934</v>
@@ -62286,7 +62291,7 @@
         <v>3468</v>
       </c>
       <c r="E269" s="33">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F269" s="33">
         <v>289</v>
@@ -62306,7 +62311,7 @@
         <v>683</v>
       </c>
       <c r="E270" s="33">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F270" s="33">
         <v>255</v>
@@ -62326,7 +62331,7 @@
         <v>2402</v>
       </c>
       <c r="E271" s="33">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F271" s="33" t="s">
         <v>2990</v>
@@ -62349,7 +62354,7 @@
         <v>3405</v>
       </c>
       <c r="E272" s="33">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F272" s="33">
         <v>299</v>
@@ -62369,7 +62374,7 @@
         <v>3469</v>
       </c>
       <c r="E273" s="33">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F273" s="33">
         <v>325</v>
@@ -62469,7 +62474,7 @@
         <v>2479</v>
       </c>
       <c r="E278" s="33">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F278" s="33">
         <v>309</v>
@@ -62529,7 +62534,7 @@
         <v>3587</v>
       </c>
       <c r="E281" s="33">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F281" s="35" t="s">
         <v>2936</v>
@@ -62629,7 +62634,7 @@
         <v>2998</v>
       </c>
       <c r="E286" s="33">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F286" s="35">
         <v>345</v>
@@ -62649,7 +62654,7 @@
         <v>2997</v>
       </c>
       <c r="E287" s="33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F287" s="35">
         <v>259</v>
@@ -62689,7 +62694,7 @@
         <v>3061</v>
       </c>
       <c r="E289" s="33">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F289" s="35">
         <v>209</v>
@@ -65282,7 +65287,7 @@
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="35">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="F9" s="33" t="s">
         <v>2810</v>
